--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,77 +401,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46082</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46082</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Balancing Lifestyle and Cannabis: Tips for a Harmonized Approach</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Are you trying to find a good balance between living well and using cannabis in your daily life? This blog post shares helpful tips to make both work together. More people are using cannabis today for many reasons, but it can be hard to fit it into a busy life. Between work, relationships, and taking […]The post Balancing Lifestyle and Cannabis: Tips for a Harmonized Approach appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D4" s="2">
         <v>46081</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/02/27/balancing-lifestyle-and-cannabis-tips-for-a-harmonized-approach/</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...find a good balance between living well and using **cannabis** in your daily life? This blog post shares helpful...
 ...to make both work together. More people are using **cannabis** today for many reasons, but it can be hard to fit...
 ...s, and taking […]The post Balancing Lifestyle and **Cannabis**: Tips for a Harmonized Approach appeared first on...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chautauqua County man receives max sentence for drug convictions - yourerie.com</t>
-        </is>
-      </c>
-      <c r="D3" s="2">
-        <v>46080</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/22w3ro6l</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46080</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/26y8lb3y</t>
         </is>
       </c>
     </row>
@@ -483,7 +493,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Control board for city backed in poll - observertoday.com</t>
+          <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
         </is>
       </c>
       <c r="D5" s="2">
@@ -491,24 +501,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28a9ls34</t>
+          <t>https://tinyurl.com/26y8lb3y</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
+          <t>Control board for city backed in poll - observertoday.com</t>
         </is>
       </c>
       <c r="D6" s="2">
@@ -516,10 +521,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/28a9ls34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905994/wjtn-news-headlines-for-fri-feb-27-2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...cotics Investigators say they seized 12.4 grams of fentanyl, a quantity of **methamphetamine** and Suboxone... and, scales and packaging material for the trafficking of ...
 ...ssession of illegal narcotics.  Officers say they found quantities of **methamphetamine**, cocaine and fentanyl in 36-year-old James Mawhir's possession when he ent...
@@ -533,41 +563,6 @@
 ...r was charged with three counts of seventh-degree criminal possession of a **controlled** substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
-        </is>
-      </c>
-      <c r="D7" s="2">
-        <v>46079</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
@@ -577,17 +572,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What to Know About High-Paying Legal Fields</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The legal industry is often associated with high-profile industries the most. Legal professionals who work in prestigious areas like corporate law, intellectual property and patent law, tax law, litigation law, healthcare law, and tech-related fields are paid high. The average median salary for lawyers in the U.S. was approximately $145,760 to $151,160. To determine what […]The post What to Know About High-Paying Legal Fields appeared first on WNY News Now.</t>
+          <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -595,49 +590,59 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/02/26/what-to-know-about-high-paying-legal-fields/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
+          <t>What to Know About High-Paying Legal Fields</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The legal industry is often associated with high-profile industries the most. Legal professionals who work in prestigious areas like corporate law, intellectual property and patent law, tax law, litigation law, healthcare law, and tech-related fields are paid high. The average median salary for lawyers in the U.S. was approximately $145,760 to $151,160. To determine what […]The post What to Know About High-Paying Legal Fields appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D9" s="2">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25hbntwu</t>
+          <t>https://wnynewsnow.com/2026/02/26/what-to-know-about-high-paying-legal-fields/</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Top 9 Law Firms for Healthcare Defense in Ontario</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1. Introduction: Healthcare Professional Defence in Ontario Ontario’s healthcare system covers many regulated fields, including medicine, nursing, pharmacy, and allied care. Each profession follows laws that set rules for conduct, licensing, and accountability. Professional colleges watch over these standards to protect patients and support honest practice. When concerns appear about someone’s work or compliance, an […]The post Top 9 Law Firms for Healthcare Defense in Ontario appeared first on WNY News Now.</t>
+          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
         </is>
       </c>
       <c r="D10" s="2">
@@ -645,49 +650,49 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/02/24/top-9-law-firms-for-healthcare-defense-in-ontario/</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/25hbntwu</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Woman arrested on warrant, drug charges in Jamestown - Newport Dispatch</t>
+          <t>Top 9 Law Firms for Healthcare Defense in Ontario</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1. Introduction: Healthcare Professional Defence in Ontario Ontario’s healthcare system covers many regulated fields, including medicine, nursing, pharmacy, and allied care. Each profession follows laws that set rules for conduct, licensing, and accountability. Professional colleges watch over these standards to protect patients and support honest practice. When concerns appear about someone’s work or compliance, an […]The post Top 9 Law Firms for Healthcare Defense in Ontario appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D11" s="2">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yb44sv4</t>
+          <t>https://wnynewsnow.com/2026/02/24/top-9-law-firms-for-healthcare-defense-in-ontario/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Tues., Feb. 24, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Schmidt announces Dylan Abbey to spend 13 years in State Prison on drug and active warrant charges...A city man has been sentenced to 13 years in state prison for three separate convictions... following his arrest last month as he was awaiting sentencing on the previous two.  Chautauqua County District Attorney Jason Schmidt has announced that 33 year-old Dylan Abbey was sentenced Monday in County Court for all three incidents that occured last year.  Schmidt says Abbey had already pled guilty in November of 2025 to two counts of third-degree criminal possession of a controlled substance... and one count of fourth-degree criminal possession.  He says the pleas covered incidents from January, April and July of last year.  In January... Schmidt says Jamestown Police tried to conduct a traffic stop on the defendant in conjunction with a search warrant that was being executed where Abbey led police on a car chase... and, the pursuit ended when he drove into a farm field and his vehicle became stuck in the snow.  JPD found several controlled substances in his possession.  In April... Officers went to take Abbey into custody on an active warrant... and, he was found in possession of a large quantity of methamphetamine.  In July... JPD responded to a complaint of an unwanted person, and found that person was Abbey... and, there were again active warrants for his arrest.  During this incident... he led officers on a foot chase... and, was finally caught and found in possession of another large quantity of meth.----At the time of Abbey’s plea... Schmidt says he was released from the County Jail under the supervision of the county's Probation Department until his sentencing date.  This past Jan. 27... he was again arrested by Jamestown police following a raid in the city.  The arrest violated the terms of Abbey’s plea agreement giving Judge David Foley the discretion to sentence him to the maximum on each conviction.  The charges from the incident in January are still pending.Forestville man arrested in Dunkirk following "Slow Speed Car Chase..."A man from Forestville faces multiple drunk driving... and, other traffic violations after allegedly leading police on a "slow-speed pursuit" in the town of Sheridan and city of Dunkirk.  Sheriff's officers say they spotted the vehicle... driven by 28 year-old Trevon Gallagher... commit a traffic violation just after Midnight Sunday... and, they tried to stop him using the vehicle's emergency lights.  However... Gallagher refused to comply... and, continued into Dunkirk where he tried to evade both sheriff's officers and Dunkirk police.  The vehicle eventually stopped... and, Gallagher was taken into custody.  After an investigation... police say he was driving while under the influence of alcohol... and, he was charged with DWI... failure to stop at a stop sign,... failure to comply with a lawful order... reckless driving... and, third-degree aggravated unlicensed operation... and, unlawfully fleeing a police officer...among others.  He was processed and taken to the county jail pending centralized arraignment.Langworthy expects Trump to focus on economy, and other matters in SOTU Speech tonight...The White House says President Donald Trump will use his State of the Union address to argue he and the Republicans in control of Congress are best suited to continue tackling the public's concerns about the cost of living.  Press secretary Karoline Leavitt also says Trump's speech tonight will be a "celebration of 250 years of America's independence."  The president is expected to proclaim the economy is booming... but, local Congressman Nick Langworthy kind of tempered that during a recent appearance in Dunkirk... saying the stock market is doing very well, and there's now "certainty" in the tax code with approval of the president's "Big, Beautiful Bill" last year.  Langworthy did acknowledge that prices remain high in a number of areas... even though inflation has cooled.  The Buffalo-area Republican says a lot of that is due to the nation's "COVID hangover" where trillions of dollars were spent to help people and businesses that were shut-down during that period.  Mr. Trump has said it's going to be a "long speech" that highlights his accomplishments in his first year back in office... and, he is expected to endorse increased military spending and tighter voter ID rules leading up to November elections that will determine political control of Congress.  Several Democrats in Congress say they plan to skip the speech in protest.Borrello lays out NYS Senate proposal to "Keep What You've Earned..."State Senate Republicans are touting a legislative package they say will deliver "real, lasting affordability" for New York residents.  Members of the Senate GOP Conference, including local lawmaker George Borrello, recently announced an initiative called "Keep What You've Earned," which they say includes the largest middle-class tax cut in the state's history.  Borrello says one of the signature bills in this package would change the state's tax code to eliminate income tax on the first $50,000 for single filers and the first $100,000 for joint filing couples.  He says this will help attract people to, and to return to New York state and make the economy bigger.  The initiative would also lower the tax rate to 4% for individuals who earn up to $250,000 and couples who make up to $500,000.  Borrello says it also includes a measure to cap annual state spending growth at inflation... or 2%... whichever is lower. </t>
+          <t>Woman arrested on warrant, drug charges in Jamestown - Newport Dispatch</t>
         </is>
       </c>
       <c r="D12" s="2">
@@ -695,10 +700,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/2yb44sv4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Tues., Feb. 24, 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Schmidt announces Dylan Abbey to spend 13 years in State Prison on drug and active warrant charges...A city man has been sentenced to 13 years in state prison for three separate convictions... following his arrest last month as he was awaiting sentencing on the previous two.  Chautauqua County District Attorney Jason Schmidt has announced that 33 year-old Dylan Abbey was sentenced Monday in County Court for all three incidents that occured last year.  Schmidt says Abbey had already pled guilty in November of 2025 to two counts of third-degree criminal possession of a controlled substance... and one count of fourth-degree criminal possession.  He says the pleas covered incidents from January, April and July of last year.  In January... Schmidt says Jamestown Police tried to conduct a traffic stop on the defendant in conjunction with a search warrant that was being executed where Abbey led police on a car chase... and, the pursuit ended when he drove into a farm field and his vehicle became stuck in the snow.  JPD found several controlled substances in his possession.  In April... Officers went to take Abbey into custody on an active warrant... and, he was found in possession of a large quantity of methamphetamine.  In July... JPD responded to a complaint of an unwanted person, and found that person was Abbey... and, there were again active warrants for his arrest.  During this incident... he led officers on a foot chase... and, was finally caught and found in possession of another large quantity of meth.----At the time of Abbey’s plea... Schmidt says he was released from the County Jail under the supervision of the county's Probation Department until his sentencing date.  This past Jan. 27... he was again arrested by Jamestown police following a raid in the city.  The arrest violated the terms of Abbey’s plea agreement giving Judge David Foley the discretion to sentence him to the maximum on each conviction.  The charges from the incident in January are still pending.Forestville man arrested in Dunkirk following "Slow Speed Car Chase..."A man from Forestville faces multiple drunk driving... and, other traffic violations after allegedly leading police on a "slow-speed pursuit" in the town of Sheridan and city of Dunkirk.  Sheriff's officers say they spotted the vehicle... driven by 28 year-old Trevon Gallagher... commit a traffic violation just after Midnight Sunday... and, they tried to stop him using the vehicle's emergency lights.  However... Gallagher refused to comply... and, continued into Dunkirk where he tried to evade both sheriff's officers and Dunkirk police.  The vehicle eventually stopped... and, Gallagher was taken into custody.  After an investigation... police say he was driving while under the influence of alcohol... and, he was charged with DWI... failure to stop at a stop sign,... failure to comply with a lawful order... reckless driving... and, third-degree aggravated unlicensed operation... and, unlawfully fleeing a police officer...among others.  He was processed and taken to the county jail pending centralized arraignment.Langworthy expects Trump to focus on economy, and other matters in SOTU Speech tonight...The White House says President Donald Trump will use his State of the Union address to argue he and the Republicans in control of Congress are best suited to continue tackling the public's concerns about the cost of living.  Press secretary Karoline Leavitt also says Trump's speech tonight will be a "celebration of 250 years of America's independence."  The president is expected to proclaim the economy is booming... but, local Congressman Nick Langworthy kind of tempered that during a recent appearance in Dunkirk... saying the stock market is doing very well, and there's now "certainty" in the tax code with approval of the president's "Big, Beautiful Bill" last year.  Langworthy did acknowledge that prices remain high in a number of areas... even though inflation has cooled.  The Buffalo-area Republican says a lot of that is due to the nation's "COVID hangover" where trillions of dollars were spent to help people and businesses that were shut-down during that period.  Mr. Trump has said it's going to be a "long speech" that highlights his accomplishments in his first year back in office... and, he is expected to endorse increased military spending and tighter voter ID rules leading up to November elections that will determine political control of Congress.  Several Democrats in Congress say they plan to skip the speech in protest.Borrello lays out NYS Senate proposal to "Keep What You've Earned..."State Senate Republicans are touting a legislative package they say will deliver "real, lasting affordability" for New York residents.  Members of the Senate GOP Conference, including local lawmaker George Borrello, recently announced an initiative called "Keep What You've Earned," which they say includes the largest middle-class tax cut in the state's history.  Borrello says one of the signature bills in this package would change the state's tax code to eliminate income tax on the first $50,000 for single filers and the first $100,000 for joint filing couples.  He says this will help attract people to, and to return to New York state and make the economy bigger.  The initiative would also lower the tax rate to 4% for individuals who earn up to $250,000 and couples who make up to $500,000.  Borrello says it also includes a measure to cap annual state spending growth at inflation... or 2%... whichever is lower. </t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46077</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905490/wjtn-news-headlines-for-tues-feb-24-2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...n active warrant... and, he was found in possession of a large quantity of **methamphetamine**.  In July... JPD responded to a complaint of an unwanted person, and ...
 Schmidt announces Dylan Abbey to spend 13 years in State Prison on **drug** and active warrant charges...A city man has been sentenced to 13 years in ...
@@ -706,7 +736,7 @@
 ...rm field and his vehicle became stuck in the snow.  JPD found several **controlled** substances in his possession.  In April... Officers went to take Abbe...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,50 +401,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>https://tinyurl.com/25hbntwu</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
+          <t>WJTN News Headlines for Mon., Mar. 2, 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
+          <t>Burham receives 25 years to life sentence for murder of Kala Hodgkin...The Jamestown-area man convicted of the murder of local mother of three, Kala Hodgkin, has been sentenced to 25 years to life in prison.  We learned just before Noon today that 37 year-old Michael Burham, who's already serving time for kidnapping and escape in Warren County, Pa., received the sentence from County Court Judge David Foley.  More when it becomes availble.St. Susan's Center announces it will remain in the Gateway Center after costs to move into former Business College building triple...The Jamestown area's largest soup kitchen will be staying in the Gateway Center on Water Street for the foreseeable future.  That after the St. Susan's Center Board of directors voted to stay at their current location.  Executive Director Cheri Rowland says the main reason is a tripling of the renovation and moving costs they were going to see to move operations into part of the former Jamestown Business College.  Rowland says... those initial projections of about $1-million... had now climbed to $3-million.  With that... she says the board decided to remain at it's current location at 31 Water Street... and, pursue tenancy with the new Gateway Lofts redevelopment project.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity."  But... over the past year... she says the center completed architectural studies, site plan approvals, and detailed construction estimates for the JBC property.  As planning advanced... projected renovation costs increased substantially — due in large part to changing the building's use from a school to food services.  The Gateway Loft's project is being led by Southern Tier Environments for Living... and, their Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Fire rescue crews rescue man who fell through the ice on a town of Portland pond...A man who had fallen through the ice on a pond in the north county was successfully rescued last weekend by local fire rescuers.  Sheriff's deputies say the county's Water Emergency Team was also called to the scene to assist Portland and Brocton fire crews at the Gravevine Estates on Route 5 shortly after Midnight Saturday.  Officers say the WET Team was able to get out to the man... and, secure him with a "life ring."  Members of the fire departments, civilian bystanders, and Sheriffs Deputies were then able to pull the man back to shore where he was treated for exposure... and, taken to a local hospital for treatment.  Deputies also remind the public that at this time of year... ice conditions can change rapidly.  If you do venture out on to the ice, please wear a PFD and check ice conditions as you go.City man sought on multiple warrants arrested following street check, and police find meth...A man from Jamestown sought on multiple arrest warrants has been arrested in the Brooklyn Square area following a street check late last week.  City police were patroling that area shortly before 1 p.m. last Friday... when they spotted 50 year-old Richard Barr.  Officers took Barr into custody on the warrants... and, a further search turned up a quantity of methamphetamine in his possession.  He was taken to the city jail on the warrants and one count of seventh-degree criminal possession of a controlled substance... and, held pending arraignment.Molitor, Borrello supporting local highway superintendents is effort to get more CHIPS funding...About 650 highway superintendents from across the state... including 10 from Chautauqua County... will be in Albany this week to lobby for more highway funding.  State Assemblyman Andrew Molitor says he is pushing for a $250-million increase in the Consolidated Highway Improvement Program -- otherwise known as CHIPS -- funding.  Molitor says there was a slight increase in that funding last year, but not enough to keep pace with inflation... which he says has seen 50% to 60% each year, and the amount funding increases are not going far enough.  Westfield Town Highway Superintendent, Dave Babcock, says boosting funding for local roads and bridges would prevent higher long-term costs for local municipalities.  ----State Senator George Borrello says Governor Kathy Hochul's 2026-27 budget keeps funding in the CHIPS program flat.  Borrello says local highway superintendents and others plan to be in Albany this coming week to lobby for more funding due to major cost increases... for supplies, concrete, and aggragate are being kept at the same or lower levels in budget this year.  Borrello says there used to be a formula used to fairly distribute CHIPS funding.  However... he says since Democrats got the majority in the Senate... it's become more political.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.Langworthy voices his support for President Trump's "Operation Epic Fury" in Iran...Local Congressman Nick Langworthy is standing firmly behind President Donald Trump's decision to attack Iran... and, kill it's leader -- the Ayatollah Ali Khamenei.  Langworthy says -- in a printed statement -- that "the Iranian regime is the world’s number one sponsor of terror and has the blood of thousands of Americans on its hands.  Their “Death to America” chants and desire to annihilate Israel are not slogans, they are actively building the nuclear weapons and missile capabilities to make it a reality and over the last four decades have taken every opportunity to kill."  The Buffalo-area Republican adds that the president gave them numerous chances to de-escalate the situation.  </t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906252/wjtn-news-headlines-for-mon-mar-2-2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...o custody on the warrants... and, a further search turned up a quantity of **methamphetamine** in his possession.  He was taken to the city jail on the warrants and...
+...l on the warrants and one count of seventh-degree criminal possession of a **controlled** substance... and, held pending arraignment.Molitor, Borrello supporting lo...</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
@@ -456,100 +462,186 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Cannabis Options Trends: What’s Popular Among Consumers Today</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Curious about what cannabis choices people like most today? You see new products, flavors, and forms show up fast, and trends shift with taste, mood, and need. From flower to vapes, edibles to drinks, options feel wider than ever. You may wonder which picks feel popular, which feel new, and which fit daily life best. […]The post Cannabis Options Trends: What’s Popular Among Consumers Today appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46083</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/02/cannabis-options-trends-whats-popular-among-consumers-today/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Curious about what **cannabis** choices people like most today? You see new produ...
+...l new, and which fit daily life best. […]The post **Cannabis** Options Trends: What’s Popular Among Consumers To...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46082</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46082</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Balancing Lifestyle and Cannabis: Tips for a Harmonized Approach</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Are you trying to find a good balance between living well and using cannabis in your daily life? This blog post shares helpful tips to make both work together. More people are using cannabis today for many reasons, but it can be hard to fit it into a busy life. Between work, relationships, and taking […]The post Balancing Lifestyle and Cannabis: Tips for a Harmonized Approach appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D7" s="2">
         <v>46081</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/02/27/balancing-lifestyle-and-cannabis-tips-for-a-harmonized-approach/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...find a good balance between living well and using **cannabis** in your daily life? This blog post shares helpful...
 ...to make both work together. More people are using **cannabis** today for many reasons, but it can be hard to fit...
 ...s, and taking […]The post Balancing Lifestyle and **Cannabis**: Tips for a Harmonized Approach appeared first on...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D8" s="2">
         <v>46080</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://tinyurl.com/26y8lb3y</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Control board for city backed in poll - observertoday.com</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D9" s="2">
         <v>46080</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://tinyurl.com/28a9ls34</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>10 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D10" s="2">
         <v>46080</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905994/wjtn-news-headlines-for-fri-feb-27-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...cotics Investigators say they seized 12.4 grams of fentanyl, a quantity of **methamphetamine** and Suboxone... and, scales and packaging material for the trafficking of ...
 ...ssession of illegal narcotics.  Officers say they found quantities of **methamphetamine**, cocaine and fentanyl in 36-year-old James Mawhir's possession when he ent...
@@ -563,172 +655,132 @@
 ...r was charged with three counts of seventh-degree criminal possession of a **controlled** substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46079</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>What to Know About High-Paying Legal Fields</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>The legal industry is often associated with high-profile industries the most. Legal professionals who work in prestigious areas like corporate law, intellectual property and patent law, tax law, litigation law, healthcare law, and tech-related fields are paid high. The average median salary for lawyers in the U.S. was approximately $145,760 to $151,160. To determine what […]The post What to Know About High-Paying Legal Fields appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46079</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/02/26/what-to-know-about-high-paying-legal-fields/</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46078</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/25hbntwu</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Top 9 Law Firms for Healthcare Defense in Ontario</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1. Introduction: Healthcare Professional Defence in Ontario Ontario’s healthcare system covers many regulated fields, including medicine, nursing, pharmacy, and allied care. Each profession follows laws that set rules for conduct, licensing, and accountability. Professional colleges watch over these standards to protect patients and support honest practice. When concerns appear about someone’s work or compliance, an […]The post Top 9 Law Firms for Healthcare Defense in Ontario appeared first on WNY News Now.</t>
+          <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
         </is>
       </c>
       <c r="D11" s="2">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/02/24/top-9-law-firms-for-healthcare-defense-in-ontario/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Woman arrested on warrant, drug charges in Jamestown - Newport Dispatch</t>
+          <t>What to Know About High-Paying Legal Fields</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The legal industry is often associated with high-profile industries the most. Legal professionals who work in prestigious areas like corporate law, intellectual property and patent law, tax law, litigation law, healthcare law, and tech-related fields are paid high. The average median salary for lawyers in the U.S. was approximately $145,760 to $151,160. To determine what […]The post What to Know About High-Paying Legal Fields appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D12" s="2">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yb44sv4</t>
+          <t>https://wnynewsnow.com/2026/02/26/what-to-know-about-high-paying-legal-fields/</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Top 9 Law Firms for Healthcare Defense in Ontario</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1. Introduction: Healthcare Professional Defence in Ontario Ontario’s healthcare system covers many regulated fields, including medicine, nursing, pharmacy, and allied care. Each profession follows laws that set rules for conduct, licensing, and accountability. Professional colleges watch over these standards to protect patients and support honest practice. When concerns appear about someone’s work or compliance, an […]The post Top 9 Law Firms for Healthcare Defense in Ontario appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46078</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/02/24/top-9-law-firms-for-healthcare-defense-in-ontario/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Tues., Feb. 24, 2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>4 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Schmidt announces Dylan Abbey to spend 13 years in State Prison on drug and active warrant charges...A city man has been sentenced to 13 years in state prison for three separate convictions... following his arrest last month as he was awaiting sentencing on the previous two.  Chautauqua County District Attorney Jason Schmidt has announced that 33 year-old Dylan Abbey was sentenced Monday in County Court for all three incidents that occured last year.  Schmidt says Abbey had already pled guilty in November of 2025 to two counts of third-degree criminal possession of a controlled substance... and one count of fourth-degree criminal possession.  He says the pleas covered incidents from January, April and July of last year.  In January... Schmidt says Jamestown Police tried to conduct a traffic stop on the defendant in conjunction with a search warrant that was being executed where Abbey led police on a car chase... and, the pursuit ended when he drove into a farm field and his vehicle became stuck in the snow.  JPD found several controlled substances in his possession.  In April... Officers went to take Abbey into custody on an active warrant... and, he was found in possession of a large quantity of methamphetamine.  In July... JPD responded to a complaint of an unwanted person, and found that person was Abbey... and, there were again active warrants for his arrest.  During this incident... he led officers on a foot chase... and, was finally caught and found in possession of another large quantity of meth.----At the time of Abbey’s plea... Schmidt says he was released from the County Jail under the supervision of the county's Probation Department until his sentencing date.  This past Jan. 27... he was again arrested by Jamestown police following a raid in the city.  The arrest violated the terms of Abbey’s plea agreement giving Judge David Foley the discretion to sentence him to the maximum on each conviction.  The charges from the incident in January are still pending.Forestville man arrested in Dunkirk following "Slow Speed Car Chase..."A man from Forestville faces multiple drunk driving... and, other traffic violations after allegedly leading police on a "slow-speed pursuit" in the town of Sheridan and city of Dunkirk.  Sheriff's officers say they spotted the vehicle... driven by 28 year-old Trevon Gallagher... commit a traffic violation just after Midnight Sunday... and, they tried to stop him using the vehicle's emergency lights.  However... Gallagher refused to comply... and, continued into Dunkirk where he tried to evade both sheriff's officers and Dunkirk police.  The vehicle eventually stopped... and, Gallagher was taken into custody.  After an investigation... police say he was driving while under the influence of alcohol... and, he was charged with DWI... failure to stop at a stop sign,... failure to comply with a lawful order... reckless driving... and, third-degree aggravated unlicensed operation... and, unlawfully fleeing a police officer...among others.  He was processed and taken to the county jail pending centralized arraignment.Langworthy expects Trump to focus on economy, and other matters in SOTU Speech tonight...The White House says President Donald Trump will use his State of the Union address to argue he and the Republicans in control of Congress are best suited to continue tackling the public's concerns about the cost of living.  Press secretary Karoline Leavitt also says Trump's speech tonight will be a "celebration of 250 years of America's independence."  The president is expected to proclaim the economy is booming... but, local Congressman Nick Langworthy kind of tempered that during a recent appearance in Dunkirk... saying the stock market is doing very well, and there's now "certainty" in the tax code with approval of the president's "Big, Beautiful Bill" last year.  Langworthy did acknowledge that prices remain high in a number of areas... even though inflation has cooled.  The Buffalo-area Republican says a lot of that is due to the nation's "COVID hangover" where trillions of dollars were spent to help people and businesses that were shut-down during that period.  Mr. Trump has said it's going to be a "long speech" that highlights his accomplishments in his first year back in office... and, he is expected to endorse increased military spending and tighter voter ID rules leading up to November elections that will determine political control of Congress.  Several Democrats in Congress say they plan to skip the speech in protest.Borrello lays out NYS Senate proposal to "Keep What You've Earned..."State Senate Republicans are touting a legislative package they say will deliver "real, lasting affordability" for New York residents.  Members of the Senate GOP Conference, including local lawmaker George Borrello, recently announced an initiative called "Keep What You've Earned," which they say includes the largest middle-class tax cut in the state's history.  Borrello says one of the signature bills in this package would change the state's tax code to eliminate income tax on the first $50,000 for single filers and the first $100,000 for joint filing couples.  He says this will help attract people to, and to return to New York state and make the economy bigger.  The initiative would also lower the tax rate to 4% for individuals who earn up to $250,000 and couples who make up to $500,000.  Borrello says it also includes a measure to cap annual state spending growth at inflation... or 2%... whichever is lower. </t>
         </is>
       </c>
-      <c r="D13" s="2">
+      <c r="D14" s="2">
         <v>46077</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905490/wjtn-news-headlines-for-tues-feb-24-2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...n active warrant... and, he was found in possession of a large quantity of **methamphetamine**.  In July... JPD responded to a complaint of an unwanted person, and ...
 Schmidt announces Dylan Abbey to spend 13 years in State Prison on **drug** and active warrant charges...A city man has been sentenced to 13 years in ...
@@ -736,7 +788,7 @@
 ...rm field and his vehicle became stuck in the snow.  JPD found several **controlled** substances in his possession.  In April... Officers went to take Abbe...</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -406,242 +406,331 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
+          <t>Four arrested on drug charges in Dunkirk - Newport Dispatch</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25hbntwu</t>
+          <t>https://tinyurl.com/2345sjk4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>WJTN News Headlines for Tues., Mar. 3, 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Michael Burham receives 25 years to life with possible parole in killing of Kala Hodgkin...The man who's pleaded guilty to murder in the death of Jamestown mother of three Kala Hodgkin has been sentenced to 25 years to life in prison with the possbility of parole.  Chautauqua County District Attorney Jason Schmidt says 37 year-old Michael Burham... who's already serving 25 to 50 years in Pennsylvania for kidnapping and escape... received the sentence Monday from County Court Judge David Foley.  Schmidt says a statement made by Hodgkin's eldest child, Colin, played a key role because of it's emotion, and describing trying to protect his siblings while Burham shot and killed his mother.  He also spoke about he and his siblings being split up with other family because of her death... which has added to their trauma.  After killing Hodgkin... Burham fled to Warren County, Pa., where he kidnapped an elderly couple, and, forced them to take him to South Carolina.  He was later found there after a massive manhunt... and, returned to Warren County.  He then escaped... and, was on the run about a week before being recaptured.  Under terms of the plea agreement... Schmidt says Burham will first serve his Pennsylania term -- concurrently with the New York one.  After that... he'll be returned to New York state to the custody of the Department of Corrections and Community Supervision for a hearing to determine if he stays in prison.  Schmidt says his office will strongly recommend no parole.City woman arrested in town of Ellicott for allegedly trying to kidnap an 8 year-old...A woman from Jamestown is accused of trying to kidnap an 8-year-old child in the town of Ellicott last weekend.  Town police were called to the unidentified location last Saturday on a report of the woman allegedly approaching the child... and, then grabbing the juvenile's coat and draging the child down an alleyway... away from her home.  Officers say another juvenile witnessed the incident... and, ran into another house to get an adult.  Police say the 8 year-old was able to get away from 33 year-old Angelea Luszcak... and, an adult came out to help the child.  Officers arrived... and, found Luszcak nearby after she had tried to run off.  She was arrested for second-degree attempted kidnapping... second-degree harassment... and, two counts of endangering the welfare of a child.  Luszcak was taken to the county jail pending arraignment, and will appear in Ellicott Town Court at a later date.Jamestown man arrested for drug possession following a traffic stop...A city man has been arrested for allegedly being found in possession of cocaine with the intent to sell following an early morning traffic stop on Jamestown's southside.  City police say they saw a vehicle commit a traffic infraction at the corner of Charles and Superior Streets about 3:30 a.m. Monday... and, stopped the vehicle.  Officers say they recovered a quantity of cocaine from the driver, 54 year-old Saron Leeper, that was packaged and ready for sale.  Leeper was arrested for third-degree criminal possession of a controlled substance, held pending arraignment.Escalating costs of construction, and upgrading new facility led St. Susan's Center officials to decided to remain at Gateway Center...A sharp increase in construction, and projected operating costs... has led officials with the Jamestown area's largest soup kitchen to decide to stay in the Gateway Center for the foreseeable future.  St. Susan's Center Executive Director Cherie Rowland says the center's Board of directors voted during a recent strategy meeting to remain at 31 Water St.  Rowland says they found their construction and moving costs alone to the former Jamestown Business College were nearly tripling from $1-million to $3-million dollars... and, says they "have to be good stewards" to the people who support them, and donate to their cause.  In addition... Rowland says they were going to have to replace some of their old equipment with new products... and, with the new location, they were going to be required to build an "all electric" kitchen facility.  She says that would increase their electric costs from between $50,000 to $60,000, to about $280,000.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity" in offered the former JBC facility on Jamestown's westside.  The new Gateway Loft's project, proposed for the Gateway Center, is being led by Southern Tier Environments for Living.  STEL Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Karlstrom appointed as new Westfield Police Chief...The village of Westfield has appointed a new police chief who has more than a decade of experience as an officer... and, a Sheriff's deputies.  Village officials and the police department Monday announced the appointment of Erik Karlstrom to replace Greg Wozniak... who recently retired from the post.  Officials say Chief Karlstrom brings a proven record of military and law enforcement leadership to the position.  He's been a village resident since returning from a combat deployment in 2013... and, was a member of the U.S. Army National Guard for 11 years.  Following his military service... Karlstrom pursued a career in law enforcement, graduating from the Chautauqua County Sheriff’s Academy 2015.  He previously served as a part-time officer with the Westfield Dept. from 2015 to 2017.... and, 2023 to present. </t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46084</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906449/wjtn-news-headlines-for-tues-mar-3-2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...l appear in Ellicott Town Court at a later date.Jamestown man arrested for **drug** possession following a traffic stop...A city man has been arrested for all...
+... sale.  Leeper was arrested for third-degree criminal possession of a **controlled** substance, held pending arraignment.Escalating costs of construction, and ...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jamestown Man Charged After Incident at ROME Warming Shelter</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – Jamestown police say a 46-year-old man is facing harassment and drug possession charges following an early morning incident at a local warming shelter. According to the Jamestown Police Department, officers assigned to the Second Platoon responded to 917 Washington Street, the ROME Warming Shelter, on March 3, 2026, at approximately 12:48 […]The post Jamestown Man Charged After Incident at ROME Warming Shelter appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46084</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/03/jamestown-man-charged-after-incident-at-rome-warming-shelter/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...ce say a 46-year-old man is facing harassment and **drug** possession charges following an early morning inc...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – DUNKIRK, NY — Four people were arrested following the execution of a narcotics search warrant Monday afternoon at an upper apartment on Lincoln Avenue, authorities said. According to the Dunkirk Police Department, officers executed a search warrant at 81 Lincoln Ave., Upper Apartment, at approximately 1:08 p.m. on March 2, 2026. […]The post Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46084</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/03/four-arrested-after-narcotics-search-warrant-in-dunkirk-meth-fentanyl-stolen-revolver-seized/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>... After Narcotics Search Warrant in Dunkirk; Meth, **Fentanyl**, Stolen Revolver Seized appeared first on WNY New...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46083</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/25hbntwu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Mon., Mar. 2, 2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Burham receives 25 years to life sentence for murder of Kala Hodgkin...The Jamestown-area man convicted of the murder of local mother of three, Kala Hodgkin, has been sentenced to 25 years to life in prison.  We learned just before Noon today that 37 year-old Michael Burham, who's already serving time for kidnapping and escape in Warren County, Pa., received the sentence from County Court Judge David Foley.  More when it becomes availble.St. Susan's Center announces it will remain in the Gateway Center after costs to move into former Business College building triple...The Jamestown area's largest soup kitchen will be staying in the Gateway Center on Water Street for the foreseeable future.  That after the St. Susan's Center Board of directors voted to stay at their current location.  Executive Director Cheri Rowland says the main reason is a tripling of the renovation and moving costs they were going to see to move operations into part of the former Jamestown Business College.  Rowland says... those initial projections of about $1-million... had now climbed to $3-million.  With that... she says the board decided to remain at it's current location at 31 Water Street... and, pursue tenancy with the new Gateway Lofts redevelopment project.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity."  But... over the past year... she says the center completed architectural studies, site plan approvals, and detailed construction estimates for the JBC property.  As planning advanced... projected renovation costs increased substantially — due in large part to changing the building's use from a school to food services.  The Gateway Loft's project is being led by Southern Tier Environments for Living... and, their Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Fire rescue crews rescue man who fell through the ice on a town of Portland pond...A man who had fallen through the ice on a pond in the north county was successfully rescued last weekend by local fire rescuers.  Sheriff's deputies say the county's Water Emergency Team was also called to the scene to assist Portland and Brocton fire crews at the Gravevine Estates on Route 5 shortly after Midnight Saturday.  Officers say the WET Team was able to get out to the man... and, secure him with a "life ring."  Members of the fire departments, civilian bystanders, and Sheriffs Deputies were then able to pull the man back to shore where he was treated for exposure... and, taken to a local hospital for treatment.  Deputies also remind the public that at this time of year... ice conditions can change rapidly.  If you do venture out on to the ice, please wear a PFD and check ice conditions as you go.City man sought on multiple warrants arrested following street check, and police find meth...A man from Jamestown sought on multiple arrest warrants has been arrested in the Brooklyn Square area following a street check late last week.  City police were patroling that area shortly before 1 p.m. last Friday... when they spotted 50 year-old Richard Barr.  Officers took Barr into custody on the warrants... and, a further search turned up a quantity of methamphetamine in his possession.  He was taken to the city jail on the warrants and one count of seventh-degree criminal possession of a controlled substance... and, held pending arraignment.Molitor, Borrello supporting local highway superintendents is effort to get more CHIPS funding...About 650 highway superintendents from across the state... including 10 from Chautauqua County... will be in Albany this week to lobby for more highway funding.  State Assemblyman Andrew Molitor says he is pushing for a $250-million increase in the Consolidated Highway Improvement Program -- otherwise known as CHIPS -- funding.  Molitor says there was a slight increase in that funding last year, but not enough to keep pace with inflation... which he says has seen 50% to 60% each year, and the amount funding increases are not going far enough.  Westfield Town Highway Superintendent, Dave Babcock, says boosting funding for local roads and bridges would prevent higher long-term costs for local municipalities.  ----State Senator George Borrello says Governor Kathy Hochul's 2026-27 budget keeps funding in the CHIPS program flat.  Borrello says local highway superintendents and others plan to be in Albany this coming week to lobby for more funding due to major cost increases... for supplies, concrete, and aggragate are being kept at the same or lower levels in budget this year.  Borrello says there used to be a formula used to fairly distribute CHIPS funding.  However... he says since Democrats got the majority in the Senate... it's become more political.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.Langworthy voices his support for President Trump's "Operation Epic Fury" in Iran...Local Congressman Nick Langworthy is standing firmly behind President Donald Trump's decision to attack Iran... and, kill it's leader -- the Ayatollah Ali Khamenei.  Langworthy says -- in a printed statement -- that "the Iranian regime is the world’s number one sponsor of terror and has the blood of thousands of Americans on its hands.  Their “Death to America” chants and desire to annihilate Israel are not slogans, they are actively building the nuclear weapons and missile capabilities to make it a reality and over the last four decades have taken every opportunity to kill."  The Buffalo-area Republican adds that the president gave them numerous chances to de-escalate the situation.  </t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D7" s="2">
         <v>46083</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906252/wjtn-news-headlines-for-mon-mar-2-2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...o custody on the warrants... and, a further search turned up a quantity of **methamphetamine** in his possession.  He was taken to the city jail on the warrants and...
 ...l on the warrants and one count of seventh-degree criminal possession of a **controlled** substance... and, held pending arraignment.Molitor, Borrello supporting lo...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Cannabis Options Trends: What’s Popular Among Consumers Today</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Curious about what cannabis choices people like most today? You see new products, flavors, and forms show up fast, and trends shift with taste, mood, and need. From flower to vapes, edibles to drinks, options feel wider than ever. You may wonder which picks feel popular, which feel new, and which fit daily life best. […]The post Cannabis Options Trends: What’s Popular Among Consumers Today appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D8" s="2">
         <v>46083</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/02/cannabis-options-trends-whats-popular-among-consumers-today/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Curious about what **cannabis** choices people like most today? You see new produ...
 ...l new, and which fit daily life best. […]The post **Cannabis** Options Trends: What’s Popular Among Consumers To...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Balancing Lifestyle and Cannabis: Tips for a Harmonized Approach</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Are you trying to find a good balance between living well and using cannabis in your daily life? This blog post shares helpful tips to make both work together. More people are using cannabis today for many reasons, but it can be hard to fit it into a busy life. Between work, relationships, and taking […]The post Balancing Lifestyle and Cannabis: Tips for a Harmonized Approach appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D7" s="2">
-        <v>46081</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/02/27/balancing-lifestyle-and-cannabis-tips-for-a-harmonized-approach/</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...find a good balance between living well and using **cannabis** in your daily life? This blog post shares helpful...
-...to make both work together. More people are using **cannabis** today for many reasons, but it can be hard to fit...
-...s, and taking […]The post Balancing Lifestyle and **Cannabis**: Tips for a Harmonized Approach appeared first on...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46080</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/26y8lb3y</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Control board for city backed in poll - observertoday.com</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D9" s="2">
-        <v>46080</v>
+        <v>46082</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28a9ls34</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46082</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/26y8lb3y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Control board for city backed in poll - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/28a9ls34</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>10 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D13" s="2">
         <v>46080</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905994/wjtn-news-headlines-for-fri-feb-27-2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...cotics Investigators say they seized 12.4 grams of fentanyl, a quantity of **methamphetamine** and Suboxone... and, scales and packaging material for the trafficking of ...
 ...ssession of illegal narcotics.  Officers say they found quantities of **methamphetamine**, cocaine and fentanyl in 36-year-old James Mawhir's possession when he ent...
@@ -655,137 +744,39 @@
 ...r was charged with three counts of seventh-degree criminal possession of a **controlled** substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46079</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>What to Know About High-Paying Legal Fields</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>The legal industry is often associated with high-profile industries the most. Legal professionals who work in prestigious areas like corporate law, intellectual property and patent law, tax law, litigation law, healthcare law, and tech-related fields are paid high. The average median salary for lawyers in the U.S. was approximately $145,760 to $151,160. To determine what […]The post What to Know About High-Paying Legal Fields appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46079</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/02/26/what-to-know-about-high-paying-legal-fields/</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Top 9 Law Firms for Healthcare Defense in Ontario</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1. Introduction: Healthcare Professional Defence in Ontario Ontario’s healthcare system covers many regulated fields, including medicine, nursing, pharmacy, and allied care. Each profession follows laws that set rules for conduct, licensing, and accountability. Professional colleges watch over these standards to protect patients and support honest practice. When concerns appear about someone’s work or compliance, an […]The post Top 9 Law Firms for Healthcare Defense in Ontario appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46078</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/02/24/top-9-law-firms-for-healthcare-defense-in-ontario/</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Tues., Feb. 24, 2026</t>
+          <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4 keyword references (WJTN)</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Schmidt announces Dylan Abbey to spend 13 years in State Prison on drug and active warrant charges...A city man has been sentenced to 13 years in state prison for three separate convictions... following his arrest last month as he was awaiting sentencing on the previous two.  Chautauqua County District Attorney Jason Schmidt has announced that 33 year-old Dylan Abbey was sentenced Monday in County Court for all three incidents that occured last year.  Schmidt says Abbey had already pled guilty in November of 2025 to two counts of third-degree criminal possession of a controlled substance... and one count of fourth-degree criminal possession.  He says the pleas covered incidents from January, April and July of last year.  In January... Schmidt says Jamestown Police tried to conduct a traffic stop on the defendant in conjunction with a search warrant that was being executed where Abbey led police on a car chase... and, the pursuit ended when he drove into a farm field and his vehicle became stuck in the snow.  JPD found several controlled substances in his possession.  In April... Officers went to take Abbey into custody on an active warrant... and, he was found in possession of a large quantity of methamphetamine.  In July... JPD responded to a complaint of an unwanted person, and found that person was Abbey... and, there were again active warrants for his arrest.  During this incident... he led officers on a foot chase... and, was finally caught and found in possession of another large quantity of meth.----At the time of Abbey’s plea... Schmidt says he was released from the County Jail under the supervision of the county's Probation Department until his sentencing date.  This past Jan. 27... he was again arrested by Jamestown police following a raid in the city.  The arrest violated the terms of Abbey’s plea agreement giving Judge David Foley the discretion to sentence him to the maximum on each conviction.  The charges from the incident in January are still pending.Forestville man arrested in Dunkirk following "Slow Speed Car Chase..."A man from Forestville faces multiple drunk driving... and, other traffic violations after allegedly leading police on a "slow-speed pursuit" in the town of Sheridan and city of Dunkirk.  Sheriff's officers say they spotted the vehicle... driven by 28 year-old Trevon Gallagher... commit a traffic violation just after Midnight Sunday... and, they tried to stop him using the vehicle's emergency lights.  However... Gallagher refused to comply... and, continued into Dunkirk where he tried to evade both sheriff's officers and Dunkirk police.  The vehicle eventually stopped... and, Gallagher was taken into custody.  After an investigation... police say he was driving while under the influence of alcohol... and, he was charged with DWI... failure to stop at a stop sign,... failure to comply with a lawful order... reckless driving... and, third-degree aggravated unlicensed operation... and, unlawfully fleeing a police officer...among others.  He was processed and taken to the county jail pending centralized arraignment.Langworthy expects Trump to focus on economy, and other matters in SOTU Speech tonight...The White House says President Donald Trump will use his State of the Union address to argue he and the Republicans in control of Congress are best suited to continue tackling the public's concerns about the cost of living.  Press secretary Karoline Leavitt also says Trump's speech tonight will be a "celebration of 250 years of America's independence."  The president is expected to proclaim the economy is booming... but, local Congressman Nick Langworthy kind of tempered that during a recent appearance in Dunkirk... saying the stock market is doing very well, and there's now "certainty" in the tax code with approval of the president's "Big, Beautiful Bill" last year.  Langworthy did acknowledge that prices remain high in a number of areas... even though inflation has cooled.  The Buffalo-area Republican says a lot of that is due to the nation's "COVID hangover" where trillions of dollars were spent to help people and businesses that were shut-down during that period.  Mr. Trump has said it's going to be a "long speech" that highlights his accomplishments in his first year back in office... and, he is expected to endorse increased military spending and tighter voter ID rules leading up to November elections that will determine political control of Congress.  Several Democrats in Congress say they plan to skip the speech in protest.Borrello lays out NYS Senate proposal to "Keep What You've Earned..."State Senate Republicans are touting a legislative package they say will deliver "real, lasting affordability" for New York residents.  Members of the Senate GOP Conference, including local lawmaker George Borrello, recently announced an initiative called "Keep What You've Earned," which they say includes the largest middle-class tax cut in the state's history.  Borrello says one of the signature bills in this package would change the state's tax code to eliminate income tax on the first $50,000 for single filers and the first $100,000 for joint filing couples.  He says this will help attract people to, and to return to New York state and make the economy bigger.  The initiative would also lower the tax rate to 4% for individuals who earn up to $250,000 and couples who make up to $500,000.  Borrello says it also includes a measure to cap annual state spending growth at inflation... or 2%... whichever is lower. </t>
+          <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
         </is>
       </c>
       <c r="D14" s="2">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905490/wjtn-news-headlines-for-tues-feb-24-2026</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>...n active warrant... and, he was found in possession of a large quantity of **methamphetamine**.  In July... JPD responded to a complaint of an unwanted person, and ...
-Schmidt announces Dylan Abbey to spend 13 years in State Prison on **drug** and active warrant charges...A city man has been sentenced to 13 years in ...
-...in November of 2025 to two counts of third-degree criminal possession of a **controlled** substance... and one count of fourth-degree criminal possession.  He ...
-...rm field and his vehicle became stuck in the snow.  JPD found several **controlled** substances in his possession.  In April... Officers went to take Abbe...</t>
+          <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,268 +401,281 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Four arrested on drug charges in Dunkirk - Newport Dispatch</t>
+          <t>9 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2345sjk4</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
+...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
+..., others are pending.  Four arrested in Dunkirk during Lincoln Avenue **drug** bust...Four north county residents have been arrested in a drug raid in th...
+...oln Avenue drug bust...Four north county residents have been arrested in a **drug** raid in the city of Dunkirk early Monday afternoon.  Sheriff's office...
+...minal possession of stolen property... and, second-degree criminally using **drug** paraphernalia.  Austin was charged with three counts of third-degree ...
+...iminal possession of stolen property... and second-degree criminally using **drug** paraphernalia.  Eggelston was charged with seventh-degree criminal po...
+...s charged with second... third and seventh-degree criminal possession of a **controlled** substance... third-degree criminal possession of a weapon... fourth-degree...
+...tin was charged with three counts of third-degree criminal possession of a **controlled** substance... and second and seventh-degree criminal possession of drugs......
+....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Four Charged After Drugs, Weapon Found In Dunkirk Home - Post Journal</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46085</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/255e9aau</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Four arrested on drug charges in Dunkirk - Newport Dispatch</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46085</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2345sjk4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Tues., Mar. 3, 2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Michael Burham receives 25 years to life with possible parole in killing of Kala Hodgkin...The man who's pleaded guilty to murder in the death of Jamestown mother of three Kala Hodgkin has been sentenced to 25 years to life in prison with the possbility of parole.  Chautauqua County District Attorney Jason Schmidt says 37 year-old Michael Burham... who's already serving 25 to 50 years in Pennsylvania for kidnapping and escape... received the sentence Monday from County Court Judge David Foley.  Schmidt says a statement made by Hodgkin's eldest child, Colin, played a key role because of it's emotion, and describing trying to protect his siblings while Burham shot and killed his mother.  He also spoke about he and his siblings being split up with other family because of her death... which has added to their trauma.  After killing Hodgkin... Burham fled to Warren County, Pa., where he kidnapped an elderly couple, and, forced them to take him to South Carolina.  He was later found there after a massive manhunt... and, returned to Warren County.  He then escaped... and, was on the run about a week before being recaptured.  Under terms of the plea agreement... Schmidt says Burham will first serve his Pennsylania term -- concurrently with the New York one.  After that... he'll be returned to New York state to the custody of the Department of Corrections and Community Supervision for a hearing to determine if he stays in prison.  Schmidt says his office will strongly recommend no parole.City woman arrested in town of Ellicott for allegedly trying to kidnap an 8 year-old...A woman from Jamestown is accused of trying to kidnap an 8-year-old child in the town of Ellicott last weekend.  Town police were called to the unidentified location last Saturday on a report of the woman allegedly approaching the child... and, then grabbing the juvenile's coat and draging the child down an alleyway... away from her home.  Officers say another juvenile witnessed the incident... and, ran into another house to get an adult.  Police say the 8 year-old was able to get away from 33 year-old Angelea Luszcak... and, an adult came out to help the child.  Officers arrived... and, found Luszcak nearby after she had tried to run off.  She was arrested for second-degree attempted kidnapping... second-degree harassment... and, two counts of endangering the welfare of a child.  Luszcak was taken to the county jail pending arraignment, and will appear in Ellicott Town Court at a later date.Jamestown man arrested for drug possession following a traffic stop...A city man has been arrested for allegedly being found in possession of cocaine with the intent to sell following an early morning traffic stop on Jamestown's southside.  City police say they saw a vehicle commit a traffic infraction at the corner of Charles and Superior Streets about 3:30 a.m. Monday... and, stopped the vehicle.  Officers say they recovered a quantity of cocaine from the driver, 54 year-old Saron Leeper, that was packaged and ready for sale.  Leeper was arrested for third-degree criminal possession of a controlled substance, held pending arraignment.Escalating costs of construction, and upgrading new facility led St. Susan's Center officials to decided to remain at Gateway Center...A sharp increase in construction, and projected operating costs... has led officials with the Jamestown area's largest soup kitchen to decide to stay in the Gateway Center for the foreseeable future.  St. Susan's Center Executive Director Cherie Rowland says the center's Board of directors voted during a recent strategy meeting to remain at 31 Water St.  Rowland says they found their construction and moving costs alone to the former Jamestown Business College were nearly tripling from $1-million to $3-million dollars... and, says they "have to be good stewards" to the people who support them, and donate to their cause.  In addition... Rowland says they were going to have to replace some of their old equipment with new products... and, with the new location, they were going to be required to build an "all electric" kitchen facility.  She says that would increase their electric costs from between $50,000 to $60,000, to about $280,000.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity" in offered the former JBC facility on Jamestown's westside.  The new Gateway Loft's project, proposed for the Gateway Center, is being led by Southern Tier Environments for Living.  STEL Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Karlstrom appointed as new Westfield Police Chief...The village of Westfield has appointed a new police chief who has more than a decade of experience as an officer... and, a Sheriff's deputies.  Village officials and the police department Monday announced the appointment of Erik Karlstrom to replace Greg Wozniak... who recently retired from the post.  Officials say Chief Karlstrom brings a proven record of military and law enforcement leadership to the position.  He's been a village resident since returning from a combat deployment in 2013... and, was a member of the U.S. Army National Guard for 11 years.  Following his military service... Karlstrom pursued a career in law enforcement, graduating from the Chautauqua County Sheriff’s Academy 2015.  He previously served as a part-time officer with the Westfield Dept. from 2015 to 2017.... and, 2023 to present. </t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D5" s="2">
         <v>46084</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906449/wjtn-news-headlines-for-tues-mar-3-2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...l appear in Ellicott Town Court at a later date.Jamestown man arrested for **drug** possession following a traffic stop...A city man has been arrested for all...
 ... sale.  Leeper was arrested for third-degree criminal possession of a **controlled** substance, held pending arraignment.Escalating costs of construction, and ...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged After Incident at ROME Warming Shelter</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – Jamestown police say a 46-year-old man is facing harassment and drug possession charges following an early morning incident at a local warming shelter. According to the Jamestown Police Department, officers assigned to the Second Platoon responded to 917 Washington Street, the ROME Warming Shelter, on March 3, 2026, at approximately 12:48 […]The post Jamestown Man Charged After Incident at ROME Warming Shelter appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/03/jamestown-man-charged-after-incident-at-rome-warming-shelter/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...ce say a 46-year-old man is facing harassment and **drug** possession charges following an early morning inc...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – DUNKIRK, NY — Four people were arrested following the execution of a narcotics search warrant Monday afternoon at an upper apartment on Lincoln Avenue, authorities said. According to the Dunkirk Police Department, officers executed a search warrant at 81 Lincoln Ave., Upper Apartment, at approximately 1:08 p.m. on March 2, 2026. […]The post Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/03/four-arrested-after-narcotics-search-warrant-in-dunkirk-meth-fentanyl-stolen-revolver-seized/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>... After Narcotics Search Warrant in Dunkirk; Meth, **Fentanyl**, Stolen Revolver Seized appeared first on WNY New...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
+          <t>Jamestown Man Charged After Incident at ROME Warming Shelter</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – Jamestown police say a 46-year-old man is facing harassment and drug possession charges following an early morning incident at a local warming shelter. According to the Jamestown Police Department, officers assigned to the Second Platoon responded to 917 Washington Street, the ROME Warming Shelter, on March 3, 2026, at approximately 12:48 […]The post Jamestown Man Charged After Incident at ROME Warming Shelter appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25hbntwu</t>
+          <t>https://wnynewsnow.com/2026/03/03/jamestown-man-charged-after-incident-at-rome-warming-shelter/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...ce say a 46-year-old man is facing harassment and **drug** possession charges following an early morning inc...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – DUNKIRK, NY — Four people were arrested following the execution of a narcotics search warrant Monday afternoon at an upper apartment on Lincoln Avenue, authorities said. According to the Dunkirk Police Department, officers executed a search warrant at 81 Lincoln Ave., Upper Apartment, at approximately 1:08 p.m. on March 2, 2026. […]The post Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46084</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/03/four-arrested-after-narcotics-search-warrant-in-dunkirk-meth-fentanyl-stolen-revolver-seized/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>... After Narcotics Search Warrant in Dunkirk; Meth, **Fentanyl**, Stolen Revolver Seized appeared first on WNY New...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46083</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/25hbntwu</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Mon., Mar. 2, 2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Burham receives 25 years to life sentence for murder of Kala Hodgkin...The Jamestown-area man convicted of the murder of local mother of three, Kala Hodgkin, has been sentenced to 25 years to life in prison.  We learned just before Noon today that 37 year-old Michael Burham, who's already serving time for kidnapping and escape in Warren County, Pa., received the sentence from County Court Judge David Foley.  More when it becomes availble.St. Susan's Center announces it will remain in the Gateway Center after costs to move into former Business College building triple...The Jamestown area's largest soup kitchen will be staying in the Gateway Center on Water Street for the foreseeable future.  That after the St. Susan's Center Board of directors voted to stay at their current location.  Executive Director Cheri Rowland says the main reason is a tripling of the renovation and moving costs they were going to see to move operations into part of the former Jamestown Business College.  Rowland says... those initial projections of about $1-million... had now climbed to $3-million.  With that... she says the board decided to remain at it's current location at 31 Water Street... and, pursue tenancy with the new Gateway Lofts redevelopment project.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity."  But... over the past year... she says the center completed architectural studies, site plan approvals, and detailed construction estimates for the JBC property.  As planning advanced... projected renovation costs increased substantially — due in large part to changing the building's use from a school to food services.  The Gateway Loft's project is being led by Southern Tier Environments for Living... and, their Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Fire rescue crews rescue man who fell through the ice on a town of Portland pond...A man who had fallen through the ice on a pond in the north county was successfully rescued last weekend by local fire rescuers.  Sheriff's deputies say the county's Water Emergency Team was also called to the scene to assist Portland and Brocton fire crews at the Gravevine Estates on Route 5 shortly after Midnight Saturday.  Officers say the WET Team was able to get out to the man... and, secure him with a "life ring."  Members of the fire departments, civilian bystanders, and Sheriffs Deputies were then able to pull the man back to shore where he was treated for exposure... and, taken to a local hospital for treatment.  Deputies also remind the public that at this time of year... ice conditions can change rapidly.  If you do venture out on to the ice, please wear a PFD and check ice conditions as you go.City man sought on multiple warrants arrested following street check, and police find meth...A man from Jamestown sought on multiple arrest warrants has been arrested in the Brooklyn Square area following a street check late last week.  City police were patroling that area shortly before 1 p.m. last Friday... when they spotted 50 year-old Richard Barr.  Officers took Barr into custody on the warrants... and, a further search turned up a quantity of methamphetamine in his possession.  He was taken to the city jail on the warrants and one count of seventh-degree criminal possession of a controlled substance... and, held pending arraignment.Molitor, Borrello supporting local highway superintendents is effort to get more CHIPS funding...About 650 highway superintendents from across the state... including 10 from Chautauqua County... will be in Albany this week to lobby for more highway funding.  State Assemblyman Andrew Molitor says he is pushing for a $250-million increase in the Consolidated Highway Improvement Program -- otherwise known as CHIPS -- funding.  Molitor says there was a slight increase in that funding last year, but not enough to keep pace with inflation... which he says has seen 50% to 60% each year, and the amount funding increases are not going far enough.  Westfield Town Highway Superintendent, Dave Babcock, says boosting funding for local roads and bridges would prevent higher long-term costs for local municipalities.  ----State Senator George Borrello says Governor Kathy Hochul's 2026-27 budget keeps funding in the CHIPS program flat.  Borrello says local highway superintendents and others plan to be in Albany this coming week to lobby for more funding due to major cost increases... for supplies, concrete, and aggragate are being kept at the same or lower levels in budget this year.  Borrello says there used to be a formula used to fairly distribute CHIPS funding.  However... he says since Democrats got the majority in the Senate... it's become more political.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.Langworthy voices his support for President Trump's "Operation Epic Fury" in Iran...Local Congressman Nick Langworthy is standing firmly behind President Donald Trump's decision to attack Iran... and, kill it's leader -- the Ayatollah Ali Khamenei.  Langworthy says -- in a printed statement -- that "the Iranian regime is the world’s number one sponsor of terror and has the blood of thousands of Americans on its hands.  Their “Death to America” chants and desire to annihilate Israel are not slogans, they are actively building the nuclear weapons and missile capabilities to make it a reality and over the last four decades have taken every opportunity to kill."  The Buffalo-area Republican adds that the president gave them numerous chances to de-escalate the situation.  </t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D9" s="2">
         <v>46083</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906252/wjtn-news-headlines-for-mon-mar-2-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...o custody on the warrants... and, a further search turned up a quantity of **methamphetamine** in his possession.  He was taken to the city jail on the warrants and...
 ...l on the warrants and one count of seventh-degree criminal possession of a **controlled** substance... and, held pending arraignment.Molitor, Borrello supporting lo...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Cannabis Options Trends: What’s Popular Among Consumers Today</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Curious about what cannabis choices people like most today? You see new products, flavors, and forms show up fast, and trends shift with taste, mood, and need. From flower to vapes, edibles to drinks, options feel wider than ever. You may wonder which picks feel popular, which feel new, and which fit daily life best. […]The post Cannabis Options Trends: What’s Popular Among Consumers Today appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D10" s="2">
         <v>46083</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/02/cannabis-options-trends-whats-popular-among-consumers-today/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Curious about what **cannabis** choices people like most today? You see new produ...
 ...l new, and which fit daily life best. […]The post **Cannabis** Options Trends: What’s Popular Among Consumers To...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
@@ -674,63 +687,133 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
+          <t>Bluebell fire burning near Chautauqua Park in Boulder fully contained - Longmont Times-Call</t>
         </is>
       </c>
       <c r="D11" s="2">
-        <v>46080</v>
+        <v>46082</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/26y8lb3y</t>
+          <t>https://tinyurl.com/2xubor7g</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Control board for city backed in poll - observertoday.com</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D12" s="2">
-        <v>46080</v>
+        <v>46082</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28a9ls34</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46082</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/26y8lb3y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Control board for city backed in poll - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/28a9ls34</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>10 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="D13" s="2">
+      <c r="D16" s="2">
         <v>46080</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905994/wjtn-news-headlines-for-fri-feb-27-2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...cotics Investigators say they seized 12.4 grams of fentanyl, a quantity of **methamphetamine** and Suboxone... and, scales and packaging material for the trafficking of ...
 ...ssession of illegal narcotics.  Officers say they found quantities of **methamphetamine**, cocaine and fentanyl in 36-year-old James Mawhir's possession when he ent...
@@ -744,42 +827,42 @@
 ...r was charged with three counts of seventh-degree criminal possession of a **controlled** substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>1 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
         </is>
       </c>
-      <c r="D14" s="2">
+      <c r="D17" s="2">
         <v>46079</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -401,28 +401,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>9 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D4" s="2">
         <v>46086</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
 ...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
@@ -435,304 +495,259 @@
 ....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Four Charged After Drugs, Weapon Found In Dunkirk Home - Post Journal</t>
-        </is>
-      </c>
-      <c r="D3" s="2">
-        <v>46085</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/255e9aau</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Four arrested on drug charges in Dunkirk - Newport Dispatch</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46085</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2345sjk4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Four Charged After Drugs, Weapon Found In Dunkirk Home - Post Journal</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46085</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/255e9aau</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Four arrested on drug charges in Dunkirk - Newport Dispatch</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46085</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2345sjk4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Tues., Mar. 3, 2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Michael Burham receives 25 years to life with possible parole in killing of Kala Hodgkin...The man who's pleaded guilty to murder in the death of Jamestown mother of three Kala Hodgkin has been sentenced to 25 years to life in prison with the possbility of parole.  Chautauqua County District Attorney Jason Schmidt says 37 year-old Michael Burham... who's already serving 25 to 50 years in Pennsylvania for kidnapping and escape... received the sentence Monday from County Court Judge David Foley.  Schmidt says a statement made by Hodgkin's eldest child, Colin, played a key role because of it's emotion, and describing trying to protect his siblings while Burham shot and killed his mother.  He also spoke about he and his siblings being split up with other family because of her death... which has added to their trauma.  After killing Hodgkin... Burham fled to Warren County, Pa., where he kidnapped an elderly couple, and, forced them to take him to South Carolina.  He was later found there after a massive manhunt... and, returned to Warren County.  He then escaped... and, was on the run about a week before being recaptured.  Under terms of the plea agreement... Schmidt says Burham will first serve his Pennsylania term -- concurrently with the New York one.  After that... he'll be returned to New York state to the custody of the Department of Corrections and Community Supervision for a hearing to determine if he stays in prison.  Schmidt says his office will strongly recommend no parole.City woman arrested in town of Ellicott for allegedly trying to kidnap an 8 year-old...A woman from Jamestown is accused of trying to kidnap an 8-year-old child in the town of Ellicott last weekend.  Town police were called to the unidentified location last Saturday on a report of the woman allegedly approaching the child... and, then grabbing the juvenile's coat and draging the child down an alleyway... away from her home.  Officers say another juvenile witnessed the incident... and, ran into another house to get an adult.  Police say the 8 year-old was able to get away from 33 year-old Angelea Luszcak... and, an adult came out to help the child.  Officers arrived... and, found Luszcak nearby after she had tried to run off.  She was arrested for second-degree attempted kidnapping... second-degree harassment... and, two counts of endangering the welfare of a child.  Luszcak was taken to the county jail pending arraignment, and will appear in Ellicott Town Court at a later date.Jamestown man arrested for drug possession following a traffic stop...A city man has been arrested for allegedly being found in possession of cocaine with the intent to sell following an early morning traffic stop on Jamestown's southside.  City police say they saw a vehicle commit a traffic infraction at the corner of Charles and Superior Streets about 3:30 a.m. Monday... and, stopped the vehicle.  Officers say they recovered a quantity of cocaine from the driver, 54 year-old Saron Leeper, that was packaged and ready for sale.  Leeper was arrested for third-degree criminal possession of a controlled substance, held pending arraignment.Escalating costs of construction, and upgrading new facility led St. Susan's Center officials to decided to remain at Gateway Center...A sharp increase in construction, and projected operating costs... has led officials with the Jamestown area's largest soup kitchen to decide to stay in the Gateway Center for the foreseeable future.  St. Susan's Center Executive Director Cherie Rowland says the center's Board of directors voted during a recent strategy meeting to remain at 31 Water St.  Rowland says they found their construction and moving costs alone to the former Jamestown Business College were nearly tripling from $1-million to $3-million dollars... and, says they "have to be good stewards" to the people who support them, and donate to their cause.  In addition... Rowland says they were going to have to replace some of their old equipment with new products... and, with the new location, they were going to be required to build an "all electric" kitchen facility.  She says that would increase their electric costs from between $50,000 to $60,000, to about $280,000.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity" in offered the former JBC facility on Jamestown's westside.  The new Gateway Loft's project, proposed for the Gateway Center, is being led by Southern Tier Environments for Living.  STEL Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Karlstrom appointed as new Westfield Police Chief...The village of Westfield has appointed a new police chief who has more than a decade of experience as an officer... and, a Sheriff's deputies.  Village officials and the police department Monday announced the appointment of Erik Karlstrom to replace Greg Wozniak... who recently retired from the post.  Officials say Chief Karlstrom brings a proven record of military and law enforcement leadership to the position.  He's been a village resident since returning from a combat deployment in 2013... and, was a member of the U.S. Army National Guard for 11 years.  Following his military service... Karlstrom pursued a career in law enforcement, graduating from the Chautauqua County Sheriff’s Academy 2015.  He previously served as a part-time officer with the Westfield Dept. from 2015 to 2017.... and, 2023 to present. </t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D7" s="2">
         <v>46084</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906449/wjtn-news-headlines-for-tues-mar-3-2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...l appear in Ellicott Town Court at a later date.Jamestown man arrested for **drug** possession following a traffic stop...A city man has been arrested for all...
 ... sale.  Leeper was arrested for third-degree criminal possession of a **controlled** substance, held pending arraignment.Escalating costs of construction, and ...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged After Incident at ROME Warming Shelter</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – Jamestown police say a 46-year-old man is facing harassment and drug possession charges following an early morning incident at a local warming shelter. According to the Jamestown Police Department, officers assigned to the Second Platoon responded to 917 Washington Street, the ROME Warming Shelter, on March 3, 2026, at approximately 12:48 […]The post Jamestown Man Charged After Incident at ROME Warming Shelter appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/03/jamestown-man-charged-after-incident-at-rome-warming-shelter/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...ce say a 46-year-old man is facing harassment and **drug** possession charges following an early morning inc...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – DUNKIRK, NY — Four people were arrested following the execution of a narcotics search warrant Monday afternoon at an upper apartment on Lincoln Avenue, authorities said. According to the Dunkirk Police Department, officers executed a search warrant at 81 Lincoln Ave., Upper Apartment, at approximately 1:08 p.m. on March 2, 2026. […]The post Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D7" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/03/four-arrested-after-narcotics-search-warrant-in-dunkirk-meth-fentanyl-stolen-revolver-seized/</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>... After Narcotics Search Warrant in Dunkirk; Meth, **Fentanyl**, Stolen Revolver Seized appeared first on WNY New...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
+          <t>Jamestown Man Charged After Incident at ROME Warming Shelter</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – Jamestown police say a 46-year-old man is facing harassment and drug possession charges following an early morning incident at a local warming shelter. According to the Jamestown Police Department, officers assigned to the Second Platoon responded to 917 Washington Street, the ROME Warming Shelter, on March 3, 2026, at approximately 12:48 […]The post Jamestown Man Charged After Incident at ROME Warming Shelter appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D8" s="2">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25hbntwu</t>
+          <t>https://wnynewsnow.com/2026/03/03/jamestown-man-charged-after-incident-at-rome-warming-shelter/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>...ce say a 46-year-old man is facing harassment and **drug** possession charges following an early morning inc...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – DUNKIRK, NY — Four people were arrested following the execution of a narcotics search warrant Monday afternoon at an upper apartment on Lincoln Avenue, authorities said. According to the Dunkirk Police Department, officers executed a search warrant at 81 Lincoln Ave., Upper Apartment, at approximately 1:08 p.m. on March 2, 2026. […]The post Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46084</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/03/four-arrested-after-narcotics-search-warrant-in-dunkirk-meth-fentanyl-stolen-revolver-seized/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>... After Narcotics Search Warrant in Dunkirk; Meth, **Fentanyl**, Stolen Revolver Seized appeared first on WNY New...</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46083</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/25hbntwu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Mon., Mar. 2, 2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Burham receives 25 years to life sentence for murder of Kala Hodgkin...The Jamestown-area man convicted of the murder of local mother of three, Kala Hodgkin, has been sentenced to 25 years to life in prison.  We learned just before Noon today that 37 year-old Michael Burham, who's already serving time for kidnapping and escape in Warren County, Pa., received the sentence from County Court Judge David Foley.  More when it becomes availble.St. Susan's Center announces it will remain in the Gateway Center after costs to move into former Business College building triple...The Jamestown area's largest soup kitchen will be staying in the Gateway Center on Water Street for the foreseeable future.  That after the St. Susan's Center Board of directors voted to stay at their current location.  Executive Director Cheri Rowland says the main reason is a tripling of the renovation and moving costs they were going to see to move operations into part of the former Jamestown Business College.  Rowland says... those initial projections of about $1-million... had now climbed to $3-million.  With that... she says the board decided to remain at it's current location at 31 Water Street... and, pursue tenancy with the new Gateway Lofts redevelopment project.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity."  But... over the past year... she says the center completed architectural studies, site plan approvals, and detailed construction estimates for the JBC property.  As planning advanced... projected renovation costs increased substantially — due in large part to changing the building's use from a school to food services.  The Gateway Loft's project is being led by Southern Tier Environments for Living... and, their Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Fire rescue crews rescue man who fell through the ice on a town of Portland pond...A man who had fallen through the ice on a pond in the north county was successfully rescued last weekend by local fire rescuers.  Sheriff's deputies say the county's Water Emergency Team was also called to the scene to assist Portland and Brocton fire crews at the Gravevine Estates on Route 5 shortly after Midnight Saturday.  Officers say the WET Team was able to get out to the man... and, secure him with a "life ring."  Members of the fire departments, civilian bystanders, and Sheriffs Deputies were then able to pull the man back to shore where he was treated for exposure... and, taken to a local hospital for treatment.  Deputies also remind the public that at this time of year... ice conditions can change rapidly.  If you do venture out on to the ice, please wear a PFD and check ice conditions as you go.City man sought on multiple warrants arrested following street check, and police find meth...A man from Jamestown sought on multiple arrest warrants has been arrested in the Brooklyn Square area following a street check late last week.  City police were patroling that area shortly before 1 p.m. last Friday... when they spotted 50 year-old Richard Barr.  Officers took Barr into custody on the warrants... and, a further search turned up a quantity of methamphetamine in his possession.  He was taken to the city jail on the warrants and one count of seventh-degree criminal possession of a controlled substance... and, held pending arraignment.Molitor, Borrello supporting local highway superintendents is effort to get more CHIPS funding...About 650 highway superintendents from across the state... including 10 from Chautauqua County... will be in Albany this week to lobby for more highway funding.  State Assemblyman Andrew Molitor says he is pushing for a $250-million increase in the Consolidated Highway Improvement Program -- otherwise known as CHIPS -- funding.  Molitor says there was a slight increase in that funding last year, but not enough to keep pace with inflation... which he says has seen 50% to 60% each year, and the amount funding increases are not going far enough.  Westfield Town Highway Superintendent, Dave Babcock, says boosting funding for local roads and bridges would prevent higher long-term costs for local municipalities.  ----State Senator George Borrello says Governor Kathy Hochul's 2026-27 budget keeps funding in the CHIPS program flat.  Borrello says local highway superintendents and others plan to be in Albany this coming week to lobby for more funding due to major cost increases... for supplies, concrete, and aggragate are being kept at the same or lower levels in budget this year.  Borrello says there used to be a formula used to fairly distribute CHIPS funding.  However... he says since Democrats got the majority in the Senate... it's become more political.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.Langworthy voices his support for President Trump's "Operation Epic Fury" in Iran...Local Congressman Nick Langworthy is standing firmly behind President Donald Trump's decision to attack Iran... and, kill it's leader -- the Ayatollah Ali Khamenei.  Langworthy says -- in a printed statement -- that "the Iranian regime is the world’s number one sponsor of terror and has the blood of thousands of Americans on its hands.  Their “Death to America” chants and desire to annihilate Israel are not slogans, they are actively building the nuclear weapons and missile capabilities to make it a reality and over the last four decades have taken every opportunity to kill."  The Buffalo-area Republican adds that the president gave them numerous chances to de-escalate the situation.  </t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D11" s="2">
         <v>46083</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906252/wjtn-news-headlines-for-mon-mar-2-2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...o custody on the warrants... and, a further search turned up a quantity of **methamphetamine** in his possession.  He was taken to the city jail on the warrants and...
 ...l on the warrants and one count of seventh-degree criminal possession of a **controlled** substance... and, held pending arraignment.Molitor, Borrello supporting lo...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cannabis Options Trends: What’s Popular Among Consumers Today</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Curious about what cannabis choices people like most today? You see new products, flavors, and forms show up fast, and trends shift with taste, mood, and need. From flower to vapes, edibles to drinks, options feel wider than ever. You may wonder which picks feel popular, which feel new, and which fit daily life best. […]The post Cannabis Options Trends: What’s Popular Among Consumers Today appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D12" s="2">
         <v>46083</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/02/cannabis-options-trends-whats-popular-among-consumers-today/</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Curious about what **cannabis** choices people like most today? You see new produ...
 ...l new, and which fit daily life best. […]The post **Cannabis** Options Trends: What’s Popular Among Consumers To...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bluebell fire burning near Chautauqua Park in Boulder fully contained - Longmont Times-Call</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2xubor7g</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bluebell fire burning near Chautauqua Park in Boulder fully contained - Longmont Times-Call</t>
         </is>
       </c>
       <c r="D13" s="2">
@@ -740,69 +755,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>https://tinyurl.com/2xubor7g</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>New poll shows support for control board in Dunkirk - observertoday.com</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D14" s="2">
-        <v>46080</v>
+        <v>46082</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/26y8lb3y</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Control board for city backed in poll - observertoday.com</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D15" s="2">
-        <v>46080</v>
+        <v>46082</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28a9ls34</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
+          <t>Control board for city backed in poll - observertoday.com</t>
         </is>
       </c>
       <c r="D16" s="2">
@@ -810,10 +825,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/28a9ls34</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
+        </is>
+      </c>
+      <c r="D17" s="2">
+        <v>46080</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905994/wjtn-news-headlines-for-fri-feb-27-2026</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...cotics Investigators say they seized 12.4 grams of fentanyl, a quantity of **methamphetamine** and Suboxone... and, scales and packaging material for the trafficking of ...
 ...ssession of illegal narcotics.  Officers say they found quantities of **methamphetamine**, cocaine and fentanyl in 36-year-old James Mawhir's possession when he ent...
@@ -827,41 +867,6 @@
 ...r was charged with three counts of seventh-degree criminal possession of a **controlled** substance, then was arraigned, and released.   </t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Feb. 26, 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Legislature approves increased income level for Senior Property Tax Exemption, nix two other "Affordability Act of 2026" measures...Minority Democrats on the Chautauqua County Legislature were able to get one of their three proposals that make up their Affordability Act of 2026 approved at last night's meeting.  Lawmakers amended the initial proposal to increase the Senior Real Property Tax Exemption from $30,000 to $32,000.  Democrats had sought a $38,000 exemption.  The compromise was offered by Westfield-area Republican Fred Johnson... and, Jamestown Democrat Tom Nelson expressed his thanks for the move.  Nelson says" it's not as high as we wanted... (but) it's something... and, we're willing to compromise on it."  The new senior exemption was approved unanimously... and, fellow Republlican, Dalton Anthony from the Frewsburg-area... noted that Audit and Control Committee members feel this would only have a minor impact on taxes for everyone else.  That measure was approved unanimously, 17-0... with two members absent.----However... county lawmakers did not approve the rest of the Affordability Act... which included at $6-million proposal to use some of the county's $35-million undesignated fund balance to cut taxes... and, reduce the sales tax from 8% to 7.75% a percent.  Legislator Fred Johnson opposed doing both now without further review for their impacts.  It was also pointed out that a change to the sales tax would impact how much the county takes in... and, how much is shared with local municipalities.  They added that final numbers aren't known yet on how much fund balance is being used to close out the books for 2025.Langworthy calls Trump's SOTU a "bold vision for America..."Local Congressman Nick Langworthy says President Donald Trump "offered a bold vision for America" during Tuesday night's State of the Union Address to a joint session of Congress.  The Buffalo-area Republican says that vision is "growing stronger and safer every day."  Langworthy adds the speech "correctly pointed out the facts on how our America First policies are delivering results: taxes and prices are down, private sector job growth and wages are up, mortgage rates are at the lowest rate in 4 years, fentanyl trafficking is down 56-percent... and, the border is secure."  In addition... he says the president's "peace through strength mantra has made every citizen of the world safer.  His speech was filled with pride and optimism for our country, honoring our heroes and celebrating our wins, while acknowledging the steep price of freedom and the work ahead."  Langworthy says he's long supported many of the policies the president is trying to tackle next... such as such as stock trading bans for members of Congress, cracking down on corporations buying up housing stock and implementing voter ID.Investigation continuing into Lakeview Correctional Facility inmate's brutal attack on employees... The investigation is underway by the New York State Department of Corrections and Community Supervision of an alleged assault of a Lakeview Correctional employee by an inmate at the town of Portland facility.  A DOCCS spokesperson Wednesday morning confirmed that an Offender Rehabilitation Coordinator -- ORC -- was struck in the head and face a number of times by the inmate.  Security staff immediately responded and were able to restrain the inmate.  The coordinator was taken by ambulance to a local hospital; and a corrections officer who got injured was also taken to a hospital.  Neither victim has been returned to duty. Wendel says he's "deeply disturbed" by brutal assault on corrections workers, and calls for eliminating the HALT Act...In response to the assault of two corrections employees at Lakeview Correctional Facility... County Executive P.J. Wendel says he's "deeply disturbed by the brutal assault on a civilian counselor and several correction officers"  Wendel says his thoughts are with the dededicated professionals who were injured while carrying out their duties.  The Lakewood Republican adds that he stands with State Senator George Borrello and Assemblyman Andrew Molitor in supporting their proposal to repeal the HALT Act.  Wendel says since it's enactment... the number of assaults on corrections officers... medical staff... and, inmates have risen at an alarming rate."  All three concurr that the HALT Act and similar policies have taken away critical tools they need to maintain order in the state's corrections system.City of Jamestown awarded $1.7-Million dollar grant for Lead Abatement program...The city of Jamestown has been awarded $1.7-million to support a targeted lead hazard remediation initiative in the city's older rental housing stock.  City officials say the money is coming through the Housing Trust Fund Corporation under the New York State Homes &amp; Community Renewal program.  Mayor Kim Ecklund says the grant will be implemented in coordination with the Chautauqua County Health Department’s Lead Poisoning Prevention Program.  She adds the initiative represents a coordinated effort by the city, and Chautauqua County, to proactively reduce lead exposure risks within Jamestown.  County and city officials say the funding will support direct remediation activities in eligible rental units, including work on high-risk friction and impact surfaces such as windows and doors, paint stabilization, and related lead-safe rehabilitation measures.  They add that the program also provides temporary relocation assistance during active remediation... and, requires final clearance testing prior to reoccupancy to ensure units meet established safety standards.  The county's Childhood Lead and Heatly Homes Coordinator and Senior Public Health Sanitarian, Anna Powell says -- "protecting children from lead exposure requires consistent monitoring, clear standards, and timely intervention.  Proper identification of hazards and adherence to established safety standards are essential to preventing exposure." </t>
-        </is>
-      </c>
-      <c r="D17" s="2">
-        <v>46079</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905808/wjtn-news-headlines-for-thurs-feb-26-2026</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>...growth and wages are up, mortgage rates are at the lowest rate in 4 years, **fentanyl** trafficking is down 56-percent... and, the border is secure."  In add...</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -706,48 +706,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cannabis Options Trends: What’s Popular Among Consumers Today</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Curious about what cannabis choices people like most today? You see new products, flavors, and forms show up fast, and trends shift with taste, mood, and need. From flower to vapes, edibles to drinks, options feel wider than ever. You may wonder which picks feel popular, which feel new, and which fit daily life best. […]The post Cannabis Options Trends: What’s Popular Among Consumers Today appeared first on WNY News Now.</t>
+          <t>Bluebell fire burning near Chautauqua Park in Boulder fully contained - Longmont Times-Call</t>
         </is>
       </c>
       <c r="D12" s="2">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/02/cannabis-options-trends-whats-popular-among-consumers-today/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Curious about what **cannabis** choices people like most today? You see new produ...
-...l new, and which fit daily life best. […]The post **Cannabis** Options Trends: What’s Popular Among Consumers To...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/2xubor7g</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bluebell fire burning near Chautauqua Park in Boulder fully contained - Longmont Times-Call</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D13" s="2">
@@ -755,7 +739,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2xubor7g</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
@@ -767,7 +756,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
+          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D14" s="2">
@@ -775,101 +764,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D15" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Control board for city backed in poll - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D16" s="2">
-        <v>46080</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/28a9ls34</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Feb. 27, 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Five arrested in Brocton drug raid one week ago...Five people were arrested late last week following a drug raid on a home in the north county village of Brocton.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... had been investigating alleged activity at 48 Highland Ave., and, executed a search warrant early last Thursday evening.  Inside they found 36 year-old Matthew Mulville of Brocton... 34 year-old Shane Miller, and, 27 year-old Kyle Cambria of Portland... 46 year-old Danika Lemay of Dunkirk... and, 22 year-old April Decker of Sherman.  Narcotics Investigators say they seized 12.4 grams of fentanyl, a quantity of methamphetamine and Suboxone... and, scales and packaging material for the trafficking of the drugs.  All five suspects were charged with third-and fourth-degree criminal possession of a controlled substance... and second-degree criminally using drug paraphernalia.  They add Mulville was charged with first-degree criminal nuisance.  They were all taken to the county jail pending centralized arraignment.  Police add that if you see or know of suspicious or narcotics related activity in your area to call the Sheriff's Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.Legislature approves new salary range increases for management, and other employees...The Chautauqua County Legislature has approved two local laws adopting new salary ranges for some county officers and employees... and, two other directors.  However... lawmakers also discussed the need for more review of those management salaries.  Both laws were approved, 12-5 Wednesday night.  Jamestown Democrat Tom Nelson says he wanted more information... given the amount of increases some would be receiving.  Nelson says when he and others asked about the criteria for moving up those salary steps, the only one mentioned seemed to be experience.  He says he wants to be fair with employees, but, with the taxpayers, as well.  Audit and Control Committee Chairman, Dan Pavlock of the Ellington-area, said part of the reason for the changes is that some employees had "maxxed out" on their ranges... and, new ones needed to be added.  However... he was also in favor of further review.  At issue was the fact that some proposed had as much as an $89,000 difference between the bottom and the top ranges... with one being $118,000 to $207,000. Gillibrand comments on death of refugee from Myanmar in Buffalo, left by CBP outside a Tim Horton's in Buffalo...The death of a refugee from Myanmar in Buffalo... whose body was found outside a Tim Horton's restaurant late last week... is getting national attention.  U.S. Senator Kirsten Gillibrand says she has written both Homeland Security Secretary Kristi Noem... and, U.S. Customers and Border Protection Commissioner Rodney Scott... demanding a full accounting of the events and actions taken by federal agents while 56 year-old Nurul Amin Shah Alam was in their custody.  The Buffalo News reports Shah Alam... who was mostly blind and unable to communicate in English... appears to have died from a health-related matter.  However... exposure and homicide have not been ruled out.  In a printed statement... Gillibrand says Shah Alam's family and -- "our community deserve answers on the events that led to his death.  I am deeply disturbed by reports that after taking him into custody, Border Patrol agents left Mr. Shah Alam at a Tim Hortons, miles from his home, without notifying his family or attorney before he was found dead.  If true, this is absolutely unacceptable."  Family members today tell The Buffalo News they were at the holding center where Shah Alam was being held to pick him up, and were there for "hours" before learning he had been taken by federal agents.CCIDA approves new, 30-year PILOT agreement for Dunkirk Landing housing project...The developers of a $38.2 million affordable housing project in Dunkirk are getting financial assistance from the Chautauqua County Industrial Development Agency.  Earlier this week... the IDA Board approved incentives for Dunkirk Landing, LLC to support the acquisition, demolition, and new construction for the Homesteads at Dunkirk Landing project.  CCIDA Chief Executive Officer Mark Geise says Regan Development will get 30-year Payment in Lieu of Tax Agreement with $691,000 in new payments... which he says "aligns with their financing."  Geise says the "transformative" project is also getting funding from the city's Downtown Revitalization Initiative grant, and New York's Empire State Development County Infrastructure Grant Program.  He adds the project will involve demolishing an existing, dilapidated three-story building on Washington Avenue and a portion of the Save-a-Lot Plaza on East 4th Street...and the project will help to eliminate blight in that part of the city.  The project will create 78 new workforce housing units across two new buildings, as well as commercial space for daycare operation at the East 4th Street location.  It will provide an estimated 69 construction jobs during the demolition and construction period and two permanent full-time jobs directly associated with the housing portion of the project.  Work is tentatively expected to begin in mid-March... with completion by the end of November 2027.Man arrested for allegedly being in possession of drugs when he appears in Fredonia Village Court...Fredonia Police have charged a man with multiple drug counts after he allegedly entered Fredonia Village Court in possession of illegal narcotics.  Officers say they found quantities of methamphetamine, cocaine and fentanyl in 36-year-old James Mawhir's possession when he entered the courtroom Wednesday morning.  Mawhir was charged with three counts of seventh-degree criminal possession of a controlled substance, then was arraigned, and released.   </t>
-        </is>
-      </c>
-      <c r="D17" s="2">
-        <v>46080</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/905994/wjtn-news-headlines-for-fri-feb-27-2026</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>...cotics Investigators say they seized 12.4 grams of fentanyl, a quantity of **methamphetamine** and Suboxone... and, scales and packaging material for the trafficking of ...
-...ssession of illegal narcotics.  Officers say they found quantities of **methamphetamine**, cocaine and fentanyl in 36-year-old James Mawhir's possession when he ent...
-...er of Sherman.  Narcotics Investigators say they seized 12.4 grams of **fentanyl**, a quantity of methamphetamine and Suboxone... and, scales and packaging m...
-....  Officers say they found quantities of methamphetamine, cocaine and **fentanyl** in 36-year-old James Mawhir's possession when he entered the courtroom Wed...
-Five arrested in Brocton **drug** raid one week ago...Five people were arrested late last week following a d...
-...g raid one week ago...Five people were arrested late last week following a **drug** raid on a home in the north county village of Brocton.  Sheriff's off...
-...possession of a controlled substance... and second-degree criminally using **drug** paraphernalia.  They add Mulville was charged with first-degree crimi...
-... Fredonia Village Court...Fredonia Police have charged a man with multiple **drug** counts after he allegedly entered Fredonia Village Court in possession of ...
-...uspects were charged with third-and fourth-degree criminal possession of a **controlled** substance... and second-degree criminally using drug paraphernalia.  ...
-...r was charged with three counts of seventh-degree criminal possession of a **controlled** substance, then was arraigned, and released.   </t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -706,12 +706,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bluebell fire burning near Chautauqua Park in Boulder fully contained - Longmont Times-Call</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D12" s="2">
@@ -719,7 +719,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2xubor7g</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
@@ -731,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
+          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D13" s="2">
@@ -739,35 +744,10 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_Chautauqua_Today.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -703,56 +703,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dunkirk Police Nab Two for Fentanyl Possession in Traffic StopA traffic stop in the City of Dunkirk in early February led to the arrest of two people on drug charges. Dunkirk Police pulled over a vehicle after it committed an infraction on Central Avenue during the evening of February 3rd. Officers say the driv...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367099</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Hanover Pair Charged with Possessing Controlled SubstanceTwo residents of the Town of Hanover face drug-related charges after a traffic stop on Routes 5 and 20 last Tuesday. Chautauqua County Sheriff's deputies pulled over a vehicle driven by 33-year-old Ian Ward shortly after 8:45 PM, with 38-year-old Sar...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46082</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367095</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,88 +401,307 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>https://tinyurl.com/27j8l8c8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
+          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/286rn2wh</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22ssbs2g</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22pe6yfk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46090</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
+...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
+...ptical that this year's spending plan will be on time.Another associate of **drug** kingpin Joseph Zaso indicted on federal drug charges...A man and woman fro...
+... on time.Another associate of drug kingpin Joseph Zaso indicted on federal **drug** charges...A man and woman from Jamestown have been indicted on federal dru...
+...rug charges...A man and woman from Jamestown have been indicted on federal **drug** charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso. &amp;...
+...been indicted on federal drug charges tied to a conspiracy involving local **drug** "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced...
+...f life in prison.  In addition, Jackson is charged with maintaining a **drug**-involved premises.  Prosecutors say that... between 2018... and, Febr...
+...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46090</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
+...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
+...ptical that this year's spending plan will be on time.Another associate of **drug** kingpin Joseph Zaso indicted on federal drug charges...A man and woman fro...
+... on time.Another associate of drug kingpin Joseph Zaso indicted on federal **drug** charges...A man and woman from Jamestown have been indicted on federal dru...
+...rug charges...A man and woman from Jamestown have been indicted on federal **drug** charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso. &amp;...
+...been indicted on federal drug charges tied to a conspiracy involving local **drug** "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced...
+...f life in prison.  In addition, Jackson is charged with maintaining a **drug**-involved premises.  Prosecutors say that... between 2018... and, Febr...
+...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JPD Releases 2025 Annual Crime Report - Post Journal</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2yy6zfdt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>9 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D12" s="2">
         <v>46086</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
 ...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
@@ -495,211 +714,164 @@
 ....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
+...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
+..., others are pending.  Four arrested in Dunkirk during Lincoln Avenue **drug** bust...Four north county residents have been arrested in a drug raid in th...
+...oln Avenue drug bust...Four north county residents have been arrested in a **drug** raid in the city of Dunkirk early Monday afternoon.  Sheriff's office...
+...minal possession of stolen property... and, second-degree criminally using **drug** paraphernalia.  Austin was charged with three counts of third-degree ...
+...iminal possession of stolen property... and second-degree criminally using **drug** paraphernalia.  Eggelston was charged with seventh-degree criminal po...
+...s charged with second... third and seventh-degree criminal possession of a **controlled** substance... third-degree criminal possession of a weapon... fourth-degree...
+...tin was charged with three counts of third-degree criminal possession of a **controlled** substance... and second and seventh-degree criminal possession of drugs......
+....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Four Charged After Drugs, Weapon Found In Dunkirk Home - Post Journal</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D14" s="2">
         <v>46085</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://tinyurl.com/255e9aau</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Four arrested on drug charges in Dunkirk - Newport Dispatch</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D15" s="2">
         <v>46085</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://tinyurl.com/2345sjk4</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Tues., Mar. 3, 2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Michael Burham receives 25 years to life with possible parole in killing of Kala Hodgkin...The man who's pleaded guilty to murder in the death of Jamestown mother of three Kala Hodgkin has been sentenced to 25 years to life in prison with the possbility of parole.  Chautauqua County District Attorney Jason Schmidt says 37 year-old Michael Burham... who's already serving 25 to 50 years in Pennsylvania for kidnapping and escape... received the sentence Monday from County Court Judge David Foley.  Schmidt says a statement made by Hodgkin's eldest child, Colin, played a key role because of it's emotion, and describing trying to protect his siblings while Burham shot and killed his mother.  He also spoke about he and his siblings being split up with other family because of her death... which has added to their trauma.  After killing Hodgkin... Burham fled to Warren County, Pa., where he kidnapped an elderly couple, and, forced them to take him to South Carolina.  He was later found there after a massive manhunt... and, returned to Warren County.  He then escaped... and, was on the run about a week before being recaptured.  Under terms of the plea agreement... Schmidt says Burham will first serve his Pennsylania term -- concurrently with the New York one.  After that... he'll be returned to New York state to the custody of the Department of Corrections and Community Supervision for a hearing to determine if he stays in prison.  Schmidt says his office will strongly recommend no parole.City woman arrested in town of Ellicott for allegedly trying to kidnap an 8 year-old...A woman from Jamestown is accused of trying to kidnap an 8-year-old child in the town of Ellicott last weekend.  Town police were called to the unidentified location last Saturday on a report of the woman allegedly approaching the child... and, then grabbing the juvenile's coat and draging the child down an alleyway... away from her home.  Officers say another juvenile witnessed the incident... and, ran into another house to get an adult.  Police say the 8 year-old was able to get away from 33 year-old Angelea Luszcak... and, an adult came out to help the child.  Officers arrived... and, found Luszcak nearby after she had tried to run off.  She was arrested for second-degree attempted kidnapping... second-degree harassment... and, two counts of endangering the welfare of a child.  Luszcak was taken to the county jail pending arraignment, and will appear in Ellicott Town Court at a later date.Jamestown man arrested for drug possession following a traffic stop...A city man has been arrested for allegedly being found in possession of cocaine with the intent to sell following an early morning traffic stop on Jamestown's southside.  City police say they saw a vehicle commit a traffic infraction at the corner of Charles and Superior Streets about 3:30 a.m. Monday... and, stopped the vehicle.  Officers say they recovered a quantity of cocaine from the driver, 54 year-old Saron Leeper, that was packaged and ready for sale.  Leeper was arrested for third-degree criminal possession of a controlled substance, held pending arraignment.Escalating costs of construction, and upgrading new facility led St. Susan's Center officials to decided to remain at Gateway Center...A sharp increase in construction, and projected operating costs... has led officials with the Jamestown area's largest soup kitchen to decide to stay in the Gateway Center for the foreseeable future.  St. Susan's Center Executive Director Cherie Rowland says the center's Board of directors voted during a recent strategy meeting to remain at 31 Water St.  Rowland says they found their construction and moving costs alone to the former Jamestown Business College were nearly tripling from $1-million to $3-million dollars... and, says they "have to be good stewards" to the people who support them, and donate to their cause.  In addition... Rowland says they were going to have to replace some of their old equipment with new products... and, with the new location, they were going to be required to build an "all electric" kitchen facility.  She says that would increase their electric costs from between $50,000 to $60,000, to about $280,000.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity" in offered the former JBC facility on Jamestown's westside.  The new Gateway Loft's project, proposed for the Gateway Center, is being led by Southern Tier Environments for Living.  STEL Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Karlstrom appointed as new Westfield Police Chief...The village of Westfield has appointed a new police chief who has more than a decade of experience as an officer... and, a Sheriff's deputies.  Village officials and the police department Monday announced the appointment of Erik Karlstrom to replace Greg Wozniak... who recently retired from the post.  Officials say Chief Karlstrom brings a proven record of military and law enforcement leadership to the position.  He's been a village resident since returning from a combat deployment in 2013... and, was a member of the U.S. Army National Guard for 11 years.  Following his military service... Karlstrom pursued a career in law enforcement, graduating from the Chautauqua County Sheriff’s Academy 2015.  He previously served as a part-time officer with the Westfield Dept. from 2015 to 2017.... and, 2023 to present. </t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D16" s="2">
         <v>46084</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906449/wjtn-news-headlines-for-tues-mar-3-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...l appear in Ellicott Town Court at a later date.Jamestown man arrested for **drug** possession following a traffic stop...A city man has been arrested for all...
 ... sale.  Leeper was arrested for third-degree criminal possession of a **controlled** substance, held pending arraignment.Escalating costs of construction, and ...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged After Incident at ROME Warming Shelter</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – Jamestown police say a 46-year-old man is facing harassment and drug possession charges following an early morning incident at a local warming shelter. According to the Jamestown Police Department, officers assigned to the Second Platoon responded to 917 Washington Street, the ROME Warming Shelter, on March 3, 2026, at approximately 12:48 […]The post Jamestown Man Charged After Incident at ROME Warming Shelter appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Tues., Mar. 3, 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Michael Burham receives 25 years to life with possible parole in killing of Kala Hodgkin...The man who's pleaded guilty to murder in the death of Jamestown mother of three Kala Hodgkin has been sentenced to 25 years to life in prison with the possbility of parole.  Chautauqua County District Attorney Jason Schmidt says 37 year-old Michael Burham... who's already serving 25 to 50 years in Pennsylvania for kidnapping and escape... received the sentence Monday from County Court Judge David Foley.  Schmidt says a statement made by Hodgkin's eldest child, Colin, played a key role because of it's emotion, and describing trying to protect his siblings while Burham shot and killed his mother.  He also spoke about he and his siblings being split up with other family because of her death... which has added to their trauma.  After killing Hodgkin... Burham fled to Warren County, Pa., where he kidnapped an elderly couple, and, forced them to take him to South Carolina.  He was later found there after a massive manhunt... and, returned to Warren County.  He then escaped... and, was on the run about a week before being recaptured.  Under terms of the plea agreement... Schmidt says Burham will first serve his Pennsylania term -- concurrently with the New York one.  After that... he'll be returned to New York state to the custody of the Department of Corrections and Community Supervision for a hearing to determine if he stays in prison.  Schmidt says his office will strongly recommend no parole.City woman arrested in town of Ellicott for allegedly trying to kidnap an 8 year-old...A woman from Jamestown is accused of trying to kidnap an 8-year-old child in the town of Ellicott last weekend.  Town police were called to the unidentified location last Saturday on a report of the woman allegedly approaching the child... and, then grabbing the juvenile's coat and draging the child down an alleyway... away from her home.  Officers say another juvenile witnessed the incident... and, ran into another house to get an adult.  Police say the 8 year-old was able to get away from 33 year-old Angelea Luszcak... and, an adult came out to help the child.  Officers arrived... and, found Luszcak nearby after she had tried to run off.  She was arrested for second-degree attempted kidnapping... second-degree harassment... and, two counts of endangering the welfare of a child.  Luszcak was taken to the county jail pending arraignment, and will appear in Ellicott Town Court at a later date.Jamestown man arrested for drug possession following a traffic stop...A city man has been arrested for allegedly being found in possession of cocaine with the intent to sell following an early morning traffic stop on Jamestown's southside.  City police say they saw a vehicle commit a traffic infraction at the corner of Charles and Superior Streets about 3:30 a.m. Monday... and, stopped the vehicle.  Officers say they recovered a quantity of cocaine from the driver, 54 year-old Saron Leeper, that was packaged and ready for sale.  Leeper was arrested for third-degree criminal possession of a controlled substance, held pending arraignment.Escalating costs of construction, and upgrading new facility led St. Susan's Center officials to decided to remain at Gateway Center...A sharp increase in construction, and projected operating costs... has led officials with the Jamestown area's largest soup kitchen to decide to stay in the Gateway Center for the foreseeable future.  St. Susan's Center Executive Director Cherie Rowland says the center's Board of directors voted during a recent strategy meeting to remain at 31 Water St.  Rowland says they found their construction and moving costs alone to the former Jamestown Business College were nearly tripling from $1-million to $3-million dollars... and, says they "have to be good stewards" to the people who support them, and donate to their cause.  In addition... Rowland says they were going to have to replace some of their old equipment with new products... and, with the new location, they were going to be required to build an "all electric" kitchen facility.  She says that would increase their electric costs from between $50,000 to $60,000, to about $280,000.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity" in offered the former JBC facility on Jamestown's westside.  The new Gateway Loft's project, proposed for the Gateway Center, is being led by Southern Tier Environments for Living.  STEL Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Karlstrom appointed as new Westfield Police Chief...The village of Westfield has appointed a new police chief who has more than a decade of experience as an officer... and, a Sheriff's deputies.  Village officials and the police department Monday announced the appointment of Erik Karlstrom to replace Greg Wozniak... who recently retired from the post.  Officials say Chief Karlstrom brings a proven record of military and law enforcement leadership to the position.  He's been a village resident since returning from a combat deployment in 2013... and, was a member of the U.S. Army National Guard for 11 years.  Following his military service... Karlstrom pursued a career in law enforcement, graduating from the Chautauqua County Sheriff’s Academy 2015.  He previously served as a part-time officer with the Westfield Dept. from 2015 to 2017.... and, 2023 to present. </t>
+        </is>
+      </c>
+      <c r="D17" s="2">
         <v>46084</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/03/jamestown-man-charged-after-incident-at-rome-warming-shelter/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>...ce say a 46-year-old man is facing harassment and **drug** possession charges following an early morning inc...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906449/wjtn-news-headlines-for-tues-mar-3-2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>...l appear in Ellicott Town Court at a later date.Jamestown man arrested for **drug** possession following a traffic stop...A city man has been arrested for all...
+... sale.  Leeper was arrested for third-degree criminal possession of a **controlled** substance, held pending arraignment.Escalating costs of construction, and ...</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – DUNKIRK, NY — Four people were arrested following the execution of a narcotics search warrant Monday afternoon at an upper apartment on Lincoln Avenue, authorities said. According to the Dunkirk Police Department, officers executed a search warrant at 81 Lincoln Ave., Upper Apartment, at approximately 1:08 p.m. on March 2, 2026. […]The post Four Arrested After Narcotics Search Warrant in Dunkirk; Meth, Fentanyl, Stolen Revolver Seized appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/03/four-arrested-after-narcotics-search-warrant-in-dunkirk-meth-fentanyl-stolen-revolver-seized/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>... After Narcotics Search Warrant in Dunkirk; Meth, **Fentanyl**, Stolen Revolver Seized appeared first on WNY New...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Chautauqua County man sentenced to prison for his role in 2014 murder - WKBW</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46083</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/25hbntwu</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Mon., Mar. 2, 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Burham receives 25 years to life sentence for murder of Kala Hodgkin...The Jamestown-area man convicted of the murder of local mother of three, Kala Hodgkin, has been sentenced to 25 years to life in prison.  We learned just before Noon today that 37 year-old Michael Burham, who's already serving time for kidnapping and escape in Warren County, Pa., received the sentence from County Court Judge David Foley.  More when it becomes availble.St. Susan's Center announces it will remain in the Gateway Center after costs to move into former Business College building triple...The Jamestown area's largest soup kitchen will be staying in the Gateway Center on Water Street for the foreseeable future.  That after the St. Susan's Center Board of directors voted to stay at their current location.  Executive Director Cheri Rowland says the main reason is a tripling of the renovation and moving costs they were going to see to move operations into part of the former Jamestown Business College.  Rowland says... those initial projections of about $1-million... had now climbed to $3-million.  With that... she says the board decided to remain at it's current location at 31 Water Street... and, pursue tenancy with the new Gateway Lofts redevelopment project.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity."  But... over the past year... she says the center completed architectural studies, site plan approvals, and detailed construction estimates for the JBC property.  As planning advanced... projected renovation costs increased substantially — due in large part to changing the building's use from a school to food services.  The Gateway Loft's project is being led by Southern Tier Environments for Living... and, their Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Fire rescue crews rescue man who fell through the ice on a town of Portland pond...A man who had fallen through the ice on a pond in the north county was successfully rescued last weekend by local fire rescuers.  Sheriff's deputies say the county's Water Emergency Team was also called to the scene to assist Portland and Brocton fire crews at the Gravevine Estates on Route 5 shortly after Midnight Saturday.  Officers say the WET Team was able to get out to the man... and, secure him with a "life ring."  Members of the fire departments, civilian bystanders, and Sheriffs Deputies were then able to pull the man back to shore where he was treated for exposure... and, taken to a local hospital for treatment.  Deputies also remind the public that at this time of year... ice conditions can change rapidly.  If you do venture out on to the ice, please wear a PFD and check ice conditions as you go.City man sought on multiple warrants arrested following street check, and police find meth...A man from Jamestown sought on multiple arrest warrants has been arrested in the Brooklyn Square area following a street check late last week.  City police were patroling that area shortly before 1 p.m. last Friday... when they spotted 50 year-old Richard Barr.  Officers took Barr into custody on the warrants... and, a further search turned up a quantity of methamphetamine in his possession.  He was taken to the city jail on the warrants and one count of seventh-degree criminal possession of a controlled substance... and, held pending arraignment.Molitor, Borrello supporting local highway superintendents is effort to get more CHIPS funding...About 650 highway superintendents from across the state... including 10 from Chautauqua County... will be in Albany this week to lobby for more highway funding.  State Assemblyman Andrew Molitor says he is pushing for a $250-million increase in the Consolidated Highway Improvement Program -- otherwise known as CHIPS -- funding.  Molitor says there was a slight increase in that funding last year, but not enough to keep pace with inflation... which he says has seen 50% to 60% each year, and the amount funding increases are not going far enough.  Westfield Town Highway Superintendent, Dave Babcock, says boosting funding for local roads and bridges would prevent higher long-term costs for local municipalities.  ----State Senator George Borrello says Governor Kathy Hochul's 2026-27 budget keeps funding in the CHIPS program flat.  Borrello says local highway superintendents and others plan to be in Albany this coming week to lobby for more funding due to major cost increases... for supplies, concrete, and aggragate are being kept at the same or lower levels in budget this year.  Borrello says there used to be a formula used to fairly distribute CHIPS funding.  However... he says since Democrats got the majority in the Senate... it's become more political.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.Langworthy voices his support for President Trump's "Operation Epic Fury" in Iran...Local Congressman Nick Langworthy is standing firmly behind President Donald Trump's decision to attack Iran... and, kill it's leader -- the Ayatollah Ali Khamenei.  Langworthy says -- in a printed statement -- that "the Iranian regime is the world’s number one sponsor of terror and has the blood of thousands of Americans on its hands.  Their “Death to America” chants and desire to annihilate Israel are not slogans, they are actively building the nuclear weapons and missile capabilities to make it a reality and over the last four decades have taken every opportunity to kill."  The Buffalo-area Republican adds that the president gave them numerous chances to de-escalate the situation.  </t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46083</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906252/wjtn-news-headlines-for-mon-mar-2-2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...o custody on the warrants... and, a further search turned up a quantity of **methamphetamine** in his possession.  He was taken to the city jail on the warrants and...
-...l on the warrants and one count of seventh-degree criminal possession of a **controlled** substance... and, held pending arraignment.Molitor, Borrello supporting lo...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,15 +406,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
+          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27j8l8c8</t>
+          <t>https://tinyurl.com/27h57fu2</t>
         </is>
       </c>
     </row>
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
+          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -434,7 +434,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/286rn2wh</t>
+          <t>https://tinyurl.com/27j8l8c8</t>
         </is>
       </c>
     </row>
@@ -446,7 +446,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
+          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -454,7 +454,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22ssbs2g</t>
+          <t>https://tinyurl.com/286rn2wh</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
+          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D5" s="2">
@@ -474,35 +474,167 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22pe6yfk</t>
+          <t>https://tinyurl.com/28jrvqme</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22ssbs2g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty to Drug, Kidnapping Charges - TAPinto</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22pe6yfk</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907458/wjtn-news-headlines-for-tues-mar-10-2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>...as a passenger... and, found that both were in possession of a quantity of **Methamphetamine**... Fentanyl... and, plastic knuckles.  Police also found that Light w...
+...wrence Vilardo to possession with intent to distribute 40 grams or more of **fentanyl**... and, kidnapping.  Prosecutors say in December of 2022... a raid on...
+...aid on Lowery's West Cowden Place home led to seizure of about 59 grams of **Fentanyl**... $1,140 in cash... and, drug paraphernalia.  Prior to that... inves...
+...nd, found that both were in possession of a quantity of Methamphetamine... **Fentanyl**... and, plastic knuckles.  Police also found that Light was driving w...
+City man pleads guilty to federal **drug** and kidnapping charges...A man from Jamestown has pleaded guility to feder...
+...d kidnapping charges...A man from Jamestown has pleaded guility to federal **drug** and kidnapping charges in connecton with incidents in late 2022... and, la...
+...ome led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, **drug** paraphernalia.  Prior to that... investigators made two undercover pu...
+...m on the six Media One Radio Group stations.City man and woman arrested on **drug** and weapons charges after being found passed out in car...Two people from ...
+...er being found passed out in car...Two people from Jamestown face multiple **drug** and weapons possession charges after they were found passed out in a car l...
+...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia... and one count of third-degree criminal possession of a we...
+...is charged with two counts each of seventh-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia... and...
+...ns.  Hogg faces two counts of seventh-degree criminal possession of a **controlled** substance... and one of third-degree criminal possession of a weapon. &amp;nbs...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907458/wjtn-news-headlines-for-tues-mar-10-2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>...as a passenger... and, found that both were in possession of a quantity of **Methamphetamine**... Fentanyl... and, plastic knuckles.  Police also found that Light w...
+...wrence Vilardo to possession with intent to distribute 40 grams or more of **fentanyl**... and, kidnapping.  Prosecutors say in December of 2022... a raid on...
+...aid on Lowery's West Cowden Place home led to seizure of about 59 grams of **Fentanyl**... $1,140 in cash... and, drug paraphernalia.  Prior to that... inves...
+...nd, found that both were in possession of a quantity of Methamphetamine... **Fentanyl**... and, plastic knuckles.  Police also found that Light was driving w...
+City man pleads guilty to federal **drug** and kidnapping charges...A man from Jamestown has pleaded guility to feder...
+...d kidnapping charges...A man from Jamestown has pleaded guility to federal **drug** and kidnapping charges in connecton with incidents in late 2022... and, la...
+...ome led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, **drug** paraphernalia.  Prior to that... investigators made two undercover pu...
+...m on the six Media One Radio Group stations.City man and woman arrested on **drug** and weapons charges after being found passed out in car...Two people from ...
+...er being found passed out in car...Two people from Jamestown face multiple **drug** and weapons possession charges after they were found passed out in a car l...
+...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia... and one count of third-degree criminal possession of a we...
+...is charged with two counts each of seventh-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia... and...
+...ns.  Hogg faces two counts of seventh-degree criminal possession of a **controlled** substance... and one of third-degree criminal possession of a weapon. &amp;nbs...</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>8 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D10" s="2">
         <v>46090</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
 ...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
@@ -514,37 +646,37 @@
 ...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>8 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D11" s="2">
         <v>46090</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
 ...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
@@ -556,121 +688,6 @@
 ...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JPD Releases 2025 Annual Crime Report - Post Journal</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46088</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2yy6zfdt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46087</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46087</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46087</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -680,28 +697,143 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JPD Releases 2025 Annual Crime Report - Post Journal</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2yy6zfdt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>46087</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>9 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
         </is>
       </c>
-      <c r="D12" s="2">
+      <c r="D16" s="2">
         <v>46086</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
 ...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
@@ -714,37 +846,37 @@
 ....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>9 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
         </is>
       </c>
-      <c r="D13" s="2">
+      <c r="D17" s="2">
         <v>46086</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
 ...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
@@ -757,121 +889,29 @@
 ....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Four Charged After Drugs, Weapon Found In Dunkirk Home - Post Journal</t>
         </is>
       </c>
-      <c r="D14" s="2">
+      <c r="D18" s="2">
         <v>46085</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://tinyurl.com/255e9aau</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Four arrested on drug charges in Dunkirk - Newport Dispatch</t>
-        </is>
-      </c>
-      <c r="D15" s="2">
-        <v>46085</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2345sjk4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Tues., Mar. 3, 2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Michael Burham receives 25 years to life with possible parole in killing of Kala Hodgkin...The man who's pleaded guilty to murder in the death of Jamestown mother of three Kala Hodgkin has been sentenced to 25 years to life in prison with the possbility of parole.  Chautauqua County District Attorney Jason Schmidt says 37 year-old Michael Burham... who's already serving 25 to 50 years in Pennsylvania for kidnapping and escape... received the sentence Monday from County Court Judge David Foley.  Schmidt says a statement made by Hodgkin's eldest child, Colin, played a key role because of it's emotion, and describing trying to protect his siblings while Burham shot and killed his mother.  He also spoke about he and his siblings being split up with other family because of her death... which has added to their trauma.  After killing Hodgkin... Burham fled to Warren County, Pa., where he kidnapped an elderly couple, and, forced them to take him to South Carolina.  He was later found there after a massive manhunt... and, returned to Warren County.  He then escaped... and, was on the run about a week before being recaptured.  Under terms of the plea agreement... Schmidt says Burham will first serve his Pennsylania term -- concurrently with the New York one.  After that... he'll be returned to New York state to the custody of the Department of Corrections and Community Supervision for a hearing to determine if he stays in prison.  Schmidt says his office will strongly recommend no parole.City woman arrested in town of Ellicott for allegedly trying to kidnap an 8 year-old...A woman from Jamestown is accused of trying to kidnap an 8-year-old child in the town of Ellicott last weekend.  Town police were called to the unidentified location last Saturday on a report of the woman allegedly approaching the child... and, then grabbing the juvenile's coat and draging the child down an alleyway... away from her home.  Officers say another juvenile witnessed the incident... and, ran into another house to get an adult.  Police say the 8 year-old was able to get away from 33 year-old Angelea Luszcak... and, an adult came out to help the child.  Officers arrived... and, found Luszcak nearby after she had tried to run off.  She was arrested for second-degree attempted kidnapping... second-degree harassment... and, two counts of endangering the welfare of a child.  Luszcak was taken to the county jail pending arraignment, and will appear in Ellicott Town Court at a later date.Jamestown man arrested for drug possession following a traffic stop...A city man has been arrested for allegedly being found in possession of cocaine with the intent to sell following an early morning traffic stop on Jamestown's southside.  City police say they saw a vehicle commit a traffic infraction at the corner of Charles and Superior Streets about 3:30 a.m. Monday... and, stopped the vehicle.  Officers say they recovered a quantity of cocaine from the driver, 54 year-old Saron Leeper, that was packaged and ready for sale.  Leeper was arrested for third-degree criminal possession of a controlled substance, held pending arraignment.Escalating costs of construction, and upgrading new facility led St. Susan's Center officials to decided to remain at Gateway Center...A sharp increase in construction, and projected operating costs... has led officials with the Jamestown area's largest soup kitchen to decide to stay in the Gateway Center for the foreseeable future.  St. Susan's Center Executive Director Cherie Rowland says the center's Board of directors voted during a recent strategy meeting to remain at 31 Water St.  Rowland says they found their construction and moving costs alone to the former Jamestown Business College were nearly tripling from $1-million to $3-million dollars... and, says they "have to be good stewards" to the people who support them, and donate to their cause.  In addition... Rowland says they were going to have to replace some of their old equipment with new products... and, with the new location, they were going to be required to build an "all electric" kitchen facility.  She says that would increase their electric costs from between $50,000 to $60,000, to about $280,000.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity" in offered the former JBC facility on Jamestown's westside.  The new Gateway Loft's project, proposed for the Gateway Center, is being led by Southern Tier Environments for Living.  STEL Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Karlstrom appointed as new Westfield Police Chief...The village of Westfield has appointed a new police chief who has more than a decade of experience as an officer... and, a Sheriff's deputies.  Village officials and the police department Monday announced the appointment of Erik Karlstrom to replace Greg Wozniak... who recently retired from the post.  Officials say Chief Karlstrom brings a proven record of military and law enforcement leadership to the position.  He's been a village resident since returning from a combat deployment in 2013... and, was a member of the U.S. Army National Guard for 11 years.  Following his military service... Karlstrom pursued a career in law enforcement, graduating from the Chautauqua County Sheriff’s Academy 2015.  He previously served as a part-time officer with the Westfield Dept. from 2015 to 2017.... and, 2023 to present. </t>
-        </is>
-      </c>
-      <c r="D16" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906449/wjtn-news-headlines-for-tues-mar-3-2026</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>...l appear in Ellicott Town Court at a later date.Jamestown man arrested for **drug** possession following a traffic stop...A city man has been arrested for all...
-... sale.  Leeper was arrested for third-degree criminal possession of a **controlled** substance, held pending arraignment.Escalating costs of construction, and ...</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Tues., Mar. 3, 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Michael Burham receives 25 years to life with possible parole in killing of Kala Hodgkin...The man who's pleaded guilty to murder in the death of Jamestown mother of three Kala Hodgkin has been sentenced to 25 years to life in prison with the possbility of parole.  Chautauqua County District Attorney Jason Schmidt says 37 year-old Michael Burham... who's already serving 25 to 50 years in Pennsylvania for kidnapping and escape... received the sentence Monday from County Court Judge David Foley.  Schmidt says a statement made by Hodgkin's eldest child, Colin, played a key role because of it's emotion, and describing trying to protect his siblings while Burham shot and killed his mother.  He also spoke about he and his siblings being split up with other family because of her death... which has added to their trauma.  After killing Hodgkin... Burham fled to Warren County, Pa., where he kidnapped an elderly couple, and, forced them to take him to South Carolina.  He was later found there after a massive manhunt... and, returned to Warren County.  He then escaped... and, was on the run about a week before being recaptured.  Under terms of the plea agreement... Schmidt says Burham will first serve his Pennsylania term -- concurrently with the New York one.  After that... he'll be returned to New York state to the custody of the Department of Corrections and Community Supervision for a hearing to determine if he stays in prison.  Schmidt says his office will strongly recommend no parole.City woman arrested in town of Ellicott for allegedly trying to kidnap an 8 year-old...A woman from Jamestown is accused of trying to kidnap an 8-year-old child in the town of Ellicott last weekend.  Town police were called to the unidentified location last Saturday on a report of the woman allegedly approaching the child... and, then grabbing the juvenile's coat and draging the child down an alleyway... away from her home.  Officers say another juvenile witnessed the incident... and, ran into another house to get an adult.  Police say the 8 year-old was able to get away from 33 year-old Angelea Luszcak... and, an adult came out to help the child.  Officers arrived... and, found Luszcak nearby after she had tried to run off.  She was arrested for second-degree attempted kidnapping... second-degree harassment... and, two counts of endangering the welfare of a child.  Luszcak was taken to the county jail pending arraignment, and will appear in Ellicott Town Court at a later date.Jamestown man arrested for drug possession following a traffic stop...A city man has been arrested for allegedly being found in possession of cocaine with the intent to sell following an early morning traffic stop on Jamestown's southside.  City police say they saw a vehicle commit a traffic infraction at the corner of Charles and Superior Streets about 3:30 a.m. Monday... and, stopped the vehicle.  Officers say they recovered a quantity of cocaine from the driver, 54 year-old Saron Leeper, that was packaged and ready for sale.  Leeper was arrested for third-degree criminal possession of a controlled substance, held pending arraignment.Escalating costs of construction, and upgrading new facility led St. Susan's Center officials to decided to remain at Gateway Center...A sharp increase in construction, and projected operating costs... has led officials with the Jamestown area's largest soup kitchen to decide to stay in the Gateway Center for the foreseeable future.  St. Susan's Center Executive Director Cherie Rowland says the center's Board of directors voted during a recent strategy meeting to remain at 31 Water St.  Rowland says they found their construction and moving costs alone to the former Jamestown Business College were nearly tripling from $1-million to $3-million dollars... and, says they "have to be good stewards" to the people who support them, and donate to their cause.  In addition... Rowland says they were going to have to replace some of their old equipment with new products... and, with the new location, they were going to be required to build an "all electric" kitchen facility.  She says that would increase their electric costs from between $50,000 to $60,000, to about $280,000.  Rowland says they are "incredibly grateful to the Conklin family for their extraordinary generosity" in offered the former JBC facility on Jamestown's westside.  The new Gateway Loft's project, proposed for the Gateway Center, is being led by Southern Tier Environments for Living.  STEL Executive Director, Tom Whitney, says they are "pleased" that the center has decided to remain in that building.Karlstrom appointed as new Westfield Police Chief...The village of Westfield has appointed a new police chief who has more than a decade of experience as an officer... and, a Sheriff's deputies.  Village officials and the police department Monday announced the appointment of Erik Karlstrom to replace Greg Wozniak... who recently retired from the post.  Officials say Chief Karlstrom brings a proven record of military and law enforcement leadership to the position.  He's been a village resident since returning from a combat deployment in 2013... and, was a member of the U.S. Army National Guard for 11 years.  Following his military service... Karlstrom pursued a career in law enforcement, graduating from the Chautauqua County Sheriff’s Academy 2015.  He previously served as a part-time officer with the Westfield Dept. from 2015 to 2017.... and, 2023 to present. </t>
-        </is>
-      </c>
-      <c r="D17" s="2">
-        <v>46084</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906449/wjtn-news-headlines-for-tues-mar-3-2026</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>...l appear in Ellicott Town Court at a later date.Jamestown man arrested for **drug** possession following a traffic stop...A city man has been arrested for all...
-... sale.  Leeper was arrested for third-degree criminal possession of a **controlled** substance, held pending arraignment.Escalating costs of construction, and ...</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -426,112 +426,170 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
+          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27j8l8c8</t>
+          <t>https://tinyurl.com/2yyn26c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/286rn2wh</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
+          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28jrvqme</t>
+          <t>https://wnynewsnow.com/2026/03/11/jamestown-man-pleads-guilty-to-federal-fentanyl-trafficking-and-kidnapping-charges/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>... A Jamestown man has admitted in federal court to **fentanyl** trafficking and kidnapping after authorities said...
+...…]The post Jamestown Man Pleads Guilty to Federal **Fentanyl** Trafficking and Kidnapping Charges appeared first...
+...pping after authorities said he sold the powerful **opioid** and held a victim against her will for several we...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
+          <t>Substance Use vs. Abuse: How to Identify the Difference</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>In today’s society, the use of substances such as alcohol and marijuana is often woven into the fabric of social interactions and celebrations. For many, these substances can enhance experiences and create memorable moments. However, there is a fine line between enjoying substances and crossing over into substance abuse and addiction. Recognizing where that line […]The post Substance Use vs. Abuse: How to Identify the Difference appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22ssbs2g</t>
+          <t>https://wnynewsnow.com/2026/03/11/substance-use-vs-abuse-how-to-identify-the-difference/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...ociety, the use of substances such as alcohol and **marijuana** is often woven into the fabric of social interact...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Drug, Kidnapping Charges - TAPinto</t>
+          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A Jamestown man has pleaded guilty to drug trafficking and kidnapping in U.S. District Court. U.S. Attorney Michael DiGiacomo announced that 31-year old Dwayne Lowery, aka Chi Chi, pleaded guilty before U.S. District Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl and kidnapping. The charges carry a mandatory […]</t>
         </is>
       </c>
       <c r="D7" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22pe6yfk</t>
+          <t>https://www.wrfalp.com/?p=74583</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...ion with intent to distribute 40 grams or more of **fentanyl** and kidnapping. The charges carry a mandatory [&amp;#...
+A Jamestown man has pleaded guilty to **drug** trafficking and kidnapping in U.S. District Court...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WRFALP.R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
+          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -539,10 +597,115 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/27j8l8c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/286rn2wh</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/28jrvqme</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22ssbs2g</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty to Drug, Kidnapping Charges - TAPinto</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22pe6yfk</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46091</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907458/wjtn-news-headlines-for-tues-mar-10-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...as a passenger... and, found that both were in possession of a quantity of **Methamphetamine**... Fentanyl... and, plastic knuckles.  Police also found that Light w...
 ...wrence Vilardo to possession with intent to distribute 40 grams or more of **fentanyl**... and, kidnapping.  Prosecutors say in December of 2022... a raid on...
@@ -558,83 +721,37 @@
 ...ns.  Hogg faces two counts of seventh-degree criminal possession of a **controlled** substance... and one of third-degree criminal possession of a weapon. &amp;nbs...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>12 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907458/wjtn-news-headlines-for-tues-mar-10-2026</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>...as a passenger... and, found that both were in possession of a quantity of **Methamphetamine**... Fentanyl... and, plastic knuckles.  Police also found that Light w...
-...wrence Vilardo to possession with intent to distribute 40 grams or more of **fentanyl**... and, kidnapping.  Prosecutors say in December of 2022... a raid on...
-...aid on Lowery's West Cowden Place home led to seizure of about 59 grams of **Fentanyl**... $1,140 in cash... and, drug paraphernalia.  Prior to that... inves...
-...nd, found that both were in possession of a quantity of Methamphetamine... **Fentanyl**... and, plastic knuckles.  Police also found that Light was driving w...
-City man pleads guilty to federal **drug** and kidnapping charges...A man from Jamestown has pleaded guility to feder...
-...d kidnapping charges...A man from Jamestown has pleaded guility to federal **drug** and kidnapping charges in connecton with incidents in late 2022... and, la...
-...ome led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, **drug** paraphernalia.  Prior to that... investigators made two undercover pu...
-...m on the six Media One Radio Group stations.City man and woman arrested on **drug** and weapons charges after being found passed out in car...Two people from ...
-...er being found passed out in car...Two people from Jamestown face multiple **drug** and weapons possession charges after they were found passed out in a car l...
-...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia... and one count of third-degree criminal possession of a we...
-...is charged with two counts each of seventh-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia... and...
-...ns.  Hogg faces two counts of seventh-degree criminal possession of a **controlled** substance... and one of third-degree criminal possession of a weapon. &amp;nbs...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>8 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D14" s="2">
         <v>46090</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
 ...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
@@ -646,128 +763,6 @@
 ...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>8 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46090</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
-...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
-...ptical that this year's spending plan will be on time.Another associate of **drug** kingpin Joseph Zaso indicted on federal drug charges...A man and woman fro...
-... on time.Another associate of drug kingpin Joseph Zaso indicted on federal **drug** charges...A man and woman from Jamestown have been indicted on federal dru...
-...rug charges...A man and woman from Jamestown have been indicted on federal **drug** charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso. &amp;...
-...been indicted on federal drug charges tied to a conspiracy involving local **drug** "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced...
-...f life in prison.  In addition, Jackson is charged with maintaining a **drug**-involved premises.  Prosecutors say that... between 2018... and, Febr...
-...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPD Releases 2025 Annual Crime Report - Post Journal</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46088</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2yy6zfdt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46087</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46087</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
@@ -777,141 +772,80 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
+          <t>JPD Releases 2025 Annual Crime Report - Post Journal</t>
         </is>
       </c>
       <c r="D15" s="2">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/2yy6zfdt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>9 keyword references (WJTN)</t>
+          <t>Chautauqua_Today</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
+          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D16" s="2">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
-...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
-..., others are pending.  Four arrested in Dunkirk during Lincoln Avenue **drug** bust...Four north county residents have been arrested in a drug raid in th...
-...oln Avenue drug bust...Four north county residents have been arrested in a **drug** raid in the city of Dunkirk early Monday afternoon.  Sheriff's office...
-...minal possession of stolen property... and, second-degree criminally using **drug** paraphernalia.  Austin was charged with three counts of third-degree ...
-...iminal possession of stolen property... and second-degree criminally using **drug** paraphernalia.  Eggelston was charged with seventh-degree criminal po...
-...s charged with second... third and seventh-degree criminal possession of a **controlled** substance... third-degree criminal possession of a weapon... fourth-degree...
-...tin was charged with three counts of third-degree criminal possession of a **controlled** substance... and second and seventh-degree criminal possession of drugs......
-....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 4, 2026</t>
+          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9 keyword references (WJTN)</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Two Jamestown residents arrested following reported fight with driver of car on city's southside...Two city residents are accused of damaging another person's car on Jamestown's southside following a reported fight late last week.  City police say they were called to the Foote Avenue Plaza shortly before 9 p.m. last Friday for the reported altercation.  When they arrived... officers found the victim seated inside a parked vehicle that had sustained visible damage... along with one suspect -- 34 year-old Jasmine Davis -- nearby.  They found that Davis approached the victim’s car... struck it... and, threatened the victim while they were locked inside.  Police say the second suspect... 23 year-old Elijah McBride... also approached the vehicle, threw items at it, and then struck the driver-side mirror -- breaking it.  The vehicle also had a broken windshield... and, food debris on the exterior.  Davis was arrested at the scene for second-degree harassment.  McBride had fled... but, was later found at a separate location and arrested for third-degree criminal mischief... and, others are pending.  Four arrested in Dunkirk during Lincoln Avenue drug bust...Four north county residents have been arrested in a drug raid in the city of Dunkirk early Monday afternoon.  Sheriff's officers say members of their Narcotics Investigation team... along with those from Jamestown... and, Dunkirk Police... executed a search warrant at 81 Lincoln Ave. shortly after 1 p.m.  Inside... they located 28 year-old Dakota Cordell... 23 year-old Taylor Austin... 36 year-old Matthew Eggelston... and, 55 year-old Robert Ryen.  During a subsequent search... Investigators seized 331.69 grams of methamphetamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentanyl... 79l dosage units of suboxone, scales and packaging material used for trafficking drugs... along with a stolen .44 magnum revolver and just over $4,900 in cash.  Cordell was charged with second... third and seventh-degree criminal possession of a controlled substance... third-degree criminal possession of a weapon... fourth-degree criminal possession of stolen property... and, second-degree criminally using drug paraphernalia.  Austin was charged with three counts of third-degree criminal possession of a controlled substance... and second and seventh-degree criminal possession of drugs... criminal possession of a firearm... fourth-degree criminal possession of stolen property... and second-degree criminally using drug paraphernalia.  Eggelston was charged with seventh-degree criminal possession of a controlled substance... and, Ryen was charged with first-degree criminal nuisance.  The investigation is ongoing and more charges are expected.City Council weighs in on proposal to provide the city an additional $1.6-million in Temporary Municipal Aid from the state...The Jamestown City Council's Finance Committee has approved a resolution urging Governor Kathy Hochul and the state legislature to approve an additional $100-million in local, municipal aid.  For the first time Monday night... lawmakers discussed the proposal... which includes an additional $1.6-million for the city.  Committee Chairman Doug Scotchmer read the resolution... noting that the additional money was in the Governor's 30-day amendments to her budget proposal.  Scotchmer says they "applaud" the governor's proposal, and "reaffirming her commitment to strengthening New York's cities and villages."  Scotchmer also noted that the resolution also calls on the state to develop -- "a more permanent and predictable solution for unrestricted aid" to local governments.  Mayor Kim Ecklund also cautioned council members to not treat the additional aid as a windfall... because it won't likely be sent to the city by late in 2026 at the earliest.  She says they have to work to make sure it stays in the final budget plan.  The state legislature recently finished up it's budget hearings on the governor's proposed, $260-billion spending plan... and, work will begin on the Senate and Assembly's "one-house" budget bills.  The final budget is due by Apr. 1.AAA says local Gas Prices up due to Iranian Conflict...Gasoline prices in the Jamestown-area... and, the rest of New York state and the nation have spiked in recent days due to the ongoing Iranian Conflict.  That today from AAA East Central, which reports the national average for a gallon of regular, unleaded gas has jumped to $3.19... which is 20-cents more than Monday... and, 31-cents higher than a month ago.  Here in the Jamestown-area... the price began increasing Monday morning to just under $3.30 a gallon.  Prices prior to the conflict were in the area of $3.20.  Oil prices ended the day Tuesday at $74.56 a barrell on the Texas Intermediate Crude Oil.. and, briefly hit just over $77.  AAA Spokesman Jim Garrity says -- 'consumers should prepare in case gasoline prices rise even further.  At this point, all eyes are on crude oil, which accounts for 50 to 60 cents of each dollar you spend at the pump.  Also, demand is increasing and refineries are beginning their annual transition to summer blend gasoline, which are both trends that typically push prices higher in the spring."Public Hearing for sidewalk project on Fairmount Ave. set for Thursday...A public hearing on plans to put in new sidewalks on one side of Fairmount Avenue in the town of Busti and village of Lakewood is set for Thursday night.  The state Department of Transporation... which is undertaking the project... says the hearing will be held at the Busti Town Hall from 4:30 p.m. to 6:30 p.m.  DOT officials say there will be a formal presentation at 5:30 p.m.., and, the public will be able to ask questions and provide feedback at that time.  The Project area will run from State Route 474 to Elmcrest Avenue... and will entail a repaiving of the road from Winch Road to Elmcrest... along with the construction of new sidewalks on one side of the roadway from Route 474 to Shadyside Avenue. </t>
+          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
         </is>
       </c>
       <c r="D17" s="2">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906687/wjtn-news-headlines-for-wed-mar-4-2026</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>....  During a subsequent search... Investigators seized 331.69 grams of **methamphetamine**, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of fentan...
-...tamine, 5.35 grams of cocaine, 2.42 grams of crack cocaine, 14.55 grams of **fentanyl**... 79l dosage units of suboxone, scales and packaging material used for tr...
-..., others are pending.  Four arrested in Dunkirk during Lincoln Avenue **drug** bust...Four north county residents have been arrested in a drug raid in th...
-...oln Avenue drug bust...Four north county residents have been arrested in a **drug** raid in the city of Dunkirk early Monday afternoon.  Sheriff's office...
-...minal possession of stolen property... and, second-degree criminally using **drug** paraphernalia.  Austin was charged with three counts of third-degree ...
-...iminal possession of stolen property... and second-degree criminally using **drug** paraphernalia.  Eggelston was charged with seventh-degree criminal po...
-...s charged with second... third and seventh-degree criminal possession of a **controlled** substance... third-degree criminal possession of a weapon... fourth-degree...
-...tin was charged with three counts of third-degree criminal possession of a **controlled** substance... and second and seventh-degree criminal possession of drugs......
-....  Eggelston was charged with seventh-degree criminal possession of a **controlled** substance... and, Ryen was charged with first-degree criminal nuisance. &amp;n...</t>
+          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Four Charged After Drugs, Weapon Found In Dunkirk Home - Post Journal</t>
-        </is>
-      </c>
-      <c r="D18" s="2">
-        <v>46085</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/255e9aau</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,306 +406,492 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
+          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27h57fu2</t>
+          <t>https://tinyurl.com/27xq83cr</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
+          <t>12 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yyn26c6</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907822/wjtn-news-headlines-for-thurs-mar-12-2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>..., seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of **methamphetamine**, scales and packaging used to traffic narcotics... a high-capacity magazin...
+... into custody and a subsequent search of the vehicle located a quantity of **methamphetamine**.  She was taken to the city jail where she was held pending arraignme...
+... Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of **fentanyl**, 4.5 grams of methamphetamine, scales and packaging used to traffic narcot...
+City man arrested during **drug** bust on Lincoln St...A man from Jamestown has been arrested on multiple dr...
+...ug bust on Lincoln St...A man from Jamestown has been arrested on multiple **drug** and weapons possession charges following a raid Wednesday afternoon on the...
+...ree criminal possession of a weapon... and, second-degree criminally using **drug** paraphernalia.  Santiago was held pending arraignment in city court. ...
+...p line at 483-8477.Second city man arrested during Fluvanna Ave. Extention **drug** raid...Another city man has been arrested on drug and weapons possession c...
+... Fluvanna Ave. Extention drug raid...Another city man has been arrested on **drug** and weapons possession charges following a raid on a home in the Fluvanna ...
+...gree criminal possession of a weapon... and second-degree criminally using **drug** paraphernalia.  Grayson was held in the county jail pending centraliz...
+...charged Santiago with five counts of third-degree criminal possession of a **controlled** substance.... second-and third-degree criminal possession of a weapon... a...
+...cash.  Grayson was charged with third-degree criminal possession of a **controlled** substance... fourth-degree criminal possession of a weapon... and second-d...
+...Leandra's Law... unsafe backing... seventh-degree criminal possession of a **controlled** substance... and, two counts of endangering the welfare of a child.Gillibr...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
+          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
+          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
+          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46093</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2cofmq97</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46093</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22dxk5ay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46093</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/266pwgl9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WRFA-LP 107.9 FM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46093</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.wrfalp.com/?p=74599</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>News_search_WRFALP.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/27h57fu2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2yyn26c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D12" s="2">
         <v>46092</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/11/jamestown-man-pleads-guilty-to-federal-fentanyl-trafficking-and-kidnapping-charges/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>... A Jamestown man has admitted in federal court to **fentanyl** trafficking and kidnapping after authorities said...
 ...…]The post Jamestown Man Pleads Guilty to Federal **Fentanyl** Trafficking and Kidnapping Charges appeared first...
 ...pping after authorities said he sold the powerful **opioid** and held a victim against her will for several we...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Substance Use vs. Abuse: How to Identify the Difference</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>In today’s society, the use of substances such as alcohol and marijuana is often woven into the fabric of social interactions and celebrations. For many, these substances can enhance experiences and create memorable moments. However, there is a fine line between enjoying substances and crossing over into substance abuse and addiction. Recognizing where that line […]The post Substance Use vs. Abuse: How to Identify the Difference appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D13" s="2">
         <v>46092</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/11/substance-use-vs-abuse-how-to-identify-the-difference/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...ociety, the use of substances such as alcohol and **marijuana** is often woven into the fabric of social interact...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>A Jamestown man has pleaded guilty to drug trafficking and kidnapping in U.S. District Court. U.S. Attorney Michael DiGiacomo announced that 31-year old Dwayne Lowery, aka Chi Chi, pleaded guilty before U.S. District Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl and kidnapping. The charges carry a mandatory […]</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D14" s="2">
         <v>46092</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://www.wrfalp.com/?p=74583</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...ion with intent to distribute 40 grams or more of **fentanyl** and kidnapping. The charges carry a mandatory [&amp;#...
 A Jamestown man has pleaded guilty to **drug** trafficking and kidnapping in U.S. District Court...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_WRFALP.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D15" s="2">
         <v>46091</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://tinyurl.com/27j8l8c8</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D16" s="2">
         <v>46091</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/286rn2wh</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/29zlopsm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D17" s="2">
         <v>46091</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://tinyurl.com/28jrvqme</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D18" s="2">
         <v>46091</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://tinyurl.com/22ssbs2g</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jamestown Man Pleads Guilty to Drug, Kidnapping Charges - TAPinto</t>
         </is>
       </c>
-      <c r="D12" s="2">
+      <c r="D19" s="2">
         <v>46091</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://tinyurl.com/22pe6yfk</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>12 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
         </is>
       </c>
-      <c r="D13" s="2">
+      <c r="D20" s="2">
         <v>46091</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907458/wjtn-news-headlines-for-tues-mar-10-2026</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>...as a passenger... and, found that both were in possession of a quantity of **Methamphetamine**... Fentanyl... and, plastic knuckles.  Police also found that Light w...
 ...wrence Vilardo to possession with intent to distribute 40 grams or more of **fentanyl**... and, kidnapping.  Prosecutors say in December of 2022... a raid on...
@@ -721,37 +907,37 @@
 ...ns.  Hogg faces two counts of seventh-degree criminal possession of a **controlled** substance... and one of third-degree criminal possession of a weapon. &amp;nbs...</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>8 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
         </is>
       </c>
-      <c r="D14" s="2">
+      <c r="D21" s="2">
         <v>46090</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
 ...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
@@ -763,89 +949,34 @@
 ...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JPD Releases 2025 Annual Crime Report - Post Journal</t>
-        </is>
-      </c>
-      <c r="D15" s="2">
-        <v>46088</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2yy6zfdt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Chautauqua_Today</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
         </is>
       </c>
-      <c r="D16" s="2">
+      <c r="D22" s="2">
         <v>46087</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Mar. 5, 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>City man arrested following disorderly person incident, and hitting a JPD officer...A man from Jamestown has been arrested after allegedly hitting a responding police officer in the face during an incident on the city's northside.  Jamestown police were called to the scene shortly before 2 p.m. Wednesday for a report of a disorderly person.  Officers say 65 year-old Christopher Murray was allegedly obstructing traffic... and, when they tried to investigate... Murray allegedly began yelling and struck one of them.  After a brief struggle... he was taken into custody... and, held pending arraignment on charges of second-degree assault... and, resisting arrest.  The officer was treated for minor injuries.Two from Panama-area arrested during raid for stealing several items -- including an ATV...         Two people from Panama have been arrested following an investigation into a number of stolen items that were found in their house during a raid late last month.  Sheriff's officers say they executed a search warrant at 7453 Wiltise Rd. in the Town Clymer back on Feb. 27.  The Sheriff's Department SWAT Team made entry... and, they found 37 year-old James Murray... and, 33 year-old Emily Walker inside.  Deputies took both into custody... and, found the stolen items... which included a Polaris ATV.  Both Murray and Walker are charged with third-degree criminal possession of stolen property... and, were arraigned.  They were issued appearance tickets for Clymer Town Court at a later date.Assembly Republicans propose energy relief "LOWER" Plan...Republicans in the New York State Assembly have unveiled legislation they say will address growing concerns over the state's energy costs and grid reliability.  Minority Leader Ed Ra announced the "Lights On With Energy Relief (LOWER)" Plan during a press conference in Albany.  Ra says the proposal offers a "course correction" that will deliver help to households across the state that are being burdened by ever increasing costs... noting that electric rates are up about 47%.  Local Assemblyman Andrew Molitor says the legislative package contains $2-billion in relief for ratepayers.  Molitor... a Westfield Republican... says the plan would also pause the state's Climate Act mandates, such as restrictions on natural gas and electrification of school buses, until reliability and feasibility studies are conducted. County gets $250,000 State Grant to more efforts to develop more affordable and workforce housing...Chautauqua County has received a $250,000 dollar state grant to help advance efforts to create more affordable and workforce housing.  The county's Department of Planning and Development has announced it's been awarded the quarter of a million dollars throught the state's Homes and Community Renewal -- "Technical Assistance to Grow Pro-Housing Communities" -- program.  County Executive P.J. Wendel says the funding will advance the county's Housing Market Analysis and Development Strategy developed with the county's Partnership for Economic Growth.  Wendel says it's not a large amount... but, he says the department is often able to leverage those dollars 5 and 6-times over.  The Department says the funding will be used to "advance housing site readiness, zoning updates, and implementation of the County’s Housing Strategy to expand affordable and workforce housing opportunities."  Two projects -- one in Jamestown and the other in Dunkirk -- recently took major steps forward... and, Wendel says they want to continue that momentum to other communities as well.  The department reports the funding will help fully develop an inventory of potential housing sites... finding five sites to be selected to move from pre-development analysis to construction readiness... and, a developers forum.Dunkirk man charged with DWI after rollover accident Tuesday...A Dunkirk man suffered minor injuries and is facing charges following a rollover crash in the north county city late Tuesday afternoon. Dunkirk Police, along with Dunkirk Fire and Alstar Ambulance, were called to the area of Central Avenue and East Green Street at about 4:15 p.m., and, found a vehicle on its roof with one person trapped inside.  Fire and rescue personnel extricated 54-year-old Michael Lemanski and took him to a local hospital.  Officers determined that the vehicle struck a traffic control pole at the intersection and also damaged a private home before the vehicle rolled over.  After further investigation, Lemanski was charged with driving while intoxicated... fourth--degree criminal mischief, and several vehicle and traffic violations.  He was released with tickets.Jamestown man arrested after allegedly pushing woman down stairs during domestic dispute...A city man has been arrested for allegedly shoving a woman down a short flight of stairs during a domestic incident on Jamestown's northside.  City police were called to the unidentified location shortly before 8 a.m. Tuesday for a "physical domestic dispute."  On arrival... officers say they found that 51 year-old Doughshon Gholston had pushed the female victim down the stairs... causing minor injuries.  Police say Gholston initially resisted arrest... but, was taken into custody following a brief struggle.  He's charged with third-degree assault... and, resisting arrest.  He was held pending arraignment. </t>
-        </is>
-      </c>
-      <c r="D17" s="2">
-        <v>46087</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/906892/wjtn-news-headlines-for-thurs-mar-5-2026</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>... After further investigation, Lemanski was charged with driving while **intoxicated**... fourth--degree criminal mischief, and several vehicle and traffic viola...</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,7 +406,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
+          <t>Jamestown man pleads guilty to sex trafficking, drug conspiracy in Buffalo - Newport Dispatch</t>
         </is>
       </c>
       <c r="D2" s="2">
@@ -414,24 +414,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27xq83cr</t>
+          <t>https://tinyurl.com/25tdatxt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
+          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -439,10 +434,74 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/27xq83cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46094</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907978/wjtn-news-headlines-for-fri-mar-13-2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...m Jamestown has been arrested on federal charges for allegedly trafficking **methamphetamine**... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michae...
+...old Taylor Hernandez was arrested for possession with intent to distribute **methamphetamine**.  Prosecutors say that... according to the complaint... members of th...
+...me... and, seized about 181 grams of meth... about 23.5 grams of suspected **fentanyl**... drug paraphernalia, and more than $4,100 in cash.  If convicted......
+...s say that... according to the complaint... members of the Jamestown Metro **Drug** Task Force executed a search warrant at Hernandez’s Falconer Street ...
+...eized about 181 grams of meth... about 23.5 grams of suspected fentanyl... **drug** paraphernalia, and more than $4,100 in cash.  If convicted... DiGiaco...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46094</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907822/wjtn-news-headlines-for-thurs-mar-12-2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>..., seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of **methamphetamine**, scales and packaging used to traffic narcotics... a high-capacity magazin...
 ... into custody and a subsequent search of the vehicle located a quantity of **methamphetamine**.  She was taken to the city jail where she was held pending arraignme...
@@ -458,79 +517,39 @@
 ...Leandra's Law... unsafe backing... seventh-degree criminal possession of a **controlled** substance... and, two counts of endangering the welfare of a child.Gillibr...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46093</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2cofmq97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
+          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22dxk5ay</t>
+          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -542,7 +561,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
+          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -550,24 +569,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/266pwgl9</t>
+          <t>https://tinyurl.com/2cofmq97</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WRFA-LP 107.9 FM</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
+          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -575,32 +589,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.wrfalp.com/?p=74599</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>News_search_WRFALP.R</t>
+          <t>https://tinyurl.com/266pwgl9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
+          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
         </is>
       </c>
       <c r="D9" s="2">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27h57fu2</t>
+          <t>https://www.wrfalp.com/?p=74599</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_WRFALP.R</t>
         </is>
       </c>
     </row>
@@ -612,7 +631,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
+          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
         </is>
       </c>
       <c r="D10" s="2">
@@ -620,24 +639,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yyn26c6</t>
+          <t>https://tinyurl.com/27h57fu2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
+          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D11" s="2">
@@ -645,34 +659,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/2yyn26c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
+          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
         </is>
       </c>
       <c r="D12" s="2">
@@ -680,51 +684,51 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/03/11/jamestown-man-pleads-guilty-to-federal-fentanyl-trafficking-and-kidnapping-charges/</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>... A Jamestown man has admitted in federal court to **fentanyl** trafficking and kidnapping after authorities said...
 ...…]The post Jamestown Man Pleads Guilty to Federal **Fentanyl** Trafficking and Kidnapping Charges appeared first...
 ...pping after authorities said he sold the powerful **opioid** and held a victim against her will for several we...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Substance Use vs. Abuse: How to Identify the Difference</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>In today’s society, the use of substances such as alcohol and marijuana is often woven into the fabric of social interactions and celebrations. For many, these substances can enhance experiences and create memorable moments. However, there is a fine line between enjoying substances and crossing over into substance abuse and addiction. Recognizing where that line […]The post Substance Use vs. Abuse: How to Identify the Difference appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46092</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/11/substance-use-vs-abuse-how-to-identify-the-difference/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>...ociety, the use of substances such as alcohol and **marijuana** is often woven into the fabric of social interact...</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -734,17 +738,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WRFA-LP 107.9 FM</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping</t>
+          <t>Substance Use vs. Abuse: How to Identify the Difference</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A Jamestown man has pleaded guilty to drug trafficking and kidnapping in U.S. District Court. U.S. Attorney Michael DiGiacomo announced that 31-year old Dwayne Lowery, aka Chi Chi, pleaded guilty before U.S. District Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl and kidnapping. The charges carry a mandatory […]</t>
+          <t>In today’s society, the use of substances such as alcohol and marijuana is often woven into the fabric of social interactions and celebrations. For many, these substances can enhance experiences and create memorable moments. However, there is a fine line between enjoying substances and crossing over into substance abuse and addiction. Recognizing where that line […]The post Substance Use vs. Abuse: How to Identify the Difference appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D14" s="2">
@@ -752,38 +756,53 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/03/11/substance-use-vs-abuse-how-to-identify-the-difference/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>...ociety, the use of substances such as alcohol and **marijuana** is often woven into the fabric of social interact...</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WRFA-LP 107.9 FM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A Jamestown man has pleaded guilty to drug trafficking and kidnapping in U.S. District Court. U.S. Attorney Michael DiGiacomo announced that 31-year old Dwayne Lowery, aka Chi Chi, pleaded guilty before U.S. District Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl and kidnapping. The charges carry a mandatory […]</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>https://www.wrfalp.com/?p=74583</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...ion with intent to distribute 40 grams or more of **fentanyl** and kidnapping. The charges carry a mandatory [&amp;#...
 A Jamestown man has pleaded guilty to **drug** trafficking and kidnapping in U.S. District Court...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>News_search_WRFALP.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
-        </is>
-      </c>
-      <c r="D15" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/27j8l8c8</t>
         </is>
       </c>
     </row>
@@ -795,7 +814,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Drug , Kidnapping Charges - TAPinto</t>
+          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
         </is>
       </c>
       <c r="D16" s="2">
@@ -803,7 +822,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29zlopsm</t>
+          <t>https://tinyurl.com/27j8l8c8</t>
         </is>
       </c>
     </row>
@@ -815,7 +834,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
+          <t>Jamestown Man Pleads Guilty to Drug, Kidnapping Charges - TAPinto</t>
         </is>
       </c>
       <c r="D17" s="2">
@@ -823,7 +842,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28jrvqme</t>
+          <t>https://tinyurl.com/22pe6yfk</t>
         </is>
       </c>
     </row>
@@ -835,7 +854,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
+          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D18" s="2">
@@ -843,7 +862,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22ssbs2g</t>
+          <t>https://tinyurl.com/28jrvqme</t>
         </is>
       </c>
     </row>
@@ -855,7 +874,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Drug, Kidnapping Charges - TAPinto</t>
+          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
         </is>
       </c>
       <c r="D19" s="2">
@@ -863,7 +882,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22pe6yfk</t>
+          <t>https://tinyurl.com/22ssbs2g</t>
         </is>
       </c>
     </row>
@@ -955,31 +974,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Westfield Pair Charged with Drug Possession in BroctonTwo Westfield residents are facing misdemeanor drug possession charges after an investigation into a suspicious situation in the Village of Brocton. Chautauqua County Sheriff's deputies were alerted to the incident on East Main Street during the afte...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D22" s="2">
-        <v>46087</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367143</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown man pleads guilty to sex trafficking, drug conspiracy in Buffalo - Newport Dispatch</t>
+          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
         </is>
       </c>
       <c r="D2" s="2">
@@ -414,19 +414,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25tdatxt</t>
+          <t>https://tinyurl.com/27xq83cr</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -434,35 +439,10 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27xq83cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907978/wjtn-news-headlines-for-fri-mar-13-2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...m Jamestown has been arrested on federal charges for allegedly trafficking **methamphetamine**... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michae...
 ...old Taylor Hernandez was arrested for possession with intent to distribute **methamphetamine**.  Prosecutors say that... according to the complaint... members of th...
@@ -471,37 +451,37 @@
 ...eized about 181 grams of meth... about 23.5 grams of suspected fentanyl... **drug** paraphernalia, and more than $4,100 in cash.  If convicted... DiGiaco...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>12 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D4" s="2">
         <v>46094</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907822/wjtn-news-headlines-for-thurs-mar-12-2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>..., seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of **methamphetamine**, scales and packaging used to traffic narcotics... a high-capacity magazin...
 ... into custody and a subsequent search of the vehicle located a quantity of **methamphetamine**.  She was taken to the city jail where she was held pending arraignme...
@@ -517,39 +497,59 @@
 ...Leandra's Law... unsafe backing... seventh-degree criminal possession of a **controlled** substance... and, two counts of endangering the welfare of a child.Gillibr...</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46094</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
+          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/2cofmq97</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
+          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -569,7 +569,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2cofmq97</t>
+          <t>https://tinyurl.com/22dxk5ay</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,7 +406,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
+          <t>Jamestown man pleads guilty to sex trafficking, drug conspiracy in Buffalo - Newport Dispatch</t>
         </is>
       </c>
       <c r="D2" s="2">
@@ -414,24 +414,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27xq83cr</t>
+          <t>https://tinyurl.com/25tdatxt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
+          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -439,10 +434,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/27xq83cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46094</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907978/wjtn-news-headlines-for-fri-mar-13-2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...m Jamestown has been arrested on federal charges for allegedly trafficking **methamphetamine**... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michae...
 ...old Taylor Hernandez was arrested for possession with intent to distribute **methamphetamine**.  Prosecutors say that... according to the complaint... members of th...
@@ -451,37 +471,37 @@
 ...eized about 181 grams of meth... about 23.5 grams of suspected fentanyl... **drug** paraphernalia, and more than $4,100 in cash.  If convicted... DiGiaco...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>12 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D5" s="2">
         <v>46094</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907822/wjtn-news-headlines-for-thurs-mar-12-2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>..., seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of **methamphetamine**, scales and packaging used to traffic narcotics... a high-capacity magazin...
 ... into custody and a subsequent search of the vehicle located a quantity of **methamphetamine**.  She was taken to the city jail where she was held pending arraignme...
@@ -497,59 +517,39 @@
 ...Leandra's Law... unsafe backing... seventh-degree criminal possession of a **controlled** substance... and, two counts of endangering the welfare of a child.Gillibr...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
+          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2cofmq97</t>
+          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
+          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -569,7 +569,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22dxk5ay</t>
+          <t>https://tinyurl.com/2cofmq97</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
+          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -589,24 +589,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/266pwgl9</t>
+          <t>https://tinyurl.com/22dxk5ay</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WRFA-LP 107.9 FM</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
+          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
         </is>
       </c>
       <c r="D9" s="2">
@@ -614,32 +609,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.wrfalp.com/?p=74599</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WRFALP.R</t>
+          <t>https://tinyurl.com/266pwgl9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
+          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
         </is>
       </c>
       <c r="D10" s="2">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27h57fu2</t>
+          <t>https://www.wrfalp.com/?p=74599</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>News_search_WRFALP.R</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
+          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
         </is>
       </c>
       <c r="D11" s="2">
@@ -659,24 +659,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yyn26c6</t>
+          <t>https://tinyurl.com/27h57fu2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
+          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D12" s="2">
@@ -684,34 +679,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/2yyn26c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
+          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
         </is>
       </c>
       <c r="D13" s="2">
@@ -719,51 +704,51 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <v>46092</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/03/11/jamestown-man-pleads-guilty-to-federal-fentanyl-trafficking-and-kidnapping-charges/</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>... A Jamestown man has admitted in federal court to **fentanyl** trafficking and kidnapping after authorities said...
 ...…]The post Jamestown Man Pleads Guilty to Federal **Fentanyl** Trafficking and Kidnapping Charges appeared first...
 ...pping after authorities said he sold the powerful **opioid** and held a victim against her will for several we...</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Substance Use vs. Abuse: How to Identify the Difference</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>In today’s society, the use of substances such as alcohol and marijuana is often woven into the fabric of social interactions and celebrations. For many, these substances can enhance experiences and create memorable moments. However, there is a fine line between enjoying substances and crossing over into substance abuse and addiction. Recognizing where that line […]The post Substance Use vs. Abuse: How to Identify the Difference appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46092</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/11/substance-use-vs-abuse-how-to-identify-the-difference/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>...ociety, the use of substances such as alcohol and **marijuana** is often woven into the fabric of social interact...</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -814,7 +799,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jamestown man admits kidnapping and drug charges: 'Looking for fast money' - Buffalo News</t>
+          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D16" s="2">
@@ -822,19 +807,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27j8l8c8</t>
+          <t>https://tinyurl.com/28jrvqme</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty to Drug, Kidnapping Charges - TAPinto</t>
+          <t>12 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
         </is>
       </c>
       <c r="D17" s="2">
@@ -842,75 +832,10 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22pe6yfk</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
-        </is>
-      </c>
-      <c r="D18" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/28jrvqme</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Jamestown man pleads guilty to kidnapping, drug charge - wivb.com</t>
-        </is>
-      </c>
-      <c r="D19" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/22ssbs2g</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>12 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
-        </is>
-      </c>
-      <c r="D20" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907458/wjtn-news-headlines-for-tues-mar-10-2026</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...as a passenger... and, found that both were in possession of a quantity of **Methamphetamine**... Fentanyl... and, plastic knuckles.  Police also found that Light w...
 ...wrence Vilardo to possession with intent to distribute 40 grams or more of **fentanyl**... and, kidnapping.  Prosecutors say in December of 2022... a raid on...
@@ -926,49 +851,7 @@
 ...ns.  Hogg faces two counts of seventh-degree criminal possession of a **controlled** substance... and one of third-degree criminal possession of a weapon. &amp;nbs...</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Mon., Mar. 9, 2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>8 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Westfield man arrested after alleged shooting, car chase with police...A man from Westfield is accused of shooting a woman during an altercation at a home in the village... and, leading police on a vehicle and foot pursuit into the town of Pomfret.  Fredonia Police say the shooting occurred shortly before 7:30 last Saturday night... with the suspect then fleeing the scene.  Westfield Police say the suspect... identified as 52 year-old Jahmaul Johnson... shot and wounded the woman during an altercation at the home.  Police say the pursuit went through the village of Fredonia, and about 20 minutes after the shooting, the vehicle crashed on Van Buren Road just outside the village.  Johnson then ran off on foot, and officers from multiple agencies began searching for him.  He was later found and taken into custody by Chautauqua County Sheriff's officers.  Westfield police say the shooting victim is in stable condition.  A "shelter in place" advisory was issued for residents in the area of Van Buren... Chestnut... and, Farel Roads... and, Johnson Street while police searched for the suspect.  He was found about 9:15 p.m.High speed pursuit in Jamestown leads to arrest of city man...A city man faces several charges following a high-speed pursuit that began in downtown Jamestown... and, ended on the city's southside.  Jamestown police say a patrol saw a vehicle leaving a business at a high-rate of speed after officers had been called for a disorderly person just after 12:30 a.m. Sunday.  Police caught up to the vehicle and tried to make a traffic stop.  However... the operator... later found to be 35 year-old Tyler Anderson... didn't comply, and led officers on the pursuit.  During the chase... police say Anderson failed to stop at a posted stop sign... and, nearly struck another vehicle while speeding.  The car ultimately came to a stop on the southside... and, officers took him into custody without further incident.  Anderson was charged with first-degree reckless endangerment... driving while intoxicated... and, fleeing a police officer in the a motor vehicle.  At the city jail... they say Anderson intentionally flooded his cell by tampering with the plumbing.  He was additionally charged with third-degree criminal tampering... and, held pending arraignment.Man arrested for spraying graffitti on Lakewood village, and Busti town properities arrested again...A man from Lakewood accused of spray painting graffitti on village and town of Busti property last year... was arrested again after trying to flee his home late last week.  Lakewood-Busti Police say they executed an arrest warrant at the home of 47 year-old Jeffrey Hamilton this past Thursday night.  Police say he was found quickly... and, taken into custody on charges of Felony third-degree criminal mischief... and, making graffiti.  He was arraigned in Busti Town Court, and released pending a future court appearance.  Hamilton was intially arrested last May on multiple charges of making graffiti and criminal tampering after police investigated a complaint of multiple cars being spray painted for two days in late April.  He had been arrested prior to that on a different matter... and, soon after being released... he spray painted a Lakewood-Busti police car... and, several other vehicles.  He also allegedly spray painted other village and town property.Borrello says Senate and Assembly to begin work on their "one-house budget" bills this week, but, still expects a late spending plan...Negotiations towards a final budget for New York State's upcoming fiscal year begin this week... when the Senate and Assembly present their "one-house" budgets.  This following recent hearings in Albany over Governor Kathy Hochul's proposed $260 billion spending plan.  Local state senator George Borrello has long been critical of past state budgets containing controversial policy items... such as Wetland regulations, and Bail Reform.  He says they're often "hidden" in the spending plan... and, adds it "has to end."  Borrello says he believes one of the major sticking points in negotiations will be over provisions of the controversial Climate Act.  The Sunset Bay Republican says his Democratic colleagues are "digging their heels in" on that policy, despite pushback from Hochul.  Borrello says he's heard that some 27 Democratic Senators have wrote Hochul urging her not to make any changes to the policy.  A final budget is due on Apr. 1... but, Borrello says he's skeptical that this year's spending plan will be on time.Another associate of drug kingpin Joseph Zaso indicted on federal drug charges...A man and woman from Jamestown have been indicted on federal drug charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced that a grand jury has returned the indictment charging 39 year-old James Jackson... and, 37 year-old Alicia Osar... with narcotics conspiracy, which carries a mandatory minimum penalty of 10 years in prison and a maximum of life in prison.  In addition, Jackson is charged with maintaining a drug-involved premises.  Prosecutors say that... between 2018... and, February of last year... Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell fentanyl.  In addition... between 2019, and 2021, Jackson is accused of using a Bush Street home in Jamestown to make and sell heroin, crack cocaine, cocaine and methamphetamine.  Jackson is being detained... while Osar is released on conditions.  Both Brown and Zaso were previously convicted and are awaiting sentencing.</t>
-        </is>
-      </c>
-      <c r="D21" s="2">
-        <v>46090</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907226/wjtn-news-headlines-for-mon-mar-9-2026</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>...reet home in Jamestown to make and sell heroin, crack cocaine, cocaine and **methamphetamine**.  Jackson is being detained... while Osar is released on conditions. ...
-...Jackson and Osar conspired with Zaso... Ernest Brown... and others to sell **fentanyl**.  In addition... between 2019, and 2021, Jackson is accused of using ...
-...ptical that this year's spending plan will be on time.Another associate of **drug** kingpin Joseph Zaso indicted on federal drug charges...A man and woman fro...
-... on time.Another associate of drug kingpin Joseph Zaso indicted on federal **drug** charges...A man and woman from Jamestown have been indicted on federal dru...
-...rug charges...A man and woman from Jamestown have been indicted on federal **drug** charges tied to a conspiracy involving local drug "kingpin" Joseph Zaso. &amp;...
-...been indicted on federal drug charges tied to a conspiracy involving local **drug** "kingpin" Joseph Zaso.  U.S. Attorney Michael DiGiacomo has announced...
-...f life in prison.  In addition, Jackson is charged with maintaining a **drug**-involved premises.  Prosecutors say that... between 2018... and, Febr...
-...erson was charged with first-degree reckless endangerment... driving while **intoxicated**... and, fleeing a police officer in the a motor vehicle.  At the city...</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,57 +401,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for St. Patrick's Day, Tues., Mar. 17, 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown man pleads guilty to sex trafficking, drug conspiracy in Buffalo - Newport Dispatch</t>
+          <t>11 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jamestown-area receives between 4 and 8 inches of snow in St. Patrick's Eve and Day snowstorm...Some parts of Chautauqua County received several inches of snow during the storm that accompanied a cold front last night through this morning.  The National Weather Service in Buffalo reports 8-and-a-half inches of the white stuff in Cassadaga... and about 6 in the Mayville area.  Here in the Jamestown-area... we got about 4 inches.  That's right about where Forecaster Steve Welch with the National Weather Service in Buffalo said we would be late Monday... with 2 to 4 inches generally in the Western New York area.  He says there may be a couple more inches falling during the day today.  We remain under a Winter Weather Advisory until 8 o'clock tonight.  Jamestown street closed about five-hours Sunday night after high winds blow roof off vacant building downtown...The Jamestown Department of Development was able to safely get the roof off a vacant building on East Second Street late Sunday night.  Officials say the roof was partially torn off shortly after 5 p.m. during the wind storm.  City police closed off East Second from Prendergast to Foote Avenues.  A front-loader was brought in to remove the roof... and, the street reopened shortly before 10:30 p.m. Three arrested during Forest Park drug bust in Jamestown late Monday morning...        Three people from Jamestown have been arrested following a drug raid on a home on the city's southside late Monday morning.  Sheriff's officers say their Narcotics Investigators along with those from Jamestown... executed a search warrant at 7 Forest Park about 10:45 a.m., and, found 39 year-old Ronaldo Galarza... 19 year-old Ronaldo Galarza, Jr. and 39 year-old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of fentanyl... and, packaging used for the sale and distribution of narcotics.  All three suspects were charged with third and fourth-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  Each suspect was issued appearance tickets for city court... and, the investigation is ongoing with additional arrests expected.  If you have any information about suspicious or narcotics related activity in your area... call the Sheriff's Office Narcotics Investigators Tip line at either 1-800-344-8702 or 664-2420... or the JPD Tip line at 483-8477.JPS begins budget process by reviewing first draft of $120.8-million spending plan...There's no tax increase in the Jamestown Public School's proposed 2026-27 budget proposal... which totals about $120.8-million.  The school board recently got it's first look at the first draft of the spending plan... which Assistant Superintendent for Finance and Operations Brittany Spry says increases spending by about $5.2-million... which is a 4.5% increase.  Spry says the biggest increases come in programming with some new positions to be filled.  She says they include a new assistant principal and secretary for the district's Innovation Center at the former Rodgers School... and six middle school teachers.  Much of the money to cover the increased costs is coming from an increase in state school aid.  Once final state aid figures are known... the district will move to finalize a spending plan for voters to act on in May.  Thomas pleads guilty in Mendoza drug and sex trafficking case...A Jamestown man has pleaded guilty in federal court to drug and sex trafficking conspiracy charges in connection with a case against a local drug kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-old Kelvin Thomas entered the plea last Friday before U.S. District Court Judge John Sinatra, Jr. to conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl, and conspiracy to commit sex trafficking.  Prosecutors say between October and December 2022, Thomas conspired with Zaid Mendoza and Cora Waddington to conduct a sex trafficking operation involving two individuals with drug addictions.  As part of the conspiracy... they say Thomas, Mendoza, and Waddington, provided shelter to the victims at a West Main Street home in Falconer... and, provided them with food, clothing, and daily quantities of heroin/fentanyl in exchange for them doing commercial sex acts for money, with the proceeds going to Mendoza.  Thomas assisted the operation by securing and communicating with commercial sex buyers, posting online advertisements with photographs of the two victims on Skipthegames.com.  He also transported the two victims to calls away from the residence, and provided protection and assistance to sex trafficking victims while they were on those "out" calls.  Thomas was paid in drugs by Mendoza or Waddington.  The charges carry a mandatory minimum penalty of five years and a maximum of life.City woman arrested for allegedly shoplifting more than $1,000 worth of items from Lakewood Wal-Mart SuperCenter...A woman from Jamestown has been arrested for allegedly stealing more than $1,000 worth of merchandise last weekend from the Lakewood Wal-Mart SuperCenter.  Lakewood-Busti Police say they were called to the 350 Fairmount Ave. location shortly after 7 p.m. last Sunday night.  Officerss say 47 year-old Kathryn Fisher allegedly passed all points of sale with $1,071 worth of items without paying for them.  Fisher was arrested for fourth-degree grand larceny... and, was released with an appearance ticket for Busti Town Court.  </t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25tdatxt</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908342/wjtn-news-headlines-for-st-patrick-s-day-tues-mar-17-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of **fentanyl**... and, packaging used for the sale and distribution of narcotics.  A...
+... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl**, and conspiracy to commit sex trafficking.  Prosecutors say between O...
+...... and, provided them with food, clothing, and daily quantities of heroin/**fentanyl** in exchange for them doing commercial sex acts for money, with the proceed...
+... reopened shortly before 10:30 p.m. Three arrested during Forest Park **drug** bust in Jamestown late Monday morning...        T...
+...sp;   Three people from Jamestown have been arrested following a **drug** raid on a home on the city's southside late Monday morning.  Sheriff'...
+...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia.  Each suspect was issued appearance tickets for city c...
+...ng plan for voters to act on in May.  Thomas pleads guilty in Mendoza **drug** and sex trafficking case...A Jamestown man has pleaded guilty in federal c...
+... trafficking case...A Jamestown man has pleaded guilty in federal court to **drug** and sex trafficking conspiracy charges in connection with a case against a...
+...x trafficking conspiracy charges in connection with a case against a local **drug** kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-...
+...gton to conduct a sex trafficking operation involving two individuals with **drug** addictions.  As part of the conspiracy... they say Thomas, Mendoza, a...
+...uspects were charged with third and fourth-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
+          <t>Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — Three Jamestown residents are facing felony drug charges after authorities executed a search warrant and seized fentanyl at a Forest Park residence. Investigators with the Jamestown Police Department and the Chautauqua County Sheriff’s Office executed a search warrant at 7 Forest Park at approximately 10:45 a.m. on March […]The post Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27xq83cr</t>
+          <t>https://wnynewsnow.com/2026/03/17/three-charged-after-jamestown-search-warrant-nets-fentanyl-seizure/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>... authorities executed a search warrant and seized **fentanyl** at a Forest Park residence. Investigators with th...
+...Three Charged After Jamestown Search Warrant Nets **Fentanyl** Seizure appeared first on WNY News Now.
+....Y. — Three Jamestown residents are facing felony **drug** charges after authorities executed a search warra...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
+          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -459,10 +496,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/27xq83cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46094</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907978/wjtn-news-headlines-for-fri-mar-13-2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...m Jamestown has been arrested on federal charges for allegedly trafficking **methamphetamine**... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michae...
 ...old Taylor Hernandez was arrested for possession with intent to distribute **methamphetamine**.  Prosecutors say that... according to the complaint... members of th...
@@ -471,37 +533,37 @@
 ...eized about 181 grams of meth... about 23.5 grams of suspected fentanyl... **drug** paraphernalia, and more than $4,100 in cash.  If convicted... DiGiaco...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>12 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="2">
         <v>46094</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907822/wjtn-news-headlines-for-thurs-mar-12-2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>..., seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of **methamphetamine**, scales and packaging used to traffic narcotics... a high-capacity magazin...
 ... into custody and a subsequent search of the vehicle located a quantity of **methamphetamine**.  She was taken to the city jail where she was held pending arraignme...
@@ -517,59 +579,39 @@
 ...Leandra's Law... unsafe backing... seventh-degree criminal possession of a **controlled** substance... and, two counts of endangering the welfare of a child.Gillibr...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jamestown, NY – Drug Bust: Man Arrested After Fentanyl, Crack Seizure on Lincoln St - Country Herald</t>
+          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D7" s="2">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2cofmq97</t>
+          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -651,7 +693,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chautauqua County man admits to sex-trafficking and narcotics conspiracies - Buffalo News</t>
+          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D11" s="2">
@@ -659,19 +701,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27h57fu2</t>
+          <t>https://tinyurl.com/2yyn26c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
         </is>
       </c>
       <c r="D12" s="2">
@@ -679,24 +726,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yyn26c6</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
+          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D13" s="2">
@@ -704,156 +761,55 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
+          <t>https://wnynewsnow.com/2026/03/11/jamestown-man-pleads-guilty-to-federal-fentanyl-trafficking-and-kidnapping-charges/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46092</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/11/jamestown-man-pleads-guilty-to-federal-fentanyl-trafficking-and-kidnapping-charges/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>... A Jamestown man has admitted in federal court to **fentanyl** trafficking and kidnapping after authorities said...
 ...…]The post Jamestown Man Pleads Guilty to Federal **Fentanyl** Trafficking and Kidnapping Charges appeared first...
 ...pping after authorities said he sold the powerful **opioid** and held a victim against her will for several we...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>A Jamestown man has pleaded guilty to drug trafficking and kidnapping in U.S. District Court. U.S. Attorney Michael DiGiacomo announced that 31-year old Dwayne Lowery, aka Chi Chi, pleaded guilty before U.S. District Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl and kidnapping. The charges carry a mandatory […]</t>
         </is>
       </c>
-      <c r="D15" s="2">
+      <c r="D14" s="2">
         <v>46092</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://www.wrfalp.com/?p=74583</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...ion with intent to distribute 40 grams or more of **fentanyl** and kidnapping. The charges carry a mandatory [&amp;#...
 A Jamestown man has pleaded guilty to **drug** trafficking and kidnapping in U.S. District Court...</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_WRFALP.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Crime Is Down 2.35% In Jamestown For 2025 - WRFA-LP 107.9 FM</t>
-        </is>
-      </c>
-      <c r="D16" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/28jrvqme</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Tues., Mar. 10, 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>City man pleads guilty to federal drug and kidnapping charges...A man from Jamestown has pleaded guility to federal drug and kidnapping charges in connecton with incidents in late 2022... and, late 2023.  U.S. Attorney Michael DiGiacomo has announced thhat 31 year-old Dwayne -- "Chi Chi" -- Lowery entered the plea before U.S. District Court Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl... and, kidnapping.  Prosecutors say in December of 2022... a raid on Lowery's West Cowden Place home led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, drug paraphernalia.  Prior to that... investigators made two undercover purchases from Lowery,.  In mid-October of 2023... Lowery invited a woman to a North Union Street home in Olean... and, for the next 22 days... the victim was held by Lowery at various locations, including homes he was associated with in Buffalo and Olean... and, a Buffalo hotel.  Prosecutors say when the victim tried to flee... Lowery prevented her from doing so.  In November of 2023... the victim escaped Lowery’s Buffalo home, and reported the matter to police.  DiGiacomo says the conviction carries a mandatory minimum of five years in prison... a maximum of life, and a $5-million fine.  Lowery is to be sentenced on July 20.Second suspect arrested in connection with July 2025 shooting in Jamestown...     A second suspect accused of being involved in a shooting incident on Jamestown's eastside last July has been arrested on an attempted murder charge.  City police say they have now arrested 24 year-old Ian Sanchez in connection with the incident that occured on July 24 of last year in the area of East Second and Cheney Streets.  Officers found an unidentified man who suffered several gunshot wounds, and was seriously injured.  Police say the primary suspect... 23 year-old Xavier Ramos of Jamestown... was arrested the day following the incident for first-degree assault and criminal possession of a weapon.  Ramos remains jailed.  Police took Sanchez into custody late last Friday after being indicted by the Chautauqua County Grand Jury on one count each of attempted murder... and, first-degree assault.  Sanchez was arraigned Monday morning... and, taken to the county jail on $100,000 cash bail. Wendel looking forward to new initiatives from Jefferson Project in 2026...A couple of new strategies are to be implemented to help deal with Harmful Algae Blooms on Chautauqua Lake this year.  However... there remain no easy answers to the long-standing issue.  That from Chautauqua County Executive P.J. Wendel on the recent update from a member of the Jefferson Project to the county legislature.  Wendel says he looks forward to see what those strategies are... which will focus mainly on the Harmful Algal Blooms, and what causes them.  The Jefferson Project is into it's fifth-year of studying the role of excessive nutrients from run-off into the lake... and, how they help form the blooms.  Their focus has been using advance sensors, lake surveys, and modeling to identify drivers of HABs.  Wendel says critics say the findings are "jaded" because Chautauqua Institution has been the main funder of the project... but, he begs to differ.  He made his comments for last weekend's "Community Spotlight" program on the six Media One Radio Group stations.City man and woman arrested on drug and weapons charges after being found passed out in car...Two people from Jamestown face multiple drug and weapons possession charges after they were found passed out in a car last week at an eastside intersection.  City police were called to check on the well-being of the pair on Monday, Mar. 1 at 5 p.m.  Officers say they found the driver, Christopher Light, and Aimee Hogg who was a passenger... and, found that both were in possession of a quantity of Methamphetamine... Fentanyl... and, plastic knuckles.  Police also found that Light was driving while under the influence of drugs.  Light is charged with two counts each of seventh-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia... and one count of third-degree criminal possession of a weapon... driving while ability impaired... and, several traffic infractions.  Hogg faces two counts of seventh-degree criminal possession of a controlled substance... and one of third-degree criminal possession of a weapon.  Both were taken to the city jail pending arraignment.Jamestown man arrested for throwing bananas at business worker Monday...A man from Jamestown has been arrested for allegedly throwing several bananas at an employee of an eastside business that had previously banned him from the store.  City police were called to the location about 7 a.m. Monday on a report of a man throwing items at the worker.  Once they arrived... officers determined that 41-year-old Kenneth Walker had become upset and threw the bananas at the employee... damaging store property.  Police were able to locate Walker a short distance away... but, he refused verbal commands from officers.  Following a brief struggle, Walker was arrested for second-degree harassment... third-degree burglary... fourth-degree criminal mischief... and, resisting arrest.  He was take to the city jail pending arraignment.City man arrested following domestic incident...A man from Jamestown has been arrested following a domestic incident in which he allegedly punched a television set... breaking it... on the city's eastside.  Jamestown police say they were called to the scene shortly after 10 PM last Friday... and, spoke with the victim.  The victim said they were arguing with 32 year-old Angel Torres when he punched the TV... breaking it where it no longer worked.  Officers say Torres fled the scene... but, was later found a short distance away.  He was arrested for third-degree criminal mischief... and, jailed pending arraignment.      </t>
-        </is>
-      </c>
-      <c r="D17" s="2">
-        <v>46091</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907458/wjtn-news-headlines-for-tues-mar-10-2026</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>...as a passenger... and, found that both were in possession of a quantity of **Methamphetamine**... Fentanyl... and, plastic knuckles.  Police also found that Light w...
-...wrence Vilardo to possession with intent to distribute 40 grams or more of **fentanyl**... and, kidnapping.  Prosecutors say in December of 2022... a raid on...
-...aid on Lowery's West Cowden Place home led to seizure of about 59 grams of **Fentanyl**... $1,140 in cash... and, drug paraphernalia.  Prior to that... inves...
-...nd, found that both were in possession of a quantity of Methamphetamine... **Fentanyl**... and, plastic knuckles.  Police also found that Light was driving w...
-City man pleads guilty to federal **drug** and kidnapping charges...A man from Jamestown has pleaded guility to feder...
-...d kidnapping charges...A man from Jamestown has pleaded guility to federal **drug** and kidnapping charges in connecton with incidents in late 2022... and, la...
-...ome led to seizure of about 59 grams of Fentanyl... $1,140 in cash... and, **drug** paraphernalia.  Prior to that... investigators made two undercover pu...
-...m on the six Media One Radio Group stations.City man and woman arrested on **drug** and weapons charges after being found passed out in car...Two people from ...
-...er being found passed out in car...Two people from Jamestown face multiple **drug** and weapons possession charges after they were found passed out in a car l...
-...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia... and one count of third-degree criminal possession of a we...
-...is charged with two counts each of seventh-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia... and...
-...ns.  Hogg faces two counts of seventh-degree criminal possession of a **controlled** substance... and one of third-degree criminal possession of a weapon. &amp;nbs...</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,28 +401,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>WJTN News Headlines for Wed., Mar. 18, 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Quattrone says Sheriff's Dive Team finds Emerson's truck in Chautauqua Lake between Bemus and Greenhurst...The pick-up truck associated with a missing Lakewood man has been found submerged in Chautauqua Lake near the town of Ellery.  However... weather conditions have prevented Sheriff's Department Dive Team members from locating 64 year-old Daniel "Scott" Emerson.  Emerson was last seen on Mar. 3... but, Sheriff Jim Quattrone says his department received some tips and video from a location between Greenhurst and Bemus Point.  Quattrone says they received the video Monday morning... and, quickly got the Sheriff's marine boat and sonar out to that area and found the vehicle.  However... that was the day the temperature plummeted during the afternoon... and, divers has issues with air tanks freezing once they got out of the water.  With the weather still below freezing... Quattrone says the dive team will head back out Thursday.  He says they were able to find the top of the truck... which was at least partially submerged in mud and other debris.  Late last week... Lakewood-Busti Police urged residents and businesses located along the Chautauqua Lake shoreline for any help regarding Emerson's whereabouts.  Police say he was believed to be driving his maroon-colored F-150 that was last seen on Fairmount and Lakeview Avenues in the village around 12:30 a.m. the day he went missing.  If you have any information... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and drug-possession charges...A man from Jamestown has been arrested on multiple drug possession charges following a raid on a southside home early Tuesday afternoon.  Sheriff's officers say their narcotics investigators... along with those from Jamestown police... executed a search warrant on the upper apartment at 313 Prather Ave. shortly after Noon.  The suspect... 26 year-old Devonte Green -- who had a State Parole warrant for his arrest -- was seen leaving the residence in a vehicle just prior to the raid.  Jamestown police tried to conduct a vehicle stop... but, Green continued for a short distance in the car before he was arrested following a brief foot chase.  Deputies say their search of the home, Green and his vehicle led to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  Green was held pending arraignment on charges including: third-and-seventh-degree criminal possession of a controlled substance... and, resisting arrest.Schmidt announces indictment against Westfield man who allegedly shot village woman, in front of children...A Westfield man who allegedly shot a woman... then led police on a vehicle pursuit earlier this month, faces several charges related to both incidents.  Chautauqua County District Attorney Jason Schmidt says a grand jury has indicted 52-year-old Jahmaul Johnson on eight counts, including second-degree attempted murder.  Schmidt says that top charge stems from a shooting that occurred on Route 20 in the village during the evening of Mar. 7... he says Judge Stephen Cass presided over the matter, and a "not guilty" plea was entered for the defendant.  After the shooting... Johnson fled the scene, leading to a pursuit that ended when he crashed his getaway vehicle into a ditch.  He was taken into custody in the Town of Pomfret a short time later that evening.  Schmidt says Johnson also faces three violent felonies related to a handgun and magazine he allegedly possessed... along with four counts of endangering the welfare of a child.  Schmidt says Johnson pleaded not guilty at his arraignment Tuesday morning before being remanded to the Chautauqua County Jail on $1-million cash bail... $2-million property bond.  He says a disovery conference will be held on Apr. 13.  If convicted, Johnson faces up to 25 years in prison on the attempted murder charge and up to 15 years on the weapon counts, adding that there's a possibility of those sentences running consecutively.  The victim was taken to an Erie, Pa. hospital, and is recovering from her injuries.Site work beginning for new Brook's Hospital in Fredonia...Initial site work for the new Northern Chautauqua Hospital project in Fredonia gets underway this week.  The announcement late Monday by Kaleida Health comes in the wake of its January filing in conjunction with Brooks-TLC of a building permit with the village of Fredonia for the hospital's construction.  Turner Construction Company subcontracted with Fredonia-based S. St. George General Contracting to perform the preliminary site work, including setting up temporary staging areas, fencing the property, and grading the site.  Initial work will depend on the weather... and the need for the land to drain and dry out.  The $223.8 million project is planned as a one-story, 133,000 facility at 412 East Main St.  It will replace the existing Brooks Hospital in the city of Dunkirk.Molitor part of Assembly-Senate Budget Conference Committee to deal with Human Services...The deadline for a new state budget is fast approaching... and, work is continuing in the New York State Assembly and Senate on a final spending plan.  With that... more legislative hearings involving conference committees are underway.  Local State Assemblyman Andrew Molitor is an alternate for the committee on Human Services... which means he'll be able to ask questions and offer input about Medicaid and other "safety net" programs.  The Assembly's $272-billion, "one-house" budget includes a 1% income tax cut for low and middle income earners... but, Molitor says it's not enough.  Ideally, he says he would like to see all income taxes eliminated.  Molitor says he remains hopeful there will be a budget acted on by the Apr. 1 deadline. </t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908600/wjtn-news-headlines-for-wed-mar-18-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...arch of the home, Green and his vehicle led to the seizure of 2.3 grams of **fentanyl**... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  G...
+...ed to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin **mushrooms**... along with $131 cash.  Green was held pending arraignment on charg...
+..... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and **drug**-possession charges...A man from Jamestown has been arrested on multiple dr...
+...ug-possession charges...A man from Jamestown has been arrested on multiple **drug** possession charges following a raid on a southside home early Tuesday afte...
+...nt on charges including: third-and-seventh-degree criminal possession of a **controlled** substance... and, resisting arrest.Schmidt announces indictment against We...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46099</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/28g35pus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for St. Patrick's Day, Tues., Mar. 17, 2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>11 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Jamestown-area receives between 4 and 8 inches of snow in St. Patrick's Eve and Day snowstorm...Some parts of Chautauqua County received several inches of snow during the storm that accompanied a cold front last night through this morning.  The National Weather Service in Buffalo reports 8-and-a-half inches of the white stuff in Cassadaga... and about 6 in the Mayville area.  Here in the Jamestown-area... we got about 4 inches.  That's right about where Forecaster Steve Welch with the National Weather Service in Buffalo said we would be late Monday... with 2 to 4 inches generally in the Western New York area.  He says there may be a couple more inches falling during the day today.  We remain under a Winter Weather Advisory until 8 o'clock tonight.  Jamestown street closed about five-hours Sunday night after high winds blow roof off vacant building downtown...The Jamestown Department of Development was able to safely get the roof off a vacant building on East Second Street late Sunday night.  Officials say the roof was partially torn off shortly after 5 p.m. during the wind storm.  City police closed off East Second from Prendergast to Foote Avenues.  A front-loader was brought in to remove the roof... and, the street reopened shortly before 10:30 p.m. Three arrested during Forest Park drug bust in Jamestown late Monday morning...        Three people from Jamestown have been arrested following a drug raid on a home on the city's southside late Monday morning.  Sheriff's officers say their Narcotics Investigators along with those from Jamestown... executed a search warrant at 7 Forest Park about 10:45 a.m., and, found 39 year-old Ronaldo Galarza... 19 year-old Ronaldo Galarza, Jr. and 39 year-old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of fentanyl... and, packaging used for the sale and distribution of narcotics.  All three suspects were charged with third and fourth-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  Each suspect was issued appearance tickets for city court... and, the investigation is ongoing with additional arrests expected.  If you have any information about suspicious or narcotics related activity in your area... call the Sheriff's Office Narcotics Investigators Tip line at either 1-800-344-8702 or 664-2420... or the JPD Tip line at 483-8477.JPS begins budget process by reviewing first draft of $120.8-million spending plan...There's no tax increase in the Jamestown Public School's proposed 2026-27 budget proposal... which totals about $120.8-million.  The school board recently got it's first look at the first draft of the spending plan... which Assistant Superintendent for Finance and Operations Brittany Spry says increases spending by about $5.2-million... which is a 4.5% increase.  Spry says the biggest increases come in programming with some new positions to be filled.  She says they include a new assistant principal and secretary for the district's Innovation Center at the former Rodgers School... and six middle school teachers.  Much of the money to cover the increased costs is coming from an increase in state school aid.  Once final state aid figures are known... the district will move to finalize a spending plan for voters to act on in May.  Thomas pleads guilty in Mendoza drug and sex trafficking case...A Jamestown man has pleaded guilty in federal court to drug and sex trafficking conspiracy charges in connection with a case against a local drug kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-old Kelvin Thomas entered the plea last Friday before U.S. District Court Judge John Sinatra, Jr. to conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl, and conspiracy to commit sex trafficking.  Prosecutors say between October and December 2022, Thomas conspired with Zaid Mendoza and Cora Waddington to conduct a sex trafficking operation involving two individuals with drug addictions.  As part of the conspiracy... they say Thomas, Mendoza, and Waddington, provided shelter to the victims at a West Main Street home in Falconer... and, provided them with food, clothing, and daily quantities of heroin/fentanyl in exchange for them doing commercial sex acts for money, with the proceeds going to Mendoza.  Thomas assisted the operation by securing and communicating with commercial sex buyers, posting online advertisements with photographs of the two victims on Skipthegames.com.  He also transported the two victims to calls away from the residence, and provided protection and assistance to sex trafficking victims while they were on those "out" calls.  Thomas was paid in drugs by Mendoza or Waddington.  The charges carry a mandatory minimum penalty of five years and a maximum of life.City woman arrested for allegedly shoplifting more than $1,000 worth of items from Lakewood Wal-Mart SuperCenter...A woman from Jamestown has been arrested for allegedly stealing more than $1,000 worth of merchandise last weekend from the Lakewood Wal-Mart SuperCenter.  Lakewood-Busti Police say they were called to the 350 Fairmount Ave. location shortly after 7 p.m. last Sunday night.  Officerss say 47 year-old Kathryn Fisher allegedly passed all points of sale with $1,071 worth of items without paying for them.  Fisher was arrested for fourth-degree grand larceny... and, was released with an appearance ticket for Busti Town Court.  </t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D4" s="2">
         <v>46098</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908342/wjtn-news-headlines-for-st-patrick-s-day-tues-mar-17-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of **fentanyl**... and, packaging used for the sale and distribution of narcotics.  A...
 ... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl**, and conspiracy to commit sex trafficking.  Prosecutors say between O...
@@ -437,94 +496,94 @@
 ...uspects were charged with third and fourth-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, N.Y. — Three Jamestown residents are facing felony drug charges after authorities executed a search warrant and seized fentanyl at a Forest Park residence. Investigators with the Jamestown Police Department and the Chautauqua County Sheriff’s Office executed a search warrant at 7 Forest Park at approximately 10:45 a.m. on March […]The post Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D5" s="2">
         <v>46098</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/17/three-charged-after-jamestown-search-warrant-nets-fentanyl-seizure/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>... authorities executed a search warrant and seized **fentanyl** at a Forest Park residence. Investigators with th...
 ...Three Charged After Jamestown Search Warrant Nets **Fentanyl** Seizure appeared first on WNY News Now.
 ....Y. — Three Jamestown residents are facing felony **drug** charges after authorities executed a search warra...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D6" s="2">
         <v>46094</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://tinyurl.com/27xq83cr</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D7" s="2">
         <v>46094</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907978/wjtn-news-headlines-for-fri-mar-13-2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...m Jamestown has been arrested on federal charges for allegedly trafficking **methamphetamine**... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michae...
 ...old Taylor Hernandez was arrested for possession with intent to distribute **methamphetamine**.  Prosecutors say that... according to the complaint... members of th...
@@ -533,37 +592,37 @@
 ...eized about 181 grams of meth... about 23.5 grams of suspected fentanyl... **drug** paraphernalia, and more than $4,100 in cash.  If convicted... DiGiaco...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>12 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D8" s="2">
         <v>46094</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907822/wjtn-news-headlines-for-thurs-mar-12-2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>..., seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of **methamphetamine**, scales and packaging used to traffic narcotics... a high-capacity magazin...
 ... into custody and a subsequent search of the vehicle located a quantity of **methamphetamine**.  She was taken to the city jail where she was held pending arraignme...
@@ -579,96 +638,51 @@
 ...Leandra's Law... unsafe backing... seventh-degree criminal possession of a **controlled** substance... and, two counts of endangering the welfare of a child.Gillibr...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D7" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46093</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/22dxk5ay</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
+          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D9" s="2">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/266pwgl9</t>
+          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WRFA-LP 107.9 FM</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
+          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
         </is>
       </c>
       <c r="D10" s="2">
@@ -676,12 +690,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.wrfalp.com/?p=74599</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_WRFALP.R</t>
+          <t>https://tinyurl.com/22dxk5ay</t>
         </is>
       </c>
     </row>
@@ -693,121 +702,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping - WRFA-LP 107.9 FM</t>
+          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
         </is>
       </c>
       <c r="D11" s="2">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yyn26c6</t>
+          <t>https://tinyurl.com/266pwgl9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 11, 2026</t>
+          <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
+          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North county man arrested following two traffic stops, and pursuit with Sheriff's officers and Dunkirk police...A man from Dunkirk faces numerous charges following two traffic stops... and, a short vehicle pursuit... that began in the town of Hanover early Tuesday morning and ended in Dunkirk.  Sheriff's officers say they stopped 45 year-old David Topliffe shortly before 1 a.m. for an inspection violation.  However... further investigation led deputies to again pursue Topliffe into the city of Dunkirk.  Shortly after 2 a.m., Dunkirk police say they spotted Topliffe's car traveling north on the 500 block of Swan Street.  The officer tried to stop the vehicle for multiple traffic infractions... but, the driver failed to comply.  They began a pursuit that continued until Topliffe stopped in the parking lot of a local business.  Police say Topliffe refused to comply with the officer's verbal commands... and, began resisting arrest.  He was finally taken into custody... and, was found to be operating the vehicle with a revoked non-driver ID only.  Topliffe was processed on charges of unlawfully fleeing a police officer... second-degree obstruction... resisting arrest... and, numerous vehicle and traffic citations.  He was released with apperance tickets.No. Harmony arrested after being warned to not have dogs, and two are found on his property...A town of North Harmony man awaiting final disposition of his animal cruelty case from last Fall... has been arrested again for having dogs on his property.  Sheriff's officers say they received notification Monday afternoon that 64 year-old Scott Humble was in possession of two, five-month old Kesshound dogs on his Route 394 property.  Deputies got a search warrant for the property, and, the dogs were found in a rear kennel.  A court order, previously issued in North Harmony Town Court last Oct. 16... explicitly prohibited Humble from owning, harboring, or having custody or control of any animals until final disposition of his pending case.  That stemmed from a late September incident when eight dogs were found dead... and, several others were found neglected.  The two dogs found Monday were seized and forfeited to the Chautauqua County Humane Society.  Humble was issued appearance tickets for two counts of second-degree criminal contempt... and is to appear in Town Court at a future date.Ecklund praises city Grants Coordinator, and others efforts to get grants for city...The city of Jamestown is continuing to see success in applying for... and, receiving both federal and state grant money.  That from Mayor Kim Ecklund... who recently touted the awarding of a $1.7-million state grant to help eliminate lead in some of the city's oldest houses.  Ecklund praised the work of city Grants Coordinator and Writer, Paula Pichon... and, says the grant will help the city and Dept. of Development to remove lead paint from some of the city's older housing stock.  Homes built before 1978 were often painted with lead paint... which young children can accidently can injest... causing significant health issues.  Ecklund also noted a $250,000 grant that Development Director Crystal Surdyk was able to obtain as a "pro-housing" community.  She adds that funding will come from the state's Homes and Community Renewal program in an effort to support two major initiatives -- one, the acceleration of housing development, and addressing buildings that are deteriorating.  They also hope the funding will combat absentee landlords in the city.City announces St. Patrick's Day "Turn River Green" this coming Saturday... The city of Jamestown will again be co-hosting the annual downtown celebration of "Turn the River Green" along the Chadakoin River this Saturday.  Mayor Kim Ecklund's Office says the event... which is put on jointly with Collaborative Children's Solutions... will be held -- beginning at 10 a.m. -- along the Riverwalk next to the Jamestown Area Medical Associates building.  City Councilman Tony Dolce says the highlight of the morning will be at 11 a.m. when the Board of Public Utilities and the "Luckly Leprechaun" turn the river green... and adds the material used by the BPU to turn the river green is harmless... and, is used to smoke test water lines by the utility.  Jamestown man arrested on warrants during street check...A man wanted in both Jamestown and Warren, Pa. has been arrested following a street check on Jamestown's southside Tuesday evening.  City police say a patrol in the area of Forest Avenue spotted 50 year-old James Lindsay III walking along the road... and, knew of the warrants.  Officers arrested Lindsay... and, found him in possession of a small quantity of crack cocaine.  He was taken to the city jail on one count of seventh-degree criminal possession of a controlled substance... fugitive from justice... and, on his Jamestown warrant.  Lindsay will be held pending arraignment and extradition.Former Randolph Postal Carrier pleads guilty to stealing items in the mail...A former Postal Service carrier in Randolph has pleaded guilty to stealing multiple items that had been mailed... and, she was entrusted to carry nearly three years ago.  U.S. Attorney Michael DiGiacomo announced Tuesday that 47 year-old Melissa Olson entered the plea before U.S. District Court Judge John Sinatra, Jr. to theft of mail by postal employee, which carries a maximum penalty of five years in prison, and a $250,000 fine.  Prosecutors say Olson was hired in 2023 as a rural carrier associate assigned to the Randolph Post Office.  Between April and May of that year... Olson opened a stamped, first-class mail envelope she was to deliver... and, removed a Visa gift card.  They add that Olson also admitted that she opened various envelopes later in 2023... and, rifled through the items, delaying their delivery. </t>
+          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
         </is>
       </c>
       <c r="D12" s="2">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907619/wjtn-news-headlines-for-wed-mar-11-2026</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>...n to the city jail on one count of seventh-degree criminal possession of a **controlled** substance... fugitive from justice... and, on his Jamestown warrant.  ...</t>
+          <t>https://www.wrfalp.com/?p=74599</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has admitted in federal court to fentanyl trafficking and kidnapping after authorities said he sold the powerful opioid and held a victim against her will for several weeks. U.S. Attorney Michael DiGiacomo announced that Dwayne Lowery, also known as “Chi Chi,” 31, of Jamestown, pleaded […]The post Jamestown Man Pleads Guilty to Federal Fentanyl Trafficking and Kidnapping Charges appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46092</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/11/jamestown-man-pleads-guilty-to-federal-fentanyl-trafficking-and-kidnapping-charges/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>... A Jamestown man has admitted in federal court to **fentanyl** trafficking and kidnapping after authorities said...
-...…]The post Jamestown Man Pleads Guilty to Federal **Fentanyl** Trafficking and Kidnapping Charges appeared first...
-...pping after authorities said he sold the powerful **opioid** and held a victim against her will for several we...</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WRFA-LP 107.9 FM</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Jamestown Man Pleads Guilty To Drug Trafficking, Kidnapping</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>A Jamestown man has pleaded guilty to drug trafficking and kidnapping in U.S. District Court. U.S. Attorney Michael DiGiacomo announced that 31-year old Dwayne Lowery, aka Chi Chi, pleaded guilty before U.S. District Judge Lawrence Vilardo to possession with intent to distribute 40 grams or more of fentanyl and kidnapping. The charges carry a mandatory […]</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46092</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://www.wrfalp.com/?p=74583</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>...ion with intent to distribute 40 grams or more of **fentanyl** and kidnapping. The charges carry a mandatory [&amp;#...
-A Jamestown man has pleaded guilty to **drug** trafficking and kidnapping in U.S. District Court...</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_WRFALP.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,28 +401,128 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Seven charged after Jamestown raid - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/23f2p5o9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>City man charged after narcotics investigation - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22k76srp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2cbvhcbl</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/26xalbhz</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22rgnb4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Wed., Mar. 18, 2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Quattrone says Sheriff's Dive Team finds Emerson's truck in Chautauqua Lake between Bemus and Greenhurst...The pick-up truck associated with a missing Lakewood man has been found submerged in Chautauqua Lake near the town of Ellery.  However... weather conditions have prevented Sheriff's Department Dive Team members from locating 64 year-old Daniel "Scott" Emerson.  Emerson was last seen on Mar. 3... but, Sheriff Jim Quattrone says his department received some tips and video from a location between Greenhurst and Bemus Point.  Quattrone says they received the video Monday morning... and, quickly got the Sheriff's marine boat and sonar out to that area and found the vehicle.  However... that was the day the temperature plummeted during the afternoon... and, divers has issues with air tanks freezing once they got out of the water.  With the weather still below freezing... Quattrone says the dive team will head back out Thursday.  He says they were able to find the top of the truck... which was at least partially submerged in mud and other debris.  Late last week... Lakewood-Busti Police urged residents and businesses located along the Chautauqua Lake shoreline for any help regarding Emerson's whereabouts.  Police say he was believed to be driving his maroon-colored F-150 that was last seen on Fairmount and Lakeview Avenues in the village around 12:30 a.m. the day he went missing.  If you have any information... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and drug-possession charges...A man from Jamestown has been arrested on multiple drug possession charges following a raid on a southside home early Tuesday afternoon.  Sheriff's officers say their narcotics investigators... along with those from Jamestown police... executed a search warrant on the upper apartment at 313 Prather Ave. shortly after Noon.  The suspect... 26 year-old Devonte Green -- who had a State Parole warrant for his arrest -- was seen leaving the residence in a vehicle just prior to the raid.  Jamestown police tried to conduct a vehicle stop... but, Green continued for a short distance in the car before he was arrested following a brief foot chase.  Deputies say their search of the home, Green and his vehicle led to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  Green was held pending arraignment on charges including: third-and-seventh-degree criminal possession of a controlled substance... and, resisting arrest.Schmidt announces indictment against Westfield man who allegedly shot village woman, in front of children...A Westfield man who allegedly shot a woman... then led police on a vehicle pursuit earlier this month, faces several charges related to both incidents.  Chautauqua County District Attorney Jason Schmidt says a grand jury has indicted 52-year-old Jahmaul Johnson on eight counts, including second-degree attempted murder.  Schmidt says that top charge stems from a shooting that occurred on Route 20 in the village during the evening of Mar. 7... he says Judge Stephen Cass presided over the matter, and a "not guilty" plea was entered for the defendant.  After the shooting... Johnson fled the scene, leading to a pursuit that ended when he crashed his getaway vehicle into a ditch.  He was taken into custody in the Town of Pomfret a short time later that evening.  Schmidt says Johnson also faces three violent felonies related to a handgun and magazine he allegedly possessed... along with four counts of endangering the welfare of a child.  Schmidt says Johnson pleaded not guilty at his arraignment Tuesday morning before being remanded to the Chautauqua County Jail on $1-million cash bail... $2-million property bond.  He says a disovery conference will be held on Apr. 13.  If convicted, Johnson faces up to 25 years in prison on the attempted murder charge and up to 15 years on the weapon counts, adding that there's a possibility of those sentences running consecutively.  The victim was taken to an Erie, Pa. hospital, and is recovering from her injuries.Site work beginning for new Brook's Hospital in Fredonia...Initial site work for the new Northern Chautauqua Hospital project in Fredonia gets underway this week.  The announcement late Monday by Kaleida Health comes in the wake of its January filing in conjunction with Brooks-TLC of a building permit with the village of Fredonia for the hospital's construction.  Turner Construction Company subcontracted with Fredonia-based S. St. George General Contracting to perform the preliminary site work, including setting up temporary staging areas, fencing the property, and grading the site.  Initial work will depend on the weather... and the need for the land to drain and dry out.  The $223.8 million project is planned as a one-story, 133,000 facility at 412 East Main St.  It will replace the existing Brooks Hospital in the city of Dunkirk.Molitor part of Assembly-Senate Budget Conference Committee to deal with Human Services...The deadline for a new state budget is fast approaching... and, work is continuing in the New York State Assembly and Senate on a final spending plan.  With that... more legislative hearings involving conference committees are underway.  Local State Assemblyman Andrew Molitor is an alternate for the committee on Human Services... which means he'll be able to ask questions and offer input about Medicaid and other "safety net" programs.  The Assembly's $272-billion, "one-house" budget includes a 1% income tax cut for low and middle income earners... but, Molitor says it's not enough.  Ideally, he says he would like to see all income taxes eliminated.  Molitor says he remains hopeful there will be a budget acted on by the Apr. 1 deadline. </t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D7" s="2">
         <v>46100</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908600/wjtn-news-headlines-for-wed-mar-18-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...arch of the home, Green and his vehicle led to the seizure of 2.3 grams of **fentanyl**... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  G...
 ...ed to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin **mushrooms**... along with $131 cash.  Green was held pending arraignment on charg...
@@ -431,57 +531,238 @@
 ...nt on charges including: third-and-seventh-degree criminal possession of a **controlled** substance... and, resisting arrest.Schmidt announces indictment against We...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – ASHFORD, N.Y. — Two Cattaraugus County men were arrested on felony drug charges following a traffic stop and investigation that led to the discovery of suspected cocaine, according to the Cattaraugus County Sheriff’s Office. Authorities report that the incident occurred on March 18, 2026, at approximately 7:47 p.m. in the Town […]The post Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/19/traffic-stop-in-ashford-leads-to-cocaine-seizure-two-arrested-on-felony-drug-charges/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>...wo Cattaraugus County men were arrested on felony **drug** charges following a traffic stop and investigatio...
+... Leads to Cocaine Seizure, Two Arrested on Felony **Drug** Charges appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – DUNKIRK, N.Y. — A narcotics investigation in the City of Dunkirk led to the seizure of fentanyl, crack cocaine, and methamphetamine, along with the arrest of a 45-year-old man on multiple felony drug charges. Authorities executed a search warrant at a lower apartment at 209 Lincoln Avenue on March 18, 2026, […]The post Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/19/dunkirk-man-arrested-after-multi-agency-narcotics-raid-on-lincoln-avenue/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>...ed to the seizure of fentanyl, crack cocaine, and **methamphetamine**, along with the arrest of a 45-year-old man on mu...
+...tion in the City of Dunkirk led to the seizure of **fentanyl**, crack cocaine, and methamphetamine, along with t...
+...he arrest of a 45-year-old man on multiple felony **drug** charges. Authorities executed a search warrant at...</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A multi-agency narcotics investigation led to seven arrests Tuesday afternoon after authorities executed a search warrant at a Jamestown apartment, seizing fentanyl, crack cocaine, and other drug-related items. According to investigators, the search warrant was carried out around 3:39 p.m. on March 17, 2026, at 28 Euclid Ave., […]The post Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/19/seven-arrested-after-jamestown-narcotics-raid-fentanyl-and-cocaine-seized/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>... search warrant at a Jamestown apartment, seizing **fentanyl**, crack cocaine, and other drug-related items. Acc...
+...st Seven Arrested After Jamestown Narcotics Raid, **Fentanyl** and Cocaine Seized appeared first on WNY News Now...
+...tment, seizing fentanyl, crack cocaine, and other **drug**-related items. According to investigators, the se...</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, NY — A Niagara Falls man was taken into custody early Thursday after Jamestown police allegedly found him driving while impaired by drugs during a traffic stop on the city’s east side. According to the Jamestown Police Department, the incident occurred at approximately 1:14 a.m. on March 19, 2026. Officers […]The post Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/19/jamestown-man-charged-with-drug-impaired-driving-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>.... Officers […]The post Jamestown Man Charged With **Drug**-Impaired Driving Following Early Morning Traffic ...</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Jamestown man was taken into custody Tuesday after a narcotics investigation led to the execution of a search warrant and the seizure of controlled substances, according to local authorities. Narcotics investigators from the Chautauqua County Sheriff’s Office and Jamestown Police Department executed a search warrant at an […]The post Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/19/jamestown-man-arrested-after-narcotics-search-warrant-yields-fentanyl-and-psilocybin/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>...an Arrested After Narcotics Search Warrant Yields **Fentanyl** and Psilocybin appeared first on WNY News Now.
+... execution of a search warrant and the seizure of **controlled** substances, according to local authorities. Narco...</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D13" s="2">
         <v>46099</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://tinyurl.com/28g35pus</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WJTN News Headlines for St. Patrick's Day, Tues., Mar. 17, 2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>11 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Jamestown-area receives between 4 and 8 inches of snow in St. Patrick's Eve and Day snowstorm...Some parts of Chautauqua County received several inches of snow during the storm that accompanied a cold front last night through this morning.  The National Weather Service in Buffalo reports 8-and-a-half inches of the white stuff in Cassadaga... and about 6 in the Mayville area.  Here in the Jamestown-area... we got about 4 inches.  That's right about where Forecaster Steve Welch with the National Weather Service in Buffalo said we would be late Monday... with 2 to 4 inches generally in the Western New York area.  He says there may be a couple more inches falling during the day today.  We remain under a Winter Weather Advisory until 8 o'clock tonight.  Jamestown street closed about five-hours Sunday night after high winds blow roof off vacant building downtown...The Jamestown Department of Development was able to safely get the roof off a vacant building on East Second Street late Sunday night.  Officials say the roof was partially torn off shortly after 5 p.m. during the wind storm.  City police closed off East Second from Prendergast to Foote Avenues.  A front-loader was brought in to remove the roof... and, the street reopened shortly before 10:30 p.m. Three arrested during Forest Park drug bust in Jamestown late Monday morning...        Three people from Jamestown have been arrested following a drug raid on a home on the city's southside late Monday morning.  Sheriff's officers say their Narcotics Investigators along with those from Jamestown... executed a search warrant at 7 Forest Park about 10:45 a.m., and, found 39 year-old Ronaldo Galarza... 19 year-old Ronaldo Galarza, Jr. and 39 year-old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of fentanyl... and, packaging used for the sale and distribution of narcotics.  All three suspects were charged with third and fourth-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  Each suspect was issued appearance tickets for city court... and, the investigation is ongoing with additional arrests expected.  If you have any information about suspicious or narcotics related activity in your area... call the Sheriff's Office Narcotics Investigators Tip line at either 1-800-344-8702 or 664-2420... or the JPD Tip line at 483-8477.JPS begins budget process by reviewing first draft of $120.8-million spending plan...There's no tax increase in the Jamestown Public School's proposed 2026-27 budget proposal... which totals about $120.8-million.  The school board recently got it's first look at the first draft of the spending plan... which Assistant Superintendent for Finance and Operations Brittany Spry says increases spending by about $5.2-million... which is a 4.5% increase.  Spry says the biggest increases come in programming with some new positions to be filled.  She says they include a new assistant principal and secretary for the district's Innovation Center at the former Rodgers School... and six middle school teachers.  Much of the money to cover the increased costs is coming from an increase in state school aid.  Once final state aid figures are known... the district will move to finalize a spending plan for voters to act on in May.  Thomas pleads guilty in Mendoza drug and sex trafficking case...A Jamestown man has pleaded guilty in federal court to drug and sex trafficking conspiracy charges in connection with a case against a local drug kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-old Kelvin Thomas entered the plea last Friday before U.S. District Court Judge John Sinatra, Jr. to conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl, and conspiracy to commit sex trafficking.  Prosecutors say between October and December 2022, Thomas conspired with Zaid Mendoza and Cora Waddington to conduct a sex trafficking operation involving two individuals with drug addictions.  As part of the conspiracy... they say Thomas, Mendoza, and Waddington, provided shelter to the victims at a West Main Street home in Falconer... and, provided them with food, clothing, and daily quantities of heroin/fentanyl in exchange for them doing commercial sex acts for money, with the proceeds going to Mendoza.  Thomas assisted the operation by securing and communicating with commercial sex buyers, posting online advertisements with photographs of the two victims on Skipthegames.com.  He also transported the two victims to calls away from the residence, and provided protection and assistance to sex trafficking victims while they were on those "out" calls.  Thomas was paid in drugs by Mendoza or Waddington.  The charges carry a mandatory minimum penalty of five years and a maximum of life.City woman arrested for allegedly shoplifting more than $1,000 worth of items from Lakewood Wal-Mart SuperCenter...A woman from Jamestown has been arrested for allegedly stealing more than $1,000 worth of merchandise last weekend from the Lakewood Wal-Mart SuperCenter.  Lakewood-Busti Police say they were called to the 350 Fairmount Ave. location shortly after 7 p.m. last Sunday night.  Officerss say 47 year-old Kathryn Fisher allegedly passed all points of sale with $1,071 worth of items without paying for them.  Fisher was arrested for fourth-degree grand larceny... and, was released with an appearance ticket for Busti Town Court.  </t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D14" s="2">
         <v>46098</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908342/wjtn-news-headlines-for-st-patrick-s-day-tues-mar-17-2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of **fentanyl**... and, packaging used for the sale and distribution of narcotics.  A...
 ... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl**, and conspiracy to commit sex trafficking.  Prosecutors say between O...
@@ -496,94 +777,74 @@
 ...uspects were charged with third and fourth-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, N.Y. — Three Jamestown residents are facing felony drug charges after authorities executed a search warrant and seized fentanyl at a Forest Park residence. Investigators with the Jamestown Police Department and the Chautauqua County Sheriff’s Office executed a search warrant at 7 Forest Park at approximately 10:45 a.m. on March […]The post Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D15" s="2">
         <v>46098</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/17/three-charged-after-jamestown-search-warrant-nets-fentanyl-seizure/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>... authorities executed a search warrant and seized **fentanyl** at a Forest Park residence. Investigators with th...
 ...Three Charged After Jamestown Search Warrant Nets **Fentanyl** Seizure appeared first on WNY News Now.
 ....Y. — Three Jamestown residents are facing felony **drug** charges after authorities executed a search warra...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Jamestown men charged with drug, weapons possession - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
+        </is>
+      </c>
+      <c r="D16" s="2">
         <v>46094</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/27xq83cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
-        </is>
-      </c>
-      <c r="D7" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907978/wjtn-news-headlines-for-fri-mar-13-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...m Jamestown has been arrested on federal charges for allegedly trafficking **methamphetamine**... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michae...
 ...old Taylor Hernandez was arrested for possession with intent to distribute **methamphetamine**.  Prosecutors say that... according to the complaint... members of th...
@@ -592,155 +853,9 @@
 ...eized about 181 grams of meth... about 23.5 grams of suspected fentanyl... **drug** paraphernalia, and more than $4,100 in cash.  If convicted... DiGiaco...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Mar. 12, 2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>12 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>City man arrested during drug bust on Lincoln St...A man from Jamestown has been arrested on multiple drug and weapons possession charges following a raid Wednesday afternoon on the city's eastside.  Sheriff's officers say narcotics investigators from their department... and, Jamestown police... executed a search warrant on two apartments at 300 Lincoln St. shortly before 3 p.m.  Deputies say they arrested 43 year-old Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of methamphetamine, scales and packaging used to traffic narcotics... a high-capacity magazine, a .32 caliber revolver and $80 in cash.  Officers charged Santiago with five counts of third-degree criminal possession of a controlled substance.... second-and third-degree criminal possession of a weapon... and, second-degree criminally using drug paraphernalia.  Santiago was held pending arraignment in city court.  Anyone with information about suspicious or narcotics related activity in their area is asked to call the Sheriff's Department Narcotics Investigators tip line at 1-800-344-8702... or 664-2420... or the JPD tip line at 483-8477.Second city man arrested during Fluvanna Ave. Extention drug raid...Another city man has been arrested on drug and weapons possession charges following a raid on a home in the Fluvanna Avenue area of the town of Ellicott.  Sheriff's officers say narcotics investigators executed the search warrant at 3138 Fluvanna Ave. Ext. about 1:30 p.m. Tuesday.  Investigators say they spotted the suspect... 51 year-old Larry Grayson, Jr., leaving the home just prior to the raid... and, he was stopped a short distance away.  Officers say he was found in possession of 3.8 grams of crack cocaine, scales and packaging used for trafficking narcotics... a .22-caliber rifle... and, just over $1,000 in cash.  Grayson was charged with third-degree criminal possession of a controlled substance... fourth-degree criminal possession of a weapon... and second-degree criminally using drug paraphernalia.  Grayson was held in the county jail pending centralized arraignment.  City woman accused of being under influence of drugs after her car backs into school bus...A Jamestown woman faces major consequences after her car allegedly backed into a school bus last week... causing a relatively minor accident.  However... 34 year-old Emily Depane is accused of doing it while under the influence of drugs... and, with two children under the age of 16 in the car with her.  Jamestown police say they were notified of the accident... which occured in the area of Martin Road and Brad Street about 3 p.m. last Thursday, Mar. 5.  Officers say their investigation determined that Depane backed into the bus... causing a minor collision.  However... police say she was apparently driving while impaired... and, the two children were her passengers.  Depane was taken into custody and a subsequent search of the vehicle located a quantity of methamphetamine.  She was taken to the city jail where she was held pending arraignment for driving while ability impaired by drugs... DWAI -- with a passenger under the age of 16 -- a violation of Leandra's Law... unsafe backing... seventh-degree criminal possession of a controlled substance... and, two counts of endangering the welfare of a child.Gillibrand introduces legislation to return tariff money to small businesses...It's a "one-two punch" that's hitting New Yorkers directly in the wallet.  That from Democrat U.S. Senator Kirsten Gillibrand... who says that punch is being inflicted by President Trump's tariff wars... and, the War in Iran.  During a Zoom Press Conference Wednesday... Gillibrand said -- even after some of his tariffs were struck down by the U.S. Supreme Court -- the president "doubled-down" on the tariffs... which will increase from 10% to 15% -- which means higher prices for everyone.  She adds the president also doubled down on a war the American people "don't like."  Gillibrand cited at least one New Yorker... who said his home heating costs have double in recent weeks... and, faces other increased costs because petrolium is used in so many products.  In response... Gillibrand says she's proposed a measure to help small businesses recoup money lost from tariffs, and can pass down savings to consumers.  She introduced the Small Business Liberation 2.0 Act... that would exempt small businesses from the president's newest tariffs, and would refund at least some of the tariff monies charged to businesses they can pass on to their customers.  Since the War in Iran started... Gillibrand says the average price for a gallon of regular, unleaded gas in New York state has risen by 44-cents.  The U.S. campaign of airstrikes with Israel against Iran is now into it's 13th day.Jamestown woman arrested for allegedly hitting child in the head with plastic baseball bat...A woman from Jamestown is accused of hitting her young son with a plastic bat... and, injuring him... during a domestic incident Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child as a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907822/wjtn-news-headlines-for-thurs-mar-12-2026</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>..., seized 29.4 grams of crack cocaine, 39.6 grams of fentanyl, 4.5 grams of **methamphetamine**, scales and packaging used to traffic narcotics... a high-capacity magazin...
-... into custody and a subsequent search of the vehicle located a quantity of **methamphetamine**.  She was taken to the city jail where she was held pending arraignme...
-... Andrew Santiago... and, seized 29.4 grams of crack cocaine, 39.6 grams of **fentanyl**, 4.5 grams of methamphetamine, scales and packaging used to traffic narcot...
-City man arrested during **drug** bust on Lincoln St...A man from Jamestown has been arrested on multiple dr...
-...ug bust on Lincoln St...A man from Jamestown has been arrested on multiple **drug** and weapons possession charges following a raid Wednesday afternoon on the...
-...ree criminal possession of a weapon... and, second-degree criminally using **drug** paraphernalia.  Santiago was held pending arraignment in city court. ...
-...p line at 483-8477.Second city man arrested during Fluvanna Ave. Extention **drug** raid...Another city man has been arrested on drug and weapons possession c...
-... Fluvanna Ave. Extention drug raid...Another city man has been arrested on **drug** and weapons possession charges following a raid on a home in the Fluvanna ...
-...gree criminal possession of a weapon... and second-degree criminally using **drug** paraphernalia.  Grayson was held in the county jail pending centraliz...
-...charged Santiago with five counts of third-degree criminal possession of a **controlled** substance.... second-and third-degree criminal possession of a weapon... a...
-...cash.  Grayson was charged with third-degree criminal possession of a **controlled** substance... fourth-degree criminal possession of a weapon... and second-d...
-...Leandra's Law... unsafe backing... seventh-degree criminal possession of a **controlled** substance... and, two counts of endangering the welfare of a child.Gillibr...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cardiology Symptoms and Risk Factors: What You Need to Know</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Heart health is one of the most important aspects of overall wellbeing. Many people ignore early warning signs of heart problems until they become serious. Understanding cardiology symptoms and risk factors can help you detect potential heart issues early and take the right steps to protect your health. Healthcare providers such as Liv Hospital emphasize […]The post Cardiology Symptoms and Risk Factors: What You Need to Know appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/13/cardiology-symptoms-and-risk-factors-what-you-need-to-know/</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jamestown man pleads guilty to sex trafficking - Fingerlakes1.com</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46093</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/22dxk5ay</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>City Men Charged With Drug, Weapons Possession - Post Journal</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46093</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/266pwgl9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WRFA-LP 107.9 FM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Project To Finish Sewering Chautauqua Lake Underway</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Plans to finish a project to establish public sewer service around Chautauqua Lake are underway. Chautauqua County Executive PJ Wendel said Phase 3 of the South &amp; Center Chautauqua Lake Sewer District (SCCLSD) expansion will extend public sewer infrastructure from Point Chautauqua to Midway State Park. This will effectively close the remaining gap and completing the […]</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46093</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://www.wrfalp.com/?p=74599</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_WRFALP.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,15 +406,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Seven charged after Jamestown raid - observertoday.com</t>
+          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23f2p5o9</t>
+          <t>https://tinyurl.com/28g35pus</t>
         </is>
       </c>
     </row>
@@ -446,15 +446,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
+          <t>Seven charged after Jamestown raid - observertoday.com</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2cbvhcbl</t>
+          <t>https://tinyurl.com/23f2p5o9</t>
         </is>
       </c>
     </row>
@@ -466,15 +466,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
+          <t>Telegram Outages Spike in Kremlin’s Push for Digital Control - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/26xalbhz</t>
+          <t>https://tinyurl.com/2xr4ut6j</t>
         </is>
       </c>
     </row>
@@ -486,43 +486,177 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
+          <t>Putin Furthers Civil Society Facade as Tool of Control - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22rgnb4x</t>
+          <t>https://tinyurl.com/22tofx85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>WJTN News Headlines for Fri., Mar. 20, 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Police able to bring Emerson's reported truck out of lake... no word on his situation...The search resumed this morning for the missing Lakewood man... whose pick-up truck was found submerged in Chautauqua Lake earlier this week.  We have seen on-line "chatter" that the truck has been brought out of the lake.  However... that has NOT been confirmed.  We have calls into Chautauqua County Sheriff Jim Quattrone, but, have not heard back  Earlier today, Quattrone said his department's Dive Team had been joined by others from Erie and Niagara Counties... and, New York State Police at the scene.  Divers went back into the water near Bemus Point this morning to attach floation devices to bring the truck to the surface.  Quattrone says murky water... and, the fact the truck is in a few feet of mud and muck at the bottom... have hampered efforts.  Police are still trying to locate 64 year-old Daniel "Scott" Emerson... who was last seen on Mar. 3. Fire heavily damages first-floor of multiple-family dwelling in Jamestown...Flames have heavily-damaged the first floor of a three-story, multi-family home on Jamestown's southside.   City Fire Captain Dan Balling says firefighters were called to the scene at 517 Newland Ave. shortly after 1 p.m., and, found heavy smoke, and fire on the first floor.  Balling credited crews with making a quick stop on the flames... and, confining the blaze to the first floor.  He says an off-duty shift was called in... and, the fire was knocked down in less than 30 minutes.  Balling says there was heat damage to the second and third-floors.  The house was occupied... but, everyone got out safely.  Two firefighters suffered minor injuries.  The cause is under investigation.City man arrested for allegedly injuring and holding a woman against her will...A man from Jamestown faces contempt and other charges after allegedly hurting and holding a woman against her will at an eastside home.  In addition... city police accuse 26 year-old Angel Ramos-Gonzalez of holding the woman so long that officers found three children living in "deplorable conditions."  Jamestown police were called to the scene for a domestic dispute just after 8 a.m. Thursday.  Officers had been told that Ramos-Gonzalez had violated an order of protection... and, on arrival... found him inside a bedroom closet where he was taken into custody.  In addition to holding the woman against her will... Ramos-Gonzalez is also accused of biting the woman, causing minor injuries.  He's charged with two counts of aggravated criminal contempt... unlawful imprisonment... third-degree assault... and, three counts of endangering the welfare of a child.  He was jailed pending arraignment.Borrello calls State Senate "One-House" Budget a "Train Wreck..."The process to craft a final, 2026-27 state budget is continuing now that both the State Senate and Assembly have presented their "one-house" spending plans.  Both budgets call for additional spending compared to Governor Kathy Hochul's, more than $260-billion proposal.  The Senate's one-house budget amounts to just under $270-billion... and, is about $7.1-billion more than Hochul's budget.  State Senator George Borrello calls it a "fiscal train wreck" with residents suffered under higher utility bills... and, "nothing was offered in relief."  Borrello says the Senate Democrats' "wish list" includes $5.6 billion in higher taxes.  He says it also contains no changes to the Climate Act... and, a rejection of Hochul's proposal to crack down on car insurance fraud and lawsuit abuse.  The Sunset Bay Republican believes what's positive in the budget is "far outshadowed" by the negative in terms of "waste, fraud and abuse."  He adds there are also too many gimmicks in the budget that really aren't enough to provide relief.  A final state budget is due by Apr. 1.County DMV urges residents about possible "Double Charge" issue with debit and credit card usage at DMV...Some New York State Department of Motor Vehicles offices are reporting seeing some customers getting "double-charged" for services using debit or credit cards for a single transaction.  In a press release this morning.. the Chautauqua County DMV is now urging their customers to use either cash or checks right now.  Officials say it's not happening "with every debit or credit card transaction, the problem has persisted since the state DMV went live with the DRIVES software update in February.  Unfortunately... local DMV offices are not authorized to issue refunds directly, and the state DMV is taking 3-to-5 business days to process refunds.  County Clerk Greg Carlson says they -- and other local DMVs are actively communicatin the issue to the state since the DRIVES rollout last month... but, they are still occuring.  Carlson says the county's three DMV offices will continue to process debit and credit card transactions, but encourages customers to use cash or check when completing in-person transactions until the state resolves the issue.Man from Ashville arrested for DWI after single-car accident in the town of Chautauqua...A man from Ashville faces a drunk driving charge following a single-car crash in the town of Chautauqua this past Wednesday night.  Sheriff's officers say they were called to the scene on Route 394 -- at Moore Road -- shortly before Midnight to investigate.  Deputies say they found that 37 year-old Phillip Grobe was driving while intoxicated at the time of the accident.  Grobe was arrested for DWI, Driving with a blood alcohol content of .08 or more... moved from lane unsafely... speed not reasonable and prudent... and, unreasonable speed with special hazards.  He was issued appearance tickets for Chautauqua Town Court at a later date.  No injuries were reported in the accident.     </t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908944/wjtn-news-headlines-for-fri-mar-20-2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...p;Deputies say they found that 37 year-old Phillip Grobe was driving while **intoxicated** at the time of the accident.  Grobe was arrested for DWI, Driving wit...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jamestown Drug Raid: Seven Arrested and Major Fentanyl Seized</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>In a major narcotics bust on March 17, 2026, authorities in Jamestown, New York, executed a search warrant at an apartment and arrested seven individuals who were allegedly up to no good. The Chautauqua County Sheriff’s Office, along with the Jamestown Police Department and even the SWAT team, raided the location, only to find a shocking amount of fentanyl, crack cocaine, and drug paraphernalia.During the raid, investigators seized around 32.5 grams of fentanyl, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,373 in cashâdefinitely not pocket change! The suspects ranged in age from 26 to 61 and included names like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple drug possession charges.Interestingly, among the arrested were individuals with outstanding warrants, which adds yet another layer to this already tangled web of drug-related offenses. Itâs a stark reminder that sometimes, what happens behind closed doors isnât as harmless as it seems. Letâs hope this bust serves as a wake-up call for those involved in the local narcotics trade, but it also makes you wonderâhow many more like this are happening in towns across the country?</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908851/jamestown-drug-raid-seven-arrested-and-major-fentanyl-seized</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>...even the SWAT team, raided the location, only to find a shocking amount of **fentanyl**, crack cocaine, and drug paraphernalia.During the raid, investigators seiz...
+...g paraphernalia.During the raid, investigators seized around 32.5 grams of **fentanyl**, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,3...
+...e location, only to find a shocking amount of fentanyl, crack cocaine, and **drug** paraphernalia.During the raid, investigators seized around 32.5 grams of f...
+...ames like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple **drug** possession charges.Interestingly, among the arrested were individuals with...
+...ding warrants, which adds yet another layer to this already tangled web of **drug**-related offenses. Itâs a stark reminder that sometimes, ...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2cbvhcbl</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/26xalbhz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22rgnb4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Wed., Mar. 18, 2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Quattrone says Sheriff's Dive Team finds Emerson's truck in Chautauqua Lake between Bemus and Greenhurst...The pick-up truck associated with a missing Lakewood man has been found submerged in Chautauqua Lake near the town of Ellery.  However... weather conditions have prevented Sheriff's Department Dive Team members from locating 64 year-old Daniel "Scott" Emerson.  Emerson was last seen on Mar. 3... but, Sheriff Jim Quattrone says his department received some tips and video from a location between Greenhurst and Bemus Point.  Quattrone says they received the video Monday morning... and, quickly got the Sheriff's marine boat and sonar out to that area and found the vehicle.  However... that was the day the temperature plummeted during the afternoon... and, divers has issues with air tanks freezing once they got out of the water.  With the weather still below freezing... Quattrone says the dive team will head back out Thursday.  He says they were able to find the top of the truck... which was at least partially submerged in mud and other debris.  Late last week... Lakewood-Busti Police urged residents and businesses located along the Chautauqua Lake shoreline for any help regarding Emerson's whereabouts.  Police say he was believed to be driving his maroon-colored F-150 that was last seen on Fairmount and Lakeview Avenues in the village around 12:30 a.m. the day he went missing.  If you have any information... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and drug-possession charges...A man from Jamestown has been arrested on multiple drug possession charges following a raid on a southside home early Tuesday afternoon.  Sheriff's officers say their narcotics investigators... along with those from Jamestown police... executed a search warrant on the upper apartment at 313 Prather Ave. shortly after Noon.  The suspect... 26 year-old Devonte Green -- who had a State Parole warrant for his arrest -- was seen leaving the residence in a vehicle just prior to the raid.  Jamestown police tried to conduct a vehicle stop... but, Green continued for a short distance in the car before he was arrested following a brief foot chase.  Deputies say their search of the home, Green and his vehicle led to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  Green was held pending arraignment on charges including: third-and-seventh-degree criminal possession of a controlled substance... and, resisting arrest.Schmidt announces indictment against Westfield man who allegedly shot village woman, in front of children...A Westfield man who allegedly shot a woman... then led police on a vehicle pursuit earlier this month, faces several charges related to both incidents.  Chautauqua County District Attorney Jason Schmidt says a grand jury has indicted 52-year-old Jahmaul Johnson on eight counts, including second-degree attempted murder.  Schmidt says that top charge stems from a shooting that occurred on Route 20 in the village during the evening of Mar. 7... he says Judge Stephen Cass presided over the matter, and a "not guilty" plea was entered for the defendant.  After the shooting... Johnson fled the scene, leading to a pursuit that ended when he crashed his getaway vehicle into a ditch.  He was taken into custody in the Town of Pomfret a short time later that evening.  Schmidt says Johnson also faces three violent felonies related to a handgun and magazine he allegedly possessed... along with four counts of endangering the welfare of a child.  Schmidt says Johnson pleaded not guilty at his arraignment Tuesday morning before being remanded to the Chautauqua County Jail on $1-million cash bail... $2-million property bond.  He says a disovery conference will be held on Apr. 13.  If convicted, Johnson faces up to 25 years in prison on the attempted murder charge and up to 15 years on the weapon counts, adding that there's a possibility of those sentences running consecutively.  The victim was taken to an Erie, Pa. hospital, and is recovering from her injuries.Site work beginning for new Brook's Hospital in Fredonia...Initial site work for the new Northern Chautauqua Hospital project in Fredonia gets underway this week.  The announcement late Monday by Kaleida Health comes in the wake of its January filing in conjunction with Brooks-TLC of a building permit with the village of Fredonia for the hospital's construction.  Turner Construction Company subcontracted with Fredonia-based S. St. George General Contracting to perform the preliminary site work, including setting up temporary staging areas, fencing the property, and grading the site.  Initial work will depend on the weather... and the need for the land to drain and dry out.  The $223.8 million project is planned as a one-story, 133,000 facility at 412 East Main St.  It will replace the existing Brooks Hospital in the city of Dunkirk.Molitor part of Assembly-Senate Budget Conference Committee to deal with Human Services...The deadline for a new state budget is fast approaching... and, work is continuing in the New York State Assembly and Senate on a final spending plan.  With that... more legislative hearings involving conference committees are underway.  Local State Assemblyman Andrew Molitor is an alternate for the committee on Human Services... which means he'll be able to ask questions and offer input about Medicaid and other "safety net" programs.  The Assembly's $272-billion, "one-house" budget includes a 1% income tax cut for low and middle income earners... but, Molitor says it's not enough.  Ideally, he says he would like to see all income taxes eliminated.  Molitor says he remains hopeful there will be a budget acted on by the Apr. 1 deadline. </t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D12" s="2">
         <v>46100</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908600/wjtn-news-headlines-for-wed-mar-18-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...arch of the home, Green and his vehicle led to the seizure of 2.3 grams of **fentanyl**... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  G...
 ...ed to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin **mushrooms**... along with $131 cash.  Green was held pending arraignment on charg...
@@ -531,238 +665,218 @@
 ...nt on charges including: third-and-seventh-degree criminal possession of a **controlled** substance... and, resisting arrest.Schmidt announces indictment against We...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>(WNY News Now) – ASHFORD, N.Y. — Two Cattaraugus County men were arrested on felony drug charges following a traffic stop and investigation that led to the discovery of suspected cocaine, according to the Cattaraugus County Sheriff’s Office. Authorities report that the incident occurred on March 18, 2026, at approximately 7:47 p.m. in the Town […]The post Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D13" s="2">
         <v>46100</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/traffic-stop-in-ashford-leads-to-cocaine-seizure-two-arrested-on-felony-drug-charges/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...wo Cattaraugus County men were arrested on felony **drug** charges following a traffic stop and investigatio...
 ... Leads to Cocaine Seizure, Two Arrested on Felony **Drug** Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>(WNY News Now) – DUNKIRK, N.Y. — A narcotics investigation in the City of Dunkirk led to the seizure of fentanyl, crack cocaine, and methamphetamine, along with the arrest of a 45-year-old man on multiple felony drug charges. Authorities executed a search warrant at a lower apartment at 209 Lincoln Avenue on March 18, 2026, […]The post Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D14" s="2">
         <v>46100</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/dunkirk-man-arrested-after-multi-agency-narcotics-raid-on-lincoln-avenue/</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...ed to the seizure of fentanyl, crack cocaine, and **methamphetamine**, along with the arrest of a 45-year-old man on mu...
 ...tion in the City of Dunkirk led to the seizure of **fentanyl**, crack cocaine, and methamphetamine, along with t...
 ...he arrest of a 45-year-old man on multiple felony **drug** charges. Authorities executed a search warrant at...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, N.Y. — A multi-agency narcotics investigation led to seven arrests Tuesday afternoon after authorities executed a search warrant at a Jamestown apartment, seizing fentanyl, crack cocaine, and other drug-related items. According to investigators, the search warrant was carried out around 3:39 p.m. on March 17, 2026, at 28 Euclid Ave., […]The post Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D15" s="2">
         <v>46100</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/seven-arrested-after-jamestown-narcotics-raid-fentanyl-and-cocaine-seized/</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>... search warrant at a Jamestown apartment, seizing **fentanyl**, crack cocaine, and other drug-related items. Acc...
 ...st Seven Arrested After Jamestown Narcotics Raid, **Fentanyl** and Cocaine Seized appeared first on WNY News Now...
 ...tment, seizing fentanyl, crack cocaine, and other **drug**-related items. According to investigators, the se...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, NY — A Niagara Falls man was taken into custody early Thursday after Jamestown police allegedly found him driving while impaired by drugs during a traffic stop on the city’s east side. According to the Jamestown Police Department, the incident occurred at approximately 1:14 a.m. on March 19, 2026. Officers […]The post Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D16" s="2">
         <v>46100</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/jamestown-man-charged-with-drug-impaired-driving-following-early-morning-traffic-stop/</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>.... Officers […]The post Jamestown Man Charged With **Drug**-Impaired Driving Following Early Morning Traffic ...</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, N.Y. — A Jamestown man was taken into custody Tuesday after a narcotics investigation led to the execution of a search warrant and the seizure of controlled substances, according to local authorities. Narcotics investigators from the Chautauqua County Sheriff’s Office and Jamestown Police Department executed a search warrant at an […]The post Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D12" s="2">
+      <c r="D17" s="2">
         <v>46100</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/jamestown-man-arrested-after-narcotics-search-warrant-yields-fentanyl-and-psilocybin/</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...an Arrested After Narcotics Search Warrant Yields **Fentanyl** and Psilocybin appeared first on WNY News Now.
 ... execution of a search warrant and the seizure of **controlled** substances, according to local authorities. Narco...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46099</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/28g35pus</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>WJTN News Headlines for St. Patrick's Day, Tues., Mar. 17, 2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>11 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Jamestown-area receives between 4 and 8 inches of snow in St. Patrick's Eve and Day snowstorm...Some parts of Chautauqua County received several inches of snow during the storm that accompanied a cold front last night through this morning.  The National Weather Service in Buffalo reports 8-and-a-half inches of the white stuff in Cassadaga... and about 6 in the Mayville area.  Here in the Jamestown-area... we got about 4 inches.  That's right about where Forecaster Steve Welch with the National Weather Service in Buffalo said we would be late Monday... with 2 to 4 inches generally in the Western New York area.  He says there may be a couple more inches falling during the day today.  We remain under a Winter Weather Advisory until 8 o'clock tonight.  Jamestown street closed about five-hours Sunday night after high winds blow roof off vacant building downtown...The Jamestown Department of Development was able to safely get the roof off a vacant building on East Second Street late Sunday night.  Officials say the roof was partially torn off shortly after 5 p.m. during the wind storm.  City police closed off East Second from Prendergast to Foote Avenues.  A front-loader was brought in to remove the roof... and, the street reopened shortly before 10:30 p.m. Three arrested during Forest Park drug bust in Jamestown late Monday morning...        Three people from Jamestown have been arrested following a drug raid on a home on the city's southside late Monday morning.  Sheriff's officers say their Narcotics Investigators along with those from Jamestown... executed a search warrant at 7 Forest Park about 10:45 a.m., and, found 39 year-old Ronaldo Galarza... 19 year-old Ronaldo Galarza, Jr. and 39 year-old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of fentanyl... and, packaging used for the sale and distribution of narcotics.  All three suspects were charged with third and fourth-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  Each suspect was issued appearance tickets for city court... and, the investigation is ongoing with additional arrests expected.  If you have any information about suspicious or narcotics related activity in your area... call the Sheriff's Office Narcotics Investigators Tip line at either 1-800-344-8702 or 664-2420... or the JPD Tip line at 483-8477.JPS begins budget process by reviewing first draft of $120.8-million spending plan...There's no tax increase in the Jamestown Public School's proposed 2026-27 budget proposal... which totals about $120.8-million.  The school board recently got it's first look at the first draft of the spending plan... which Assistant Superintendent for Finance and Operations Brittany Spry says increases spending by about $5.2-million... which is a 4.5% increase.  Spry says the biggest increases come in programming with some new positions to be filled.  She says they include a new assistant principal and secretary for the district's Innovation Center at the former Rodgers School... and six middle school teachers.  Much of the money to cover the increased costs is coming from an increase in state school aid.  Once final state aid figures are known... the district will move to finalize a spending plan for voters to act on in May.  Thomas pleads guilty in Mendoza drug and sex trafficking case...A Jamestown man has pleaded guilty in federal court to drug and sex trafficking conspiracy charges in connection with a case against a local drug kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-old Kelvin Thomas entered the plea last Friday before U.S. District Court Judge John Sinatra, Jr. to conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl, and conspiracy to commit sex trafficking.  Prosecutors say between October and December 2022, Thomas conspired with Zaid Mendoza and Cora Waddington to conduct a sex trafficking operation involving two individuals with drug addictions.  As part of the conspiracy... they say Thomas, Mendoza, and Waddington, provided shelter to the victims at a West Main Street home in Falconer... and, provided them with food, clothing, and daily quantities of heroin/fentanyl in exchange for them doing commercial sex acts for money, with the proceeds going to Mendoza.  Thomas assisted the operation by securing and communicating with commercial sex buyers, posting online advertisements with photographs of the two victims on Skipthegames.com.  He also transported the two victims to calls away from the residence, and provided protection and assistance to sex trafficking victims while they were on those "out" calls.  Thomas was paid in drugs by Mendoza or Waddington.  The charges carry a mandatory minimum penalty of five years and a maximum of life.City woman arrested for allegedly shoplifting more than $1,000 worth of items from Lakewood Wal-Mart SuperCenter...A woman from Jamestown has been arrested for allegedly stealing more than $1,000 worth of merchandise last weekend from the Lakewood Wal-Mart SuperCenter.  Lakewood-Busti Police say they were called to the 350 Fairmount Ave. location shortly after 7 p.m. last Sunday night.  Officerss say 47 year-old Kathryn Fisher allegedly passed all points of sale with $1,071 worth of items without paying for them.  Fisher was arrested for fourth-degree grand larceny... and, was released with an appearance ticket for Busti Town Court.  </t>
         </is>
       </c>
-      <c r="D14" s="2">
+      <c r="D18" s="2">
         <v>46098</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908342/wjtn-news-headlines-for-st-patrick-s-day-tues-mar-17-2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>...old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of **fentanyl**... and, packaging used for the sale and distribution of narcotics.  A...
 ... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl**, and conspiracy to commit sex trafficking.  Prosecutors say between O...
@@ -777,85 +891,46 @@
 ...uspects were charged with third and fourth-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, N.Y. — Three Jamestown residents are facing felony drug charges after authorities executed a search warrant and seized fentanyl at a Forest Park residence. Investigators with the Jamestown Police Department and the Chautauqua County Sheriff’s Office executed a search warrant at 7 Forest Park at approximately 10:45 a.m. on March […]The post Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D15" s="2">
+      <c r="D19" s="2">
         <v>46098</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/17/three-charged-after-jamestown-search-warrant-nets-fentanyl-seizure/</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>... authorities executed a search warrant and seized **fentanyl** at a Forest Park residence. Investigators with th...
 ...Three Charged After Jamestown Search Warrant Nets **Fentanyl** Seizure appeared first on WNY News Now.
 ....Y. — Three Jamestown residents are facing felony **drug** charges after authorities executed a search warra...</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Mar. 13, 2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Fire heavily damages apartment in home on Jamestown's westside Thursday night...Quick response by Jamestown firefighters contained an apartment fire to that apartment Thursday night on the city's westside.  Fire Battalion Chief Nate Alm says crews were called to the scene at 50 Norton Ave. shortly after 7 p.m., and, says first responding crews saw smoke coming from the building after receiving multiple phone calls about it.  When they arrived... Alm says crews found the apartment on fire.  He says two engine companies were quickly on the scene... and, had the blaze knocked down fairly quickly.  He says one crew helped get one person out of the building... and, to an Alstar ambulance to be taken for treatment.  Alm says no one else was hurt... and fire damage was confined to the apartment.  He says an off-duty shift of 15 and one commander was called in to assist.  City fire investigators were called in to look for the cause... but, it was still under investigation last night.  "Targeted" shooting incident puts both Ring Elementary and Washington Middle Schools on lockdown early Thursday afternoon...It was a reported shooting incident on Jamestown's eastside early yesterday afternoon that led to brief lockdowns at Ring Elementary and Washington Middle Schools.  City police say they were called to the area of Buffalo and Crescent Streets just before 1:30 p.m. on reports of shots fired.  Officers say further investigation showed that the suspect forcibly entered an occupied home in the area, armed with a gun.  During the incident, the suspect fled the residence and while doing so fired the gun... and, hit the side of the residence before fleeing the scene in a vehicle.  There are no injuries that resulted from the incident... and, police were able to determine that the shooting was a result of a targeted attack on the occupants of the home.  No arrests have been made... and, at this time, police say the investigation is on going.  Anyone with information is asked to call the JPD TIP Line at 483-TIPS -- that's 483-8477... or the Jamestown Police Dept's command line at 483-7536.  Once city police gave the all-clear... both schools resumed normal operations and dismissal took place as usual.  City woman arrested on federal charges for allegedly trafficking drugs during January raid...A woman from Jamestown has been arrested on federal charges for allegedly trafficking methamphetamine... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michael DiGiacomo has announced that 31 year-old Taylor Hernandez was arrested for possession with intent to distribute methamphetamine.  Prosecutors say that... according to the complaint... members of the Jamestown Metro Drug Task Force executed a search warrant at Hernandez’s Falconer Street home... and, seized about 181 grams of meth... about 23.5 grams of suspected fentanyl... drug paraphernalia, and more than $4,100 in cash.  If convicted... DiGiacomo says Hernandez faces a maximum penalty of 20 years in prison and a $1-million fine.Woman from Jamestown arrested after allegedly hitting child with plastic bat...A woman from Jamestown is accused of hitting her young son with a plastic baseball bat... and, injuring him... during a domestic incident last Wednesday night on the city's eastside.  Officers say they were called to the location shortly after 8 p.m., and, their investigation showed that 39 year-old Amy Anderson had struck the child a a form of "disciplinary action."  Police say the child did suffer an injury... which also caused swelling to the top of the child's head.  Officers arrested Anderson without incident for third-degree assault... and, endangering the welfare of a child.  She was held pending arraignment.Gillibrand voices on-going opposition to SAVE Act still before the U.S. Senate...  As with recent polling of Americans... there is bi-partisan support for a measure that would require voter identification to vote in federal elections.  However... while Republicans support the "Safeguard American Voting Eligibility" -- or SAVE Act... Democrats continue to voice concern that it will take voting eligibility away from millions of Americans.  Among those is New York Senator Kirsten Gillibrand... who says... under the current proposal... even a driver's license isn't enough.  She says you need a birth certificate that matches your current name... so if you have a birth certificate, but, if it's just in your maiden name, you have to get it changed.  She adds about half the population also doesn't have a valid passport... which is also needed in some cases.  Gillibrand adds that the measure would also make it difficult for active military service members to vote.  The Democrat says the SAVE Act is being pushed by President Donald Trump because he believes it's the only way Congress will remain in Republican hands after the mid-term elections... and, that's why they are fighting against the legislation and calling on Republicans to negotiate a true, bi-partisan bill.  The SAVE Act was approved in the House of Representatives last year.  However... in the Senate, the measure is the subject of a Democrat fillibuster, that requires 60 yes votes to bring it to the floor.  Currently... Republicans have a 53-47 majority in the Senate.     </t>
-        </is>
-      </c>
-      <c r="D16" s="2">
-        <v>46094</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/907978/wjtn-news-headlines-for-fri-mar-13-2026</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>...m Jamestown has been arrested on federal charges for allegedly trafficking **methamphetamine**... and, other drugs during a raid last Jan. 15.  U.S. Attorney Michae...
-...old Taylor Hernandez was arrested for possession with intent to distribute **methamphetamine**.  Prosecutors say that... according to the complaint... members of th...
-...me... and, seized about 181 grams of meth... about 23.5 grams of suspected **fentanyl**... drug paraphernalia, and more than $4,100 in cash.  If convicted......
-...s say that... according to the complaint... members of the Jamestown Metro **Drug** Task Force executed a search warrant at Hernandez’s Falconer Street ...
-...eized about 181 grams of meth... about 23.5 grams of suspected fentanyl... **drug** paraphernalia, and more than $4,100 in cash.  If convicted... DiGiaco...</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -410,7 +410,7 @@
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46102</v>
+        <v>46103</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>City man charged after narcotics investigation - observertoday.com</t>
+          <t>Seven charged after Jamestown raid - observertoday.com</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -434,7 +434,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22k76srp</t>
+          <t>https://tinyurl.com/23f2p5o9</t>
         </is>
       </c>
     </row>
@@ -446,7 +446,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Seven charged after Jamestown raid - observertoday.com</t>
+          <t>City man charged after narcotics investigation - observertoday.com</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -454,7 +454,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23f2p5o9</t>
+          <t>https://tinyurl.com/22k76srp</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,60 +401,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46103</v>
+        <v>46104</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28g35pus</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Seven charged after Jamestown raid - observertoday.com</t>
+          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23f2p5o9</t>
+          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>City man charged after narcotics investigation - observertoday.com</t>
+          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22k76srp</t>
+          <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -466,7 +511,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Telegram Outages Spike in Kremlin’s Push for Digital Control - The Jamestown Foundation</t>
+          <t>Seven charged after Jamestown raid - observertoday.com</t>
         </is>
       </c>
       <c r="D5" s="2">
@@ -474,7 +519,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2xr4ut6j</t>
+          <t>https://tinyurl.com/23f2p5o9</t>
         </is>
       </c>
     </row>
@@ -486,7 +531,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Putin Furthers Civil Society Facade as Tool of Control - The Jamestown Foundation</t>
+          <t>City man charged after narcotics investigation - observertoday.com</t>
         </is>
       </c>
       <c r="D6" s="2">
@@ -494,24 +539,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22tofx85</t>
+          <t>https://tinyurl.com/22k76srp</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Mar. 20, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Police able to bring Emerson's reported truck out of lake... no word on his situation...The search resumed this morning for the missing Lakewood man... whose pick-up truck was found submerged in Chautauqua Lake earlier this week.  We have seen on-line "chatter" that the truck has been brought out of the lake.  However... that has NOT been confirmed.  We have calls into Chautauqua County Sheriff Jim Quattrone, but, have not heard back  Earlier today, Quattrone said his department's Dive Team had been joined by others from Erie and Niagara Counties... and, New York State Police at the scene.  Divers went back into the water near Bemus Point this morning to attach floation devices to bring the truck to the surface.  Quattrone says murky water... and, the fact the truck is in a few feet of mud and muck at the bottom... have hampered efforts.  Police are still trying to locate 64 year-old Daniel "Scott" Emerson... who was last seen on Mar. 3. Fire heavily damages first-floor of multiple-family dwelling in Jamestown...Flames have heavily-damaged the first floor of a three-story, multi-family home on Jamestown's southside.   City Fire Captain Dan Balling says firefighters were called to the scene at 517 Newland Ave. shortly after 1 p.m., and, found heavy smoke, and fire on the first floor.  Balling credited crews with making a quick stop on the flames... and, confining the blaze to the first floor.  He says an off-duty shift was called in... and, the fire was knocked down in less than 30 minutes.  Balling says there was heat damage to the second and third-floors.  The house was occupied... but, everyone got out safely.  Two firefighters suffered minor injuries.  The cause is under investigation.City man arrested for allegedly injuring and holding a woman against her will...A man from Jamestown faces contempt and other charges after allegedly hurting and holding a woman against her will at an eastside home.  In addition... city police accuse 26 year-old Angel Ramos-Gonzalez of holding the woman so long that officers found three children living in "deplorable conditions."  Jamestown police were called to the scene for a domestic dispute just after 8 a.m. Thursday.  Officers had been told that Ramos-Gonzalez had violated an order of protection... and, on arrival... found him inside a bedroom closet where he was taken into custody.  In addition to holding the woman against her will... Ramos-Gonzalez is also accused of biting the woman, causing minor injuries.  He's charged with two counts of aggravated criminal contempt... unlawful imprisonment... third-degree assault... and, three counts of endangering the welfare of a child.  He was jailed pending arraignment.Borrello calls State Senate "One-House" Budget a "Train Wreck..."The process to craft a final, 2026-27 state budget is continuing now that both the State Senate and Assembly have presented their "one-house" spending plans.  Both budgets call for additional spending compared to Governor Kathy Hochul's, more than $260-billion proposal.  The Senate's one-house budget amounts to just under $270-billion... and, is about $7.1-billion more than Hochul's budget.  State Senator George Borrello calls it a "fiscal train wreck" with residents suffered under higher utility bills... and, "nothing was offered in relief."  Borrello says the Senate Democrats' "wish list" includes $5.6 billion in higher taxes.  He says it also contains no changes to the Climate Act... and, a rejection of Hochul's proposal to crack down on car insurance fraud and lawsuit abuse.  The Sunset Bay Republican believes what's positive in the budget is "far outshadowed" by the negative in terms of "waste, fraud and abuse."  He adds there are also too many gimmicks in the budget that really aren't enough to provide relief.  A final state budget is due by Apr. 1.County DMV urges residents about possible "Double Charge" issue with debit and credit card usage at DMV...Some New York State Department of Motor Vehicles offices are reporting seeing some customers getting "double-charged" for services using debit or credit cards for a single transaction.  In a press release this morning.. the Chautauqua County DMV is now urging their customers to use either cash or checks right now.  Officials say it's not happening "with every debit or credit card transaction, the problem has persisted since the state DMV went live with the DRIVES software update in February.  Unfortunately... local DMV offices are not authorized to issue refunds directly, and the state DMV is taking 3-to-5 business days to process refunds.  County Clerk Greg Carlson says they -- and other local DMVs are actively communicatin the issue to the state since the DRIVES rollout last month... but, they are still occuring.  Carlson says the county's three DMV offices will continue to process debit and credit card transactions, but encourages customers to use cash or check when completing in-person transactions until the state resolves the issue.Man from Ashville arrested for DWI after single-car accident in the town of Chautauqua...A man from Ashville faces a drunk driving charge following a single-car crash in the town of Chautauqua this past Wednesday night.  Sheriff's officers say they were called to the scene on Route 394 -- at Moore Road -- shortly before Midnight to investigate.  Deputies say they found that 37 year-old Phillip Grobe was driving while intoxicated at the time of the accident.  Grobe was arrested for DWI, Driving with a blood alcohol content of .08 or more... moved from lane unsafely... speed not reasonable and prudent... and, unreasonable speed with special hazards.  He was issued appearance tickets for Chautauqua Town Court at a later date.  No injuries were reported in the accident.     </t>
+          <t>Telegram Outages Spike in Kremlin’s Push for Digital Control - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -519,34 +559,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908944/wjtn-news-headlines-for-fri-mar-20-2026</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...p;Deputies say they found that 37 year-old Phillip Grobe was driving while **intoxicated** at the time of the accident.  Grobe was arrested for DWI, Driving wit...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/2xr4ut6j</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamestown Drug Raid: Seven Arrested and Major Fentanyl Seized</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>In a major narcotics bust on March 17, 2026, authorities in Jamestown, New York, executed a search warrant at an apartment and arrested seven individuals who were allegedly up to no good. The Chautauqua County Sheriff’s Office, along with the Jamestown Police Department and even the SWAT team, raided the location, only to find a shocking amount of fentanyl, crack cocaine, and drug paraphernalia.During the raid, investigators seized around 32.5 grams of fentanyl, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,373 in cashâdefinitely not pocket change! The suspects ranged in age from 26 to 61 and included names like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple drug possession charges.Interestingly, among the arrested were individuals with outstanding warrants, which adds yet another layer to this already tangled web of drug-related offenses. Itâs a stark reminder that sometimes, what happens behind closed doors isnât as harmless as it seems. Letâs hope this bust serves as a wake-up call for those involved in the local narcotics trade, but it also makes you wonderâhow many more like this are happening in towns across the country?</t>
+          <t>Putin Furthers Civil Society Facade as Tool of Control - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -554,10 +579,70 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/22tofx85</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Mar. 20, 2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Police able to bring Emerson's reported truck out of lake... no word on his situation...The search resumed this morning for the missing Lakewood man... whose pick-up truck was found submerged in Chautauqua Lake earlier this week.  We have seen on-line "chatter" that the truck has been brought out of the lake.  However... that has NOT been confirmed.  We have calls into Chautauqua County Sheriff Jim Quattrone, but, have not heard back  Earlier today, Quattrone said his department's Dive Team had been joined by others from Erie and Niagara Counties... and, New York State Police at the scene.  Divers went back into the water near Bemus Point this morning to attach floation devices to bring the truck to the surface.  Quattrone says murky water... and, the fact the truck is in a few feet of mud and muck at the bottom... have hampered efforts.  Police are still trying to locate 64 year-old Daniel "Scott" Emerson... who was last seen on Mar. 3. Fire heavily damages first-floor of multiple-family dwelling in Jamestown...Flames have heavily-damaged the first floor of a three-story, multi-family home on Jamestown's southside.   City Fire Captain Dan Balling says firefighters were called to the scene at 517 Newland Ave. shortly after 1 p.m., and, found heavy smoke, and fire on the first floor.  Balling credited crews with making a quick stop on the flames... and, confining the blaze to the first floor.  He says an off-duty shift was called in... and, the fire was knocked down in less than 30 minutes.  Balling says there was heat damage to the second and third-floors.  The house was occupied... but, everyone got out safely.  Two firefighters suffered minor injuries.  The cause is under investigation.City man arrested for allegedly injuring and holding a woman against her will...A man from Jamestown faces contempt and other charges after allegedly hurting and holding a woman against her will at an eastside home.  In addition... city police accuse 26 year-old Angel Ramos-Gonzalez of holding the woman so long that officers found three children living in "deplorable conditions."  Jamestown police were called to the scene for a domestic dispute just after 8 a.m. Thursday.  Officers had been told that Ramos-Gonzalez had violated an order of protection... and, on arrival... found him inside a bedroom closet where he was taken into custody.  In addition to holding the woman against her will... Ramos-Gonzalez is also accused of biting the woman, causing minor injuries.  He's charged with two counts of aggravated criminal contempt... unlawful imprisonment... third-degree assault... and, three counts of endangering the welfare of a child.  He was jailed pending arraignment.Borrello calls State Senate "One-House" Budget a "Train Wreck..."The process to craft a final, 2026-27 state budget is continuing now that both the State Senate and Assembly have presented their "one-house" spending plans.  Both budgets call for additional spending compared to Governor Kathy Hochul's, more than $260-billion proposal.  The Senate's one-house budget amounts to just under $270-billion... and, is about $7.1-billion more than Hochul's budget.  State Senator George Borrello calls it a "fiscal train wreck" with residents suffered under higher utility bills... and, "nothing was offered in relief."  Borrello says the Senate Democrats' "wish list" includes $5.6 billion in higher taxes.  He says it also contains no changes to the Climate Act... and, a rejection of Hochul's proposal to crack down on car insurance fraud and lawsuit abuse.  The Sunset Bay Republican believes what's positive in the budget is "far outshadowed" by the negative in terms of "waste, fraud and abuse."  He adds there are also too many gimmicks in the budget that really aren't enough to provide relief.  A final state budget is due by Apr. 1.County DMV urges residents about possible "Double Charge" issue with debit and credit card usage at DMV...Some New York State Department of Motor Vehicles offices are reporting seeing some customers getting "double-charged" for services using debit or credit cards for a single transaction.  In a press release this morning.. the Chautauqua County DMV is now urging their customers to use either cash or checks right now.  Officials say it's not happening "with every debit or credit card transaction, the problem has persisted since the state DMV went live with the DRIVES software update in February.  Unfortunately... local DMV offices are not authorized to issue refunds directly, and the state DMV is taking 3-to-5 business days to process refunds.  County Clerk Greg Carlson says they -- and other local DMVs are actively communicatin the issue to the state since the DRIVES rollout last month... but, they are still occuring.  Carlson says the county's three DMV offices will continue to process debit and credit card transactions, but encourages customers to use cash or check when completing in-person transactions until the state resolves the issue.Man from Ashville arrested for DWI after single-car accident in the town of Chautauqua...A man from Ashville faces a drunk driving charge following a single-car crash in the town of Chautauqua this past Wednesday night.  Sheriff's officers say they were called to the scene on Route 394 -- at Moore Road -- shortly before Midnight to investigate.  Deputies say they found that 37 year-old Phillip Grobe was driving while intoxicated at the time of the accident.  Grobe was arrested for DWI, Driving with a blood alcohol content of .08 or more... moved from lane unsafely... speed not reasonable and prudent... and, unreasonable speed with special hazards.  He was issued appearance tickets for Chautauqua Town Court at a later date.  No injuries were reported in the accident.     </t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908944/wjtn-news-headlines-for-fri-mar-20-2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>...p;Deputies say they found that 37 year-old Phillip Grobe was driving while **intoxicated** at the time of the accident.  Grobe was arrested for DWI, Driving wit...</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jamestown Drug Raid: Seven Arrested and Major Fentanyl Seized</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>In a major narcotics bust on March 17, 2026, authorities in Jamestown, New York, executed a search warrant at an apartment and arrested seven individuals who were allegedly up to no good. The Chautauqua County Sheriff’s Office, along with the Jamestown Police Department and even the SWAT team, raided the location, only to find a shocking amount of fentanyl, crack cocaine, and drug paraphernalia.During the raid, investigators seized around 32.5 grams of fentanyl, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,373 in cashâdefinitely not pocket change! The suspects ranged in age from 26 to 61 and included names like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple drug possession charges.Interestingly, among the arrested were individuals with outstanding warrants, which adds yet another layer to this already tangled web of drug-related offenses. Itâs a stark reminder that sometimes, what happens behind closed doors isnât as harmless as it seems. Letâs hope this bust serves as a wake-up call for those involved in the local narcotics trade, but it also makes you wonderâhow many more like this are happening in towns across the country?</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908851/jamestown-drug-raid-seven-arrested-and-major-fentanyl-seized</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...even the SWAT team, raided the location, only to find a shocking amount of **fentanyl**, crack cocaine, and drug paraphernalia.During the raid, investigators seiz...
 ...g paraphernalia.During the raid, investigators seized around 32.5 grams of **fentanyl**, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,3...
@@ -566,49 +651,9 @@
 ...ding warrants, which adds yet another layer to this already tangled web of **drug**-related offenses. Itâs a stark reminder that sometimes, ...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2cbvhcbl</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/26xalbhz</t>
         </is>
       </c>
     </row>
@@ -620,7 +665,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
+          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
         </is>
       </c>
       <c r="D11" s="2">
@@ -628,24 +673,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22rgnb4x</t>
+          <t>https://tinyurl.com/2cbvhcbl</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 18, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Quattrone says Sheriff's Dive Team finds Emerson's truck in Chautauqua Lake between Bemus and Greenhurst...The pick-up truck associated with a missing Lakewood man has been found submerged in Chautauqua Lake near the town of Ellery.  However... weather conditions have prevented Sheriff's Department Dive Team members from locating 64 year-old Daniel "Scott" Emerson.  Emerson was last seen on Mar. 3... but, Sheriff Jim Quattrone says his department received some tips and video from a location between Greenhurst and Bemus Point.  Quattrone says they received the video Monday morning... and, quickly got the Sheriff's marine boat and sonar out to that area and found the vehicle.  However... that was the day the temperature plummeted during the afternoon... and, divers has issues with air tanks freezing once they got out of the water.  With the weather still below freezing... Quattrone says the dive team will head back out Thursday.  He says they were able to find the top of the truck... which was at least partially submerged in mud and other debris.  Late last week... Lakewood-Busti Police urged residents and businesses located along the Chautauqua Lake shoreline for any help regarding Emerson's whereabouts.  Police say he was believed to be driving his maroon-colored F-150 that was last seen on Fairmount and Lakeview Avenues in the village around 12:30 a.m. the day he went missing.  If you have any information... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and drug-possession charges...A man from Jamestown has been arrested on multiple drug possession charges following a raid on a southside home early Tuesday afternoon.  Sheriff's officers say their narcotics investigators... along with those from Jamestown police... executed a search warrant on the upper apartment at 313 Prather Ave. shortly after Noon.  The suspect... 26 year-old Devonte Green -- who had a State Parole warrant for his arrest -- was seen leaving the residence in a vehicle just prior to the raid.  Jamestown police tried to conduct a vehicle stop... but, Green continued for a short distance in the car before he was arrested following a brief foot chase.  Deputies say their search of the home, Green and his vehicle led to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  Green was held pending arraignment on charges including: third-and-seventh-degree criminal possession of a controlled substance... and, resisting arrest.Schmidt announces indictment against Westfield man who allegedly shot village woman, in front of children...A Westfield man who allegedly shot a woman... then led police on a vehicle pursuit earlier this month, faces several charges related to both incidents.  Chautauqua County District Attorney Jason Schmidt says a grand jury has indicted 52-year-old Jahmaul Johnson on eight counts, including second-degree attempted murder.  Schmidt says that top charge stems from a shooting that occurred on Route 20 in the village during the evening of Mar. 7... he says Judge Stephen Cass presided over the matter, and a "not guilty" plea was entered for the defendant.  After the shooting... Johnson fled the scene, leading to a pursuit that ended when he crashed his getaway vehicle into a ditch.  He was taken into custody in the Town of Pomfret a short time later that evening.  Schmidt says Johnson also faces three violent felonies related to a handgun and magazine he allegedly possessed... along with four counts of endangering the welfare of a child.  Schmidt says Johnson pleaded not guilty at his arraignment Tuesday morning before being remanded to the Chautauqua County Jail on $1-million cash bail... $2-million property bond.  He says a disovery conference will be held on Apr. 13.  If convicted, Johnson faces up to 25 years in prison on the attempted murder charge and up to 15 years on the weapon counts, adding that there's a possibility of those sentences running consecutively.  The victim was taken to an Erie, Pa. hospital, and is recovering from her injuries.Site work beginning for new Brook's Hospital in Fredonia...Initial site work for the new Northern Chautauqua Hospital project in Fredonia gets underway this week.  The announcement late Monday by Kaleida Health comes in the wake of its January filing in conjunction with Brooks-TLC of a building permit with the village of Fredonia for the hospital's construction.  Turner Construction Company subcontracted with Fredonia-based S. St. George General Contracting to perform the preliminary site work, including setting up temporary staging areas, fencing the property, and grading the site.  Initial work will depend on the weather... and the need for the land to drain and dry out.  The $223.8 million project is planned as a one-story, 133,000 facility at 412 East Main St.  It will replace the existing Brooks Hospital in the city of Dunkirk.Molitor part of Assembly-Senate Budget Conference Committee to deal with Human Services...The deadline for a new state budget is fast approaching... and, work is continuing in the New York State Assembly and Senate on a final spending plan.  With that... more legislative hearings involving conference committees are underway.  Local State Assemblyman Andrew Molitor is an alternate for the committee on Human Services... which means he'll be able to ask questions and offer input about Medicaid and other "safety net" programs.  The Assembly's $272-billion, "one-house" budget includes a 1% income tax cut for low and middle income earners... but, Molitor says it's not enough.  Ideally, he says he would like to see all income taxes eliminated.  Molitor says he remains hopeful there will be a budget acted on by the Apr. 1 deadline. </t>
+          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
         </is>
       </c>
       <c r="D12" s="2">
@@ -653,10 +693,75 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/26xalbhz</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/22rgnb4x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Complete coverage: The saga of the state-funded drug manufacturing plant in Dunkirk - Buffalo News</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/27bqx4hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Wed., Mar. 18, 2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quattrone says Sheriff's Dive Team finds Emerson's truck in Chautauqua Lake between Bemus and Greenhurst...The pick-up truck associated with a missing Lakewood man has been found submerged in Chautauqua Lake near the town of Ellery.  However... weather conditions have prevented Sheriff's Department Dive Team members from locating 64 year-old Daniel "Scott" Emerson.  Emerson was last seen on Mar. 3... but, Sheriff Jim Quattrone says his department received some tips and video from a location between Greenhurst and Bemus Point.  Quattrone says they received the video Monday morning... and, quickly got the Sheriff's marine boat and sonar out to that area and found the vehicle.  However... that was the day the temperature plummeted during the afternoon... and, divers has issues with air tanks freezing once they got out of the water.  With the weather still below freezing... Quattrone says the dive team will head back out Thursday.  He says they were able to find the top of the truck... which was at least partially submerged in mud and other debris.  Late last week... Lakewood-Busti Police urged residents and businesses located along the Chautauqua Lake shoreline for any help regarding Emerson's whereabouts.  Police say he was believed to be driving his maroon-colored F-150 that was last seen on Fairmount and Lakeview Avenues in the village around 12:30 a.m. the day he went missing.  If you have any information... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and drug-possession charges...A man from Jamestown has been arrested on multiple drug possession charges following a raid on a southside home early Tuesday afternoon.  Sheriff's officers say their narcotics investigators... along with those from Jamestown police... executed a search warrant on the upper apartment at 313 Prather Ave. shortly after Noon.  The suspect... 26 year-old Devonte Green -- who had a State Parole warrant for his arrest -- was seen leaving the residence in a vehicle just prior to the raid.  Jamestown police tried to conduct a vehicle stop... but, Green continued for a short distance in the car before he was arrested following a brief foot chase.  Deputies say their search of the home, Green and his vehicle led to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  Green was held pending arraignment on charges including: third-and-seventh-degree criminal possession of a controlled substance... and, resisting arrest.Schmidt announces indictment against Westfield man who allegedly shot village woman, in front of children...A Westfield man who allegedly shot a woman... then led police on a vehicle pursuit earlier this month, faces several charges related to both incidents.  Chautauqua County District Attorney Jason Schmidt says a grand jury has indicted 52-year-old Jahmaul Johnson on eight counts, including second-degree attempted murder.  Schmidt says that top charge stems from a shooting that occurred on Route 20 in the village during the evening of Mar. 7... he says Judge Stephen Cass presided over the matter, and a "not guilty" plea was entered for the defendant.  After the shooting... Johnson fled the scene, leading to a pursuit that ended when he crashed his getaway vehicle into a ditch.  He was taken into custody in the Town of Pomfret a short time later that evening.  Schmidt says Johnson also faces three violent felonies related to a handgun and magazine he allegedly possessed... along with four counts of endangering the welfare of a child.  Schmidt says Johnson pleaded not guilty at his arraignment Tuesday morning before being remanded to the Chautauqua County Jail on $1-million cash bail... $2-million property bond.  He says a disovery conference will be held on Apr. 13.  If convicted, Johnson faces up to 25 years in prison on the attempted murder charge and up to 15 years on the weapon counts, adding that there's a possibility of those sentences running consecutively.  The victim was taken to an Erie, Pa. hospital, and is recovering from her injuries.Site work beginning for new Brook's Hospital in Fredonia...Initial site work for the new Northern Chautauqua Hospital project in Fredonia gets underway this week.  The announcement late Monday by Kaleida Health comes in the wake of its January filing in conjunction with Brooks-TLC of a building permit with the village of Fredonia for the hospital's construction.  Turner Construction Company subcontracted with Fredonia-based S. St. George General Contracting to perform the preliminary site work, including setting up temporary staging areas, fencing the property, and grading the site.  Initial work will depend on the weather... and the need for the land to drain and dry out.  The $223.8 million project is planned as a one-story, 133,000 facility at 412 East Main St.  It will replace the existing Brooks Hospital in the city of Dunkirk.Molitor part of Assembly-Senate Budget Conference Committee to deal with Human Services...The deadline for a new state budget is fast approaching... and, work is continuing in the New York State Assembly and Senate on a final spending plan.  With that... more legislative hearings involving conference committees are underway.  Local State Assemblyman Andrew Molitor is an alternate for the committee on Human Services... which means he'll be able to ask questions and offer input about Medicaid and other "safety net" programs.  The Assembly's $272-billion, "one-house" budget includes a 1% income tax cut for low and middle income earners... but, Molitor says it's not enough.  Ideally, he says he would like to see all income taxes eliminated.  Molitor says he remains hopeful there will be a budget acted on by the Apr. 1 deadline. </t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908600/wjtn-news-headlines-for-wed-mar-18-2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...arch of the home, Green and his vehicle led to the seizure of 2.3 grams of **fentanyl**... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  G...
 ...ed to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin **mushrooms**... along with $131 cash.  Green was held pending arraignment on charg...
@@ -665,218 +770,238 @@
 ...nt on charges including: third-and-seventh-degree criminal possession of a **controlled** substance... and, resisting arrest.Schmidt announces indictment against We...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>(WNY News Now) – ASHFORD, N.Y. — Two Cattaraugus County men were arrested on felony drug charges following a traffic stop and investigation that led to the discovery of suspected cocaine, according to the Cattaraugus County Sheriff’s Office. Authorities report that the incident occurred on March 18, 2026, at approximately 7:47 p.m. in the Town […]The post Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D13" s="2">
+      <c r="D16" s="2">
         <v>46100</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/traffic-stop-in-ashford-leads-to-cocaine-seizure-two-arrested-on-felony-drug-charges/</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...wo Cattaraugus County men were arrested on felony **drug** charges following a traffic stop and investigatio...
 ... Leads to Cocaine Seizure, Two Arrested on Felony **Drug** Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>(WNY News Now) – DUNKIRK, N.Y. — A narcotics investigation in the City of Dunkirk led to the seizure of fentanyl, crack cocaine, and methamphetamine, along with the arrest of a 45-year-old man on multiple felony drug charges. Authorities executed a search warrant at a lower apartment at 209 Lincoln Avenue on March 18, 2026, […]The post Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D14" s="2">
+      <c r="D17" s="2">
         <v>46100</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/dunkirk-man-arrested-after-multi-agency-narcotics-raid-on-lincoln-avenue/</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...ed to the seizure of fentanyl, crack cocaine, and **methamphetamine**, along with the arrest of a 45-year-old man on mu...
 ...tion in the City of Dunkirk led to the seizure of **fentanyl**, crack cocaine, and methamphetamine, along with t...
 ...he arrest of a 45-year-old man on multiple felony **drug** charges. Authorities executed a search warrant at...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, N.Y. — A multi-agency narcotics investigation led to seven arrests Tuesday afternoon after authorities executed a search warrant at a Jamestown apartment, seizing fentanyl, crack cocaine, and other drug-related items. According to investigators, the search warrant was carried out around 3:39 p.m. on March 17, 2026, at 28 Euclid Ave., […]The post Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D15" s="2">
+      <c r="D18" s="2">
         <v>46100</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/seven-arrested-after-jamestown-narcotics-raid-fentanyl-and-cocaine-seized/</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>... search warrant at a Jamestown apartment, seizing **fentanyl**, crack cocaine, and other drug-related items. Acc...
 ...st Seven Arrested After Jamestown Narcotics Raid, **Fentanyl** and Cocaine Seized appeared first on WNY News Now...
 ...tment, seizing fentanyl, crack cocaine, and other **drug**-related items. According to investigators, the se...</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, NY — A Niagara Falls man was taken into custody early Thursday after Jamestown police allegedly found him driving while impaired by drugs during a traffic stop on the city’s east side. According to the Jamestown Police Department, the incident occurred at approximately 1:14 a.m. on March 19, 2026. Officers […]The post Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D16" s="2">
+      <c r="D19" s="2">
         <v>46100</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/jamestown-man-charged-with-drug-impaired-driving-following-early-morning-traffic-stop/</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>.... Officers […]The post Jamestown Man Charged With **Drug**-Impaired Driving Following Early Morning Traffic ...</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, N.Y. — A Jamestown man was taken into custody Tuesday after a narcotics investigation led to the execution of a search warrant and the seizure of controlled substances, according to local authorities. Narcotics investigators from the Chautauqua County Sheriff’s Office and Jamestown Police Department executed a search warrant at an […]The post Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D17" s="2">
+      <c r="D20" s="2">
         <v>46100</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/jamestown-man-arrested-after-narcotics-search-warrant-yields-fentanyl-and-psilocybin/</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>...an Arrested After Narcotics Search Warrant Yields **Fentanyl** and Psilocybin appeared first on WNY News Now.
 ... execution of a search warrant and the seizure of **controlled** substances, according to local authorities. Narco...</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
+        </is>
+      </c>
+      <c r="D21" s="2">
+        <v>46099</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2y89u94m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>WJTN News Headlines for St. Patrick's Day, Tues., Mar. 17, 2026</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>11 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Jamestown-area receives between 4 and 8 inches of snow in St. Patrick's Eve and Day snowstorm...Some parts of Chautauqua County received several inches of snow during the storm that accompanied a cold front last night through this morning.  The National Weather Service in Buffalo reports 8-and-a-half inches of the white stuff in Cassadaga... and about 6 in the Mayville area.  Here in the Jamestown-area... we got about 4 inches.  That's right about where Forecaster Steve Welch with the National Weather Service in Buffalo said we would be late Monday... with 2 to 4 inches generally in the Western New York area.  He says there may be a couple more inches falling during the day today.  We remain under a Winter Weather Advisory until 8 o'clock tonight.  Jamestown street closed about five-hours Sunday night after high winds blow roof off vacant building downtown...The Jamestown Department of Development was able to safely get the roof off a vacant building on East Second Street late Sunday night.  Officials say the roof was partially torn off shortly after 5 p.m. during the wind storm.  City police closed off East Second from Prendergast to Foote Avenues.  A front-loader was brought in to remove the roof... and, the street reopened shortly before 10:30 p.m. Three arrested during Forest Park drug bust in Jamestown late Monday morning...        Three people from Jamestown have been arrested following a drug raid on a home on the city's southside late Monday morning.  Sheriff's officers say their Narcotics Investigators along with those from Jamestown... executed a search warrant at 7 Forest Park about 10:45 a.m., and, found 39 year-old Ronaldo Galarza... 19 year-old Ronaldo Galarza, Jr. and 39 year-old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of fentanyl... and, packaging used for the sale and distribution of narcotics.  All three suspects were charged with third and fourth-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  Each suspect was issued appearance tickets for city court... and, the investigation is ongoing with additional arrests expected.  If you have any information about suspicious or narcotics related activity in your area... call the Sheriff's Office Narcotics Investigators Tip line at either 1-800-344-8702 or 664-2420... or the JPD Tip line at 483-8477.JPS begins budget process by reviewing first draft of $120.8-million spending plan...There's no tax increase in the Jamestown Public School's proposed 2026-27 budget proposal... which totals about $120.8-million.  The school board recently got it's first look at the first draft of the spending plan... which Assistant Superintendent for Finance and Operations Brittany Spry says increases spending by about $5.2-million... which is a 4.5% increase.  Spry says the biggest increases come in programming with some new positions to be filled.  She says they include a new assistant principal and secretary for the district's Innovation Center at the former Rodgers School... and six middle school teachers.  Much of the money to cover the increased costs is coming from an increase in state school aid.  Once final state aid figures are known... the district will move to finalize a spending plan for voters to act on in May.  Thomas pleads guilty in Mendoza drug and sex trafficking case...A Jamestown man has pleaded guilty in federal court to drug and sex trafficking conspiracy charges in connection with a case against a local drug kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-old Kelvin Thomas entered the plea last Friday before U.S. District Court Judge John Sinatra, Jr. to conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl, and conspiracy to commit sex trafficking.  Prosecutors say between October and December 2022, Thomas conspired with Zaid Mendoza and Cora Waddington to conduct a sex trafficking operation involving two individuals with drug addictions.  As part of the conspiracy... they say Thomas, Mendoza, and Waddington, provided shelter to the victims at a West Main Street home in Falconer... and, provided them with food, clothing, and daily quantities of heroin/fentanyl in exchange for them doing commercial sex acts for money, with the proceeds going to Mendoza.  Thomas assisted the operation by securing and communicating with commercial sex buyers, posting online advertisements with photographs of the two victims on Skipthegames.com.  He also transported the two victims to calls away from the residence, and provided protection and assistance to sex trafficking victims while they were on those "out" calls.  Thomas was paid in drugs by Mendoza or Waddington.  The charges carry a mandatory minimum penalty of five years and a maximum of life.City woman arrested for allegedly shoplifting more than $1,000 worth of items from Lakewood Wal-Mart SuperCenter...A woman from Jamestown has been arrested for allegedly stealing more than $1,000 worth of merchandise last weekend from the Lakewood Wal-Mart SuperCenter.  Lakewood-Busti Police say they were called to the 350 Fairmount Ave. location shortly after 7 p.m. last Sunday night.  Officerss say 47 year-old Kathryn Fisher allegedly passed all points of sale with $1,071 worth of items without paying for them.  Fisher was arrested for fourth-degree grand larceny... and, was released with an appearance ticket for Busti Town Court.  </t>
         </is>
       </c>
-      <c r="D18" s="2">
+      <c r="D22" s="2">
         <v>46098</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908342/wjtn-news-headlines-for-st-patrick-s-day-tues-mar-17-2026</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>...old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of **fentanyl**... and, packaging used for the sale and distribution of narcotics.  A...
 ... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl**, and conspiracy to commit sex trafficking.  Prosecutors say between O...
@@ -891,46 +1016,9 @@
 ...uspects were charged with third and fourth-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — Three Jamestown residents are facing felony drug charges after authorities executed a search warrant and seized fentanyl at a Forest Park residence. Investigators with the Jamestown Police Department and the Chautauqua County Sheriff’s Office executed a search warrant at 7 Forest Park at approximately 10:45 a.m. on March […]The post Three Charged After Jamestown Search Warrant Nets Fentanyl Seizure appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D19" s="2">
-        <v>46098</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/17/three-charged-after-jamestown-search-warrant-nets-fentanyl-seizure/</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>... authorities executed a search warrant and seized **fentanyl** at a Forest Park residence. Investigators with th...
-...Three Charged After Jamestown Search Warrant Nets **Fentanyl** Seizure appeared first on WNY News Now.
-....Y. — Three Jamestown residents are facing felony **drug** charges after authorities executed a search warra...</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,7 +401,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
+          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -411,15 +411,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
+          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -436,17 +436,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -454,17 +454,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -489,12 +489,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
+          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
+          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -506,20 +506,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Seven charged after Jamestown raid - observertoday.com</t>
+          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23f2p5o9</t>
+          <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -551,7 +566,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Telegram Outages Spike in Kremlin’s Push for Digital Control - The Jamestown Foundation</t>
+          <t>Seven charged after Jamestown raid - observertoday.com</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -559,7 +574,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2xr4ut6j</t>
+          <t>https://tinyurl.com/23f2p5o9</t>
         </is>
       </c>
     </row>
@@ -586,17 +601,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Mar. 20, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Police able to bring Emerson's reported truck out of lake... no word on his situation...The search resumed this morning for the missing Lakewood man... whose pick-up truck was found submerged in Chautauqua Lake earlier this week.  We have seen on-line "chatter" that the truck has been brought out of the lake.  However... that has NOT been confirmed.  We have calls into Chautauqua County Sheriff Jim Quattrone, but, have not heard back  Earlier today, Quattrone said his department's Dive Team had been joined by others from Erie and Niagara Counties... and, New York State Police at the scene.  Divers went back into the water near Bemus Point this morning to attach floation devices to bring the truck to the surface.  Quattrone says murky water... and, the fact the truck is in a few feet of mud and muck at the bottom... have hampered efforts.  Police are still trying to locate 64 year-old Daniel "Scott" Emerson... who was last seen on Mar. 3. Fire heavily damages first-floor of multiple-family dwelling in Jamestown...Flames have heavily-damaged the first floor of a three-story, multi-family home on Jamestown's southside.   City Fire Captain Dan Balling says firefighters were called to the scene at 517 Newland Ave. shortly after 1 p.m., and, found heavy smoke, and fire on the first floor.  Balling credited crews with making a quick stop on the flames... and, confining the blaze to the first floor.  He says an off-duty shift was called in... and, the fire was knocked down in less than 30 minutes.  Balling says there was heat damage to the second and third-floors.  The house was occupied... but, everyone got out safely.  Two firefighters suffered minor injuries.  The cause is under investigation.City man arrested for allegedly injuring and holding a woman against her will...A man from Jamestown faces contempt and other charges after allegedly hurting and holding a woman against her will at an eastside home.  In addition... city police accuse 26 year-old Angel Ramos-Gonzalez of holding the woman so long that officers found three children living in "deplorable conditions."  Jamestown police were called to the scene for a domestic dispute just after 8 a.m. Thursday.  Officers had been told that Ramos-Gonzalez had violated an order of protection... and, on arrival... found him inside a bedroom closet where he was taken into custody.  In addition to holding the woman against her will... Ramos-Gonzalez is also accused of biting the woman, causing minor injuries.  He's charged with two counts of aggravated criminal contempt... unlawful imprisonment... third-degree assault... and, three counts of endangering the welfare of a child.  He was jailed pending arraignment.Borrello calls State Senate "One-House" Budget a "Train Wreck..."The process to craft a final, 2026-27 state budget is continuing now that both the State Senate and Assembly have presented their "one-house" spending plans.  Both budgets call for additional spending compared to Governor Kathy Hochul's, more than $260-billion proposal.  The Senate's one-house budget amounts to just under $270-billion... and, is about $7.1-billion more than Hochul's budget.  State Senator George Borrello calls it a "fiscal train wreck" with residents suffered under higher utility bills... and, "nothing was offered in relief."  Borrello says the Senate Democrats' "wish list" includes $5.6 billion in higher taxes.  He says it also contains no changes to the Climate Act... and, a rejection of Hochul's proposal to crack down on car insurance fraud and lawsuit abuse.  The Sunset Bay Republican believes what's positive in the budget is "far outshadowed" by the negative in terms of "waste, fraud and abuse."  He adds there are also too many gimmicks in the budget that really aren't enough to provide relief.  A final state budget is due by Apr. 1.County DMV urges residents about possible "Double Charge" issue with debit and credit card usage at DMV...Some New York State Department of Motor Vehicles offices are reporting seeing some customers getting "double-charged" for services using debit or credit cards for a single transaction.  In a press release this morning.. the Chautauqua County DMV is now urging their customers to use either cash or checks right now.  Officials say it's not happening "with every debit or credit card transaction, the problem has persisted since the state DMV went live with the DRIVES software update in February.  Unfortunately... local DMV offices are not authorized to issue refunds directly, and the state DMV is taking 3-to-5 business days to process refunds.  County Clerk Greg Carlson says they -- and other local DMVs are actively communicatin the issue to the state since the DRIVES rollout last month... but, they are still occuring.  Carlson says the county's three DMV offices will continue to process debit and credit card transactions, but encourages customers to use cash or check when completing in-person transactions until the state resolves the issue.Man from Ashville arrested for DWI after single-car accident in the town of Chautauqua...A man from Ashville faces a drunk driving charge following a single-car crash in the town of Chautauqua this past Wednesday night.  Sheriff's officers say they were called to the scene on Route 394 -- at Moore Road -- shortly before Midnight to investigate.  Deputies say they found that 37 year-old Phillip Grobe was driving while intoxicated at the time of the accident.  Grobe was arrested for DWI, Driving with a blood alcohol content of .08 or more... moved from lane unsafely... speed not reasonable and prudent... and, unreasonable speed with special hazards.  He was issued appearance tickets for Chautauqua Town Court at a later date.  No injuries were reported in the accident.     </t>
+          <t>Telegram Outages Spike in Kremlin’s Push for Digital Control - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D9" s="2">
@@ -604,34 +614,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908944/wjtn-news-headlines-for-fri-mar-20-2026</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>...p;Deputies say they found that 37 year-old Phillip Grobe was driving while **intoxicated** at the time of the accident.  Grobe was arrested for DWI, Driving wit...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/2xr4ut6j</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jamestown Drug Raid: Seven Arrested and Major Fentanyl Seized</t>
+          <t>WJTN News Headlines for Fri., Mar. 20, 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5 keyword references (WJTN)</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>In a major narcotics bust on March 17, 2026, authorities in Jamestown, New York, executed a search warrant at an apartment and arrested seven individuals who were allegedly up to no good. The Chautauqua County Sheriff’s Office, along with the Jamestown Police Department and even the SWAT team, raided the location, only to find a shocking amount of fentanyl, crack cocaine, and drug paraphernalia.During the raid, investigators seized around 32.5 grams of fentanyl, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,373 in cashâdefinitely not pocket change! The suspects ranged in age from 26 to 61 and included names like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple drug possession charges.Interestingly, among the arrested were individuals with outstanding warrants, which adds yet another layer to this already tangled web of drug-related offenses. Itâs a stark reminder that sometimes, what happens behind closed doors isnât as harmless as it seems. Letâs hope this bust serves as a wake-up call for those involved in the local narcotics trade, but it also makes you wonderâhow many more like this are happening in towns across the country?</t>
+          <t>Police able to bring Emerson's reported truck out of lake... no word on his situation...The search resumed this morning for the missing Lakewood man... whose pick-up truck was found submerged in Chautauqua Lake earlier this week.  We have seen on-line "chatter" that the truck has been brought out of the lake.  However... that has NOT been confirmed.  We have calls into Chautauqua County Sheriff Jim Quattrone, but, have not heard back  Earlier today, Quattrone said his department's Dive Team had been joined by others from Erie and Niagara Counties... and, New York State Police at the scene.  Divers went back into the water near Bemus Point this morning to attach floation devices to bring the truck to the surface.  Quattrone says murky water... and, the fact the truck is in a few feet of mud and muck at the bottom... have hampered efforts.  Police are still trying to locate 64 year-old Daniel "Scott" Emerson... who was last seen on Mar. 3. Fire heavily damages first-floor of multiple-family dwelling in Jamestown...Flames have heavily-damaged the first floor of a three-story, multi-family home on Jamestown's southside.   City Fire Captain Dan Balling says firefighters were called to the scene at 517 Newland Ave. shortly after 1 p.m., and, found heavy smoke, and fire on the first floor.  Balling credited crews with making a quick stop on the flames... and, confining the blaze to the first floor.  He says an off-duty shift was called in... and, the fire was knocked down in less than 30 minutes.  Balling says there was heat damage to the second and third-floors.  The house was occupied... but, everyone got out safely.  Two firefighters suffered minor injuries.  The cause is under investigation.City man arrested for allegedly injuring and holding a woman against her will...A man from Jamestown faces contempt and other charges after allegedly hurting and holding a woman against her will at an eastside home.  In addition... city police accuse 26 year-old Angel Ramos-Gonzalez of holding the woman so long that officers found three children living in "deplorable conditions."  Jamestown police were called to the scene for a domestic dispute just after 8 a.m. Thursday.  Officers had been told that Ramos-Gonzalez had violated an order of protection... and, on arrival... found him inside a bedroom closet where he was taken into custody.  In addition to holding the woman against her will... Ramos-Gonzalez is also accused of biting the woman, causing minor injuries.  He's charged with two counts of aggravated criminal contempt... unlawful imprisonment... third-degree assault... and, three counts of endangering the welfare of a child.  He was jailed pending arraignment.Borrello calls State Senate "One-House" Budget a "Train Wreck..."The process to craft a final, 2026-27 state budget is continuing now that both the State Senate and Assembly have presented their "one-house" spending plans.  Both budgets call for additional spending compared to Governor Kathy Hochul's, more than $260-billion proposal.  The Senate's one-house budget amounts to just under $270-billion... and, is about $7.1-billion more than Hochul's budget.  State Senator George Borrello calls it a "fiscal train wreck" with residents suffered under higher utility bills... and, "nothing was offered in relief."  Borrello says the Senate Democrats' "wish list" includes $5.6 billion in higher taxes.  He says it also contains no changes to the Climate Act... and, a rejection of Hochul's proposal to crack down on car insurance fraud and lawsuit abuse.  The Sunset Bay Republican believes what's positive in the budget is "far outshadowed" by the negative in terms of "waste, fraud and abuse."  He adds there are also too many gimmicks in the budget that really aren't enough to provide relief.  A final state budget is due by Apr. 1.County DMV urges residents about possible "Double Charge" issue with debit and credit card usage at DMV...Some New York State Department of Motor Vehicles offices are reporting seeing some customers getting "double-charged" for services using debit or credit cards for a single transaction.  In a press release this morning.. the Chautauqua County DMV is now urging their customers to use either cash or checks right now.  Officials say it's not happening "with every debit or credit card transaction, the problem has persisted since the state DMV went live with the DRIVES software update in February.  Unfortunately... local DMV offices are not authorized to issue refunds directly, and the state DMV is taking 3-to-5 business days to process refunds.  County Clerk Greg Carlson says they -- and other local DMVs are actively communicatin the issue to the state since the DRIVES rollout last month... but, they are still occuring.  Carlson says the county's three DMV offices will continue to process debit and credit card transactions, but encourages customers to use cash or check when completing in-person transactions until the state resolves the issue.Man from Ashville arrested for DWI after single-car accident in the town of Chautauqua...A man from Ashville faces a drunk driving charge following a single-car crash in the town of Chautauqua this past Wednesday night.  Sheriff's officers say they were called to the scene on Route 394 -- at Moore Road -- shortly before Midnight to investigate.  Deputies say they found that 37 year-old Phillip Grobe was driving while intoxicated at the time of the accident.  Grobe was arrested for DWI, Driving with a blood alcohol content of .08 or more... moved from lane unsafely... speed not reasonable and prudent... and, unreasonable speed with special hazards.  He was issued appearance tickets for Chautauqua Town Court at a later date.  No injuries were reported in the accident.     </t>
         </is>
       </c>
       <c r="D10" s="2">
@@ -639,10 +639,45 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908944/wjtn-news-headlines-for-fri-mar-20-2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>...p;Deputies say they found that 37 year-old Phillip Grobe was driving while **intoxicated** at the time of the accident.  Grobe was arrested for DWI, Driving wit...</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jamestown Drug Raid: Seven Arrested and Major Fentanyl Seized</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>In a major narcotics bust on March 17, 2026, authorities in Jamestown, New York, executed a search warrant at an apartment and arrested seven individuals who were allegedly up to no good. The Chautauqua County Sheriff’s Office, along with the Jamestown Police Department and even the SWAT team, raided the location, only to find a shocking amount of fentanyl, crack cocaine, and drug paraphernalia.During the raid, investigators seized around 32.5 grams of fentanyl, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,373 in cashâdefinitely not pocket change! The suspects ranged in age from 26 to 61 and included names like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple drug possession charges.Interestingly, among the arrested were individuals with outstanding warrants, which adds yet another layer to this already tangled web of drug-related offenses. Itâs a stark reminder that sometimes, what happens behind closed doors isnât as harmless as it seems. Letâs hope this bust serves as a wake-up call for those involved in the local narcotics trade, but it also makes you wonderâhow many more like this are happening in towns across the country?</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46101</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908851/jamestown-drug-raid-seven-arrested-and-major-fentanyl-seized</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...even the SWAT team, raided the location, only to find a shocking amount of **fentanyl**, crack cocaine, and drug paraphernalia.During the raid, investigators seiz...
 ...g paraphernalia.During the raid, investigators seized around 32.5 grams of **fentanyl**, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,3...
@@ -651,29 +686,9 @@
 ...ding warrants, which adds yet another layer to this already tangled web of **drug**-related offenses. Itâs a stark reminder that sometimes, ...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2cbvhcbl</t>
         </is>
       </c>
     </row>
@@ -685,7 +700,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
+          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
         </is>
       </c>
       <c r="D12" s="2">
@@ -693,7 +708,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/26xalbhz</t>
+          <t>https://tinyurl.com/2cbvhcbl</t>
         </is>
       </c>
     </row>
@@ -924,101 +939,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Jamestown man was taken into custody Tuesday after a narcotics investigation led to the execution of a search warrant and the seizure of controlled substances, according to local authorities. Narcotics investigators from the Chautauqua County Sheriff’s Office and Jamestown Police Department executed a search warrant at an […]The post Jamestown Man Arrested After Narcotics Search Warrant Yields Fentanyl and Psilocybin appeared first on WNY News Now.</t>
+          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
         </is>
       </c>
       <c r="D20" s="2">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/19/jamestown-man-arrested-after-narcotics-search-warrant-yields-fentanyl-and-psilocybin/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>...an Arrested After Narcotics Search Warrant Yields **Fentanyl** and Psilocybin appeared first on WNY News Now.
-... execution of a search warrant and the seizure of **controlled** substances, according to local authorities. Narco...</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
-        </is>
-      </c>
-      <c r="D21" s="2">
-        <v>46099</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2y89u94m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for St. Patrick's Day, Tues., Mar. 17, 2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>11 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Jamestown-area receives between 4 and 8 inches of snow in St. Patrick's Eve and Day snowstorm...Some parts of Chautauqua County received several inches of snow during the storm that accompanied a cold front last night through this morning.  The National Weather Service in Buffalo reports 8-and-a-half inches of the white stuff in Cassadaga... and about 6 in the Mayville area.  Here in the Jamestown-area... we got about 4 inches.  That's right about where Forecaster Steve Welch with the National Weather Service in Buffalo said we would be late Monday... with 2 to 4 inches generally in the Western New York area.  He says there may be a couple more inches falling during the day today.  We remain under a Winter Weather Advisory until 8 o'clock tonight.  Jamestown street closed about five-hours Sunday night after high winds blow roof off vacant building downtown...The Jamestown Department of Development was able to safely get the roof off a vacant building on East Second Street late Sunday night.  Officials say the roof was partially torn off shortly after 5 p.m. during the wind storm.  City police closed off East Second from Prendergast to Foote Avenues.  A front-loader was brought in to remove the roof... and, the street reopened shortly before 10:30 p.m. Three arrested during Forest Park drug bust in Jamestown late Monday morning...        Three people from Jamestown have been arrested following a drug raid on a home on the city's southside late Monday morning.  Sheriff's officers say their Narcotics Investigators along with those from Jamestown... executed a search warrant at 7 Forest Park about 10:45 a.m., and, found 39 year-old Ronaldo Galarza... 19 year-old Ronaldo Galarza, Jr. and 39 year-old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of fentanyl... and, packaging used for the sale and distribution of narcotics.  All three suspects were charged with third and fourth-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  Each suspect was issued appearance tickets for city court... and, the investigation is ongoing with additional arrests expected.  If you have any information about suspicious or narcotics related activity in your area... call the Sheriff's Office Narcotics Investigators Tip line at either 1-800-344-8702 or 664-2420... or the JPD Tip line at 483-8477.JPS begins budget process by reviewing first draft of $120.8-million spending plan...There's no tax increase in the Jamestown Public School's proposed 2026-27 budget proposal... which totals about $120.8-million.  The school board recently got it's first look at the first draft of the spending plan... which Assistant Superintendent for Finance and Operations Brittany Spry says increases spending by about $5.2-million... which is a 4.5% increase.  Spry says the biggest increases come in programming with some new positions to be filled.  She says they include a new assistant principal and secretary for the district's Innovation Center at the former Rodgers School... and six middle school teachers.  Much of the money to cover the increased costs is coming from an increase in state school aid.  Once final state aid figures are known... the district will move to finalize a spending plan for voters to act on in May.  Thomas pleads guilty in Mendoza drug and sex trafficking case...A Jamestown man has pleaded guilty in federal court to drug and sex trafficking conspiracy charges in connection with a case against a local drug kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-old Kelvin Thomas entered the plea last Friday before U.S. District Court Judge John Sinatra, Jr. to conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl, and conspiracy to commit sex trafficking.  Prosecutors say between October and December 2022, Thomas conspired with Zaid Mendoza and Cora Waddington to conduct a sex trafficking operation involving two individuals with drug addictions.  As part of the conspiracy... they say Thomas, Mendoza, and Waddington, provided shelter to the victims at a West Main Street home in Falconer... and, provided them with food, clothing, and daily quantities of heroin/fentanyl in exchange for them doing commercial sex acts for money, with the proceeds going to Mendoza.  Thomas assisted the operation by securing and communicating with commercial sex buyers, posting online advertisements with photographs of the two victims on Skipthegames.com.  He also transported the two victims to calls away from the residence, and provided protection and assistance to sex trafficking victims while they were on those "out" calls.  Thomas was paid in drugs by Mendoza or Waddington.  The charges carry a mandatory minimum penalty of five years and a maximum of life.City woman arrested for allegedly shoplifting more than $1,000 worth of items from Lakewood Wal-Mart SuperCenter...A woman from Jamestown has been arrested for allegedly stealing more than $1,000 worth of merchandise last weekend from the Lakewood Wal-Mart SuperCenter.  Lakewood-Busti Police say they were called to the 350 Fairmount Ave. location shortly after 7 p.m. last Sunday night.  Officerss say 47 year-old Kathryn Fisher allegedly passed all points of sale with $1,071 worth of items without paying for them.  Fisher was arrested for fourth-degree grand larceny... and, was released with an appearance ticket for Busti Town Court.  </t>
-        </is>
-      </c>
-      <c r="D22" s="2">
-        <v>46098</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908342/wjtn-news-headlines-for-st-patrick-s-day-tues-mar-17-2026</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>...old Rashaira Garcia-Figueroa.  Investigators also found 19.3 grams of **fentanyl**... and, packaging used for the sale and distribution of narcotics.  A...
-... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl**, and conspiracy to commit sex trafficking.  Prosecutors say between O...
-...... and, provided them with food, clothing, and daily quantities of heroin/**fentanyl** in exchange for them doing commercial sex acts for money, with the proceed...
-... reopened shortly before 10:30 p.m. Three arrested during Forest Park **drug** bust in Jamestown late Monday morning...        T...
-...sp;   Three people from Jamestown have been arrested following a **drug** raid on a home on the city's southside late Monday morning.  Sheriff'...
-...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia.  Each suspect was issued appearance tickets for city c...
-...ng plan for voters to act on in May.  Thomas pleads guilty in Mendoza **drug** and sex trafficking case...A Jamestown man has pleaded guilty in federal c...
-... trafficking case...A Jamestown man has pleaded guilty in federal court to **drug** and sex trafficking conspiracy charges in connection with a case against a...
-...x trafficking conspiracy charges in connection with a case against a local **drug** kingpin.  U.S. Attorney Michael DiGiacomo has announced that 43 year-...
-...gton to conduct a sex trafficking operation involving two individuals with **drug** addictions.  As part of the conspiracy... they say Thomas, Mendoza, a...
-...uspects were charged with third and fourth-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/28g35pus</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,122 +401,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
+          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - Erie News Now</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/249k877s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
+          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/279l6oks</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
+          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
         </is>
       </c>
       <c r="D5" s="2">
@@ -524,57 +494,87 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
+          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>City man charged after narcotics investigation - observertoday.com</t>
+          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22k76srp</t>
+          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Seven charged after Jamestown raid - observertoday.com</t>
+          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D7" s="2">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23f2p5o9</t>
+          <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
+          <t>City man charged after narcotics investigation - observertoday.com</t>
         </is>
       </c>
       <c r="D13" s="2">
@@ -728,7 +728,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22rgnb4x</t>
+          <t>https://tinyurl.com/278puyft</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Complete coverage: The saga of the state-funded drug manufacturing plant in Dunkirk - Buffalo News</t>
+          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
         </is>
       </c>
       <c r="D14" s="2">
@@ -748,24 +748,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/27bqx4hz</t>
+          <t>https://tinyurl.com/26xalbhz</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Mar. 18, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Quattrone says Sheriff's Dive Team finds Emerson's truck in Chautauqua Lake between Bemus and Greenhurst...The pick-up truck associated with a missing Lakewood man has been found submerged in Chautauqua Lake near the town of Ellery.  However... weather conditions have prevented Sheriff's Department Dive Team members from locating 64 year-old Daniel "Scott" Emerson.  Emerson was last seen on Mar. 3... but, Sheriff Jim Quattrone says his department received some tips and video from a location between Greenhurst and Bemus Point.  Quattrone says they received the video Monday morning... and, quickly got the Sheriff's marine boat and sonar out to that area and found the vehicle.  However... that was the day the temperature plummeted during the afternoon... and, divers has issues with air tanks freezing once they got out of the water.  With the weather still below freezing... Quattrone says the dive team will head back out Thursday.  He says they were able to find the top of the truck... which was at least partially submerged in mud and other debris.  Late last week... Lakewood-Busti Police urged residents and businesses located along the Chautauqua Lake shoreline for any help regarding Emerson's whereabouts.  Police say he was believed to be driving his maroon-colored F-150 that was last seen on Fairmount and Lakeview Avenues in the village around 12:30 a.m. the day he went missing.  If you have any information... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and drug-possession charges...A man from Jamestown has been arrested on multiple drug possession charges following a raid on a southside home early Tuesday afternoon.  Sheriff's officers say their narcotics investigators... along with those from Jamestown police... executed a search warrant on the upper apartment at 313 Prather Ave. shortly after Noon.  The suspect... 26 year-old Devonte Green -- who had a State Parole warrant for his arrest -- was seen leaving the residence in a vehicle just prior to the raid.  Jamestown police tried to conduct a vehicle stop... but, Green continued for a short distance in the car before he was arrested following a brief foot chase.  Deputies say their search of the home, Green and his vehicle led to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  Green was held pending arraignment on charges including: third-and-seventh-degree criminal possession of a controlled substance... and, resisting arrest.Schmidt announces indictment against Westfield man who allegedly shot village woman, in front of children...A Westfield man who allegedly shot a woman... then led police on a vehicle pursuit earlier this month, faces several charges related to both incidents.  Chautauqua County District Attorney Jason Schmidt says a grand jury has indicted 52-year-old Jahmaul Johnson on eight counts, including second-degree attempted murder.  Schmidt says that top charge stems from a shooting that occurred on Route 20 in the village during the evening of Mar. 7... he says Judge Stephen Cass presided over the matter, and a "not guilty" plea was entered for the defendant.  After the shooting... Johnson fled the scene, leading to a pursuit that ended when he crashed his getaway vehicle into a ditch.  He was taken into custody in the Town of Pomfret a short time later that evening.  Schmidt says Johnson also faces three violent felonies related to a handgun and magazine he allegedly possessed... along with four counts of endangering the welfare of a child.  Schmidt says Johnson pleaded not guilty at his arraignment Tuesday morning before being remanded to the Chautauqua County Jail on $1-million cash bail... $2-million property bond.  He says a disovery conference will be held on Apr. 13.  If convicted, Johnson faces up to 25 years in prison on the attempted murder charge and up to 15 years on the weapon counts, adding that there's a possibility of those sentences running consecutively.  The victim was taken to an Erie, Pa. hospital, and is recovering from her injuries.Site work beginning for new Brook's Hospital in Fredonia...Initial site work for the new Northern Chautauqua Hospital project in Fredonia gets underway this week.  The announcement late Monday by Kaleida Health comes in the wake of its January filing in conjunction with Brooks-TLC of a building permit with the village of Fredonia for the hospital's construction.  Turner Construction Company subcontracted with Fredonia-based S. St. George General Contracting to perform the preliminary site work, including setting up temporary staging areas, fencing the property, and grading the site.  Initial work will depend on the weather... and the need for the land to drain and dry out.  The $223.8 million project is planned as a one-story, 133,000 facility at 412 East Main St.  It will replace the existing Brooks Hospital in the city of Dunkirk.Molitor part of Assembly-Senate Budget Conference Committee to deal with Human Services...The deadline for a new state budget is fast approaching... and, work is continuing in the New York State Assembly and Senate on a final spending plan.  With that... more legislative hearings involving conference committees are underway.  Local State Assemblyman Andrew Molitor is an alternate for the committee on Human Services... which means he'll be able to ask questions and offer input about Medicaid and other "safety net" programs.  The Assembly's $272-billion, "one-house" budget includes a 1% income tax cut for low and middle income earners... but, Molitor says it's not enough.  Ideally, he says he would like to see all income taxes eliminated.  Molitor says he remains hopeful there will be a budget acted on by the Apr. 1 deadline. </t>
+          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
         </is>
       </c>
       <c r="D15" s="2">
@@ -773,38 +768,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908600/wjtn-news-headlines-for-wed-mar-18-2026</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>...arch of the home, Green and his vehicle led to the seizure of 2.3 grams of **fentanyl**... and, 4.7 grams of psilocybin mushrooms... along with $131 cash.  G...
-...ed to the seizure of 2.3 grams of fentanyl... and, 4.7 grams of psilocybin **mushrooms**... along with $131 cash.  Green was held pending arraignment on charg...
-..... call Lakewood-Busti Police at 763-9563.City man arrested on warrant and **drug**-possession charges...A man from Jamestown has been arrested on multiple dr...
-...ug-possession charges...A man from Jamestown has been arrested on multiple **drug** possession charges following a raid on a southside home early Tuesday afte...
-...nt on charges including: third-and-seventh-degree criminal possession of a **controlled** substance... and, resisting arrest.Schmidt announces indictment against We...</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/22rgnb4x</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – ASHFORD, N.Y. — Two Cattaraugus County men were arrested on felony drug charges following a traffic stop and investigation that led to the discovery of suspected cocaine, according to the Cattaraugus County Sheriff’s Office. Authorities report that the incident occurred on March 18, 2026, at approximately 7:47 p.m. in the Town […]The post Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges appeared first on WNY News Now.</t>
+          <t>Complete coverage: The saga of the state-funded drug manufacturing plant in Dunkirk - Buffalo News</t>
         </is>
       </c>
       <c r="D16" s="2">
@@ -812,147 +788,80 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/27bqx4hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – ASHFORD, N.Y. — Two Cattaraugus County men were arrested on felony drug charges following a traffic stop and investigation that led to the discovery of suspected cocaine, according to the Cattaraugus County Sheriff’s Office. Authorities report that the incident occurred on March 18, 2026, at approximately 7:47 p.m. in the Town […]The post Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D17" s="2">
+        <v>46100</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/03/19/traffic-stop-in-ashford-leads-to-cocaine-seizure-two-arrested-on-felony-drug-charges/</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...wo Cattaraugus County men were arrested on felony **drug** charges following a traffic stop and investigatio...
 ... Leads to Cocaine Seizure, Two Arrested on Felony **Drug** Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>(WNY News Now) – DUNKIRK, N.Y. — A narcotics investigation in the City of Dunkirk led to the seizure of fentanyl, crack cocaine, and methamphetamine, along with the arrest of a 45-year-old man on multiple felony drug charges. Authorities executed a search warrant at a lower apartment at 209 Lincoln Avenue on March 18, 2026, […]The post Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D17" s="2">
+      <c r="D18" s="2">
         <v>46100</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/03/19/dunkirk-man-arrested-after-multi-agency-narcotics-raid-on-lincoln-avenue/</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>...ed to the seizure of fentanyl, crack cocaine, and **methamphetamine**, along with the arrest of a 45-year-old man on mu...
 ...tion in the City of Dunkirk led to the seizure of **fentanyl**, crack cocaine, and methamphetamine, along with t...
 ...he arrest of a 45-year-old man on multiple felony **drug** charges. Authorities executed a search warrant at...</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A multi-agency narcotics investigation led to seven arrests Tuesday afternoon after authorities executed a search warrant at a Jamestown apartment, seizing fentanyl, crack cocaine, and other drug-related items. According to investigators, the search warrant was carried out around 3:39 p.m. on March 17, 2026, at 28 Euclid Ave., […]The post Seven Arrested After Jamestown Narcotics Raid, Fentanyl and Cocaine Seized appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D18" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/19/seven-arrested-after-jamestown-narcotics-raid-fentanyl-and-cocaine-seized/</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>... search warrant at a Jamestown apartment, seizing **fentanyl**, crack cocaine, and other drug-related items. Acc...
-...st Seven Arrested After Jamestown Narcotics Raid, **Fentanyl** and Cocaine Seized appeared first on WNY News Now...
-...tment, seizing fentanyl, crack cocaine, and other **drug**-related items. According to investigators, the se...</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, NY — A Niagara Falls man was taken into custody early Thursday after Jamestown police allegedly found him driving while impaired by drugs during a traffic stop on the city’s east side. According to the Jamestown Police Department, the incident occurred at approximately 1:14 a.m. on March 19, 2026. Officers […]The post Jamestown Man Charged With Drug-Impaired Driving Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D19" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/19/jamestown-man-charged-with-drug-impaired-driving-following-early-morning-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>.... Officers […]The post Jamestown Man Charged With **Drug**-Impaired Driving Following Early Morning Traffic ...</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Jamestown woman pleads guilty to narcotics and firearms charges - MSN</t>
-        </is>
-      </c>
-      <c r="D20" s="2">
-        <v>46099</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/28g35pus</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -692,179 +692,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Jamestown, NY — Seven Charged After Euclid Ave Search Warrant; Fentanyl, Cocaine Seized - Country Herald</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2cbvhcbl</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>City man charged after narcotics investigation - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/278puyft</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Thirteen tonnes of cocaine seized in Dunkirk in two weeks - Brussels Signal</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/26xalbhz</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Seven Arrested in Jamestown Drug Bust - Erie News Now</t>
-        </is>
-      </c>
-      <c r="D15" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/22rgnb4x</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Complete coverage: The saga of the state-funded drug manufacturing plant in Dunkirk - Buffalo News</t>
-        </is>
-      </c>
-      <c r="D16" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/27bqx4hz</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – ASHFORD, N.Y. — Two Cattaraugus County men were arrested on felony drug charges following a traffic stop and investigation that led to the discovery of suspected cocaine, according to the Cattaraugus County Sheriff’s Office. Authorities report that the incident occurred on March 18, 2026, at approximately 7:47 p.m. in the Town […]The post Traffic Stop in Ashford Leads to Cocaine Seizure, Two Arrested on Felony Drug Charges appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D17" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/19/traffic-stop-in-ashford-leads-to-cocaine-seizure-two-arrested-on-felony-drug-charges/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>...wo Cattaraugus County men were arrested on felony **drug** charges following a traffic stop and investigatio...
-... Leads to Cocaine Seizure, Two Arrested on Felony **Drug** Charges appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – DUNKIRK, N.Y. — A narcotics investigation in the City of Dunkirk led to the seizure of fentanyl, crack cocaine, and methamphetamine, along with the arrest of a 45-year-old man on multiple felony drug charges. Authorities executed a search warrant at a lower apartment at 209 Lincoln Avenue on March 18, 2026, […]The post Dunkirk Man Arrested After Multi-Agency Narcotics Raid on Lincoln Avenue appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D18" s="2">
-        <v>46100</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/19/dunkirk-man-arrested-after-multi-agency-narcotics-raid-on-lincoln-avenue/</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>...ed to the seizure of fentanyl, crack cocaine, and **methamphetamine**, along with the arrest of a 45-year-old man on mu...
-...tion in the City of Dunkirk led to the seizure of **fentanyl**, crack cocaine, and methamphetamine, along with t...
-...he arrest of a 45-year-old man on multiple felony **drug** charges. Authorities executed a search warrant at...</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -434,7 +434,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/279l6oks</t>
+          <t>https://tinyurl.com/28pxerct</t>
         </is>
       </c>
     </row>
@@ -575,120 +575,6 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Putin Furthers Civil Society Facade as Tool of Control - The Jamestown Foundation</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46101</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/22tofx85</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Telegram Outages Spike in Kremlin’s Push for Digital Control - The Jamestown Foundation</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46101</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2xr4ut6j</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Mar. 20, 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Police able to bring Emerson's reported truck out of lake... no word on his situation...The search resumed this morning for the missing Lakewood man... whose pick-up truck was found submerged in Chautauqua Lake earlier this week.  We have seen on-line "chatter" that the truck has been brought out of the lake.  However... that has NOT been confirmed.  We have calls into Chautauqua County Sheriff Jim Quattrone, but, have not heard back  Earlier today, Quattrone said his department's Dive Team had been joined by others from Erie and Niagara Counties... and, New York State Police at the scene.  Divers went back into the water near Bemus Point this morning to attach floation devices to bring the truck to the surface.  Quattrone says murky water... and, the fact the truck is in a few feet of mud and muck at the bottom... have hampered efforts.  Police are still trying to locate 64 year-old Daniel "Scott" Emerson... who was last seen on Mar. 3. Fire heavily damages first-floor of multiple-family dwelling in Jamestown...Flames have heavily-damaged the first floor of a three-story, multi-family home on Jamestown's southside.   City Fire Captain Dan Balling says firefighters were called to the scene at 517 Newland Ave. shortly after 1 p.m., and, found heavy smoke, and fire on the first floor.  Balling credited crews with making a quick stop on the flames... and, confining the blaze to the first floor.  He says an off-duty shift was called in... and, the fire was knocked down in less than 30 minutes.  Balling says there was heat damage to the second and third-floors.  The house was occupied... but, everyone got out safely.  Two firefighters suffered minor injuries.  The cause is under investigation.City man arrested for allegedly injuring and holding a woman against her will...A man from Jamestown faces contempt and other charges after allegedly hurting and holding a woman against her will at an eastside home.  In addition... city police accuse 26 year-old Angel Ramos-Gonzalez of holding the woman so long that officers found three children living in "deplorable conditions."  Jamestown police were called to the scene for a domestic dispute just after 8 a.m. Thursday.  Officers had been told that Ramos-Gonzalez had violated an order of protection... and, on arrival... found him inside a bedroom closet where he was taken into custody.  In addition to holding the woman against her will... Ramos-Gonzalez is also accused of biting the woman, causing minor injuries.  He's charged with two counts of aggravated criminal contempt... unlawful imprisonment... third-degree assault... and, three counts of endangering the welfare of a child.  He was jailed pending arraignment.Borrello calls State Senate "One-House" Budget a "Train Wreck..."The process to craft a final, 2026-27 state budget is continuing now that both the State Senate and Assembly have presented their "one-house" spending plans.  Both budgets call for additional spending compared to Governor Kathy Hochul's, more than $260-billion proposal.  The Senate's one-house budget amounts to just under $270-billion... and, is about $7.1-billion more than Hochul's budget.  State Senator George Borrello calls it a "fiscal train wreck" with residents suffered under higher utility bills... and, "nothing was offered in relief."  Borrello says the Senate Democrats' "wish list" includes $5.6 billion in higher taxes.  He says it also contains no changes to the Climate Act... and, a rejection of Hochul's proposal to crack down on car insurance fraud and lawsuit abuse.  The Sunset Bay Republican believes what's positive in the budget is "far outshadowed" by the negative in terms of "waste, fraud and abuse."  He adds there are also too many gimmicks in the budget that really aren't enough to provide relief.  A final state budget is due by Apr. 1.County DMV urges residents about possible "Double Charge" issue with debit and credit card usage at DMV...Some New York State Department of Motor Vehicles offices are reporting seeing some customers getting "double-charged" for services using debit or credit cards for a single transaction.  In a press release this morning.. the Chautauqua County DMV is now urging their customers to use either cash or checks right now.  Officials say it's not happening "with every debit or credit card transaction, the problem has persisted since the state DMV went live with the DRIVES software update in February.  Unfortunately... local DMV offices are not authorized to issue refunds directly, and the state DMV is taking 3-to-5 business days to process refunds.  County Clerk Greg Carlson says they -- and other local DMVs are actively communicatin the issue to the state since the DRIVES rollout last month... but, they are still occuring.  Carlson says the county's three DMV offices will continue to process debit and credit card transactions, but encourages customers to use cash or check when completing in-person transactions until the state resolves the issue.Man from Ashville arrested for DWI after single-car accident in the town of Chautauqua...A man from Ashville faces a drunk driving charge following a single-car crash in the town of Chautauqua this past Wednesday night.  Sheriff's officers say they were called to the scene on Route 394 -- at Moore Road -- shortly before Midnight to investigate.  Deputies say they found that 37 year-old Phillip Grobe was driving while intoxicated at the time of the accident.  Grobe was arrested for DWI, Driving with a blood alcohol content of .08 or more... moved from lane unsafely... speed not reasonable and prudent... and, unreasonable speed with special hazards.  He was issued appearance tickets for Chautauqua Town Court at a later date.  No injuries were reported in the accident.     </t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46101</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908944/wjtn-news-headlines-for-fri-mar-20-2026</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>...p;Deputies say they found that 37 year-old Phillip Grobe was driving while **intoxicated** at the time of the accident.  Grobe was arrested for DWI, Driving wit...</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jamestown Drug Raid: Seven Arrested and Major Fentanyl Seized</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>In a major narcotics bust on March 17, 2026, authorities in Jamestown, New York, executed a search warrant at an apartment and arrested seven individuals who were allegedly up to no good. The Chautauqua County Sheriff’s Office, along with the Jamestown Police Department and even the SWAT team, raided the location, only to find a shocking amount of fentanyl, crack cocaine, and drug paraphernalia.During the raid, investigators seized around 32.5 grams of fentanyl, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,373 in cashâdefinitely not pocket change! The suspects ranged in age from 26 to 61 and included names like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple drug possession charges.Interestingly, among the arrested were individuals with outstanding warrants, which adds yet another layer to this already tangled web of drug-related offenses. Itâs a stark reminder that sometimes, what happens behind closed doors isnât as harmless as it seems. Letâs hope this bust serves as a wake-up call for those involved in the local narcotics trade, but it also makes you wonderâhow many more like this are happening in towns across the country?</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46101</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/908851/jamestown-drug-raid-seven-arrested-and-major-fentanyl-seized</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...even the SWAT team, raided the location, only to find a shocking amount of **fentanyl**, crack cocaine, and drug paraphernalia.During the raid, investigators seiz...
-...g paraphernalia.During the raid, investigators seized around 32.5 grams of **fentanyl**, 11.3 grams of crack cocaine, a stash of suboxone, and a hefty sum of $3,3...
-...e location, only to find a shocking amount of fentanyl, crack cocaine, and **drug** paraphernalia.During the raid, investigators seized around 32.5 grams of f...
-...ames like Jaqwan L. Martin and Anthony J. Wallace Jr., all facing multiple **drug** possession charges.Interestingly, among the arrested were individuals with...
-...ding warrants, which adds yet another layer to this already tangled web of **drug**-related offenses. Itâs a stark reminder that sometimes, ...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,15 +406,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - Erie News Now</t>
+          <t>Tine – Chautauqua County Humane Society - Post Journal</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46106</v>
+        <v>46109</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/249k877s</t>
+          <t>https://tinyurl.com/22ccohnp</t>
         </is>
       </c>
     </row>
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
+          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - Erie News Now</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -434,49 +434,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28pxerct</t>
+          <t>https://tinyurl.com/249k877s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
+          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/279l6oks</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
+          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -486,15 +471,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
+          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -511,17 +496,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
         </is>
       </c>
       <c r="D6" s="2">
@@ -529,17 +514,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
@@ -551,12 +536,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -564,15 +549,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,35 +406,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tine – Chautauqua County Humane Society - Post Journal</t>
+          <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/22ccohnp</t>
+          <t>https://tinyurl.com/yor47nm9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - Erie News Now</t>
+          <t>Is CBD Flower Legal in the UK in 2026?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CBD flower sits in one of the most debated corners of UK drug law. Buyers, retailers, and even some legal professionals disagree on where the line is, and that disagreement has real consequences for anyone looking to buy or sell it. If you’re searching for premium CBD flowers in the UK, the first thing you […]The post Is CBD Flower Legal in the UK in 2026? appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/249k877s</t>
+          <t>https://wnynewsnow.com/2026/03/29/is-cbd-flower-legal-in-the-uk-in-2026/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...wer sits in one of the most debated corners of UK **drug** law. Buyers, retailers, and even some legal profe...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -446,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
+          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - erienewsnow.com</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -454,49 +469,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/279l6oks</t>
+          <t>https://tinyurl.com/249k877s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
+          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/28pxerct</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
+          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -506,15 +506,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
+          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -531,17 +531,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
+          <t>1 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -549,17 +549,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -584,15 +584,50 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46104</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,15 +406,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
+          <t>Russia at Risk of Losing Control of Railways in Armenia - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/yor47nm9</t>
+          <t>https://tinyurl.com/2y3ek5nh</t>
         </is>
       </c>
     </row>
@@ -426,25 +426,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Is CBD Flower Legal in the UK in 2026?</t>
+          <t>Prior Felon Sentenced to 70 Months in Federal Prison for Drug and Gun Charges</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CBD flower sits in one of the most debated corners of UK drug law. Buyers, retailers, and even some legal professionals disagree on where the line is, and that disagreement has real consequences for anyone looking to buy or sell it. If you’re searching for premium CBD flowers in the UK, the first thing you […]The post Is CBD Flower Legal in the UK in 2026? appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Niagara Falls man previously convicted of a felony has been sentenced to more than five years in federal prison for drug trafficking and firearm-related offenses, federal prosecutors announced. Eric Rivera, 39, was sentenced to 70 months in prison by U.S. District Judge Richard J. Arcara after being […]The post Prior Felon Sentenced to 70 Months in Federal Prison for Drug and Gun Charges appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/29/is-cbd-flower-legal-in-the-uk-in-2026/</t>
+          <t>https://wnynewsnow.com/2026/03/31/prior-felon-sentenced-to-70-months-in-federal-prison-for-drug-and-gun-charges/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>...wer sits in one of the most debated corners of UK **drug** law. Buyers, retailers, and even some legal profe...</t>
+          <t>...ced to more than five years in federal prison for **drug** trafficking and firearm-related offenses, federal...
+...elon Sentenced to 70 Months in Federal Prison for **Drug** and Gun Charges appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -456,105 +457,133 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - erienewsnow.com</t>
+          <t>Jamestown Man Arrested on Drug, Traffic Charges Following Vehicle Stop</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 60-year-old Jamestown resident was taken into custody Saturday afternoon after a traffic stop led to the discovery of suspected narcotics, a suspended license, and multiple outstanding warrants. According to the Jamestown Police Department, officers from the department’s 2nd Platoon conducted a vehicle stop at approximately 3:30 p.m. […]The post Jamestown Man Arrested on Drug, Traffic Charges Following Vehicle Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/249k877s</t>
+          <t>https://wnynewsnow.com/2026/03/31/jamestown-man-arrested-on-drug-traffic-charges-following-vehicle-stop/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...y 3:30 p.m. […]The post Jamestown Man Arrested on **Drug**, Traffic Charges Following Vehicle Stop appeared ...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
+          <t>Jamestown Man Arrested on Warrant, Drug Charge Following Street Check</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 46-year-old Jamestown man was taken into custody Monday afternoon after police identified him during a proactive patrol and discovered an active warrant and suspected drugs. Jamestown Police report that officers were conducting a GIVE (Gun Involved Violence Elimination) detail on March 30, 2026, at approximately 4:53 p.m. […]The post Jamestown Man Arrested on Warrant, Drug Charge Following Street Check appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/28pxerct</t>
+          <t>https://wnynewsnow.com/2026/03/31/jamestown-man-arrested-on-warrant-drug-charge-following-street-check/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>...m. […]The post Jamestown Man Arrested on Warrant, **Drug** Charge Following Street Check appeared first on W...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Tues., Mar. 24, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Shooting incident in Dunkirk leads to shelter in place with suspect barricaded...Residents in the area of Franklin Avenue in the city of Dunkirk are being asked to shelter in place following a report of shots fired Tuesday morning.  Dunkirk police are confirming the incident... which was called in about 6:20 a.m.  Police also tell us that no injuries were reported, and a subject was barricaded.  The shelter in place advisory was first announced through an NY Alert.  Police find Emerson's truck with rolled down window, indicated he was able to get out.  Search for him resumes Wednesday...Police are continuing their search for the missing Lakewood man whose truck was found in Chautauqua Lake late last week.  Lakewood-Busti Police Chief Matthew Bentley updated the Lakewood Village Board at Monday night's meeting about the search for 64 year-old Daniel "Scott" Emerson.  Bentley did present some new information during the meeting... noting that while Emerson was not in the vehicle... the window was rolled down on the back-driver's side.  He says they believe that Emerson tried to escape the vehicle... but, wasn't able to make it safely to the surface.  Emerson's truck was found in Chautauqua Lake near the Veterans Memorial Bridge on Monday, Mar. 16... and, divers were finally able to get it to the surface last Friday.  Bentley says the Sheriff's Department dive team was out yesterday with their underwater sonar... and, plan to resume looking in that area Wednesday.North county man arrested for allegedly stealing, and setting camper on fire...A man from the town of Villanova is accused of stealing a camper... then setting it on fire and destroying it.  Sheriff's deputies say they were called to the scene in the hamlet of Forestville for the reported theft.  Following an investigation... officers say they found that 25 year-old Ethan Guest... allegedly started the missing camper on fire... and, it was a total loss -- unbeknownst to the owner of the camper.  Early Monday afternoon... a warrant was issued by Villanova Town Court for Guest's arrest on one count each of third-degree arson... and, third-degree criminal mischief.  He was arrested without incident... and, taken to the county jail pending arraignment.Borrello and Molitor react to new of Refresco canceling it's grape contracts with local growers...A north county beverage processing company's decision to cancel all of its grape contracts is being described by Chautauqua County's two state lawmakers as a "significant setback" for local growers. State Senator George Borrello and Assemblyman Andrew Molitor say the impact of the actions by Refresco threatens jobs, related businesses, and the economic stability of entire communities.  Borrello says he was informed that Refresco was leaving the processing business... but, he said they're still gathering information.  Borrello adds that he has reached out to State Agriculture and Markets Commissioner Richard Ball, along with several elected officials and the Chautauqua County Industrial Development Agency to find solutions... including getting some relief for local grape producers, and finding a new market for their product.  Grape growers were informed about Refresco's decision in a letter this week.  Refresco operates a facility in Dunkirk.CLA answers questions about weed harvesting on lake, and where the weeds go...Some of the questions from last Saturday's Chautauqua Lake Symposium centered on where the Lake Association can harvest weeds... and, where those weeds are taken.  The questions came up during a question and answer session following all the presentations.  CLA Executive Director Heather Nolan-Caskey says -- for the most part -- the State Dept. of Environmental Conservation allows them to harvest most anywhere on the lake... except where there are no homeowners, or fish "zones."  There was also a question about where the 20-million to 25-million pounds of weeds they harvest each year go.  Nolan-Caskey says most of those weeds go to local farms... and, are used for composting.  Once the invasive Elodea weeds began covering the lake's south basin late year... the CLA stepped up efforts to clear those areas... and, with the help of local towns, and the county, they were able to truck the harvested weeds to local farms. City woman arrested for Felony DWI, and driving the wrong way...A woman from Jamestown has been arrested for drunk driving after allegedly running a red light at a southside intersection... while traveling the wrong way.  City police say a patrol in the area of South Main Street and the Arterial spotted the car go through the red light just after 2 a.m. Sunday.  Officers stopped the vehicle... which was driven by 44 year-old Tiffany Haight... and, determined she was driving drunk.  Haight submitted to a breath test... which resulted in a .17 blood alcohol content.  Police say they later found that she had a pervious DWI conviction in the past 10 years, making this DWI a Felony.  They add she was also operating the vehicle with a revoked driver's license... and, she was additionally charged with first-degree aggravated unlicensed operation.  Haight was taken to the city jail pending arraignment.Fredonia man arrested for DWAI, and speeding...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.</t>
+          <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909355/wjtn-news-headlines-for-tues-mar-24-2026</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
+          <t>https://tinyurl.com/29jtkdaf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Mon., Mar. 23, 2026</t>
+          <t>WJTN News Headlines for Mon., Mar. 30, 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1 keyword references (WJTN)</t>
+          <t>14 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Man from Mayville arrested for assault and unlawful imprisonment...A Mayville man is accused of threatening and assaulting another person... and, holding them against their will early last weekend.  Sheriff's deputies say they were called to a village address shortly before 4 a.m. Saturday for a recent "physical altercation."  Officers say their investigation found that 41 year-old Kevn Appelbe intentionally hurt the victim... threatened their life... and, held them against their will during the incident.  Deputies found Appelbe... and, he was arrested for third-degree assault... third-degree menacing... and, second-degree unlawful imprisonment.  He was jailed pending centralized arraignment... and, will appear in Chautauqua Town Court at a later date.City teen arrested for allegedly choking, and unlawfully holding victim against their will...A Jamestown teenager has been arrested for allegedly pinning another person to the ground... and, hitting and choking them.  City police say they were called to a southside location just after 7 PM last Friday for a domestic incident.  Officer say they found that 18 year-old Angel Rosa had pinned the victim to the ground... grabbed their neck... and, repeatedly struck them.  Police arrested Rosa was for second-degree unlawful imprisonment... and, criminal obstruction of breathing -- or blood circulation.  He was held pending arraignment.Emerson's pick-up truck pulled from lake waters; but he is still missing...           The truck belonging to a Lakewood man reported missing early this month has been recovered from Chautauqua Lake.  However... the Chautauqua County Sheriff's Department reports that 64 year-old Daniel "Scott" Emerson was not found inside... and, he remain missing.  Officers say the truck was towed by boat to Long Point State Park... where it was removed from the lake.  The Sheriff's Office Water Emergency Team was assisted by Lakewood-Busti Police... State Park Police... the State Police, Erie County, and Niagara County Dive Teams... and, County Emergency Services.  Deputies say the recovery took several days and was impeded by difficult weather conditions... and, poor underwater visibility.  Several ivers spent significant time in murky, frigid water in order to conduct this recovery.  Anyone living on Chautauqua Lake and may have camera footage of this truck driving on the lake on March 3rd, is encouraged to contact the Lakewood-Busti Police or the Sheriff's Department's Criminal Investigation Division.  A likely time of that footage would be between 4 a.m. and 7 a.m. on Mar. 3.  The search for Emerson is on-going.Leader of Lake and Watershed Mgmt Alliance highlights three recommendations for lake in 2026...The head of the Chautauqua Lake and Watershed Management Alliance is making three recommendations to members, and other lake groups for the coming season.  A.J. Reyes is a Certified Lake Manager for GEI Consultants... and, has been hired to develop strategies for dealing with lake issues.  One recommendation is how to more quickly deal with the excessive Elodea growth in the south basin last Spring.  Reyes is proposing the Chautauqua Lake Association focus on "cutting lanes" with their weed harvesters... and, he says they need to decide on whether to create them yearly, and where they need to be.  Reyes was the final speaker during the third-annual Chautauqua Lake Symposium held at the Chautauqua Harbor Hotel in Celoron.  He says another recommendation is pulling together a Technical Advisory Group to work on strategies against a new invasive weed -- the Starry Stonewort.  He says the TAG would have a group of experts familiar with the Starry Stonewort, and how to deal with it.  Reyes also recommended a consolidated effort to look at... and, review what has worked in stemming weeds and improving water quality in the lake.  He says that would run the gamit from weed harvesting... to herbicide use.  County Executive P.J. Wendel... who hosted the symposium... was pleased with how it went, and the participation in the program.  North County man arrested for speeding and driving under influence of drugs...A man from Fredonia has been arrested for driving while under the influence of drugs after being stopped for speeding in the north county.  Sheriff's officers say a patrol stopped the speeding vehicle in Fredonia shortly before 1 a.m. last Friday... and, found the operator -- Frank Rivera-Montero -- was driving while impaired by drugs.  He was arrested for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a controlled substance.  Rivera-Montero was arraigned and issued appearance tickets for Fredonia Village Court.Jamestown man arreste for threatening phone call to person with "stay-away" order of protection against him...A city man has been arrested for allegedly making a threatening phone call to a person who had an order of protection against him.  Jamestown police say they were called to a southside address shortly after 1 p.m. Thursday for a complaint from earlier in the day.  Officers investigated... and, determined that 35 year-old Demetrius Goldsmith had called and threatened the victim.  Police found Goldsmith a short time later at a separate address... and, he was arrested for first-degree criminal contempt... and, second-degree aggravated harassment.  He was jailed pending arraignment.</t>
+          <t>Four city residents arrested in drug bust late last week...Four people from Jamestown face multiple drug-related charges following a raid on an apartment on the city's westside.  Sheriff's officers say their Narcotics Investigators... and, those from Jamestown... executed a search warrant at 114 West Seventh St. just after 4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of methamphetamine... along with scales and packaging materials used to traffic drugs.  They also seized $4,094 dollars in cash.  Officers arrested 30 year-old James Eastham and 27 year-old Amber Eaton both for second-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  They add that 51 year-old Tracy Brown was arrested for third-degree criminal possession of a controlled substance... second-degree criminally using drug paraphernalia... and, second-degree criminal contempt.  Police arrested 42 year-old Randy Wright for third-degree criminal possession of a controlled Substance... second-degree criminally using drug paraphernalia... and, first-degree criminal contempt.  All four were taken to the city jail pending arraignment.  Anyone with information on illegal narcotics or other criminal activity is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702... or 664-2420... or the JPD Tip line at 483-8477.Catt. County man arrested for allegedly driving with four-times the legal limit of alcohol in his system...A Randolph man is accused of having nearly four times the legal limit of alcohol in his system when he crashed his car on Jamestown's eastside last Saturday morning.  City police were called to the scene on East Fourth Street about 10:30 a.m. on a report of a vehicle leaving the scene of an accident with heavy front-end damage.  Officers say they located the car... and, the driver -- identified as 45 year-old James Bliss -- a short distance away with the airbag deployed.  Police say they determined that Bliss had been driving while intoxicated... and, he ws arrested.  He was taken to the city jail where he consented to a blood test.  Officers say they blood test indicated Bliss's BAC was nearly four times the legal limit of .08%.  He was charged with DWI... Aggravated DWI... and, leaving the scene of a property damage accident.  Bliss was later issued appearance tickets... and, released to a sober third party.More than 300 attend "No Kings" Rally at Jamestown's Dow Park...More than 300 protestors showed up on a bitterly cold morning Saturday at Jamestown's Dow Park for the latest "No Kings" Rally... and, the first since the start of the War in Iran.  The event was hosted by the Jamestown Justice Coalition... and, others.  Coalition member Kate Ebersole spoke at the beginning... reminding those on hand this was a "peaceful" protest.  Coalition Founder Justin Hubbard while they were there to protest the war... and, the Trump Administration's policies... Saturday's rally was not the end.  Hubbard called the rally "a launching pad" to fuel the work they can do in the community, and let their voices be heard.  He also noted that the Jamestown Justice Coalition has just become a 501(c)4... which allows it to advocate... and, raise money.  The last rally raised more than $1,300 for the "New Neighbors Coalition" which supports and advocates for immigrants just arriving in the Jamestown-area.---Saturday's rally raised money for the effort to replace one of the three statues for the Underground Railroad Tableau... which was stolen from Dow Park n 2021.  Hubbard says says it's important to replace that statue because of Jamestown's place in the history of the Underground Railroad. Borrello and Blakeman call for full audit of NYS CDL testing and licensing in wake of 2025 bus crash on NYS Thruway...The region's State Senator is among those calling on a full audit of how commercial drivers are tested... licensed... and monitored in New York.  Sunset Bay Republican George Borrello joined Nassau County Executive and Republican gubernatorial candidate Bruce Blakeman late last week to call for the audit... arguing that last year's deadly bus crash in Pembroke -- along with a series of other recent cases -- has raised serious questions about the integrity of the state’s commercial driver licensing system and whether critical safety standards are being properly enforced.  The pair... along with others... spoke near the site of the Aug. 22, 2025 tour bus crash on the State Thruway near Pembroke, which killed five people and injured more than 40 others.  The driver was later indicted on five counts each of manslaughter and criminally negligent homicide.  At a court hearing... Borrello says the man required a Mandarin interpreter, raising questions about his English proficiency... and, whether New York properly enforced federal CDL standards.Jamestown man gets 10 years in federal prison for trafficking meth...A city man who was an associate of a major, Jamestown-area drug dealer has been sentenced to 10 years in federal prison for trafficking methamphetamine.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-old Aaron Miller, who was convicted of conspiracy to possess with intent to distribute, and to distribute, methamphetamine, received the sentence in U.S. District Court in Buffalo.  Prosecutors say that Miller bought and sold methamphetamine, and cocaine for profit and for his own use.  He received large quantities of meth and cocaine from co-defendant Jun Martinez, the drug dealer, and others.  Miller then distributed the drugs to other individuals in the Jamestown area for profit.  DiGiacomo says co-defendants Jun Martinez, La Huynh, and Antasia Babcock were previously convicted and are awaiting sentencing. </t>
         </is>
       </c>
       <c r="D7" s="2">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/909181/wjtn-news-headlines-for-mon-mar-23-2026</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910080/wjtn-news-headlines-for-mon-mar-30-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>...for speeding... DWAI-Drugs... and, seventh-degree criminal possession of a **controlled** substance.  Rivera-Montero was arraigned and issued appearance ticket...</t>
+          <t>...4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of **methamphetamine**... along with scales and packaging materials used to traffic drugs.  ...
+...ug dealer has been sentenced to 10 years in federal prison for trafficking **methamphetamine**.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-...
+...ted of conspiracy to possess with intent to distribute, and to distribute, **methamphetamine**, received the sentence in U.S. District Court in Buffalo.  Prosecutor...
+...strict Court in Buffalo.  Prosecutors say that Miller bought and sold **methamphetamine**, and cocaine for profit and for his own use.  He received large quant...
+Four city residents arrested in **drug** bust late last week...Four people from Jamestown face multiple drug-relate...
+...ted in drug bust late last week...Four people from Jamestown face multiple **drug**-related charges following a raid on an apartment on the city's westside. &amp;...
+...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia.  They add that 51 year-old Tracy Brown was arrested fo...
+...nal possession of a controlled substance... second-degree criminally using **drug** paraphernalia... and, second-degree criminal contempt.  Police arrest...
+...fficking meth...A city man who was an associate of a major, Jamestown-area **drug** dealer has been sentenced to 10 years in federal prison for trafficking me...
+...d large quantities of meth and cocaine from co-defendant Jun Martinez, the **drug** dealer, and others.  Miller then distributed the drugs to other indiv...
+...ployed.  Police say they determined that Bliss had been driving while **intoxicated**... and, he ws arrested.  He was taken to the city jail where he conse...
+...nd 27 year-old Amber Eaton both for second-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...
+...ear-old Tracy Brown was arrested for third-degree criminal possession of a **controlled** substance... second-degree criminally using drug paraphernalia... and, sec...
+...rrested 42 year-old Randy Wright for third-degree criminal possession of a **controlled** Substance... second-degree criminally using drug paraphernalia... and, fir...</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -571,25 +600,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop</t>
+          <t>Four Arrested After Jamestown Drug Raid; Over 200 Grams of Meth Seized</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Lakewood man is facing multiple charges after a traffic stop early Sunday morning in the City of Jamestown led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on West Third Street at approximately 1:07 a.m. on March […]The post Lakewood Man Charged with Aggravated DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — Four Jamestown residents are facing felony drug charges following the execution of a search warrant that resulted in the seizure of a large quantity of methamphetamine and cash, according to local authorities. Narcotics investigators from the Chautauqua County Sheriff’s Office and Jamestown Police Department executed a search warrant […]The post Four Arrested After Jamestown Drug Raid; Over 200 Grams of Meth Seized appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D8" s="2">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/lakewood-man-charged-with-aggravated-dwi-following-early-morning-traffic-stop/</t>
+          <t>https://wnynewsnow.com/2026/03/30/four-arrested-after-jamestown-drug-raid-over-200-grams-of-meth-seized/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>...g in the City of Jamestown led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+          <t>...at resulted in the seizure of a large quantity of **methamphetamine** and cash, according to local authorities. Narcoti...
+...N.Y. — Four Jamestown residents are facing felony **drug** charges following the execution of a search warra...
+...warrant […]The post Four Arrested After Jamestown **Drug** Raid; Over 200 Grams of Meth Seized appeared firs...</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -606,30 +637,175 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street</t>
+          <t>Randolph Man Charged with Aggravated DWI After Leaving Scene of Crash In Jamestown</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(WNY News Now) – FREDONIA, N.Y. — A traffic stop for speeding early Friday morning in the Village of Fredonia led to the arrest of a local man on drug-related driving charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 12:50 a.m. on March 20, 2026, a vehicle was stopped on […]The post Fredonia Man Charged with DWAI-Drugs Following Traffic Stop on Main Street appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – A Randolph man is facing multiple charges after police say he left the scene of a property damage accident in Jamestown while allegedly intoxicated. JAMESTOWN, N.Y. — Officers from the Jamestown Police Department responded to a reported motor vehicle accident at the intersection of East 4th Street and North Main Street […]The post Randolph Man Charged with Aggravated DWI After Leaving Scene of Crash In Jamestown appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D9" s="2">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/23/fredonia-man-charged-with-dwai-drugs-following-traffic-stop-on-main-street/</t>
+          <t>https://wnynewsnow.com/2026/03/30/randolph-man-charged-with-aggravated-dwi-after-leaving-scene-of-crash-in-jamestown/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>...e of Fredonia led to the arrest of a local man on **drug**-related driving charges, according to the Chautau...</t>
+          <t>...erty damage accident in Jamestown while allegedly **intoxicated**. JAMESTOWN, N.Y. — Officers from the Jamestown Po...</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jamestown Man Charged with DWI Following Early Morning Traffic Stop in Pomfret</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – POMFRET, N.Y. — A Jamestown man is facing multiple charges after a traffic stop early Sunday morning in the Town of Pomfret led to a driving while intoxicated arrest. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on Route 60 at approximately 2:31 a.m. on March 29. […]The post Jamestown Man Charged with DWI Following Early Morning Traffic Stop in Pomfret appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/30/jamestown-man-charged-with-dwi-following-early-morning-traffic-stop-in-pomfret/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>...ing in the Town of Pomfret led to a driving while **intoxicated** arrest. According to the Chautauqua County Sherif...</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Falconer Man Charged with DWI Following Early Morning Traffic Stop in Ellicott</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – ELLICOTT, N.Y. — A Falconer man faces multiple charges after a traffic stop early Saturday morning in the Town of Ellicott led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on Fairmount Avenue at approximately 1:46 a.m. on March 28, 2026. […]The post Falconer Man Charged with DWI Following Early Morning Traffic Stop in Ellicott appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/30/falconer-man-charged-with-dwi-following-early-morning-traffic-stop-in-ellicott/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>...ng in the Town of Ellicott led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hanover Man Charged with DWI Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – HANOVER, N.Y. — A 62-year-old man was arrested early Sunday morning after a traffic stop in the Town of Hanover led to driving while intoxicated charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 1:38 a.m. on March 29, 2026, a vehicle was stopped near the intersection […]The post Hanover Man Charged with DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/03/30/hanover-man-charged-with-dwi-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>... stop in the Town of Hanover led to driving while **intoxicated** charges, according to the Chautauqua County Sheri...</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - Erie News Now</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>46106</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/249k877s</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <v>46106</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/279l6oks</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,56 +401,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Wed., Apr. 1, 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Russia at Risk of Losing Control of Railways in Armenia - The Jamestown Foundation</t>
+          <t>3 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NYS budget late for sixth-straight year, legislature approves one-week extender...For the sixth-year in a row... New York will have a late state budget, although negotiations between legislative leaders and Governor Kathy Hochul are ongoing.  In a late afternoon press release Tuesday... Assembly Minority Leader Ed Ra said -- "the  only credit Democrats deserve is that, weeks ago, they stopped pretending they were ever capable of delivering a spending plan on time."  With that... a budget extender has been approved to keep the government funded for a week.  Local State Senator George Borrello noted the main sticking point remains.  New York's controversial Climate Leadership and Community Protection Act.  However... Ra -- a Long Island Republican -- says "it epitomizes the dysfunction that surfaces whenever Albany Democrats are forced to complete the most important part of their job."  The governor's proposal totaled $262-billion dollars... while Democrats in the Assembly and Senate propose budgets much larger.  Last year... a final budget was not in place until May 8.Ecklund hopeful city will receive additional, $1-million in State Aid in new budget... but, also says it's time for New York to get real about funding for local governments...As negotiations continue on a new state budget... local municipalities in line to receive additional, temporary aid... are continuing to push the legislature to do that.  The Jamestown City Council approved a resolution Monday night that urges lawmakers in Albany to add that $100-million to the 2026-27 budget.  The city would receive an additional $1-million of that aid.  However... while appreciating Governor Kathy Hochul's proposal... Mayor Kim Ecklund says there needs to be more, additional, permanent aid... with a better process in place.  She says lack of that makes "budgeting very hard."  Ecklund and other mayors... including past Jamestown mayors Eddie Sundquist and Sam Teresi... often talked about the state needing to increase municipal aid more regularily.  If the temporary aid is added to the final budget... the city would receive nearly $1.6-million in aid from New York state.  Woman from Jamestown arrested on 17 counts of endangering after allowing her three young children to be unsupervised multiple times...A city woman has been arrested on 17 counts of endangering the welfare of a child for allegedly leaving her three young child unsupervised multiple times.  Jamestown police say they took 31 year-old Amanda Pearsall into custody Monday afternoon on multiple arrest warrants at an East Second Street address.  Officers say Pearsall was accused of leaving the children... ages 5-months... one-year, and 4-years old... unsupervised in their home in November of last year.  She was arraigned in city court and released pending further court action.Severe thunderstorms produce torrential downpours and hail in north county late Tuesday...Severe thunderstorms with torrential rain and hail rolled through northern Chautauqua County Tuesday afternoon.  A severe thunderstorm warning was issued... with several reports of flooding, downed trees and powerlines impacting several areas.  Meteorologist David Thomas with the National Weather Service in Buffalo says the heavy rainfall around the southern tier... causing mostly ponding and lower level flooding.  Some creeks in the region also overflowed.  Thomas reports that golf ball-sized hail rained through the Gowanda area yesterday, which caused damage to houses and cars... and, resulted in the closing of the Gowanda Central Schools Wednesday.  He also reports that the county saw an estimated 2-3 inches of rainfall across the northern portions of the county. Jamestown man arrested on warrant, meth possession during street check...A city man has been arrested on an active arrest warrant and a drug charge following a street check on Jamestown's northside.  City police say they spotted 45 year-old James Hall walking in the area of North Main and West Sixth Streets shortly before 5 p.m. Monday... and, arrested him without incident.  Oficers say they allegedly found Hall in possession of a small quantity of methamphetamine... and, he was additionally charged with seventh-degree criminal possession of a controlled substance... along with the warrant.  He was held pending arraignment.Gasoline prices continue rising in Jamestown and Chautauqua County...The average cost for a gallon of regular, unleaded gasoline in the Jamestown-area is nearing the $4 a gallon mark as the conflict in Iran continues.  AAA East Central reported Monday that the average price for a gallon in the Jamestown-area was 22 cents higher that last week... and, this week started at $3.92 cents.  However... over the past day... some service stations showed a price of $3.96... and, a few were at $4 a gallon... with one at $4.06.  Nationally... AAA says the average price is about $3.99 a gallon... which is 4-cents higher than the past week... and, crude oil prices remain high as the Iran conflict hits the four-week mark.  The national average could reached $4.02 a gallon Tuesday for the first time since August 2022 when the Ukraine-Russian War broke out.  Gas demand is also on the rise as spring break season continues.  The Energy Information Administration reports gasoline demand increased last week... but, total domestic gas supply decreased.  Boil Water Order lifted Tuesday in Fredonia...The Boil Water Order in the north county village of Fredonia was lifted Tuesday after two consecutive days of testing found turbidity levels safe for consumption.  That from the village, and Chautauqua County Health Department.... who add this also goes for customers in the town of Pomfret.  Officials say operations have returned to "normal..." and, testing indicates that the water in the distribution system is safe for drinking, cooking, making ice, brushing teeth, and making coffee.    </t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2y3ek5nh</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910538/wjtn-news-headlines-for-wed-apr-1-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...Oficers say they allegedly found Hall in possession of a small quantity of **methamphetamine**... and, he was additionally charged with seventh-degree criminal possessio...
+...eet check...A city man has been arrested on an active arrest warrant and a **drug** charge following a street check on Jamestown's northside.  City polic...
+..., he was additionally charged with seventh-degree criminal possession of a **controlled** substance... along with the warrant.  He was held pending arraignment...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prior Felon Sentenced to 70 Months in Federal Prison for Drug and Gun Charges</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Niagara Falls man previously convicted of a felony has been sentenced to more than five years in federal prison for drug trafficking and firearm-related offenses, federal prosecutors announced. Eric Rivera, 39, was sentenced to 70 months in prison by U.S. District Judge Richard J. Arcara after being […]The post Prior Felon Sentenced to 70 Months in Federal Prison for Drug and Gun Charges appeared first on WNY News Now.</t>
+          <t>Russia at Risk of Losing Control of Railways in Armenia - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/31/prior-felon-sentenced-to-70-months-in-federal-prison-for-drug-and-gun-charges/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>...ced to more than five years in federal prison for **drug** trafficking and firearm-related offenses, federal...
-...elon Sentenced to 70 Months in Federal Prison for **Drug** and Gun Charges appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/2y3ek5nh</t>
         </is>
       </c>
     </row>
@@ -462,25 +463,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jamestown Man Arrested on Drug, Traffic Charges Following Vehicle Stop</t>
+          <t>Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 60-year-old Jamestown resident was taken into custody Saturday afternoon after a traffic stop led to the discovery of suspected narcotics, a suspended license, and multiple outstanding warrants. According to the Jamestown Police Department, officers from the department’s 2nd Platoon conducted a vehicle stop at approximately 3:30 p.m. […]The post Jamestown Man Arrested on Drug, Traffic Charges Following Vehicle Stop appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – LOCKPORT, NY — A Niagara Falls woman was taken into custody on felony drug charges following a Niagara County Drug Task Force investigation, authorities confirmed. Daisy N. Ingram, 23, was arrested at a Niagara Street Extension address in the Town of Lockport. She faces multiple felony charges, including second-degree criminal sale […]The post Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/31/jamestown-man-arrested-on-drug-traffic-charges-following-vehicle-stop/</t>
+          <t>https://wnynewsnow.com/2026/04/01/niagara-falls-woman-arrested-on-multiple-drug-charges-in-lockport/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>...y 3:30 p.m. […]The post Jamestown Man Arrested on **Drug**, Traffic Charges Following Vehicle Stop appeared ...</t>
+          <t>...gara Falls woman was taken into custody on felony **drug** charges following a Niagara County Drug Task Forc...
+...on felony drug charges following a Niagara County **Drug** Task Force investigation, authorities confirmed. ...
+...The post Niagara Falls Woman Arrested on Multiple **Drug** Charges in Lockport appeared first on WNY News No...</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -497,25 +500,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jamestown Man Arrested on Warrant, Drug Charge Following Street Check</t>
+          <t>Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 46-year-old Jamestown man was taken into custody Monday afternoon after police identified him during a proactive patrol and discovered an active warrant and suspected drugs. Jamestown Police report that officers were conducting a GIVE (Gun Involved Violence Elimination) detail on March 30, 2026, at approximately 4:53 p.m. […]The post Jamestown Man Arrested on Warrant, Drug Charge Following Street Check appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – OLEAN, N.Y. — A Wellsville woman faces charges after a traffic stop in the City of Olean led to the discovery of a suspended license and suspected narcotics, according to the Cattaraugus County Sheriff’s Office. Cassie J. Degerstedt, 32, of Wellsville, was taken into custody at approximately 12:02 a.m. on March […]The post Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/03/31/jamestown-man-arrested-on-warrant-drug-charge-following-street-check/</t>
+          <t>https://wnynewsnow.com/2026/04/01/olean-woman-charged-with-drug-possession-unlicensed-operation-following-traffic-stop/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>...m. […]The post Jamestown Man Arrested on Warrant, **Drug** Charge Following Street Check appeared first on W...</t>
+          <t>....m. on March […]The post Olean Woman Charged with **Drug** Possession, Unlicensed Operation Following Traffi...</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -527,37 +530,49 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
+          <t>Olean Man Charged with Drug Possession Following Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – OLEAN, N.Y. — A 34-year-old Olean man was arrested Saturday evening after authorities say he was found in possession of suspected fentanyl and drug-related materials during a traffic stop. According to the Cattaraugus County Sheriff’s Office, the incident occurred on March 28, 2026, at approximately 8:24 p.m. on Washington Street in […]The post Olean Man Charged with Drug Possession Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/29jtkdaf</t>
+          <t>https://wnynewsnow.com/2026/04/01/olean-man-charged-with-drug-possession-following-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...ities say he was found in possession of suspected **fentanyl** and drug-related materials during a traffic stop....
+...was found in possession of suspected fentanyl and **drug**-related materials during a traffic stop. Accordin...
+...gton Street in […]The post Olean Man Charged with **Drug** Possession Following Traffic Stop appeared first ...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Mon., Mar. 30, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Four city residents arrested in drug bust late last week...Four people from Jamestown face multiple drug-related charges following a raid on an apartment on the city's westside.  Sheriff's officers say their Narcotics Investigators... and, those from Jamestown... executed a search warrant at 114 West Seventh St. just after 4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of methamphetamine... along with scales and packaging materials used to traffic drugs.  They also seized $4,094 dollars in cash.  Officers arrested 30 year-old James Eastham and 27 year-old Amber Eaton both for second-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  They add that 51 year-old Tracy Brown was arrested for third-degree criminal possession of a controlled substance... second-degree criminally using drug paraphernalia... and, second-degree criminal contempt.  Police arrested 42 year-old Randy Wright for third-degree criminal possession of a controlled Substance... second-degree criminally using drug paraphernalia... and, first-degree criminal contempt.  All four were taken to the city jail pending arraignment.  Anyone with information on illegal narcotics or other criminal activity is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702... or 664-2420... or the JPD Tip line at 483-8477.Catt. County man arrested for allegedly driving with four-times the legal limit of alcohol in his system...A Randolph man is accused of having nearly four times the legal limit of alcohol in his system when he crashed his car on Jamestown's eastside last Saturday morning.  City police were called to the scene on East Fourth Street about 10:30 a.m. on a report of a vehicle leaving the scene of an accident with heavy front-end damage.  Officers say they located the car... and, the driver -- identified as 45 year-old James Bliss -- a short distance away with the airbag deployed.  Police say they determined that Bliss had been driving while intoxicated... and, he ws arrested.  He was taken to the city jail where he consented to a blood test.  Officers say they blood test indicated Bliss's BAC was nearly four times the legal limit of .08%.  He was charged with DWI... Aggravated DWI... and, leaving the scene of a property damage accident.  Bliss was later issued appearance tickets... and, released to a sober third party.More than 300 attend "No Kings" Rally at Jamestown's Dow Park...More than 300 protestors showed up on a bitterly cold morning Saturday at Jamestown's Dow Park for the latest "No Kings" Rally... and, the first since the start of the War in Iran.  The event was hosted by the Jamestown Justice Coalition... and, others.  Coalition member Kate Ebersole spoke at the beginning... reminding those on hand this was a "peaceful" protest.  Coalition Founder Justin Hubbard while they were there to protest the war... and, the Trump Administration's policies... Saturday's rally was not the end.  Hubbard called the rally "a launching pad" to fuel the work they can do in the community, and let their voices be heard.  He also noted that the Jamestown Justice Coalition has just become a 501(c)4... which allows it to advocate... and, raise money.  The last rally raised more than $1,300 for the "New Neighbors Coalition" which supports and advocates for immigrants just arriving in the Jamestown-area.---Saturday's rally raised money for the effort to replace one of the three statues for the Underground Railroad Tableau... which was stolen from Dow Park n 2021.  Hubbard says says it's important to replace that statue because of Jamestown's place in the history of the Underground Railroad. Borrello and Blakeman call for full audit of NYS CDL testing and licensing in wake of 2025 bus crash on NYS Thruway...The region's State Senator is among those calling on a full audit of how commercial drivers are tested... licensed... and monitored in New York.  Sunset Bay Republican George Borrello joined Nassau County Executive and Republican gubernatorial candidate Bruce Blakeman late last week to call for the audit... arguing that last year's deadly bus crash in Pembroke -- along with a series of other recent cases -- has raised serious questions about the integrity of the state’s commercial driver licensing system and whether critical safety standards are being properly enforced.  The pair... along with others... spoke near the site of the Aug. 22, 2025 tour bus crash on the State Thruway near Pembroke, which killed five people and injured more than 40 others.  The driver was later indicted on five counts each of manslaughter and criminally negligent homicide.  At a court hearing... Borrello says the man required a Mandarin interpreter, raising questions about his English proficiency... and, whether New York properly enforced federal CDL standards.Jamestown man gets 10 years in federal prison for trafficking meth...A city man who was an associate of a major, Jamestown-area drug dealer has been sentenced to 10 years in federal prison for trafficking methamphetamine.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-old Aaron Miller, who was convicted of conspiracy to possess with intent to distribute, and to distribute, methamphetamine, received the sentence in U.S. District Court in Buffalo.  Prosecutors say that Miller bought and sold methamphetamine, and cocaine for profit and for his own use.  He received large quantities of meth and cocaine from co-defendant Jun Martinez, the drug dealer, and others.  Miller then distributed the drugs to other individuals in the Jamestown area for profit.  DiGiacomo says co-defendants Jun Martinez, La Huynh, and Antasia Babcock were previously convicted and are awaiting sentencing. </t>
+          <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -565,10 +580,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/29jtkdaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Mon., Mar. 30, 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Four city residents arrested in drug bust late last week...Four people from Jamestown face multiple drug-related charges following a raid on an apartment on the city's westside.  Sheriff's officers say their Narcotics Investigators... and, those from Jamestown... executed a search warrant at 114 West Seventh St. just after 4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of methamphetamine... along with scales and packaging materials used to traffic drugs.  They also seized $4,094 dollars in cash.  Officers arrested 30 year-old James Eastham and 27 year-old Amber Eaton both for second-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  They add that 51 year-old Tracy Brown was arrested for third-degree criminal possession of a controlled substance... second-degree criminally using drug paraphernalia... and, second-degree criminal contempt.  Police arrested 42 year-old Randy Wright for third-degree criminal possession of a controlled Substance... second-degree criminally using drug paraphernalia... and, first-degree criminal contempt.  All four were taken to the city jail pending arraignment.  Anyone with information on illegal narcotics or other criminal activity is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702... or 664-2420... or the JPD Tip line at 483-8477.Catt. County man arrested for allegedly driving with four-times the legal limit of alcohol in his system...A Randolph man is accused of having nearly four times the legal limit of alcohol in his system when he crashed his car on Jamestown's eastside last Saturday morning.  City police were called to the scene on East Fourth Street about 10:30 a.m. on a report of a vehicle leaving the scene of an accident with heavy front-end damage.  Officers say they located the car... and, the driver -- identified as 45 year-old James Bliss -- a short distance away with the airbag deployed.  Police say they determined that Bliss had been driving while intoxicated... and, he ws arrested.  He was taken to the city jail where he consented to a blood test.  Officers say they blood test indicated Bliss's BAC was nearly four times the legal limit of .08%.  He was charged with DWI... Aggravated DWI... and, leaving the scene of a property damage accident.  Bliss was later issued appearance tickets... and, released to a sober third party.More than 300 attend "No Kings" Rally at Jamestown's Dow Park...More than 300 protestors showed up on a bitterly cold morning Saturday at Jamestown's Dow Park for the latest "No Kings" Rally... and, the first since the start of the War in Iran.  The event was hosted by the Jamestown Justice Coalition... and, others.  Coalition member Kate Ebersole spoke at the beginning... reminding those on hand this was a "peaceful" protest.  Coalition Founder Justin Hubbard while they were there to protest the war... and, the Trump Administration's policies... Saturday's rally was not the end.  Hubbard called the rally "a launching pad" to fuel the work they can do in the community, and let their voices be heard.  He also noted that the Jamestown Justice Coalition has just become a 501(c)4... which allows it to advocate... and, raise money.  The last rally raised more than $1,300 for the "New Neighbors Coalition" which supports and advocates for immigrants just arriving in the Jamestown-area.---Saturday's rally raised money for the effort to replace one of the three statues for the Underground Railroad Tableau... which was stolen from Dow Park n 2021.  Hubbard says says it's important to replace that statue because of Jamestown's place in the history of the Underground Railroad. Borrello and Blakeman call for full audit of NYS CDL testing and licensing in wake of 2025 bus crash on NYS Thruway...The region's State Senator is among those calling on a full audit of how commercial drivers are tested... licensed... and monitored in New York.  Sunset Bay Republican George Borrello joined Nassau County Executive and Republican gubernatorial candidate Bruce Blakeman late last week to call for the audit... arguing that last year's deadly bus crash in Pembroke -- along with a series of other recent cases -- has raised serious questions about the integrity of the state’s commercial driver licensing system and whether critical safety standards are being properly enforced.  The pair... along with others... spoke near the site of the Aug. 22, 2025 tour bus crash on the State Thruway near Pembroke, which killed five people and injured more than 40 others.  The driver was later indicted on five counts each of manslaughter and criminally negligent homicide.  At a court hearing... Borrello says the man required a Mandarin interpreter, raising questions about his English proficiency... and, whether New York properly enforced federal CDL standards.Jamestown man gets 10 years in federal prison for trafficking meth...A city man who was an associate of a major, Jamestown-area drug dealer has been sentenced to 10 years in federal prison for trafficking methamphetamine.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-old Aaron Miller, who was convicted of conspiracy to possess with intent to distribute, and to distribute, methamphetamine, received the sentence in U.S. District Court in Buffalo.  Prosecutors say that Miller bought and sold methamphetamine, and cocaine for profit and for his own use.  He received large quantities of meth and cocaine from co-defendant Jun Martinez, the drug dealer, and others.  Miller then distributed the drugs to other individuals in the Jamestown area for profit.  DiGiacomo says co-defendants Jun Martinez, La Huynh, and Antasia Babcock were previously convicted and are awaiting sentencing. </t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46111</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910080/wjtn-news-headlines-for-mon-mar-30-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of **methamphetamine**... along with scales and packaging materials used to traffic drugs.  ...
 ...ug dealer has been sentenced to 10 years in federal prison for trafficking **methamphetamine**.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-...
@@ -586,226 +626,9 @@
 ...rrested 42 year-old Randy Wright for third-degree criminal possession of a **controlled** Substance... second-degree criminally using drug paraphernalia... and, fir...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Four Arrested After Jamestown Drug Raid; Over 200 Grams of Meth Seized</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — Four Jamestown residents are facing felony drug charges following the execution of a search warrant that resulted in the seizure of a large quantity of methamphetamine and cash, according to local authorities. Narcotics investigators from the Chautauqua County Sheriff’s Office and Jamestown Police Department executed a search warrant […]The post Four Arrested After Jamestown Drug Raid; Over 200 Grams of Meth Seized appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46111</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/30/four-arrested-after-jamestown-drug-raid-over-200-grams-of-meth-seized/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>...at resulted in the seizure of a large quantity of **methamphetamine** and cash, according to local authorities. Narcoti...
-...N.Y. — Four Jamestown residents are facing felony **drug** charges following the execution of a search warra...
-...warrant […]The post Four Arrested After Jamestown **Drug** Raid; Over 200 Grams of Meth Seized appeared firs...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Randolph Man Charged with Aggravated DWI After Leaving Scene of Crash In Jamestown</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – A Randolph man is facing multiple charges after police say he left the scene of a property damage accident in Jamestown while allegedly intoxicated. JAMESTOWN, N.Y. — Officers from the Jamestown Police Department responded to a reported motor vehicle accident at the intersection of East 4th Street and North Main Street […]The post Randolph Man Charged with Aggravated DWI After Leaving Scene of Crash In Jamestown appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46111</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/30/randolph-man-charged-with-aggravated-dwi-after-leaving-scene-of-crash-in-jamestown/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>...erty damage accident in Jamestown while allegedly **intoxicated**. JAMESTOWN, N.Y. — Officers from the Jamestown Po...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged with DWI Following Early Morning Traffic Stop in Pomfret</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – POMFRET, N.Y. — A Jamestown man is facing multiple charges after a traffic stop early Sunday morning in the Town of Pomfret led to a driving while intoxicated arrest. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on Route 60 at approximately 2:31 a.m. on March 29. […]The post Jamestown Man Charged with DWI Following Early Morning Traffic Stop in Pomfret appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46111</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/30/jamestown-man-charged-with-dwi-following-early-morning-traffic-stop-in-pomfret/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>...ing in the Town of Pomfret led to a driving while **intoxicated** arrest. According to the Chautauqua County Sherif...</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Falconer Man Charged with DWI Following Early Morning Traffic Stop in Ellicott</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – ELLICOTT, N.Y. — A Falconer man faces multiple charges after a traffic stop early Saturday morning in the Town of Ellicott led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on Fairmount Avenue at approximately 1:46 a.m. on March 28, 2026. […]The post Falconer Man Charged with DWI Following Early Morning Traffic Stop in Ellicott appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46111</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/30/falconer-man-charged-with-dwi-following-early-morning-traffic-stop-in-ellicott/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...ng in the Town of Ellicott led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hanover Man Charged with DWI Following Early Morning Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – HANOVER, N.Y. — A 62-year-old man was arrested early Sunday morning after a traffic stop in the Town of Hanover led to driving while intoxicated charges, according to the Chautauqua County Sheriff’s Office. Deputies reported that at approximately 1:38 a.m. on March 29, 2026, a vehicle was stopped near the intersection […]The post Hanover Man Charged with DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46111</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/03/30/hanover-man-charged-with-dwi-following-early-morning-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>... stop in the Town of Hanover led to driving while **intoxicated** charges, according to the Chautauqua County Sheri...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Man Conceals Fentanyl in His Body After Jamestown Drug Bust - Erie News Now</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46106</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/249k877s</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Street check leads to 4.25 oz. fentanyl bust, weapons found: Jamestown police - MSN</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46106</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/279l6oks</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,214 +401,290 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/292m8jvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/23gxelxt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Apr. 2, 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Seinfelt, Meyers and Kreischer to headline August's National Comedy Festival in Jamestown....Two well-established names... and, one rising star have been announced as headliners for this year's 35th annual National Comedy Festival in Jamestown.  The National Comedy Center has announced that Jerry Seinfeld... Bert Kreischer... and, Seth Meyers will headline the annual festival on August 6-9 of this year.  In addition... for the first time... this year's festival will have all three headliners performing at the Northwest Arena... and, additional talent will be featured in the Stand-up Showcases and late-night comedy shows throughout the festival.  Seinfeld will headline on Thursday, Aug. 6... Kreischer will take the stage on Saturday the 8th... and, Seth Meyers will perform on Sunday, Aug. 9.  On Friday the 7th... there will be a Stand-up Showcase at the Reg Lenna Center for the Arts.  Comedy Center Executive Director Journey Gunderson says -- "this year’s festival brings together artists who represent distinct approaches to the craft. I love that audiences can experience the best of live comedy while connecting it to the larger story we preserve and share every day in Jamestown."  Tickets for the headlining shows and festival events will go on pre-sale for Comedy Center members beginning Monday, Apr. 27 at 12 p.m. EDT... and, for the general public on Friday, May 1 at Noon EDT at ComedyCenter.org.  For more information... you can also call (716)-484-2222.Sex offender arrested on new child porn charges in Jamestown...A registered sex offender from Jamestown has been arrested on new, federal child pornography charges.  U.S. Attorney Michael DiGiacomo has announced that 42 year-old John Peterson was arrested Wednesday... and, charged with distribution and possession of child pornography by a person with a prior child porn conviction.  Prosecutors say last June... the National Center for Missing and Exploited Children received a CyberTip from the messaging app "Kik" that two files of suspected child porn were uploaded between June 14-16 of 2025.  The files were uploaded with the username "hardinny41_mkc..." and, were shared with other users.  The center the received another tip from Kik on July 5... that a file of suspected child pornography was uploaded on June 28 by someone with the same username.  Subsequent investigation traced the uploaded files to Peterson.  Investigators in December obtained a warrant... and, seized Peterson’s cell phone.  They allegedly found about 9 image files... and, 5 video files of suspected child sexual abuse material.  He was convicted in 2010 in Carroll Town Court of attempted possession of a sexual performance by a child less than 16 Year of Age.  He was then convicted in 2023 in Chautauqua County Court of possessing a sexual performance by a child less than 16 Years of age, and criminal possession of a firearm.  Peterson faces a manditory minimum of 15 years in prison... a maximum of 40... and, a $250,000 fine.Borrello says, given policy differences among Democrats on Climate Act, a state budget may be later than last year...The late New York state budget will likely be later than even last year when negotiations went into early May.  Those are the feelings of State Senator George Borrello... who says... with the Apr. 1 deadline looming late Tuesday... the legislature approved a one-week budget extension.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040... but, he calls it nothing more than "window dressing..." and energy costs continue to go up.  One of the early parts of the "Climate Leadership and Community Protection Act" was a ban on use of fossils fuels to power newer, and smaller homes being built this year.  However... that was stopped by a court order... and, Hochul delayed the move for a year.  Borrello says that's merely an "Election Year" ploy to avoid the issue until after November.  He says he's spoken with officials from National Grid, who say while they're building new power plants in other states, they aren't in New York.  The legislature is soon leaving Albany for the Passover-Easter Break... and, will be back in session next Tuesday.  Governor Hochul's budget proposal totaled $262-billion... while the Senate and Assembly versions range from $8-billion to $10-billion more.Jamestown man arrested on drug charge following traffic stop...A man from Jamestown has been arrested on several warrants following a traffic stop on the city's southside last Saturday.  Jamestown police say a patrol spotted the car commit a traffic violation about 3:30 p.m., and, stopped the vehicle in the area of Cole Avenue and Myrtle Steet.  Officers say they found that the driver -- 60 year-old David Robbins -- was sought on several Jamestown and State Police bench warrants.  Police also found that Robbins was driving with a suspended license... and, was in possession of a quantity of cocaine.  He was charged with seventh-degree criminal possession of a controlled substance... second-degree aggravated unlicensed operator... and, held pending arraignment. </t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910712/wjtn-news-headlines-for-thurs-apr-2-2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...rsions range from $8-billion to $10-billion more.Jamestown man arrested on **drug** charge following traffic stop...A man from Jamestown has been arrested on ...
+...cocaine.  He was charged with seventh-degree criminal possession of a **controlled** substance... second-degree aggravated unlicensed operator... and, held pen...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Wed., Apr. 1, 2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>NYS budget late for sixth-straight year, legislature approves one-week extender...For the sixth-year in a row... New York will have a late state budget, although negotiations between legislative leaders and Governor Kathy Hochul are ongoing.  In a late afternoon press release Tuesday... Assembly Minority Leader Ed Ra said -- "the  only credit Democrats deserve is that, weeks ago, they stopped pretending they were ever capable of delivering a spending plan on time."  With that... a budget extender has been approved to keep the government funded for a week.  Local State Senator George Borrello noted the main sticking point remains.  New York's controversial Climate Leadership and Community Protection Act.  However... Ra -- a Long Island Republican -- says "it epitomizes the dysfunction that surfaces whenever Albany Democrats are forced to complete the most important part of their job."  The governor's proposal totaled $262-billion dollars... while Democrats in the Assembly and Senate propose budgets much larger.  Last year... a final budget was not in place until May 8.Ecklund hopeful city will receive additional, $1-million in State Aid in new budget... but, also says it's time for New York to get real about funding for local governments...As negotiations continue on a new state budget... local municipalities in line to receive additional, temporary aid... are continuing to push the legislature to do that.  The Jamestown City Council approved a resolution Monday night that urges lawmakers in Albany to add that $100-million to the 2026-27 budget.  The city would receive an additional $1-million of that aid.  However... while appreciating Governor Kathy Hochul's proposal... Mayor Kim Ecklund says there needs to be more, additional, permanent aid... with a better process in place.  She says lack of that makes "budgeting very hard."  Ecklund and other mayors... including past Jamestown mayors Eddie Sundquist and Sam Teresi... often talked about the state needing to increase municipal aid more regularily.  If the temporary aid is added to the final budget... the city would receive nearly $1.6-million in aid from New York state.  Woman from Jamestown arrested on 17 counts of endangering after allowing her three young children to be unsupervised multiple times...A city woman has been arrested on 17 counts of endangering the welfare of a child for allegedly leaving her three young child unsupervised multiple times.  Jamestown police say they took 31 year-old Amanda Pearsall into custody Monday afternoon on multiple arrest warrants at an East Second Street address.  Officers say Pearsall was accused of leaving the children... ages 5-months... one-year, and 4-years old... unsupervised in their home in November of last year.  She was arraigned in city court and released pending further court action.Severe thunderstorms produce torrential downpours and hail in north county late Tuesday...Severe thunderstorms with torrential rain and hail rolled through northern Chautauqua County Tuesday afternoon.  A severe thunderstorm warning was issued... with several reports of flooding, downed trees and powerlines impacting several areas.  Meteorologist David Thomas with the National Weather Service in Buffalo says the heavy rainfall around the southern tier... causing mostly ponding and lower level flooding.  Some creeks in the region also overflowed.  Thomas reports that golf ball-sized hail rained through the Gowanda area yesterday, which caused damage to houses and cars... and, resulted in the closing of the Gowanda Central Schools Wednesday.  He also reports that the county saw an estimated 2-3 inches of rainfall across the northern portions of the county. Jamestown man arrested on warrant, meth possession during street check...A city man has been arrested on an active arrest warrant and a drug charge following a street check on Jamestown's northside.  City police say they spotted 45 year-old James Hall walking in the area of North Main and West Sixth Streets shortly before 5 p.m. Monday... and, arrested him without incident.  Oficers say they allegedly found Hall in possession of a small quantity of methamphetamine... and, he was additionally charged with seventh-degree criminal possession of a controlled substance... along with the warrant.  He was held pending arraignment.Gasoline prices continue rising in Jamestown and Chautauqua County...The average cost for a gallon of regular, unleaded gasoline in the Jamestown-area is nearing the $4 a gallon mark as the conflict in Iran continues.  AAA East Central reported Monday that the average price for a gallon in the Jamestown-area was 22 cents higher that last week... and, this week started at $3.92 cents.  However... over the past day... some service stations showed a price of $3.96... and, a few were at $4 a gallon... with one at $4.06.  Nationally... AAA says the average price is about $3.99 a gallon... which is 4-cents higher than the past week... and, crude oil prices remain high as the Iran conflict hits the four-week mark.  The national average could reached $4.02 a gallon Tuesday for the first time since August 2022 when the Ukraine-Russian War broke out.  Gas demand is also on the rise as spring break season continues.  The Energy Information Administration reports gasoline demand increased last week... but, total domestic gas supply decreased.  Boil Water Order lifted Tuesday in Fredonia...The Boil Water Order in the north county village of Fredonia was lifted Tuesday after two consecutive days of testing found turbidity levels safe for consumption.  That from the village, and Chautauqua County Health Department.... who add this also goes for customers in the town of Pomfret.  Officials say operations have returned to "normal..." and, testing indicates that the water in the distribution system is safe for drinking, cooking, making ice, brushing teeth, and making coffee.    </t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D5" s="2">
         <v>46114</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910538/wjtn-news-headlines-for-wed-apr-1-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...Oficers say they allegedly found Hall in possession of a small quantity of **methamphetamine**... and, he was additionally charged with seventh-degree criminal possessio...
 ...eet check...A city man has been arrested on an active arrest warrant and a **drug** charge following a street check on Jamestown's northside.  City polic...
 ..., he was additionally charged with seventh-degree criminal possession of a **controlled** substance... along with the warrant.  He was held pending arraignment...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Russia at Risk of Losing Control of Railways in Armenia - The Jamestown Foundation</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D6" s="2">
         <v>46113</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://tinyurl.com/2y3ek5nh</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>(WNY News Now) – LOCKPORT, NY — A Niagara Falls woman was taken into custody on felony drug charges following a Niagara County Drug Task Force investigation, authorities confirmed. Daisy N. Ingram, 23, was arrested at a Niagara Street Extension address in the Town of Lockport. She faces multiple felony charges, including second-degree criminal sale […]The post Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D7" s="2">
         <v>46113</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/niagara-falls-woman-arrested-on-multiple-drug-charges-in-lockport/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...gara Falls woman was taken into custody on felony **drug** charges following a Niagara County Drug Task Forc...
 ...on felony drug charges following a Niagara County **Drug** Task Force investigation, authorities confirmed. ...
 ...The post Niagara Falls Woman Arrested on Multiple **Drug** Charges in Lockport appeared first on WNY News No...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>(WNY News Now) – OLEAN, N.Y. — A Wellsville woman faces charges after a traffic stop in the City of Olean led to the discovery of a suspended license and suspected narcotics, according to the Cattaraugus County Sheriff’s Office. Cassie J. Degerstedt, 32, of Wellsville, was taken into custody at approximately 12:02 a.m. on March […]The post Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D8" s="2">
         <v>46113</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/olean-woman-charged-with-drug-possession-unlicensed-operation-following-traffic-stop/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>....m. on March […]The post Olean Woman Charged with **Drug** Possession, Unlicensed Operation Following Traffi...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Olean Man Charged with Drug Possession Following Traffic Stop</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>(WNY News Now) – OLEAN, N.Y. — A 34-year-old Olean man was arrested Saturday evening after authorities say he was found in possession of suspected fentanyl and drug-related materials during a traffic stop. According to the Cattaraugus County Sheriff’s Office, the incident occurred on March 28, 2026, at approximately 8:24 p.m. on Washington Street in […]The post Olean Man Charged with Drug Possession Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D9" s="2">
         <v>46113</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/olean-man-charged-with-drug-possession-following-traffic-stop/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...ities say he was found in possession of suspected **fentanyl** and drug-related materials during a traffic stop....
 ...was found in possession of suspected fentanyl and **drug**-related materials during a traffic stop. Accordin...
 ...gton Street in […]The post Olean Man Charged with **Drug** Possession Following Traffic Stop appeared first ...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D10" s="2">
         <v>46111</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://tinyurl.com/29jtkdaf</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Mon., Mar. 30, 2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>14 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Four city residents arrested in drug bust late last week...Four people from Jamestown face multiple drug-related charges following a raid on an apartment on the city's westside.  Sheriff's officers say their Narcotics Investigators... and, those from Jamestown... executed a search warrant at 114 West Seventh St. just after 4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of methamphetamine... along with scales and packaging materials used to traffic drugs.  They also seized $4,094 dollars in cash.  Officers arrested 30 year-old James Eastham and 27 year-old Amber Eaton both for second-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  They add that 51 year-old Tracy Brown was arrested for third-degree criminal possession of a controlled substance... second-degree criminally using drug paraphernalia... and, second-degree criminal contempt.  Police arrested 42 year-old Randy Wright for third-degree criminal possession of a controlled Substance... second-degree criminally using drug paraphernalia... and, first-degree criminal contempt.  All four were taken to the city jail pending arraignment.  Anyone with information on illegal narcotics or other criminal activity is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702... or 664-2420... or the JPD Tip line at 483-8477.Catt. County man arrested for allegedly driving with four-times the legal limit of alcohol in his system...A Randolph man is accused of having nearly four times the legal limit of alcohol in his system when he crashed his car on Jamestown's eastside last Saturday morning.  City police were called to the scene on East Fourth Street about 10:30 a.m. on a report of a vehicle leaving the scene of an accident with heavy front-end damage.  Officers say they located the car... and, the driver -- identified as 45 year-old James Bliss -- a short distance away with the airbag deployed.  Police say they determined that Bliss had been driving while intoxicated... and, he ws arrested.  He was taken to the city jail where he consented to a blood test.  Officers say they blood test indicated Bliss's BAC was nearly four times the legal limit of .08%.  He was charged with DWI... Aggravated DWI... and, leaving the scene of a property damage accident.  Bliss was later issued appearance tickets... and, released to a sober third party.More than 300 attend "No Kings" Rally at Jamestown's Dow Park...More than 300 protestors showed up on a bitterly cold morning Saturday at Jamestown's Dow Park for the latest "No Kings" Rally... and, the first since the start of the War in Iran.  The event was hosted by the Jamestown Justice Coalition... and, others.  Coalition member Kate Ebersole spoke at the beginning... reminding those on hand this was a "peaceful" protest.  Coalition Founder Justin Hubbard while they were there to protest the war... and, the Trump Administration's policies... Saturday's rally was not the end.  Hubbard called the rally "a launching pad" to fuel the work they can do in the community, and let their voices be heard.  He also noted that the Jamestown Justice Coalition has just become a 501(c)4... which allows it to advocate... and, raise money.  The last rally raised more than $1,300 for the "New Neighbors Coalition" which supports and advocates for immigrants just arriving in the Jamestown-area.---Saturday's rally raised money for the effort to replace one of the three statues for the Underground Railroad Tableau... which was stolen from Dow Park n 2021.  Hubbard says says it's important to replace that statue because of Jamestown's place in the history of the Underground Railroad. Borrello and Blakeman call for full audit of NYS CDL testing and licensing in wake of 2025 bus crash on NYS Thruway...The region's State Senator is among those calling on a full audit of how commercial drivers are tested... licensed... and monitored in New York.  Sunset Bay Republican George Borrello joined Nassau County Executive and Republican gubernatorial candidate Bruce Blakeman late last week to call for the audit... arguing that last year's deadly bus crash in Pembroke -- along with a series of other recent cases -- has raised serious questions about the integrity of the state’s commercial driver licensing system and whether critical safety standards are being properly enforced.  The pair... along with others... spoke near the site of the Aug. 22, 2025 tour bus crash on the State Thruway near Pembroke, which killed five people and injured more than 40 others.  The driver was later indicted on five counts each of manslaughter and criminally negligent homicide.  At a court hearing... Borrello says the man required a Mandarin interpreter, raising questions about his English proficiency... and, whether New York properly enforced federal CDL standards.Jamestown man gets 10 years in federal prison for trafficking meth...A city man who was an associate of a major, Jamestown-area drug dealer has been sentenced to 10 years in federal prison for trafficking methamphetamine.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-old Aaron Miller, who was convicted of conspiracy to possess with intent to distribute, and to distribute, methamphetamine, received the sentence in U.S. District Court in Buffalo.  Prosecutors say that Miller bought and sold methamphetamine, and cocaine for profit and for his own use.  He received large quantities of meth and cocaine from co-defendant Jun Martinez, the drug dealer, and others.  Miller then distributed the drugs to other individuals in the Jamestown area for profit.  DiGiacomo says co-defendants Jun Martinez, La Huynh, and Antasia Babcock were previously convicted and are awaiting sentencing. </t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D11" s="2">
         <v>46111</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910080/wjtn-news-headlines-for-mon-mar-30-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of **methamphetamine**... along with scales and packaging materials used to traffic drugs.  ...
 ...ug dealer has been sentenced to 10 years in federal prison for trafficking **methamphetamine**.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-...
@@ -626,7 +702,7 @@
 ...rrested 42 year-old Randy Wright for third-degree criminal possession of a **controlled** Substance... second-degree criminally using drug paraphernalia... and, fir...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,15 +406,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+          <t>Dunkirk man in standoff facing federal charges for drugs, weapons - observertoday.com</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/292m8jvo</t>
+          <t>https://tinyurl.com/25f9m6qw</t>
         </is>
       </c>
     </row>
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -434,24 +434,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23gxelxt</t>
+          <t>https://tinyurl.com/2yl5qzyb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Thurs., Apr. 2, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Seinfelt, Meyers and Kreischer to headline August's National Comedy Festival in Jamestown....Two well-established names... and, one rising star have been announced as headliners for this year's 35th annual National Comedy Festival in Jamestown.  The National Comedy Center has announced that Jerry Seinfeld... Bert Kreischer... and, Seth Meyers will headline the annual festival on August 6-9 of this year.  In addition... for the first time... this year's festival will have all three headliners performing at the Northwest Arena... and, additional talent will be featured in the Stand-up Showcases and late-night comedy shows throughout the festival.  Seinfeld will headline on Thursday, Aug. 6... Kreischer will take the stage on Saturday the 8th... and, Seth Meyers will perform on Sunday, Aug. 9.  On Friday the 7th... there will be a Stand-up Showcase at the Reg Lenna Center for the Arts.  Comedy Center Executive Director Journey Gunderson says -- "this year’s festival brings together artists who represent distinct approaches to the craft. I love that audiences can experience the best of live comedy while connecting it to the larger story we preserve and share every day in Jamestown."  Tickets for the headlining shows and festival events will go on pre-sale for Comedy Center members beginning Monday, Apr. 27 at 12 p.m. EDT... and, for the general public on Friday, May 1 at Noon EDT at ComedyCenter.org.  For more information... you can also call (716)-484-2222.Sex offender arrested on new child porn charges in Jamestown...A registered sex offender from Jamestown has been arrested on new, federal child pornography charges.  U.S. Attorney Michael DiGiacomo has announced that 42 year-old John Peterson was arrested Wednesday... and, charged with distribution and possession of child pornography by a person with a prior child porn conviction.  Prosecutors say last June... the National Center for Missing and Exploited Children received a CyberTip from the messaging app "Kik" that two files of suspected child porn were uploaded between June 14-16 of 2025.  The files were uploaded with the username "hardinny41_mkc..." and, were shared with other users.  The center the received another tip from Kik on July 5... that a file of suspected child pornography was uploaded on June 28 by someone with the same username.  Subsequent investigation traced the uploaded files to Peterson.  Investigators in December obtained a warrant... and, seized Peterson’s cell phone.  They allegedly found about 9 image files... and, 5 video files of suspected child sexual abuse material.  He was convicted in 2010 in Carroll Town Court of attempted possession of a sexual performance by a child less than 16 Year of Age.  He was then convicted in 2023 in Chautauqua County Court of possessing a sexual performance by a child less than 16 Years of age, and criminal possession of a firearm.  Peterson faces a manditory minimum of 15 years in prison... a maximum of 40... and, a $250,000 fine.Borrello says, given policy differences among Democrats on Climate Act, a state budget may be later than last year...The late New York state budget will likely be later than even last year when negotiations went into early May.  Those are the feelings of State Senator George Borrello... who says... with the Apr. 1 deadline looming late Tuesday... the legislature approved a one-week budget extension.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040... but, he calls it nothing more than "window dressing..." and energy costs continue to go up.  One of the early parts of the "Climate Leadership and Community Protection Act" was a ban on use of fossils fuels to power newer, and smaller homes being built this year.  However... that was stopped by a court order... and, Hochul delayed the move for a year.  Borrello says that's merely an "Election Year" ploy to avoid the issue until after November.  He says he's spoken with officials from National Grid, who say while they're building new power plants in other states, they aren't in New York.  The legislature is soon leaving Albany for the Passover-Easter Break... and, will be back in session next Tuesday.  Governor Hochul's budget proposal totaled $262-billion... while the Senate and Assembly versions range from $8-billion to $10-billion more.Jamestown man arrested on drug charge following traffic stop...A man from Jamestown has been arrested on several warrants following a traffic stop on the city's southside last Saturday.  Jamestown police say a patrol spotted the car commit a traffic violation about 3:30 p.m., and, stopped the vehicle in the area of Cole Avenue and Myrtle Steet.  Officers say they found that the driver -- 60 year-old David Robbins -- was sought on several Jamestown and State Police bench warrants.  Police also found that Robbins was driving with a suspended license... and, was in possession of a quantity of cocaine.  He was charged with seventh-degree criminal possession of a controlled substance... second-degree aggravated unlicensed operator... and, held pending arraignment. </t>
+          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -459,232 +454,326 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/292m8jvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/23gxelxt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910825/wjtn-news-headlines-for-fri-apr-3-2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl** and cocaine... maintaining a drug involved premises... and being a user of...
+...cutors say in March of 2024... investigators made a controlled purchase of **fentanyl** from Anabell Santiago.... and, the following month... they raided the home...
+... of Santiago and her husband, Santo on Whitley Avenue.  Police seized **fentanyl**, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30...
+...eared... officers say they seized about 197-grams of suspected psychedelic **mushrooms**... about 11 pounds of suspected marijuana... three guns... about $30,000 i...
+City woman receives 8-year federal sentence for **drug** trafficking...A Jamestown woman has been sentenced to seven-years in feder...
+...oman has been sentenced to seven-years in federal prison for her role in a **drug** trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announce...
+...d to distribute, 40 grams or more of fentanyl and cocaine... maintaining a **drug** involved premises... and being a user of a controlled substance in possess...
+...xycodone, two loaded pistols, ammunition... more than $30,000 in cash, and **drug** paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sen...
+...topher Marcinowski has been charged by criminal complaint of maintaining a **drug** involved premises... and, being a felon in possession of a firearm.  ...
+...'s Narcotics Unit began assisting with an investigation into Marcinowski's **drug** trafficking activities.  During the past two months... they say inves...
+... pounds of suspected marijuana... three guns... about $30,000 in cash, and **drug** paraphernalia.  Marcinowski has three prior federal convictions... an...
+...7-grams of suspected psychedelic mushrooms... about 11 pounds of suspected **marijuana**... three guns... about $30,000 in cash, and drug paraphernalia.  Marc...
+...and, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, **oxycodone**, two loaded pistols, ammunition... more than $30,000 in cash, and drug par...
+...d cocaine... maintaining a drug involved premises... and being a user of a **controlled** substance in possession of firearms.  Prosecutors say in March of 202...
+...f firearms.  Prosecutors say in March of 2024... investigators made a **controlled** purchase of fentanyl from Anabell Santiago.... and, the following month......</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Apr. 2, 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Seinfelt, Meyers and Kreischer to headline August's National Comedy Festival in Jamestown....Two well-established names... and, one rising star have been announced as headliners for this year's 35th annual National Comedy Festival in Jamestown.  The National Comedy Center has announced that Jerry Seinfeld... Bert Kreischer... and, Seth Meyers will headline the annual festival on August 6-9 of this year.  In addition... for the first time... this year's festival will have all three headliners performing at the Northwest Arena... and, additional talent will be featured in the Stand-up Showcases and late-night comedy shows throughout the festival.  Seinfeld will headline on Thursday, Aug. 6... Kreischer will take the stage on Saturday the 8th... and, Seth Meyers will perform on Sunday, Aug. 9.  On Friday the 7th... there will be a Stand-up Showcase at the Reg Lenna Center for the Arts.  Comedy Center Executive Director Journey Gunderson says -- "this year’s festival brings together artists who represent distinct approaches to the craft. I love that audiences can experience the best of live comedy while connecting it to the larger story we preserve and share every day in Jamestown."  Tickets for the headlining shows and festival events will go on pre-sale for Comedy Center members beginning Monday, Apr. 27 at 12 p.m. EDT... and, for the general public on Friday, May 1 at Noon EDT at ComedyCenter.org.  For more information... you can also call (716)-484-2222.Sex offender arrested on new child porn charges in Jamestown...A registered sex offender from Jamestown has been arrested on new, federal child pornography charges.  U.S. Attorney Michael DiGiacomo has announced that 42 year-old John Peterson was arrested Wednesday... and, charged with distribution and possession of child pornography by a person with a prior child porn conviction.  Prosecutors say last June... the National Center for Missing and Exploited Children received a CyberTip from the messaging app "Kik" that two files of suspected child porn were uploaded between June 14-16 of 2025.  The files were uploaded with the username "hardinny41_mkc..." and, were shared with other users.  The center the received another tip from Kik on July 5... that a file of suspected child pornography was uploaded on June 28 by someone with the same username.  Subsequent investigation traced the uploaded files to Peterson.  Investigators in December obtained a warrant... and, seized Peterson’s cell phone.  They allegedly found about 9 image files... and, 5 video files of suspected child sexual abuse material.  He was convicted in 2010 in Carroll Town Court of attempted possession of a sexual performance by a child less than 16 Year of Age.  He was then convicted in 2023 in Chautauqua County Court of possessing a sexual performance by a child less than 16 Years of age, and criminal possession of a firearm.  Peterson faces a manditory minimum of 15 years in prison... a maximum of 40... and, a $250,000 fine.Borrello says, given policy differences among Democrats on Climate Act, a state budget may be later than last year...The late New York state budget will likely be later than even last year when negotiations went into early May.  Those are the feelings of State Senator George Borrello... who says... with the Apr. 1 deadline looming late Tuesday... the legislature approved a one-week budget extension.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040... but, he calls it nothing more than "window dressing..." and energy costs continue to go up.  One of the early parts of the "Climate Leadership and Community Protection Act" was a ban on use of fossils fuels to power newer, and smaller homes being built this year.  However... that was stopped by a court order... and, Hochul delayed the move for a year.  Borrello says that's merely an "Election Year" ploy to avoid the issue until after November.  He says he's spoken with officials from National Grid, who say while they're building new power plants in other states, they aren't in New York.  The legislature is soon leaving Albany for the Passover-Easter Break... and, will be back in session next Tuesday.  Governor Hochul's budget proposal totaled $262-billion... while the Senate and Assembly versions range from $8-billion to $10-billion more.Jamestown man arrested on drug charge following traffic stop...A man from Jamestown has been arrested on several warrants following a traffic stop on the city's southside last Saturday.  Jamestown police say a patrol spotted the car commit a traffic violation about 3:30 p.m., and, stopped the vehicle in the area of Cole Avenue and Myrtle Steet.  Officers say they found that the driver -- 60 year-old David Robbins -- was sought on several Jamestown and State Police bench warrants.  Police also found that Robbins was driving with a suspended license... and, was in possession of a quantity of cocaine.  He was charged with seventh-degree criminal possession of a controlled substance... second-degree aggravated unlicensed operator... and, held pending arraignment. </t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910712/wjtn-news-headlines-for-thurs-apr-2-2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...rsions range from $8-billion to $10-billion more.Jamestown man arrested on **drug** charge following traffic stop...A man from Jamestown has been arrested on ...
 ...cocaine.  He was charged with seventh-degree criminal possession of a **controlled** substance... second-degree aggravated unlicensed operator... and, held pen...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 1, 2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>NYS budget late for sixth-straight year, legislature approves one-week extender...For the sixth-year in a row... New York will have a late state budget, although negotiations between legislative leaders and Governor Kathy Hochul are ongoing.  In a late afternoon press release Tuesday... Assembly Minority Leader Ed Ra said -- "the  only credit Democrats deserve is that, weeks ago, they stopped pretending they were ever capable of delivering a spending plan on time."  With that... a budget extender has been approved to keep the government funded for a week.  Local State Senator George Borrello noted the main sticking point remains.  New York's controversial Climate Leadership and Community Protection Act.  However... Ra -- a Long Island Republican -- says "it epitomizes the dysfunction that surfaces whenever Albany Democrats are forced to complete the most important part of their job."  The governor's proposal totaled $262-billion dollars... while Democrats in the Assembly and Senate propose budgets much larger.  Last year... a final budget was not in place until May 8.Ecklund hopeful city will receive additional, $1-million in State Aid in new budget... but, also says it's time for New York to get real about funding for local governments...As negotiations continue on a new state budget... local municipalities in line to receive additional, temporary aid... are continuing to push the legislature to do that.  The Jamestown City Council approved a resolution Monday night that urges lawmakers in Albany to add that $100-million to the 2026-27 budget.  The city would receive an additional $1-million of that aid.  However... while appreciating Governor Kathy Hochul's proposal... Mayor Kim Ecklund says there needs to be more, additional, permanent aid... with a better process in place.  She says lack of that makes "budgeting very hard."  Ecklund and other mayors... including past Jamestown mayors Eddie Sundquist and Sam Teresi... often talked about the state needing to increase municipal aid more regularily.  If the temporary aid is added to the final budget... the city would receive nearly $1.6-million in aid from New York state.  Woman from Jamestown arrested on 17 counts of endangering after allowing her three young children to be unsupervised multiple times...A city woman has been arrested on 17 counts of endangering the welfare of a child for allegedly leaving her three young child unsupervised multiple times.  Jamestown police say they took 31 year-old Amanda Pearsall into custody Monday afternoon on multiple arrest warrants at an East Second Street address.  Officers say Pearsall was accused of leaving the children... ages 5-months... one-year, and 4-years old... unsupervised in their home in November of last year.  She was arraigned in city court and released pending further court action.Severe thunderstorms produce torrential downpours and hail in north county late Tuesday...Severe thunderstorms with torrential rain and hail rolled through northern Chautauqua County Tuesday afternoon.  A severe thunderstorm warning was issued... with several reports of flooding, downed trees and powerlines impacting several areas.  Meteorologist David Thomas with the National Weather Service in Buffalo says the heavy rainfall around the southern tier... causing mostly ponding and lower level flooding.  Some creeks in the region also overflowed.  Thomas reports that golf ball-sized hail rained through the Gowanda area yesterday, which caused damage to houses and cars... and, resulted in the closing of the Gowanda Central Schools Wednesday.  He also reports that the county saw an estimated 2-3 inches of rainfall across the northern portions of the county. Jamestown man arrested on warrant, meth possession during street check...A city man has been arrested on an active arrest warrant and a drug charge following a street check on Jamestown's northside.  City police say they spotted 45 year-old James Hall walking in the area of North Main and West Sixth Streets shortly before 5 p.m. Monday... and, arrested him without incident.  Oficers say they allegedly found Hall in possession of a small quantity of methamphetamine... and, he was additionally charged with seventh-degree criminal possession of a controlled substance... along with the warrant.  He was held pending arraignment.Gasoline prices continue rising in Jamestown and Chautauqua County...The average cost for a gallon of regular, unleaded gasoline in the Jamestown-area is nearing the $4 a gallon mark as the conflict in Iran continues.  AAA East Central reported Monday that the average price for a gallon in the Jamestown-area was 22 cents higher that last week... and, this week started at $3.92 cents.  However... over the past day... some service stations showed a price of $3.96... and, a few were at $4 a gallon... with one at $4.06.  Nationally... AAA says the average price is about $3.99 a gallon... which is 4-cents higher than the past week... and, crude oil prices remain high as the Iran conflict hits the four-week mark.  The national average could reached $4.02 a gallon Tuesday for the first time since August 2022 when the Ukraine-Russian War broke out.  Gas demand is also on the rise as spring break season continues.  The Energy Information Administration reports gasoline demand increased last week... but, total domestic gas supply decreased.  Boil Water Order lifted Tuesday in Fredonia...The Boil Water Order in the north county village of Fredonia was lifted Tuesday after two consecutive days of testing found turbidity levels safe for consumption.  That from the village, and Chautauqua County Health Department.... who add this also goes for customers in the town of Pomfret.  Officials say operations have returned to "normal..." and, testing indicates that the water in the distribution system is safe for drinking, cooking, making ice, brushing teeth, and making coffee.    </t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D8" s="2">
         <v>46114</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910538/wjtn-news-headlines-for-wed-apr-1-2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...Oficers say they allegedly found Hall in possession of a small quantity of **methamphetamine**... and, he was additionally charged with seventh-degree criminal possessio...
 ...eet check...A city man has been arrested on an active arrest warrant and a **drug** charge following a street check on Jamestown's northside.  City polic...
 ..., he was additionally charged with seventh-degree criminal possession of a **controlled** substance... along with the warrant.  He was held pending arraignment...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Russia at Risk of Losing Control of Railways in Armenia - The Jamestown Foundation</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D9" s="2">
         <v>46113</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://tinyurl.com/2y3ek5nh</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>(WNY News Now) – LOCKPORT, NY — A Niagara Falls woman was taken into custody on felony drug charges following a Niagara County Drug Task Force investigation, authorities confirmed. Daisy N. Ingram, 23, was arrested at a Niagara Street Extension address in the Town of Lockport. She faces multiple felony charges, including second-degree criminal sale […]The post Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D10" s="2">
         <v>46113</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/niagara-falls-woman-arrested-on-multiple-drug-charges-in-lockport/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...gara Falls woman was taken into custody on felony **drug** charges following a Niagara County Drug Task Forc...
 ...on felony drug charges following a Niagara County **Drug** Task Force investigation, authorities confirmed. ...
 ...The post Niagara Falls Woman Arrested on Multiple **Drug** Charges in Lockport appeared first on WNY News No...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>(WNY News Now) – OLEAN, N.Y. — A Wellsville woman faces charges after a traffic stop in the City of Olean led to the discovery of a suspended license and suspected narcotics, according to the Cattaraugus County Sheriff’s Office. Cassie J. Degerstedt, 32, of Wellsville, was taken into custody at approximately 12:02 a.m. on March […]The post Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D11" s="2">
         <v>46113</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/olean-woman-charged-with-drug-possession-unlicensed-operation-following-traffic-stop/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>....m. on March […]The post Olean Woman Charged with **Drug** Possession, Unlicensed Operation Following Traffi...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Olean Man Charged with Drug Possession Following Traffic Stop</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>(WNY News Now) – OLEAN, N.Y. — A 34-year-old Olean man was arrested Saturday evening after authorities say he was found in possession of suspected fentanyl and drug-related materials during a traffic stop. According to the Cattaraugus County Sheriff’s Office, the incident occurred on March 28, 2026, at approximately 8:24 p.m. on Washington Street in […]The post Olean Man Charged with Drug Possession Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D12" s="2">
         <v>46113</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/olean-man-charged-with-drug-possession-following-traffic-stop/</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...ities say he was found in possession of suspected **fentanyl** and drug-related materials during a traffic stop....
 ...was found in possession of suspected fentanyl and **drug**-related materials during a traffic stop. Accordin...
 ...gton Street in […]The post Olean Man Charged with **Drug** Possession Following Traffic Stop appeared first ...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D13" s="2">
         <v>46111</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://tinyurl.com/29jtkdaf</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Mon., Mar. 30, 2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>14 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Four city residents arrested in drug bust late last week...Four people from Jamestown face multiple drug-related charges following a raid on an apartment on the city's westside.  Sheriff's officers say their Narcotics Investigators... and, those from Jamestown... executed a search warrant at 114 West Seventh St. just after 4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of methamphetamine... along with scales and packaging materials used to traffic drugs.  They also seized $4,094 dollars in cash.  Officers arrested 30 year-old James Eastham and 27 year-old Amber Eaton both for second-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  They add that 51 year-old Tracy Brown was arrested for third-degree criminal possession of a controlled substance... second-degree criminally using drug paraphernalia... and, second-degree criminal contempt.  Police arrested 42 year-old Randy Wright for third-degree criminal possession of a controlled Substance... second-degree criminally using drug paraphernalia... and, first-degree criminal contempt.  All four were taken to the city jail pending arraignment.  Anyone with information on illegal narcotics or other criminal activity is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702... or 664-2420... or the JPD Tip line at 483-8477.Catt. County man arrested for allegedly driving with four-times the legal limit of alcohol in his system...A Randolph man is accused of having nearly four times the legal limit of alcohol in his system when he crashed his car on Jamestown's eastside last Saturday morning.  City police were called to the scene on East Fourth Street about 10:30 a.m. on a report of a vehicle leaving the scene of an accident with heavy front-end damage.  Officers say they located the car... and, the driver -- identified as 45 year-old James Bliss -- a short distance away with the airbag deployed.  Police say they determined that Bliss had been driving while intoxicated... and, he ws arrested.  He was taken to the city jail where he consented to a blood test.  Officers say they blood test indicated Bliss's BAC was nearly four times the legal limit of .08%.  He was charged with DWI... Aggravated DWI... and, leaving the scene of a property damage accident.  Bliss was later issued appearance tickets... and, released to a sober third party.More than 300 attend "No Kings" Rally at Jamestown's Dow Park...More than 300 protestors showed up on a bitterly cold morning Saturday at Jamestown's Dow Park for the latest "No Kings" Rally... and, the first since the start of the War in Iran.  The event was hosted by the Jamestown Justice Coalition... and, others.  Coalition member Kate Ebersole spoke at the beginning... reminding those on hand this was a "peaceful" protest.  Coalition Founder Justin Hubbard while they were there to protest the war... and, the Trump Administration's policies... Saturday's rally was not the end.  Hubbard called the rally "a launching pad" to fuel the work they can do in the community, and let their voices be heard.  He also noted that the Jamestown Justice Coalition has just become a 501(c)4... which allows it to advocate... and, raise money.  The last rally raised more than $1,300 for the "New Neighbors Coalition" which supports and advocates for immigrants just arriving in the Jamestown-area.---Saturday's rally raised money for the effort to replace one of the three statues for the Underground Railroad Tableau... which was stolen from Dow Park n 2021.  Hubbard says says it's important to replace that statue because of Jamestown's place in the history of the Underground Railroad. Borrello and Blakeman call for full audit of NYS CDL testing and licensing in wake of 2025 bus crash on NYS Thruway...The region's State Senator is among those calling on a full audit of how commercial drivers are tested... licensed... and monitored in New York.  Sunset Bay Republican George Borrello joined Nassau County Executive and Republican gubernatorial candidate Bruce Blakeman late last week to call for the audit... arguing that last year's deadly bus crash in Pembroke -- along with a series of other recent cases -- has raised serious questions about the integrity of the state’s commercial driver licensing system and whether critical safety standards are being properly enforced.  The pair... along with others... spoke near the site of the Aug. 22, 2025 tour bus crash on the State Thruway near Pembroke, which killed five people and injured more than 40 others.  The driver was later indicted on five counts each of manslaughter and criminally negligent homicide.  At a court hearing... Borrello says the man required a Mandarin interpreter, raising questions about his English proficiency... and, whether New York properly enforced federal CDL standards.Jamestown man gets 10 years in federal prison for trafficking meth...A city man who was an associate of a major, Jamestown-area drug dealer has been sentenced to 10 years in federal prison for trafficking methamphetamine.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-old Aaron Miller, who was convicted of conspiracy to possess with intent to distribute, and to distribute, methamphetamine, received the sentence in U.S. District Court in Buffalo.  Prosecutors say that Miller bought and sold methamphetamine, and cocaine for profit and for his own use.  He received large quantities of meth and cocaine from co-defendant Jun Martinez, the drug dealer, and others.  Miller then distributed the drugs to other individuals in the Jamestown area for profit.  DiGiacomo says co-defendants Jun Martinez, La Huynh, and Antasia Babcock were previously convicted and are awaiting sentencing. </t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D14" s="2">
         <v>46111</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910080/wjtn-news-headlines-for-mon-mar-30-2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of **methamphetamine**... along with scales and packaging materials used to traffic drugs.  ...
 ...ug dealer has been sentenced to 10 years in federal prison for trafficking **methamphetamine**.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-...
@@ -702,7 +791,7 @@
 ...rrested 42 year-old Randy Wright for third-degree criminal possession of a **controlled** Substance... second-degree criminally using drug paraphernalia... and, fir...</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
+          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - post-journal.com</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -434,7 +434,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yl5qzyb</t>
+          <t>https://tinyurl.com/292m8jvo</t>
         </is>
       </c>
     </row>
@@ -446,7 +446,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -454,7 +454,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/292m8jvo</t>
+          <t>https://tinyurl.com/2yl5qzyb</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dunkirk man in standoff facing federal charges for drugs, weapons - observertoday.com</t>
+          <t>UPMC Chautauqua hosts training sessions for rare birth emergencies - observertoday.com</t>
         </is>
       </c>
       <c r="D2" s="2">
@@ -414,7 +414,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25f9m6qw</t>
+          <t>https://tinyurl.com/23vcm7og</t>
         </is>
       </c>
     </row>
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - post-journal.com</t>
+          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
         </is>
       </c>
       <c r="D3" s="2">

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -406,35 +406,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UPMC Chautauqua hosts training sessions for rare birth emergencies - observertoday.com</t>
+          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23vcm7og</t>
+          <t>https://tinyurl.com/23hv4ts3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A Dunkirk man who is charged with shooting a Dunkirk Police Officer is facing additional charges in Federal Court. U.S. Attorney Michael DiGiacomo announced that 39-year old Christopher Marcinkowski has been charged by criminal complaint with maintaining a drug involved premises and being a felon in possession of a firearm. The charges carry a maximum […]</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/292m8jvo</t>
+          <t>https://www.wrfalp.com/?p=74945</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>... charged by criminal complaint with maintaining a **drug** involved premises and being a felon in possession...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WRFALP.R</t>
         </is>
       </c>
     </row>
@@ -446,15 +461,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
+          <t>Dunkirk man in standoff facing federal charges for drugs, weapons - observertoday.com</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yl5qzyb</t>
+          <t>https://tinyurl.com/25f9m6qw</t>
         </is>
       </c>
     </row>
@@ -466,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
         </is>
       </c>
       <c r="D5" s="2">
@@ -474,24 +489,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23gxelxt</t>
+          <t>https://tinyurl.com/292m8jvo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
+          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
         </is>
       </c>
       <c r="D6" s="2">
@@ -499,10 +509,55 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/2yl5qzyb</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/23gxelxt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910825/wjtn-news-headlines-for-fri-apr-3-2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl** and cocaine... maintaining a drug involved premises... and being a user of...
 ...cutors say in March of 2024... investigators made a controlled purchase of **fentanyl** from Anabell Santiago.... and, the following month... they raided the home...
@@ -521,279 +576,211 @@
 ...f firearms.  Prosecutors say in March of 2024... investigators made a **controlled** purchase of fentanyl from Anabell Santiago.... and, the following month......</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Apr. 2, 2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Seinfelt, Meyers and Kreischer to headline August's National Comedy Festival in Jamestown....Two well-established names... and, one rising star have been announced as headliners for this year's 35th annual National Comedy Festival in Jamestown.  The National Comedy Center has announced that Jerry Seinfeld... Bert Kreischer... and, Seth Meyers will headline the annual festival on August 6-9 of this year.  In addition... for the first time... this year's festival will have all three headliners performing at the Northwest Arena... and, additional talent will be featured in the Stand-up Showcases and late-night comedy shows throughout the festival.  Seinfeld will headline on Thursday, Aug. 6... Kreischer will take the stage on Saturday the 8th... and, Seth Meyers will perform on Sunday, Aug. 9.  On Friday the 7th... there will be a Stand-up Showcase at the Reg Lenna Center for the Arts.  Comedy Center Executive Director Journey Gunderson says -- "this year’s festival brings together artists who represent distinct approaches to the craft. I love that audiences can experience the best of live comedy while connecting it to the larger story we preserve and share every day in Jamestown."  Tickets for the headlining shows and festival events will go on pre-sale for Comedy Center members beginning Monday, Apr. 27 at 12 p.m. EDT... and, for the general public on Friday, May 1 at Noon EDT at ComedyCenter.org.  For more information... you can also call (716)-484-2222.Sex offender arrested on new child porn charges in Jamestown...A registered sex offender from Jamestown has been arrested on new, federal child pornography charges.  U.S. Attorney Michael DiGiacomo has announced that 42 year-old John Peterson was arrested Wednesday... and, charged with distribution and possession of child pornography by a person with a prior child porn conviction.  Prosecutors say last June... the National Center for Missing and Exploited Children received a CyberTip from the messaging app "Kik" that two files of suspected child porn were uploaded between June 14-16 of 2025.  The files were uploaded with the username "hardinny41_mkc..." and, were shared with other users.  The center the received another tip from Kik on July 5... that a file of suspected child pornography was uploaded on June 28 by someone with the same username.  Subsequent investigation traced the uploaded files to Peterson.  Investigators in December obtained a warrant... and, seized Peterson’s cell phone.  They allegedly found about 9 image files... and, 5 video files of suspected child sexual abuse material.  He was convicted in 2010 in Carroll Town Court of attempted possession of a sexual performance by a child less than 16 Year of Age.  He was then convicted in 2023 in Chautauqua County Court of possessing a sexual performance by a child less than 16 Years of age, and criminal possession of a firearm.  Peterson faces a manditory minimum of 15 years in prison... a maximum of 40... and, a $250,000 fine.Borrello says, given policy differences among Democrats on Climate Act, a state budget may be later than last year...The late New York state budget will likely be later than even last year when negotiations went into early May.  Those are the feelings of State Senator George Borrello... who says... with the Apr. 1 deadline looming late Tuesday... the legislature approved a one-week budget extension.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040... but, he calls it nothing more than "window dressing..." and energy costs continue to go up.  One of the early parts of the "Climate Leadership and Community Protection Act" was a ban on use of fossils fuels to power newer, and smaller homes being built this year.  However... that was stopped by a court order... and, Hochul delayed the move for a year.  Borrello says that's merely an "Election Year" ploy to avoid the issue until after November.  He says he's spoken with officials from National Grid, who say while they're building new power plants in other states, they aren't in New York.  The legislature is soon leaving Albany for the Passover-Easter Break... and, will be back in session next Tuesday.  Governor Hochul's budget proposal totaled $262-billion... while the Senate and Assembly versions range from $8-billion to $10-billion more.Jamestown man arrested on drug charge following traffic stop...A man from Jamestown has been arrested on several warrants following a traffic stop on the city's southside last Saturday.  Jamestown police say a patrol spotted the car commit a traffic violation about 3:30 p.m., and, stopped the vehicle in the area of Cole Avenue and Myrtle Steet.  Officers say they found that the driver -- 60 year-old David Robbins -- was sought on several Jamestown and State Police bench warrants.  Police also found that Robbins was driving with a suspended license... and, was in possession of a quantity of cocaine.  He was charged with seventh-degree criminal possession of a controlled substance... second-degree aggravated unlicensed operator... and, held pending arraignment. </t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D9" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910712/wjtn-news-headlines-for-thurs-apr-2-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...rsions range from $8-billion to $10-billion more.Jamestown man arrested on **drug** charge following traffic stop...A man from Jamestown has been arrested on ...
 ...cocaine.  He was charged with seventh-degree criminal possession of a **controlled** substance... second-degree aggravated unlicensed operator... and, held pen...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 1, 2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>NYS budget late for sixth-straight year, legislature approves one-week extender...For the sixth-year in a row... New York will have a late state budget, although negotiations between legislative leaders and Governor Kathy Hochul are ongoing.  In a late afternoon press release Tuesday... Assembly Minority Leader Ed Ra said -- "the  only credit Democrats deserve is that, weeks ago, they stopped pretending they were ever capable of delivering a spending plan on time."  With that... a budget extender has been approved to keep the government funded for a week.  Local State Senator George Borrello noted the main sticking point remains.  New York's controversial Climate Leadership and Community Protection Act.  However... Ra -- a Long Island Republican -- says "it epitomizes the dysfunction that surfaces whenever Albany Democrats are forced to complete the most important part of their job."  The governor's proposal totaled $262-billion dollars... while Democrats in the Assembly and Senate propose budgets much larger.  Last year... a final budget was not in place until May 8.Ecklund hopeful city will receive additional, $1-million in State Aid in new budget... but, also says it's time for New York to get real about funding for local governments...As negotiations continue on a new state budget... local municipalities in line to receive additional, temporary aid... are continuing to push the legislature to do that.  The Jamestown City Council approved a resolution Monday night that urges lawmakers in Albany to add that $100-million to the 2026-27 budget.  The city would receive an additional $1-million of that aid.  However... while appreciating Governor Kathy Hochul's proposal... Mayor Kim Ecklund says there needs to be more, additional, permanent aid... with a better process in place.  She says lack of that makes "budgeting very hard."  Ecklund and other mayors... including past Jamestown mayors Eddie Sundquist and Sam Teresi... often talked about the state needing to increase municipal aid more regularily.  If the temporary aid is added to the final budget... the city would receive nearly $1.6-million in aid from New York state.  Woman from Jamestown arrested on 17 counts of endangering after allowing her three young children to be unsupervised multiple times...A city woman has been arrested on 17 counts of endangering the welfare of a child for allegedly leaving her three young child unsupervised multiple times.  Jamestown police say they took 31 year-old Amanda Pearsall into custody Monday afternoon on multiple arrest warrants at an East Second Street address.  Officers say Pearsall was accused of leaving the children... ages 5-months... one-year, and 4-years old... unsupervised in their home in November of last year.  She was arraigned in city court and released pending further court action.Severe thunderstorms produce torrential downpours and hail in north county late Tuesday...Severe thunderstorms with torrential rain and hail rolled through northern Chautauqua County Tuesday afternoon.  A severe thunderstorm warning was issued... with several reports of flooding, downed trees and powerlines impacting several areas.  Meteorologist David Thomas with the National Weather Service in Buffalo says the heavy rainfall around the southern tier... causing mostly ponding and lower level flooding.  Some creeks in the region also overflowed.  Thomas reports that golf ball-sized hail rained through the Gowanda area yesterday, which caused damage to houses and cars... and, resulted in the closing of the Gowanda Central Schools Wednesday.  He also reports that the county saw an estimated 2-3 inches of rainfall across the northern portions of the county. Jamestown man arrested on warrant, meth possession during street check...A city man has been arrested on an active arrest warrant and a drug charge following a street check on Jamestown's northside.  City police say they spotted 45 year-old James Hall walking in the area of North Main and West Sixth Streets shortly before 5 p.m. Monday... and, arrested him without incident.  Oficers say they allegedly found Hall in possession of a small quantity of methamphetamine... and, he was additionally charged with seventh-degree criminal possession of a controlled substance... along with the warrant.  He was held pending arraignment.Gasoline prices continue rising in Jamestown and Chautauqua County...The average cost for a gallon of regular, unleaded gasoline in the Jamestown-area is nearing the $4 a gallon mark as the conflict in Iran continues.  AAA East Central reported Monday that the average price for a gallon in the Jamestown-area was 22 cents higher that last week... and, this week started at $3.92 cents.  However... over the past day... some service stations showed a price of $3.96... and, a few were at $4 a gallon... with one at $4.06.  Nationally... AAA says the average price is about $3.99 a gallon... which is 4-cents higher than the past week... and, crude oil prices remain high as the Iran conflict hits the four-week mark.  The national average could reached $4.02 a gallon Tuesday for the first time since August 2022 when the Ukraine-Russian War broke out.  Gas demand is also on the rise as spring break season continues.  The Energy Information Administration reports gasoline demand increased last week... but, total domestic gas supply decreased.  Boil Water Order lifted Tuesday in Fredonia...The Boil Water Order in the north county village of Fredonia was lifted Tuesday after two consecutive days of testing found turbidity levels safe for consumption.  That from the village, and Chautauqua County Health Department.... who add this also goes for customers in the town of Pomfret.  Officials say operations have returned to "normal..." and, testing indicates that the water in the distribution system is safe for drinking, cooking, making ice, brushing teeth, and making coffee.    </t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D10" s="2">
         <v>46114</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910538/wjtn-news-headlines-for-wed-apr-1-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...Oficers say they allegedly found Hall in possession of a small quantity of **methamphetamine**... and, he was additionally charged with seventh-degree criminal possessio...
 ...eet check...A city man has been arrested on an active arrest warrant and a **drug** charge following a street check on Jamestown's northside.  City polic...
 ..., he was additionally charged with seventh-degree criminal possession of a **controlled** substance... along with the warrant.  He was held pending arraignment...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Russia at Risk of Losing Control of Railways in Armenia - The Jamestown Foundation</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D11" s="2">
         <v>46113</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://tinyurl.com/2y3ek5nh</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>(WNY News Now) – LOCKPORT, NY — A Niagara Falls woman was taken into custody on felony drug charges following a Niagara County Drug Task Force investigation, authorities confirmed. Daisy N. Ingram, 23, was arrested at a Niagara Street Extension address in the Town of Lockport. She faces multiple felony charges, including second-degree criminal sale […]The post Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D12" s="2">
         <v>46113</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/niagara-falls-woman-arrested-on-multiple-drug-charges-in-lockport/</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...gara Falls woman was taken into custody on felony **drug** charges following a Niagara County Drug Task Forc...
 ...on felony drug charges following a Niagara County **Drug** Task Force investigation, authorities confirmed. ...
 ...The post Niagara Falls Woman Arrested on Multiple **Drug** Charges in Lockport appeared first on WNY News No...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>(WNY News Now) – OLEAN, N.Y. — A Wellsville woman faces charges after a traffic stop in the City of Olean led to the discovery of a suspended license and suspected narcotics, according to the Cattaraugus County Sheriff’s Office. Cassie J. Degerstedt, 32, of Wellsville, was taken into custody at approximately 12:02 a.m. on March […]The post Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D13" s="2">
         <v>46113</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/olean-woman-charged-with-drug-possession-unlicensed-operation-following-traffic-stop/</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>....m. on March […]The post Olean Woman Charged with **Drug** Possession, Unlicensed Operation Following Traffi...</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Olean Man Charged with Drug Possession Following Traffic Stop</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>(WNY News Now) – OLEAN, N.Y. — A 34-year-old Olean man was arrested Saturday evening after authorities say he was found in possession of suspected fentanyl and drug-related materials during a traffic stop. According to the Cattaraugus County Sheriff’s Office, the incident occurred on March 28, 2026, at approximately 8:24 p.m. on Washington Street in […]The post Olean Man Charged with Drug Possession Following Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D12" s="2">
+      <c r="D14" s="2">
         <v>46113</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/olean-man-charged-with-drug-possession-following-traffic-stop/</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...ities say he was found in possession of suspected **fentanyl** and drug-related materials during a traffic stop....
 ...was found in possession of suspected fentanyl and **drug**-related materials during a traffic stop. Accordin...
 ...gton Street in […]The post Olean Man Charged with **Drug** Possession Following Traffic Stop appeared first ...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Four charged after meth found in Jamestown apartment - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46111</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/29jtkdaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Mon., Mar. 30, 2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>14 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Four city residents arrested in drug bust late last week...Four people from Jamestown face multiple drug-related charges following a raid on an apartment on the city's westside.  Sheriff's officers say their Narcotics Investigators... and, those from Jamestown... executed a search warrant at 114 West Seventh St. just after 4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of methamphetamine... along with scales and packaging materials used to traffic drugs.  They also seized $4,094 dollars in cash.  Officers arrested 30 year-old James Eastham and 27 year-old Amber Eaton both for second-degree criminal possession of a controlled substance... and, second-degree criminally using drug paraphernalia.  They add that 51 year-old Tracy Brown was arrested for third-degree criminal possession of a controlled substance... second-degree criminally using drug paraphernalia... and, second-degree criminal contempt.  Police arrested 42 year-old Randy Wright for third-degree criminal possession of a controlled Substance... second-degree criminally using drug paraphernalia... and, first-degree criminal contempt.  All four were taken to the city jail pending arraignment.  Anyone with information on illegal narcotics or other criminal activity is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702... or 664-2420... or the JPD Tip line at 483-8477.Catt. County man arrested for allegedly driving with four-times the legal limit of alcohol in his system...A Randolph man is accused of having nearly four times the legal limit of alcohol in his system when he crashed his car on Jamestown's eastside last Saturday morning.  City police were called to the scene on East Fourth Street about 10:30 a.m. on a report of a vehicle leaving the scene of an accident with heavy front-end damage.  Officers say they located the car... and, the driver -- identified as 45 year-old James Bliss -- a short distance away with the airbag deployed.  Police say they determined that Bliss had been driving while intoxicated... and, he ws arrested.  He was taken to the city jail where he consented to a blood test.  Officers say they blood test indicated Bliss's BAC was nearly four times the legal limit of .08%.  He was charged with DWI... Aggravated DWI... and, leaving the scene of a property damage accident.  Bliss was later issued appearance tickets... and, released to a sober third party.More than 300 attend "No Kings" Rally at Jamestown's Dow Park...More than 300 protestors showed up on a bitterly cold morning Saturday at Jamestown's Dow Park for the latest "No Kings" Rally... and, the first since the start of the War in Iran.  The event was hosted by the Jamestown Justice Coalition... and, others.  Coalition member Kate Ebersole spoke at the beginning... reminding those on hand this was a "peaceful" protest.  Coalition Founder Justin Hubbard while they were there to protest the war... and, the Trump Administration's policies... Saturday's rally was not the end.  Hubbard called the rally "a launching pad" to fuel the work they can do in the community, and let their voices be heard.  He also noted that the Jamestown Justice Coalition has just become a 501(c)4... which allows it to advocate... and, raise money.  The last rally raised more than $1,300 for the "New Neighbors Coalition" which supports and advocates for immigrants just arriving in the Jamestown-area.---Saturday's rally raised money for the effort to replace one of the three statues for the Underground Railroad Tableau... which was stolen from Dow Park n 2021.  Hubbard says says it's important to replace that statue because of Jamestown's place in the history of the Underground Railroad. Borrello and Blakeman call for full audit of NYS CDL testing and licensing in wake of 2025 bus crash on NYS Thruway...The region's State Senator is among those calling on a full audit of how commercial drivers are tested... licensed... and monitored in New York.  Sunset Bay Republican George Borrello joined Nassau County Executive and Republican gubernatorial candidate Bruce Blakeman late last week to call for the audit... arguing that last year's deadly bus crash in Pembroke -- along with a series of other recent cases -- has raised serious questions about the integrity of the state’s commercial driver licensing system and whether critical safety standards are being properly enforced.  The pair... along with others... spoke near the site of the Aug. 22, 2025 tour bus crash on the State Thruway near Pembroke, which killed five people and injured more than 40 others.  The driver was later indicted on five counts each of manslaughter and criminally negligent homicide.  At a court hearing... Borrello says the man required a Mandarin interpreter, raising questions about his English proficiency... and, whether New York properly enforced federal CDL standards.Jamestown man gets 10 years in federal prison for trafficking meth...A city man who was an associate of a major, Jamestown-area drug dealer has been sentenced to 10 years in federal prison for trafficking methamphetamine.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-old Aaron Miller, who was convicted of conspiracy to possess with intent to distribute, and to distribute, methamphetamine, received the sentence in U.S. District Court in Buffalo.  Prosecutors say that Miller bought and sold methamphetamine, and cocaine for profit and for his own use.  He received large quantities of meth and cocaine from co-defendant Jun Martinez, the drug dealer, and others.  Miller then distributed the drugs to other individuals in the Jamestown area for profit.  DiGiacomo says co-defendants Jun Martinez, La Huynh, and Antasia Babcock were previously convicted and are awaiting sentencing. </t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46111</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910080/wjtn-news-headlines-for-mon-mar-30-2026</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>...4:30 p.m. last Thursday.  Police says they seized nearly 207-grams of **methamphetamine**... along with scales and packaging materials used to traffic drugs.  ...
-...ug dealer has been sentenced to 10 years in federal prison for trafficking **methamphetamine**.  U.S. Attorney Michael DiGiacomo announced late Friday that 32 year-...
-...ted of conspiracy to possess with intent to distribute, and to distribute, **methamphetamine**, received the sentence in U.S. District Court in Buffalo.  Prosecutor...
-...strict Court in Buffalo.  Prosecutors say that Miller bought and sold **methamphetamine**, and cocaine for profit and for his own use.  He received large quant...
-Four city residents arrested in **drug** bust late last week...Four people from Jamestown face multiple drug-relate...
-...ted in drug bust late last week...Four people from Jamestown face multiple **drug**-related charges following a raid on an apartment on the city's westside. &amp;...
-...ossession of a controlled substance... and, second-degree criminally using **drug** paraphernalia.  They add that 51 year-old Tracy Brown was arrested fo...
-...nal possession of a controlled substance... second-degree criminally using **drug** paraphernalia... and, second-degree criminal contempt.  Police arrest...
-...fficking meth...A city man who was an associate of a major, Jamestown-area **drug** dealer has been sentenced to 10 years in federal prison for trafficking me...
-...d large quantities of meth and cocaine from co-defendant Jun Martinez, the **drug** dealer, and others.  Miller then distributed the drugs to other indiv...
-...ployed.  Police say they determined that Bliss had been driving while **intoxicated**... and, he ws arrested.  He was taken to the city jail where he conse...
-...nd 27 year-old Amber Eaton both for second-degree criminal possession of a **controlled** substance... and, second-degree criminally using drug paraphernalia.  ...
-...ear-old Tracy Brown was arrested for third-degree criminal possession of a **controlled** substance... second-degree criminally using drug paraphernalia... and, sec...
-...rrested 42 year-old Randy Wright for third-degree criminal possession of a **controlled** Substance... second-degree criminally using drug paraphernalia... and, fir...</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -401,75 +401,107 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
+          <t>Jamestown Man Charged with DWI on Northside</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, NY — A Jamestown man was charged with driving while intoxicated following a Northside traffic stop on Saturday morning. Officers from the 1st Platoon responded at 7:15 a.m. on April 4, 2026, to reports of a potentially intoxicated driver. Upon arrival, they contacted James R. Geist, 58, of Jamestown. Through […]The post Jamestown Man Charged with DWI on Northside appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23hv4ts3</t>
+          <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-on-northside/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>... — A Jamestown man was charged with driving while **intoxicated** following a Northside traffic stop on Saturday mo...
+....m. on April 4, 2026, to reports of a potentially **intoxicated** driver. Upon arrival, they contacted James R. Gei...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WRFA-LP 107.9 FM</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges</t>
+          <t>Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A Dunkirk man who is charged with shooting a Dunkirk Police Officer is facing additional charges in Federal Court. U.S. Attorney Michael DiGiacomo announced that 39-year old Christopher Marcinkowski has been charged by criminal complaint with maintaining a drug involved premises and being a felon in possession of a firearm. The charges carry a maximum […]</t>
+          <t>(WNY News Now) – Jamestown, NY – A routine traffic stop in Jamestown led to the arrest of two Buffalo residents for possession of a controlled substance, police report. On the evening of April 3, at approximately 7:27 p.m., Jamestown Police Officers conducted a traffic stop at the intersection of Water Street and King Street […]The post Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.wrfalp.com/?p=74945</t>
+          <t>https://wnynewsnow.com/2026/04/07/two-buffalo-residents-arrested-in-jamestown-traffic-stop-for-fentanyl-possession/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>... charged by criminal complaint with maintaining a **drug** involved premises and being a felon in possession...</t>
+          <t>... Residents Arrested in Jamestown Traffic Stop for **Fentanyl** Possession appeared first on WNY News Now.
+...rest of two Buffalo residents for possession of a **controlled** substance, police report. On the evening of April...</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>News_search_WRFALP.R</t>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dunkirk man in standoff facing federal charges for drugs, weapons - observertoday.com</t>
+          <t>Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 23-year-old Jamestown resident was charged with driving while intoxicated after police responded to a report of an unresponsive driver on the city’s south side Sunday afternoon. Officers from the Jamestown Police Department’s Second Platoon were dispatched at approximately 4:27 p.m. on April 5, 2026, for a report […]The post Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46116</v>
+        <v>46119</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/25f9m6qw</t>
+          <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-after-being-found-unresponsive-in-running-vehicle/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...Jamestown resident was charged with driving while **intoxicated** after police responded to a report of an unrespon...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -481,35 +513,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/292m8jvo</t>
+          <t>https://tinyurl.com/23hv4ts3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
+          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A Dunkirk man who is charged with shooting a Dunkirk Police Officer is facing additional charges in Federal Court. U.S. Attorney Michael DiGiacomo announced that 39-year old Christopher Marcinkowski has been charged by criminal complaint with maintaining a drug involved premises and being a felon in possession of a firearm. The charges carry a maximum […]</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46115</v>
+        <v>46118</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yl5qzyb</t>
+          <t>https://www.wrfalp.com/?p=74945</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>... charged by criminal complaint with maintaining a **drug** involved premises and being a felon in possession...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WRFALP.R</t>
         </is>
       </c>
     </row>
@@ -521,32 +568,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+          <t>Dunkirk man in standoff facing federal charges for drugs, weapons - observertoday.com</t>
         </is>
       </c>
       <c r="D7" s="2">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23gxelxt</t>
+          <t>https://tinyurl.com/25f9m6qw</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
+          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -554,10 +596,75 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/2yl5qzyb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/292m8jvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/23gxelxt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46115</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910825/wjtn-news-headlines-for-fri-apr-3-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl** and cocaine... maintaining a drug involved premises... and being a user of...
 ...cutors say in March of 2024... investigators made a controlled purchase of **fentanyl** from Anabell Santiago.... and, the following month... they raided the home...
@@ -576,206 +683,114 @@
 ...f firearms.  Prosecutors say in March of 2024... investigators made a **controlled** purchase of fentanyl from Anabell Santiago.... and, the following month......</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Apr. 2, 2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Seinfelt, Meyers and Kreischer to headline August's National Comedy Festival in Jamestown....Two well-established names... and, one rising star have been announced as headliners for this year's 35th annual National Comedy Festival in Jamestown.  The National Comedy Center has announced that Jerry Seinfeld... Bert Kreischer... and, Seth Meyers will headline the annual festival on August 6-9 of this year.  In addition... for the first time... this year's festival will have all three headliners performing at the Northwest Arena... and, additional talent will be featured in the Stand-up Showcases and late-night comedy shows throughout the festival.  Seinfeld will headline on Thursday, Aug. 6... Kreischer will take the stage on Saturday the 8th... and, Seth Meyers will perform on Sunday, Aug. 9.  On Friday the 7th... there will be a Stand-up Showcase at the Reg Lenna Center for the Arts.  Comedy Center Executive Director Journey Gunderson says -- "this year’s festival brings together artists who represent distinct approaches to the craft. I love that audiences can experience the best of live comedy while connecting it to the larger story we preserve and share every day in Jamestown."  Tickets for the headlining shows and festival events will go on pre-sale for Comedy Center members beginning Monday, Apr. 27 at 12 p.m. EDT... and, for the general public on Friday, May 1 at Noon EDT at ComedyCenter.org.  For more information... you can also call (716)-484-2222.Sex offender arrested on new child porn charges in Jamestown...A registered sex offender from Jamestown has been arrested on new, federal child pornography charges.  U.S. Attorney Michael DiGiacomo has announced that 42 year-old John Peterson was arrested Wednesday... and, charged with distribution and possession of child pornography by a person with a prior child porn conviction.  Prosecutors say last June... the National Center for Missing and Exploited Children received a CyberTip from the messaging app "Kik" that two files of suspected child porn were uploaded between June 14-16 of 2025.  The files were uploaded with the username "hardinny41_mkc..." and, were shared with other users.  The center the received another tip from Kik on July 5... that a file of suspected child pornography was uploaded on June 28 by someone with the same username.  Subsequent investigation traced the uploaded files to Peterson.  Investigators in December obtained a warrant... and, seized Peterson’s cell phone.  They allegedly found about 9 image files... and, 5 video files of suspected child sexual abuse material.  He was convicted in 2010 in Carroll Town Court of attempted possession of a sexual performance by a child less than 16 Year of Age.  He was then convicted in 2023 in Chautauqua County Court of possessing a sexual performance by a child less than 16 Years of age, and criminal possession of a firearm.  Peterson faces a manditory minimum of 15 years in prison... a maximum of 40... and, a $250,000 fine.Borrello says, given policy differences among Democrats on Climate Act, a state budget may be later than last year...The late New York state budget will likely be later than even last year when negotiations went into early May.  Those are the feelings of State Senator George Borrello... who says... with the Apr. 1 deadline looming late Tuesday... the legislature approved a one-week budget extension.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040... but, he calls it nothing more than "window dressing..." and energy costs continue to go up.  One of the early parts of the "Climate Leadership and Community Protection Act" was a ban on use of fossils fuels to power newer, and smaller homes being built this year.  However... that was stopped by a court order... and, Hochul delayed the move for a year.  Borrello says that's merely an "Election Year" ploy to avoid the issue until after November.  He says he's spoken with officials from National Grid, who say while they're building new power plants in other states, they aren't in New York.  The legislature is soon leaving Albany for the Passover-Easter Break... and, will be back in session next Tuesday.  Governor Hochul's budget proposal totaled $262-billion... while the Senate and Assembly versions range from $8-billion to $10-billion more.Jamestown man arrested on drug charge following traffic stop...A man from Jamestown has been arrested on several warrants following a traffic stop on the city's southside last Saturday.  Jamestown police say a patrol spotted the car commit a traffic violation about 3:30 p.m., and, stopped the vehicle in the area of Cole Avenue and Myrtle Steet.  Officers say they found that the driver -- 60 year-old David Robbins -- was sought on several Jamestown and State Police bench warrants.  Police also found that Robbins was driving with a suspended license... and, was in possession of a quantity of cocaine.  He was charged with seventh-degree criminal possession of a controlled substance... second-degree aggravated unlicensed operator... and, held pending arraignment. </t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D12" s="2">
         <v>46115</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910712/wjtn-news-headlines-for-thurs-apr-2-2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...rsions range from $8-billion to $10-billion more.Jamestown man arrested on **drug** charge following traffic stop...A man from Jamestown has been arrested on ...
 ...cocaine.  He was charged with seventh-degree criminal possession of a **controlled** substance... second-degree aggravated unlicensed operator... and, held pen...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 1, 2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>NYS budget late for sixth-straight year, legislature approves one-week extender...For the sixth-year in a row... New York will have a late state budget, although negotiations between legislative leaders and Governor Kathy Hochul are ongoing.  In a late afternoon press release Tuesday... Assembly Minority Leader Ed Ra said -- "the  only credit Democrats deserve is that, weeks ago, they stopped pretending they were ever capable of delivering a spending plan on time."  With that... a budget extender has been approved to keep the government funded for a week.  Local State Senator George Borrello noted the main sticking point remains.  New York's controversial Climate Leadership and Community Protection Act.  However... Ra -- a Long Island Republican -- says "it epitomizes the dysfunction that surfaces whenever Albany Democrats are forced to complete the most important part of their job."  The governor's proposal totaled $262-billion dollars... while Democrats in the Assembly and Senate propose budgets much larger.  Last year... a final budget was not in place until May 8.Ecklund hopeful city will receive additional, $1-million in State Aid in new budget... but, also says it's time for New York to get real about funding for local governments...As negotiations continue on a new state budget... local municipalities in line to receive additional, temporary aid... are continuing to push the legislature to do that.  The Jamestown City Council approved a resolution Monday night that urges lawmakers in Albany to add that $100-million to the 2026-27 budget.  The city would receive an additional $1-million of that aid.  However... while appreciating Governor Kathy Hochul's proposal... Mayor Kim Ecklund says there needs to be more, additional, permanent aid... with a better process in place.  She says lack of that makes "budgeting very hard."  Ecklund and other mayors... including past Jamestown mayors Eddie Sundquist and Sam Teresi... often talked about the state needing to increase municipal aid more regularily.  If the temporary aid is added to the final budget... the city would receive nearly $1.6-million in aid from New York state.  Woman from Jamestown arrested on 17 counts of endangering after allowing her three young children to be unsupervised multiple times...A city woman has been arrested on 17 counts of endangering the welfare of a child for allegedly leaving her three young child unsupervised multiple times.  Jamestown police say they took 31 year-old Amanda Pearsall into custody Monday afternoon on multiple arrest warrants at an East Second Street address.  Officers say Pearsall was accused of leaving the children... ages 5-months... one-year, and 4-years old... unsupervised in their home in November of last year.  She was arraigned in city court and released pending further court action.Severe thunderstorms produce torrential downpours and hail in north county late Tuesday...Severe thunderstorms with torrential rain and hail rolled through northern Chautauqua County Tuesday afternoon.  A severe thunderstorm warning was issued... with several reports of flooding, downed trees and powerlines impacting several areas.  Meteorologist David Thomas with the National Weather Service in Buffalo says the heavy rainfall around the southern tier... causing mostly ponding and lower level flooding.  Some creeks in the region also overflowed.  Thomas reports that golf ball-sized hail rained through the Gowanda area yesterday, which caused damage to houses and cars... and, resulted in the closing of the Gowanda Central Schools Wednesday.  He also reports that the county saw an estimated 2-3 inches of rainfall across the northern portions of the county. Jamestown man arrested on warrant, meth possession during street check...A city man has been arrested on an active arrest warrant and a drug charge following a street check on Jamestown's northside.  City police say they spotted 45 year-old James Hall walking in the area of North Main and West Sixth Streets shortly before 5 p.m. Monday... and, arrested him without incident.  Oficers say they allegedly found Hall in possession of a small quantity of methamphetamine... and, he was additionally charged with seventh-degree criminal possession of a controlled substance... along with the warrant.  He was held pending arraignment.Gasoline prices continue rising in Jamestown and Chautauqua County...The average cost for a gallon of regular, unleaded gasoline in the Jamestown-area is nearing the $4 a gallon mark as the conflict in Iran continues.  AAA East Central reported Monday that the average price for a gallon in the Jamestown-area was 22 cents higher that last week... and, this week started at $3.92 cents.  However... over the past day... some service stations showed a price of $3.96... and, a few were at $4 a gallon... with one at $4.06.  Nationally... AAA says the average price is about $3.99 a gallon... which is 4-cents higher than the past week... and, crude oil prices remain high as the Iran conflict hits the four-week mark.  The national average could reached $4.02 a gallon Tuesday for the first time since August 2022 when the Ukraine-Russian War broke out.  Gas demand is also on the rise as spring break season continues.  The Energy Information Administration reports gasoline demand increased last week... but, total domestic gas supply decreased.  Boil Water Order lifted Tuesday in Fredonia...The Boil Water Order in the north county village of Fredonia was lifted Tuesday after two consecutive days of testing found turbidity levels safe for consumption.  That from the village, and Chautauqua County Health Department.... who add this also goes for customers in the town of Pomfret.  Officials say operations have returned to "normal..." and, testing indicates that the water in the distribution system is safe for drinking, cooking, making ice, brushing teeth, and making coffee.    </t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D13" s="2">
         <v>46114</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910538/wjtn-news-headlines-for-wed-apr-1-2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...Oficers say they allegedly found Hall in possession of a small quantity of **methamphetamine**... and, he was additionally charged with seventh-degree criminal possessio...
 ...eet check...A city man has been arrested on an active arrest warrant and a **drug** charge following a street check on Jamestown's northside.  City polic...
 ..., he was additionally charged with seventh-degree criminal possession of a **controlled** substance... along with the warrant.  He was held pending arraignment...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Russia at Risk of Losing Control of Railways in Armenia - The Jamestown Foundation</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – LOCKPORT, NY — A Niagara Falls woman was taken into custody on felony drug charges following a Niagara County Drug Task Force investigation, authorities confirmed. Daisy N. Ingram, 23, was arrested at a Niagara Street Extension address in the Town of Lockport. She faces multiple felony charges, including second-degree criminal sale […]The post Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
         <v>46113</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2y3ek5nh</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – LOCKPORT, NY — A Niagara Falls woman was taken into custody on felony drug charges following a Niagara County Drug Task Force investigation, authorities confirmed. Daisy N. Ingram, 23, was arrested at a Niagara Street Extension address in the Town of Lockport. She faces multiple felony charges, including second-degree criminal sale […]The post Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46113</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/01/niagara-falls-woman-arrested-on-multiple-drug-charges-in-lockport/</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...gara Falls woman was taken into custody on felony **drug** charges following a Niagara County Drug Task Forc...
 ...on felony drug charges following a Niagara County **Drug** Task Force investigation, authorities confirmed. ...
 ...The post Niagara Falls Woman Arrested on Multiple **Drug** Charges in Lockport appeared first on WNY News No...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – OLEAN, N.Y. — A Wellsville woman faces charges after a traffic stop in the City of Olean led to the discovery of a suspended license and suspected narcotics, according to the Cattaraugus County Sheriff’s Office. Cassie J. Degerstedt, 32, of Wellsville, was taken into custody at approximately 12:02 a.m. on March […]The post Olean Woman Charged with Drug Possession, Unlicensed Operation Following Traffic Stop appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46113</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/01/olean-woman-charged-with-drug-possession-unlicensed-operation-following-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>....m. on March […]The post Olean Woman Charged with **Drug** Possession, Unlicensed Operation Following Traffi...</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Olean Man Charged with Drug Possession Following Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – OLEAN, N.Y. — A 34-year-old Olean man was arrested Saturday evening after authorities say he was found in possession of suspected fentanyl and drug-related materials during a traffic stop. According to the Cattaraugus County Sheriff’s Office, the incident occurred on March 28, 2026, at approximately 8:24 p.m. on Washington Street in […]The post Olean Man Charged with Drug Possession Following Traffic Stop appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46113</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/01/olean-man-charged-with-drug-possession-following-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>...ities say he was found in possession of suspected **fentanyl** and drug-related materials during a traffic stop....
-...was found in possession of suspected fentanyl and **drug**-related materials during a traffic stop. Accordin...
-...gton Street in […]The post Olean Man Charged with **Drug** Possession Following Traffic Stop appeared first ...</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,104 +401,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46121</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
+...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
+...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Jamestown Man Charged with DWI on Northside</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, NY — A Jamestown man was charged with driving while intoxicated following a Northside traffic stop on Saturday morning. Officers from the 1st Platoon responded at 7:15 a.m. on April 4, 2026, to reports of a potentially intoxicated driver. Upon arrival, they contacted James R. Geist, 58, of Jamestown. Through […]The post Jamestown Man Charged with DWI on Northside appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D3" s="2">
         <v>46119</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-on-northside/</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>... — A Jamestown man was charged with driving while **intoxicated** following a Northside traffic stop on Saturday mo...
 ....m. on April 4, 2026, to reports of a potentially **intoxicated** driver. Upon arrival, they contacted James R. Gei...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>(WNY News Now) – Jamestown, NY – A routine traffic stop in Jamestown led to the arrest of two Buffalo residents for possession of a controlled substance, police report. On the evening of April 3, at approximately 7:27 p.m., Jamestown Police Officers conducted a traffic stop at the intersection of Water Street and King Street […]The post Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>46119</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/07/two-buffalo-residents-arrested-in-jamestown-traffic-stop-for-fentanyl-possession/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>... Residents Arrested in Jamestown Traffic Stop for **Fentanyl** Possession appeared first on WNY News Now.
 ...rest of two Buffalo residents for possession of a **controlled** substance, police report. On the evening of April...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 23-year-old Jamestown resident was charged with driving while intoxicated after police responded to a report of an unresponsive driver on the city’s south side Sunday afternoon. Officers from the Jamestown Police Department’s Second Platoon were dispatched at approximately 4:27 p.m. on April 5, 2026, for a report […]The post Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46119</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-after-being-found-unresponsive-in-running-vehicle/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...Jamestown resident was charged with driving while **intoxicated** after police responded to a report of an unrespon...</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -508,37 +510,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
+          <t>Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 23-year-old Jamestown resident was charged with driving while intoxicated after police responded to a report of an unresponsive driver on the city’s south side Sunday afternoon. Officers from the Jamestown Police Department’s Second Platoon were dispatched at approximately 4:27 p.m. on April 5, 2026, for a report […]The post Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23hv4ts3</t>
+          <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-after-being-found-unresponsive-in-running-vehicle/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>...Jamestown resident was charged with driving while **intoxicated** after police responded to a report of an unrespon...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WRFA-LP 107.9 FM</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>A Dunkirk man who is charged with shooting a Dunkirk Police Officer is facing additional charges in Federal Court. U.S. Attorney Michael DiGiacomo announced that 39-year old Christopher Marcinkowski has been charged by criminal complaint with maintaining a drug involved premises and being a felon in possession of a firearm. The charges carry a maximum […]</t>
+          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
         </is>
       </c>
       <c r="D6" s="2">
@@ -546,17 +558,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.wrfalp.com/?p=74945</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>... charged by criminal complaint with maintaining a **drug** involved premises and being a felon in possession...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_WRFALP.R</t>
+          <t>https://tinyurl.com/23hv4ts3</t>
         </is>
       </c>
     </row>
@@ -588,7 +590,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jamestown woman sentenced to 7 years in federal prison for fentanyl, cocaine conspiracy - Fingerlakes1.com</t>
+          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -596,7 +598,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2yl5qzyb</t>
+          <t>https://tinyurl.com/292m8jvo</t>
         </is>
       </c>
     </row>
@@ -608,7 +610,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
         </is>
       </c>
       <c r="D9" s="2">
@@ -616,19 +618,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/292m8jvo</t>
+          <t>https://tinyurl.com/23gxelxt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
+          <t>15 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
         </is>
       </c>
       <c r="D10" s="2">
@@ -636,35 +643,10 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/23gxelxt</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46115</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910825/wjtn-news-headlines-for-fri-apr-3-2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl** and cocaine... maintaining a drug involved premises... and being a user of...
 ...cutors say in March of 2024... investigators made a controlled purchase of **fentanyl** from Anabell Santiago.... and, the following month... they raided the home...
@@ -683,119 +665,45 @@
 ...f firearms.  Prosecutors say in March of 2024... investigators made a **controlled** purchase of fentanyl from Anabell Santiago.... and, the following month......</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Apr. 2, 2026</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Seinfelt, Meyers and Kreischer to headline August's National Comedy Festival in Jamestown....Two well-established names... and, one rising star have been announced as headliners for this year's 35th annual National Comedy Festival in Jamestown.  The National Comedy Center has announced that Jerry Seinfeld... Bert Kreischer... and, Seth Meyers will headline the annual festival on August 6-9 of this year.  In addition... for the first time... this year's festival will have all three headliners performing at the Northwest Arena... and, additional talent will be featured in the Stand-up Showcases and late-night comedy shows throughout the festival.  Seinfeld will headline on Thursday, Aug. 6... Kreischer will take the stage on Saturday the 8th... and, Seth Meyers will perform on Sunday, Aug. 9.  On Friday the 7th... there will be a Stand-up Showcase at the Reg Lenna Center for the Arts.  Comedy Center Executive Director Journey Gunderson says -- "this year’s festival brings together artists who represent distinct approaches to the craft. I love that audiences can experience the best of live comedy while connecting it to the larger story we preserve and share every day in Jamestown."  Tickets for the headlining shows and festival events will go on pre-sale for Comedy Center members beginning Monday, Apr. 27 at 12 p.m. EDT... and, for the general public on Friday, May 1 at Noon EDT at ComedyCenter.org.  For more information... you can also call (716)-484-2222.Sex offender arrested on new child porn charges in Jamestown...A registered sex offender from Jamestown has been arrested on new, federal child pornography charges.  U.S. Attorney Michael DiGiacomo has announced that 42 year-old John Peterson was arrested Wednesday... and, charged with distribution and possession of child pornography by a person with a prior child porn conviction.  Prosecutors say last June... the National Center for Missing and Exploited Children received a CyberTip from the messaging app "Kik" that two files of suspected child porn were uploaded between June 14-16 of 2025.  The files were uploaded with the username "hardinny41_mkc..." and, were shared with other users.  The center the received another tip from Kik on July 5... that a file of suspected child pornography was uploaded on June 28 by someone with the same username.  Subsequent investigation traced the uploaded files to Peterson.  Investigators in December obtained a warrant... and, seized Peterson’s cell phone.  They allegedly found about 9 image files... and, 5 video files of suspected child sexual abuse material.  He was convicted in 2010 in Carroll Town Court of attempted possession of a sexual performance by a child less than 16 Year of Age.  He was then convicted in 2023 in Chautauqua County Court of possessing a sexual performance by a child less than 16 Years of age, and criminal possession of a firearm.  Peterson faces a manditory minimum of 15 years in prison... a maximum of 40... and, a $250,000 fine.Borrello says, given policy differences among Democrats on Climate Act, a state budget may be later than last year...The late New York state budget will likely be later than even last year when negotiations went into early May.  Those are the feelings of State Senator George Borrello... who says... with the Apr. 1 deadline looming late Tuesday... the legislature approved a one-week budget extension.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040... but, he calls it nothing more than "window dressing..." and energy costs continue to go up.  One of the early parts of the "Climate Leadership and Community Protection Act" was a ban on use of fossils fuels to power newer, and smaller homes being built this year.  However... that was stopped by a court order... and, Hochul delayed the move for a year.  Borrello says that's merely an "Election Year" ploy to avoid the issue until after November.  He says he's spoken with officials from National Grid, who say while they're building new power plants in other states, they aren't in New York.  The legislature is soon leaving Albany for the Passover-Easter Break... and, will be back in session next Tuesday.  Governor Hochul's budget proposal totaled $262-billion... while the Senate and Assembly versions range from $8-billion to $10-billion more.Jamestown man arrested on drug charge following traffic stop...A man from Jamestown has been arrested on several warrants following a traffic stop on the city's southside last Saturday.  Jamestown police say a patrol spotted the car commit a traffic violation about 3:30 p.m., and, stopped the vehicle in the area of Cole Avenue and Myrtle Steet.  Officers say they found that the driver -- 60 year-old David Robbins -- was sought on several Jamestown and State Police bench warrants.  Police also found that Robbins was driving with a suspended license... and, was in possession of a quantity of cocaine.  He was charged with seventh-degree criminal possession of a controlled substance... second-degree aggravated unlicensed operator... and, held pending arraignment. </t>
         </is>
       </c>
-      <c r="D12" s="2">
+      <c r="D11" s="2">
         <v>46115</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910712/wjtn-news-headlines-for-thurs-apr-2-2026</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...rsions range from $8-billion to $10-billion more.Jamestown man arrested on **drug** charge following traffic stop...A man from Jamestown has been arrested on ...
 ...cocaine.  He was charged with seventh-degree criminal possession of a **controlled** substance... second-degree aggravated unlicensed operator... and, held pen...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Wed., Apr. 1, 2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NYS budget late for sixth-straight year, legislature approves one-week extender...For the sixth-year in a row... New York will have a late state budget, although negotiations between legislative leaders and Governor Kathy Hochul are ongoing.  In a late afternoon press release Tuesday... Assembly Minority Leader Ed Ra said -- "the  only credit Democrats deserve is that, weeks ago, they stopped pretending they were ever capable of delivering a spending plan on time."  With that... a budget extender has been approved to keep the government funded for a week.  Local State Senator George Borrello noted the main sticking point remains.  New York's controversial Climate Leadership and Community Protection Act.  However... Ra -- a Long Island Republican -- says "it epitomizes the dysfunction that surfaces whenever Albany Democrats are forced to complete the most important part of their job."  The governor's proposal totaled $262-billion dollars... while Democrats in the Assembly and Senate propose budgets much larger.  Last year... a final budget was not in place until May 8.Ecklund hopeful city will receive additional, $1-million in State Aid in new budget... but, also says it's time for New York to get real about funding for local governments...As negotiations continue on a new state budget... local municipalities in line to receive additional, temporary aid... are continuing to push the legislature to do that.  The Jamestown City Council approved a resolution Monday night that urges lawmakers in Albany to add that $100-million to the 2026-27 budget.  The city would receive an additional $1-million of that aid.  However... while appreciating Governor Kathy Hochul's proposal... Mayor Kim Ecklund says there needs to be more, additional, permanent aid... with a better process in place.  She says lack of that makes "budgeting very hard."  Ecklund and other mayors... including past Jamestown mayors Eddie Sundquist and Sam Teresi... often talked about the state needing to increase municipal aid more regularily.  If the temporary aid is added to the final budget... the city would receive nearly $1.6-million in aid from New York state.  Woman from Jamestown arrested on 17 counts of endangering after allowing her three young children to be unsupervised multiple times...A city woman has been arrested on 17 counts of endangering the welfare of a child for allegedly leaving her three young child unsupervised multiple times.  Jamestown police say they took 31 year-old Amanda Pearsall into custody Monday afternoon on multiple arrest warrants at an East Second Street address.  Officers say Pearsall was accused of leaving the children... ages 5-months... one-year, and 4-years old... unsupervised in their home in November of last year.  She was arraigned in city court and released pending further court action.Severe thunderstorms produce torrential downpours and hail in north county late Tuesday...Severe thunderstorms with torrential rain and hail rolled through northern Chautauqua County Tuesday afternoon.  A severe thunderstorm warning was issued... with several reports of flooding, downed trees and powerlines impacting several areas.  Meteorologist David Thomas with the National Weather Service in Buffalo says the heavy rainfall around the southern tier... causing mostly ponding and lower level flooding.  Some creeks in the region also overflowed.  Thomas reports that golf ball-sized hail rained through the Gowanda area yesterday, which caused damage to houses and cars... and, resulted in the closing of the Gowanda Central Schools Wednesday.  He also reports that the county saw an estimated 2-3 inches of rainfall across the northern portions of the county. Jamestown man arrested on warrant, meth possession during street check...A city man has been arrested on an active arrest warrant and a drug charge following a street check on Jamestown's northside.  City police say they spotted 45 year-old James Hall walking in the area of North Main and West Sixth Streets shortly before 5 p.m. Monday... and, arrested him without incident.  Oficers say they allegedly found Hall in possession of a small quantity of methamphetamine... and, he was additionally charged with seventh-degree criminal possession of a controlled substance... along with the warrant.  He was held pending arraignment.Gasoline prices continue rising in Jamestown and Chautauqua County...The average cost for a gallon of regular, unleaded gasoline in the Jamestown-area is nearing the $4 a gallon mark as the conflict in Iran continues.  AAA East Central reported Monday that the average price for a gallon in the Jamestown-area was 22 cents higher that last week... and, this week started at $3.92 cents.  However... over the past day... some service stations showed a price of $3.96... and, a few were at $4 a gallon... with one at $4.06.  Nationally... AAA says the average price is about $3.99 a gallon... which is 4-cents higher than the past week... and, crude oil prices remain high as the Iran conflict hits the four-week mark.  The national average could reached $4.02 a gallon Tuesday for the first time since August 2022 when the Ukraine-Russian War broke out.  Gas demand is also on the rise as spring break season continues.  The Energy Information Administration reports gasoline demand increased last week... but, total domestic gas supply decreased.  Boil Water Order lifted Tuesday in Fredonia...The Boil Water Order in the north county village of Fredonia was lifted Tuesday after two consecutive days of testing found turbidity levels safe for consumption.  That from the village, and Chautauqua County Health Department.... who add this also goes for customers in the town of Pomfret.  Officials say operations have returned to "normal..." and, testing indicates that the water in the distribution system is safe for drinking, cooking, making ice, brushing teeth, and making coffee.    </t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46114</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910538/wjtn-news-headlines-for-wed-apr-1-2026</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>...Oficers say they allegedly found Hall in possession of a small quantity of **methamphetamine**... and, he was additionally charged with seventh-degree criminal possessio...
-...eet check...A city man has been arrested on an active arrest warrant and a **drug** charge following a street check on Jamestown's northside.  City polic...
-..., he was additionally charged with seventh-degree criminal possession of a **controlled** substance... along with the warrant.  He was held pending arraignment...</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – LOCKPORT, NY — A Niagara Falls woman was taken into custody on felony drug charges following a Niagara County Drug Task Force investigation, authorities confirmed. Daisy N. Ingram, 23, was arrested at a Niagara Street Extension address in the Town of Lockport. She faces multiple felony charges, including second-degree criminal sale […]The post Niagara Falls Woman Arrested on Multiple Drug Charges in Lockport appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D14" s="2">
-        <v>46113</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/01/niagara-falls-woman-arrested-on-multiple-drug-charges-in-lockport/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>...gara Falls woman was taken into custody on felony **drug** charges following a Niagara County Drug Task Forc...
-...on felony drug charges following a Niagara County **Drug** Task Force investigation, authorities confirmed. ...
-...The post Niagara Falls Woman Arrested on Multiple **Drug** Charges in Lockport appeared first on WNY News No...</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,17 +401,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
+          <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3 keyword references (WJTN)</t>
+          <t>7 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
+          <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
         </is>
       </c>
       <c r="D2" s="2">
@@ -419,123 +419,129 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...rosecutors say that between 2020 to 2022, Thomas distributed quantities of **fentanyl** and cocaine he received from Joseph Zaso... and, used Facebook and Cash Ap...
+...bsp;During the conspiracy... Thomas was accused of supplying quantities of **fentanyl** to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Ma...
+... in the past month.City man to spend 8 years in federal prison for role in **drug** conspiracy...A man from Jamestown convicted for his role in a drug traffic...
+...role in drug conspiracy...A man from Jamestown convicted for his role in a **drug** trafficking conspiracy will spend the next eight-years in federal prison. ...
+...eceived from Joseph Zaso... and, used Facebook and Cash App to conduct his **drug** trafficking activities.  During the conspiracy... Thomas was accused ...
+...pired with Jose Maisonet in 2022... whom city police made three undercover **drug** purchases from.  In July 2022, police raided Thomas’ Allen Stre...
+...d Thomas’ Allen Street residence... and seized a loaded handgun, and **drug** paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted ...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46121</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
 ...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
 ...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Jamestown Man Charged with DWI on Northside</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>(WNY News Now) – JAMESTOWN, NY — A Jamestown man was charged with driving while intoxicated following a Northside traffic stop on Saturday morning. Officers from the 1st Platoon responded at 7:15 a.m. on April 4, 2026, to reports of a potentially intoxicated driver. Upon arrival, they contacted James R. Geist, 58, of Jamestown. Through […]The post Jamestown Man Charged with DWI on Northside appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>46119</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-on-northside/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>... — A Jamestown man was charged with driving while **intoxicated** following a Northside traffic stop on Saturday mo...
 ....m. on April 4, 2026, to reports of a potentially **intoxicated** driver. Upon arrival, they contacted James R. Gei...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>(WNY News Now) – Jamestown, NY – A routine traffic stop in Jamestown led to the arrest of two Buffalo residents for possession of a controlled substance, police report. On the evening of April 3, at approximately 7:27 p.m., Jamestown Police Officers conducted a traffic stop at the intersection of Water Street and King Street […]The post Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D5" s="2">
         <v>46119</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/07/two-buffalo-residents-arrested-in-jamestown-traffic-stop-for-fentanyl-possession/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>... Residents Arrested in Jamestown Traffic Stop for **Fentanyl** Possession appeared first on WNY News Now.
 ...rest of two Buffalo residents for possession of a **controlled** substance, police report. On the evening of April...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A 23-year-old Jamestown resident was charged with driving while intoxicated after police responded to a report of an unresponsive driver on the city’s south side Sunday afternoon. Officers from the Jamestown Police Department’s Second Platoon were dispatched at approximately 4:27 p.m. on April 5, 2026, for a report […]The post Jamestown Man Charged with DWI After Being Found Unresponsive in Running Vehicle appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46119</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-after-being-found-unresponsive-in-running-vehicle/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>...Jamestown resident was charged with driving while **intoxicated** after police responded to a report of an unrespon...</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -585,12 +591,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jamestown Woman Sentenced For Role In Drug Conspiracy - Post Journal</t>
+          <t>15 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
         </is>
       </c>
       <c r="D8" s="2">
@@ -598,55 +609,10 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/292m8jvo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dunkirk Man Facing Federal Charges for Drugs, Weapons - National Today</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46115</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/23gxelxt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>15 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46115</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910825/wjtn-news-headlines-for-fri-apr-3-2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl** and cocaine... maintaining a drug involved premises... and being a user of...
 ...cutors say in March of 2024... investigators made a controlled purchase of **fentanyl** from Anabell Santiago.... and, the following month... they raided the home...
@@ -665,43 +631,7 @@
 ...f firearms.  Prosecutors say in March of 2024... investigators made a **controlled** purchase of fentanyl from Anabell Santiago.... and, the following month......</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Apr. 2, 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Seinfelt, Meyers and Kreischer to headline August's National Comedy Festival in Jamestown....Two well-established names... and, one rising star have been announced as headliners for this year's 35th annual National Comedy Festival in Jamestown.  The National Comedy Center has announced that Jerry Seinfeld... Bert Kreischer... and, Seth Meyers will headline the annual festival on August 6-9 of this year.  In addition... for the first time... this year's festival will have all three headliners performing at the Northwest Arena... and, additional talent will be featured in the Stand-up Showcases and late-night comedy shows throughout the festival.  Seinfeld will headline on Thursday, Aug. 6... Kreischer will take the stage on Saturday the 8th... and, Seth Meyers will perform on Sunday, Aug. 9.  On Friday the 7th... there will be a Stand-up Showcase at the Reg Lenna Center for the Arts.  Comedy Center Executive Director Journey Gunderson says -- "this year’s festival brings together artists who represent distinct approaches to the craft. I love that audiences can experience the best of live comedy while connecting it to the larger story we preserve and share every day in Jamestown."  Tickets for the headlining shows and festival events will go on pre-sale for Comedy Center members beginning Monday, Apr. 27 at 12 p.m. EDT... and, for the general public on Friday, May 1 at Noon EDT at ComedyCenter.org.  For more information... you can also call (716)-484-2222.Sex offender arrested on new child porn charges in Jamestown...A registered sex offender from Jamestown has been arrested on new, federal child pornography charges.  U.S. Attorney Michael DiGiacomo has announced that 42 year-old John Peterson was arrested Wednesday... and, charged with distribution and possession of child pornography by a person with a prior child porn conviction.  Prosecutors say last June... the National Center for Missing and Exploited Children received a CyberTip from the messaging app "Kik" that two files of suspected child porn were uploaded between June 14-16 of 2025.  The files were uploaded with the username "hardinny41_mkc..." and, were shared with other users.  The center the received another tip from Kik on July 5... that a file of suspected child pornography was uploaded on June 28 by someone with the same username.  Subsequent investigation traced the uploaded files to Peterson.  Investigators in December obtained a warrant... and, seized Peterson’s cell phone.  They allegedly found about 9 image files... and, 5 video files of suspected child sexual abuse material.  He was convicted in 2010 in Carroll Town Court of attempted possession of a sexual performance by a child less than 16 Year of Age.  He was then convicted in 2023 in Chautauqua County Court of possessing a sexual performance by a child less than 16 Years of age, and criminal possession of a firearm.  Peterson faces a manditory minimum of 15 years in prison... a maximum of 40... and, a $250,000 fine.Borrello says, given policy differences among Democrats on Climate Act, a state budget may be later than last year...The late New York state budget will likely be later than even last year when negotiations went into early May.  Those are the feelings of State Senator George Borrello... who says... with the Apr. 1 deadline looming late Tuesday... the legislature approved a one-week budget extension.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040... but, he calls it nothing more than "window dressing..." and energy costs continue to go up.  One of the early parts of the "Climate Leadership and Community Protection Act" was a ban on use of fossils fuels to power newer, and smaller homes being built this year.  However... that was stopped by a court order... and, Hochul delayed the move for a year.  Borrello says that's merely an "Election Year" ploy to avoid the issue until after November.  He says he's spoken with officials from National Grid, who say while they're building new power plants in other states, they aren't in New York.  The legislature is soon leaving Albany for the Passover-Easter Break... and, will be back in session next Tuesday.  Governor Hochul's budget proposal totaled $262-billion... while the Senate and Assembly versions range from $8-billion to $10-billion more.Jamestown man arrested on drug charge following traffic stop...A man from Jamestown has been arrested on several warrants following a traffic stop on the city's southside last Saturday.  Jamestown police say a patrol spotted the car commit a traffic violation about 3:30 p.m., and, stopped the vehicle in the area of Cole Avenue and Myrtle Steet.  Officers say they found that the driver -- 60 year-old David Robbins -- was sought on several Jamestown and State Police bench warrants.  Police also found that Robbins was driving with a suspended license... and, was in possession of a quantity of cocaine.  He was charged with seventh-degree criminal possession of a controlled substance... second-degree aggravated unlicensed operator... and, held pending arraignment. </t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46115</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910712/wjtn-news-headlines-for-thurs-apr-2-2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...rsions range from $8-billion to $10-billion more.Jamestown man arrested on **drug** charge following traffic stop...A man from Jamestown has been arrested on ...
-...cocaine.  He was charged with seventh-degree criminal possession of a **controlled** substance... second-degree aggravated unlicensed operator... and, held pen...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,28 +401,265 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>WJTN News Headlines for Fri., Apr. 10, 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>California man convicted of drug conspiracy involving Jamestown-area dealer isentenced to 10 years, six-months in federal prison...Another key player in Jamestown-area drug trafficking circles will spend more than 10 years in federal prison.  U.S. Attorney Michael DiGiacomo announced Thursday that 43 year-old La D. Huynh of Chula Vista, Calif., who was convicted of narcotics conspiracy, was sentenced in U.S. District Court in Buffalo to 126 months in prison.  Prosecutors say that Huynh, a California-based drug trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and marijuana to other members of the conspiracy.  They included Jun Martinez, a Jamestown-based drug trafficker.  In 2019... after receiving a large amount of meth... there was a payment issue between Martinez and Huynh, and Martinez stopped taking calls from Huynh.  However... sometime in 2020... Huynh and Martinez restarted their operations... and, Huynh began shipping quantities of cocaine... a heroin/fentanyl mix... and meth in the mail, from the San Diego-area.  In September of 2020... Martinez traveled to the San Diego area and met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and fentanyl.   After the transaction... Martinez and Hughes started traveling back to the Jamestown-area... but, during the return trip... they were stopped by an Illinois State Police Trooper.  A search of the vehicle led to discovery of about 6,300 grams of methamphetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuana products... and ,they were arrested.  Martinez was previously convicted and is awaiting sentencing.Two city men indicted on drug, firearms, and kidnapping charges...Two men from Jamestown have been indicted on federal charges for drug trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury has returned a superseding indictment charging 50 year-old Blake Smith -- also known as "Sweets..." and 45 year-old Willie Graham -- also known as "Wu..." with narcotics conspiracy, Hobbs Act Robbery, kidnapping, use of a firearm during a crime of violence, and use of a firearm in furtherance of drug trafficking.  DiGiacomo adds that Smith is also charged with possession of firearms in furtherance of drug trafficking, and distribution of fentanyl causing serious bodily injury.  Prosecutors say that between February 2017, and January 2024... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, fentanyl, and cocaine in the Jamestown area.  During the conspiracy, Smith possessed a firearm.  They add that between May 9 and 11 of 2023... Smith sold fentanyl causing serious bodily injury to individuals identified as R. P. and D.C.  In March of that year... Smith and Graham are also accused of kidnapped an individual identified as D.D... and, also stole a 25-thousand dollar check from D.D. while brandishing a firearm.  Both men face a maximum of life in prison if convicted.CLPOA looking ahead to what's next after Judge annuls NYS Freshwater Wetlands Regulation Act...The head of one of the lake groups that successfully sued New York State over it's Wetland Regulations is pleased with the outcome.  However... Chautauqua Lake Property Owners Association President Jim Wehrfritz says they're also waiting to see how the Department of Environmental Conservation responds to the State Supreme Court decision annuling those regulations.  Wehrfritz says they could appeal, or they could do the environmental due diligence, and try to bring the regulations forward again.  He says... for the CLPOA... it's gratefying to see their approximately three year effort be successful... along with the other groups involved.  The Chautauqua Lake Partnership was also a plaintiff in the suit.  He says that will be one of the three main topics at tomorrow morning's 15th meeting of the CLPOA since it formed.  Wehrfritz says they'll also review the recent Chautauqua Lake Symposium... and, further discuss their push to create a centralized lake authority and district they feel would better oversee the lake.   Tomorrow's CLPOA meeting will be held at the Lawson Boat Center in Bemus Point at 9 a.m., and, will run until 10:30 a.m.  Wehrfritz says you can also Zoom into the meeting by going to Zoom -- and punching in: 6346503547... and, the password is CLPOA -- all lower case.Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient..." and, the real work on the spending plan should have been done weeks ago.  He says this week was especially frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over $262-billion... while the Assembly and Senate bills are between $8-million and $10-billion higher.  The budget was due by Apr. 1.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment.</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911734/wjtn-news-headlines-for-fri-apr-10-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...say that Huynh, a California-based drug trafficker, supplied quantities of **methamphetamine**, heroin/fentanyl, cocaine, and marijuana to other members of the conspirac...
+...met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of **methamphetamine**, cocaine, and fentanyl.   After the transaction... Martinez and Hughe...
+...er.  A search of the vehicle led to discovery of about 6,300 grams of **methamphetamine**, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuan...
+...rnia-based drug trafficker, supplied quantities of methamphetamine, heroin/**fentanyl**, cocaine, and marijuana to other members of the conspiracy.  They inc...
+... operations... and, Huynh began shipping quantities of cocaine... a heroin/**fentanyl** mix... and meth in the mail, from the San Diego-area.  In September o...
+...tor Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and **fentanyl**.   After the transaction... Martinez and Hughes started traveling bac...
+...iscovery of about 6,300 grams of methamphetamine, more than 3,100 grams of **fentanyl**... 2,241 grams of cocaine, and marijuana products... and ,they were arrest...
+...ession of firearms in furtherance of drug trafficking, and distribution of **fentanyl** causing serious bodily injury.  Prosecutors say that between February...
+.... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, **fentanyl**, and cocaine in the Jamestown area.  During the conspiracy, Smith pos...
+... a firearm.  They add that between May 9 and 11 of 2023... Smith sold **fentanyl** causing serious bodily injury to individuals identified as R. P. and D.C. ...
+California man convicted of **drug** conspiracy involving Jamestown-area dealer isentenced to 10 years, six-mon...
+...years, six-months in federal prison...Another key player in Jamestown-area **drug** trafficking circles will spend more than 10 years in federal prison.  ...
+...126 months in prison.  Prosecutors say that Huynh, a California-based **drug** trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocai...
+...ers of the conspiracy.  They included Jun Martinez, a Jamestown-based **drug** trafficker.  In 2019... after receiving a large amount of meth... the...
+...s previously convicted and is awaiting sentencing.Two city men indicted on **drug**, firearms, and kidnapping charges...Two men from Jamestown have been indic...
+...charges...Two men from Jamestown have been indicted on federal charges for **drug** trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiaco...
+...firearm during a crime of violence, and use of a firearm in furtherance of **drug** trafficking.  DiGiacomo adds that Smith is also charged with possessi...
+...s that Smith is also charged with possession of firearms in furtherance of **drug** trafficking, and distribution of fentanyl causing serious bodily injury. &amp;...
+...ker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and **marijuana** to other members of the conspiracy.  They included Jun Martinez, a Ja...
+...hetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and **marijuana** products... and ,they were arrested.  Martinez was previously convict...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A California man has been sentenced to 126 months in federal prison for his role in a multi-state narcotics trafficking operation involving methamphetamine, fentanyl, cocaine, and marijuana shipped between California and Western New York. BUFFALO, N.Y. — U.S. Attorney Michael DiGiacomo announced that La D. Huynh, 43, of Chula Vista, California, […]The post California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/10/california-man-sentenced-to-more-than-10-years-in-federal-prison-for-cross-country-drug-trafficking-conspiracy/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...i-state narcotics trafficking operation involving **methamphetamine**, fentanyl, cocaine, and marijuana shipped between...
+... trafficking operation involving methamphetamine, **fentanyl**, cocaine, and marijuana shipped between Californi...
+...Than 10 Years in Federal Prison for Cross-Country **Drug** Trafficking Conspiracy appeared first on WNY News...
+...involving methamphetamine, fentanyl, cocaine, and **marijuana** shipped between California and Western New York. ...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — Two Jamestown men have been charged in a federal superseding indictment alleging narcotics trafficking, kidnapping, and armed robbery tied to a multi-year drug conspiracy involving fentanyl, heroin, and cocaine. A federal grand jury has returned a superseding indictment charging Blake D. Smith, also known as “Sweets,” and Willie […]The post Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/10/two-jamestown-men-charged-in-federal-superseding-indictment-involving-fentanyl-sales-kidnapping-and-armed-robbery/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...ry tied to a multi-year drug conspiracy involving **fentanyl**, heroin, and cocaine. A federal grand jury has re...
+...arged in Federal Superseding Indictment Involving **Fentanyl** Sales, Kidnapping, and Armed Robbery appeared fir...
+...idnapping, and armed robbery tied to a multi-year **drug** conspiracy involving fentanyl, heroin, and cocain...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – NEWFANE, N.Y. — A two-vehicle crash in the Town of Newfane on April 8 left multiple people seriously injured, including a child, and resulted in a driving while intoxicated arrest under Leandra’s Law, according to the Niagara County Sheriff’s Office. Deputies responded at approximately 6:16 p.m. to the intersection of Day […]The post Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/10/newfane-crash-leaves-multiple-injured-driver-charged-under-leandras-law/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>...ncluding a child, and resulted in a driving while **intoxicated** arrest under Leandra’s Law, according to the Niag...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has been sentenced to eight years in federal prison for his involvement in a drug trafficking conspiracy involving fentanyl and cocaine. U.S. Attorney Michael DiGiacomo announced that Jaquez Thomas, 22, of Jamestown, was sentenced to 96 months in prison by U.S. District Judge John L. […]The post Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/10/jamestown-man-sentenced-to-8-years-in-federal-prison-for-role-in-drug-conspiracy/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...vement in a drug trafficking conspiracy involving **fentanyl** and cocaine. U.S. Attorney Michael DiGiacomo anno...
+... years in federal prison for his involvement in a **drug** trafficking conspiracy involving fentanyl and coc...
+...entenced to 8 Years in Federal Prison for Role in **Drug** Conspiracy appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rochester Man Pleads Guilty to Federal Drug and Firearm Charges</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Rochester man has pleaded guilty to federal drug trafficking and firearm offenses following a multi-agency investigation into narcotics activity in Monroe County. Juan Sosa, 30, of Rochester, entered his plea before Chief U.S. District Judge Elizabeth A. Wolford to charges of possession with intent to distribute 100 […]The post Rochester Man Pleads Guilty to Federal Drug and Firearm Charges appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/10/rochester-man-pleads-guilty-to-federal-drug-and-firearm-charges/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>.... — A Rochester man has pleaded guilty to federal **drug** trafficking and firearm offenses following a mult...
+...…]The post Rochester Man Pleads Guilty to Federal **Drug** and Firearm Charges appeared first on WNY News No...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>7 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D8" s="2">
         <v>46121</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...rosecutors say that between 2020 to 2022, Thomas distributed quantities of **fentanyl** and cocaine he received from Joseph Zaso... and, used Facebook and Cash Ap...
 ...bsp;During the conspiracy... Thomas was accused of supplying quantities of **fentanyl** to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Ma...
@@ -433,207 +670,66 @@
 ...d Thomas’ Allen Street residence... and seized a loaded handgun, and **drug** paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted ...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D9" s="2">
         <v>46121</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
 ...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
 ...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Jamestown Man Charged with DWI on Northside</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – JAMESTOWN, NY — A Jamestown man was charged with driving while intoxicated following a Northside traffic stop on Saturday morning. Officers from the 1st Platoon responded at 7:15 a.m. on April 4, 2026, to reports of a potentially intoxicated driver. Upon arrival, they contacted James R. Geist, 58, of Jamestown. Through […]The post Jamestown Man Charged with DWI on Northside appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46119</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/07/jamestown-man-charged-with-dwi-on-northside/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>... — A Jamestown man was charged with driving while **intoxicated** following a Northside traffic stop on Saturday mo...
-....m. on April 4, 2026, to reports of a potentially **intoxicated** driver. Upon arrival, they contacted James R. Gei...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – Jamestown, NY – A routine traffic stop in Jamestown led to the arrest of two Buffalo residents for possession of a controlled substance, police report. On the evening of April 3, at approximately 7:27 p.m., Jamestown Police Officers conducted a traffic stop at the intersection of Water Street and King Street […]The post Two Buffalo Residents Arrested in Jamestown Traffic Stop for Fentanyl Possession appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46119</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/07/two-buffalo-residents-arrested-in-jamestown-traffic-stop-for-fentanyl-possession/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>... Residents Arrested in Jamestown Traffic Stop for **Fentanyl** Possession appeared first on WNY News Now.
-...rest of two Buffalo residents for possession of a **controlled** substance, police report. On the evening of April...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D10" s="2">
         <v>46118</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://tinyurl.com/23hv4ts3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dunkirk man in standoff facing federal charges for drugs, weapons - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D7" s="2">
-        <v>46116</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/25f9m6qw</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Apr. 3, 2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>15 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>City woman receives 8-year federal sentence for drug trafficking...A Jamestown woman has been sentenced to seven-years in federal prison for her role in a drug trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announced that 53 year-old Anabell Santiago received the 84 month sentence Thursday in U.S. District Court in Buffalo.  Santiago had been convicted of conspiracy to possess with intent to distribute, and to distribute, 40 grams or more of fentanyl and cocaine... maintaining a drug involved premises... and being a user of a controlled substance in possession of firearms.  Prosecutors say in March of 2024... investigators made a controlled purchase of fentanyl from Anabell Santiago.... and, the following month... they raided the home of Santiago and her husband, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30,000 in cash, and drug paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sentenced to serve 11 years in prison.Dunkirk man accused of shooting, and injuring a police officer, now facing federal charges...The Dunkirk man accused of attempted murder of a police officer following last week's nearly seven-hour stand-off... now faces federal charges in the case.  U.S. Attorney Michael DiGiacomo has announced that 39 year-old Christopher Marcinowski has been charged by criminal complaint of maintaining a drug involved premises... and, being a felon in possession of a firearm.  Prosecutors say this past February... the Sheriff's Department's Narcotics Unit began assisting with an investigation into Marcinowski's drug trafficking activities.  During the past two months... they say investigators found numerous plastic baggies which tested positive for cocaine in two garbage "pulls" at Marcinkowski's residence on Franklin Avenue.  On Mar. 24... police executed a search warrant on the home... but, as the raid began... Marcinowski fired two rounds from a firearm, one of which struck an officer.  The stand-off took place after that... and, ended when a police negotiator got Marcinowski to surrender without incident.----Once the home was cleared... officers say they seized about 197-grams of suspected psychedelic mushrooms... about 11 pounds of suspected marijuana... three guns... about $30,000 in cash, and drug paraphernalia.  Marcinowski has three prior federal convictions... and, if convicted this time... he faces a maximum penalty of 20 years in prison and a $500,000 fine.Wendel says subject of potential countywide policing services during consolidation and merger talks in north county... Two recent meetings about shaping the future of northern Chautauqua County included a concept that the county has previously explored -- countywide policing. It was part of talks about consolidations, mergers and shared services in the county that date back as far as the 1960s, according to Chautauqua County Executive P.J. Wendel. He says the logistics of operating a law enforcement agency can be done quickly... because a lot of things are already being done jointly.  Wendel says an idea that was brought up during the meetings of north county leaders was having all the north county police departments working together as a "North Metro," and the south county departments together as a "South Metro."  He says it's one way to start the process.  Wendel cited Nassau and Suffolk counties as two examples of countywide police departments in New York. Borrello says legislature approved one budget bill before leaving Albany...Local State Senator George Borrello says only one of New York's nearly dozen budget bills has been passed.  But... how soon the others will be dealt with remains up in the air.  Borrello says the budget extender approved Tuesday gets lawmakers until Apr. 8 to resolve the matter.  The Sunset Bay Republican says neither the Senate nor Assembly have even agreed on the budget numbers yet... and, only the debt service budget has been approved so far.  He says there are at least nine other budget bills that need to be approved.  Borrello says the main sticking point remains Governor Kathy Hochul's desire to push back climate legislation goals until 2040.  However... he says energy costs are still rising... and, two agencies... the Public Service Commission, and the state's Energy Research and Development Agency are already warning of potential, rolling black-outs -- especially in New York City.  Hochul has delayed implimentation of part of the "Climate Leadership and Community Protection Act..." for this year after a court delayed it's taking effect.  Borrello says it's merely an "Election Year" ploy to avoid the issue until after November.Man from Lakewood arrested for stealing scrap metal from behind car dealership...A Lakewood man has been arrested for allegedly stealing scrap metal from behind a Fairmount Avenue car dealership this past Monday night.  Lakewood-Busti Police say they were called to the scene at Shults Hyundai at 181 East Fairmount Ave. shortly before 11 p.m., and, caught Tyler Manelick in the act.  Officers say Manelick was arrested for petty larceny... and, was issued an appearance ticket for Busti Town Court at a later date.Stateline Speedway race car show underway...The annual Stateline Speedway car show is underway at the Chautauqua Mall in Lakewood though Saturday night.  Dozens of race cars from the track's Super Late Model... Crate Late Model... Outlaw E-Mods... and others are on the floor.  Opening Night for Stateline... which is celebrating it's 70th season... will be on Saturday, Apr. 25. </t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46115</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/910825/wjtn-news-headlines-for-fri-apr-3-2026</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>... possess with intent to distribute, and to distribute, 40 grams or more of **fentanyl** and cocaine... maintaining a drug involved premises... and being a user of...
-...cutors say in March of 2024... investigators made a controlled purchase of **fentanyl** from Anabell Santiago.... and, the following month... they raided the home...
-... of Santiago and her husband, Santo on Whitley Avenue.  Police seized **fentanyl**, crack cocaine, oxycodone, two loaded pistols, ammunition... more than $30...
-...eared... officers say they seized about 197-grams of suspected psychedelic **mushrooms**... about 11 pounds of suspected marijuana... three guns... about $30,000 i...
-City woman receives 8-year federal sentence for **drug** trafficking...A Jamestown woman has been sentenced to seven-years in feder...
-...oman has been sentenced to seven-years in federal prison for her role in a **drug** trafficking conspiracy.  U.S. Attorney Michael DiGiacomo has announce...
-...d to distribute, 40 grams or more of fentanyl and cocaine... maintaining a **drug** involved premises... and being a user of a controlled substance in possess...
-...xycodone, two loaded pistols, ammunition... more than $30,000 in cash, and **drug** paraphernalia.  DiGiacomo says Santos Santiago was convicted, and sen...
-...topher Marcinowski has been charged by criminal complaint of maintaining a **drug** involved premises... and, being a felon in possession of a firearm.  ...
-...'s Narcotics Unit began assisting with an investigation into Marcinowski's **drug** trafficking activities.  During the past two months... they say inves...
-... pounds of suspected marijuana... three guns... about $30,000 in cash, and **drug** paraphernalia.  Marcinowski has three prior federal convictions... an...
-...7-grams of suspected psychedelic mushrooms... about 11 pounds of suspected **marijuana**... three guns... about $30,000 in cash, and drug paraphernalia.  Marc...
-...and, Santo on Whitley Avenue.  Police seized fentanyl, crack cocaine, **oxycodone**, two loaded pistols, ammunition... more than $30,000 in cash, and drug par...
-...d cocaine... maintaining a drug involved premises... and being a user of a **controlled** substance in possession of firearms.  Prosecutors say in March of 202...
-...f firearms.  Prosecutors say in March of 2024... investigators made a **controlled** purchase of fentanyl from Anabell Santiago.... and, the following month......</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,28 +401,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46123</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Fri., Apr. 10, 2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>20 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>California man convicted of drug conspiracy involving Jamestown-area dealer isentenced to 10 years, six-months in federal prison...Another key player in Jamestown-area drug trafficking circles will spend more than 10 years in federal prison.  U.S. Attorney Michael DiGiacomo announced Thursday that 43 year-old La D. Huynh of Chula Vista, Calif., who was convicted of narcotics conspiracy, was sentenced in U.S. District Court in Buffalo to 126 months in prison.  Prosecutors say that Huynh, a California-based drug trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and marijuana to other members of the conspiracy.  They included Jun Martinez, a Jamestown-based drug trafficker.  In 2019... after receiving a large amount of meth... there was a payment issue between Martinez and Huynh, and Martinez stopped taking calls from Huynh.  However... sometime in 2020... Huynh and Martinez restarted their operations... and, Huynh began shipping quantities of cocaine... a heroin/fentanyl mix... and meth in the mail, from the San Diego-area.  In September of 2020... Martinez traveled to the San Diego area and met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and fentanyl.   After the transaction... Martinez and Hughes started traveling back to the Jamestown-area... but, during the return trip... they were stopped by an Illinois State Police Trooper.  A search of the vehicle led to discovery of about 6,300 grams of methamphetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuana products... and ,they were arrested.  Martinez was previously convicted and is awaiting sentencing.Two city men indicted on drug, firearms, and kidnapping charges...Two men from Jamestown have been indicted on federal charges for drug trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury has returned a superseding indictment charging 50 year-old Blake Smith -- also known as "Sweets..." and 45 year-old Willie Graham -- also known as "Wu..." with narcotics conspiracy, Hobbs Act Robbery, kidnapping, use of a firearm during a crime of violence, and use of a firearm in furtherance of drug trafficking.  DiGiacomo adds that Smith is also charged with possession of firearms in furtherance of drug trafficking, and distribution of fentanyl causing serious bodily injury.  Prosecutors say that between February 2017, and January 2024... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, fentanyl, and cocaine in the Jamestown area.  During the conspiracy, Smith possessed a firearm.  They add that between May 9 and 11 of 2023... Smith sold fentanyl causing serious bodily injury to individuals identified as R. P. and D.C.  In March of that year... Smith and Graham are also accused of kidnapped an individual identified as D.D... and, also stole a 25-thousand dollar check from D.D. while brandishing a firearm.  Both men face a maximum of life in prison if convicted.CLPOA looking ahead to what's next after Judge annuls NYS Freshwater Wetlands Regulation Act...The head of one of the lake groups that successfully sued New York State over it's Wetland Regulations is pleased with the outcome.  However... Chautauqua Lake Property Owners Association President Jim Wehrfritz says they're also waiting to see how the Department of Environmental Conservation responds to the State Supreme Court decision annuling those regulations.  Wehrfritz says they could appeal, or they could do the environmental due diligence, and try to bring the regulations forward again.  He says... for the CLPOA... it's gratefying to see their approximately three year effort be successful... along with the other groups involved.  The Chautauqua Lake Partnership was also a plaintiff in the suit.  He says that will be one of the three main topics at tomorrow morning's 15th meeting of the CLPOA since it formed.  Wehrfritz says they'll also review the recent Chautauqua Lake Symposium... and, further discuss their push to create a centralized lake authority and district they feel would better oversee the lake.   Tomorrow's CLPOA meeting will be held at the Lawson Boat Center in Bemus Point at 9 a.m., and, will run until 10:30 a.m.  Wehrfritz says you can also Zoom into the meeting by going to Zoom -- and punching in: 6346503547... and, the password is CLPOA -- all lower case.Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient..." and, the real work on the spending plan should have been done weeks ago.  He says this week was especially frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over $262-billion... while the Assembly and Senate bills are between $8-million and $10-billion higher.  The budget was due by Apr. 1.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D3" s="2">
         <v>46122</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911734/wjtn-news-headlines-for-fri-apr-10-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...say that Huynh, a California-based drug trafficker, supplied quantities of **methamphetamine**, heroin/fentanyl, cocaine, and marijuana to other members of the conspirac...
 ...met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of **methamphetamine**, cocaine, and fentanyl.   After the transaction... Martinez and Hughe...
@@ -446,37 +471,37 @@
 ...hetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and **marijuana** products... and ,they were arrested.  Martinez was previously convict...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>(WNY News Now) – A California man has been sentenced to 126 months in federal prison for his role in a multi-state narcotics trafficking operation involving methamphetamine, fentanyl, cocaine, and marijuana shipped between California and Western New York. BUFFALO, N.Y. — U.S. Attorney Michael DiGiacomo announced that La D. Huynh, 43, of Chula Vista, California, […]The post California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>46122</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/california-man-sentenced-to-more-than-10-years-in-federal-prison-for-cross-country-drug-trafficking-conspiracy/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...i-state narcotics trafficking operation involving **methamphetamine**, fentanyl, cocaine, and marijuana shipped between...
 ... trafficking operation involving methamphetamine, **fentanyl**, cocaine, and marijuana shipped between Californi...
@@ -484,78 +509,43 @@
 ...involving methamphetamine, fentanyl, cocaine, and **marijuana** shipped between California and Western New York. ...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — Two Jamestown men have been charged in a federal superseding indictment alleging narcotics trafficking, kidnapping, and armed robbery tied to a multi-year drug conspiracy involving fentanyl, heroin, and cocaine. A federal grand jury has returned a superseding indictment charging Blake D. Smith, also known as “Sweets,” and Willie […]The post Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D5" s="2">
         <v>46122</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/two-jamestown-men-charged-in-federal-superseding-indictment-involving-fentanyl-sales-kidnapping-and-armed-robbery/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...ry tied to a multi-year drug conspiracy involving **fentanyl**, heroin, and cocaine. A federal grand jury has re...
 ...arged in Federal Superseding Indictment Involving **Fentanyl** Sales, Kidnapping, and Armed Robbery appeared fir...
 ...idnapping, and armed robbery tied to a multi-year **drug** conspiracy involving fentanyl, heroin, and cocain...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – NEWFANE, N.Y. — A two-vehicle crash in the Town of Newfane on April 8 left multiple people seriously injured, including a child, and resulted in a driving while intoxicated arrest under Leandra’s Law, according to the Niagara County Sheriff’s Office. Deputies responded at approximately 6:16 p.m. to the intersection of Day […]The post Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46122</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/10/newfane-crash-leaves-multiple-injured-driver-charged-under-leandras-law/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>...ncluding a child, and resulted in a driving while **intoxicated** arrest under Leandra’s Law, according to the Niag...</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -570,12 +560,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy</t>
+          <t>Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has been sentenced to eight years in federal prison for his involvement in a drug trafficking conspiracy involving fentanyl and cocaine. U.S. Attorney Michael DiGiacomo announced that Jaquez Thomas, 22, of Jamestown, was sentenced to 96 months in prison by U.S. District Judge John L. […]The post Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – NEWFANE, N.Y. — A two-vehicle crash in the Town of Newfane on April 8 left multiple people seriously injured, including a child, and resulted in a driving while intoxicated arrest under Leandra’s Law, according to the Niagara County Sheriff’s Office. Deputies responded at approximately 6:16 p.m. to the intersection of Day […]The post Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
@@ -583,83 +573,118 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/04/10/newfane-crash-leaves-multiple-injured-driver-charged-under-leandras-law/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...ncluding a child, and resulted in a driving while **intoxicated** arrest under Leandra’s Law, according to the Niag...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has been sentenced to eight years in federal prison for his involvement in a drug trafficking conspiracy involving fentanyl and cocaine. U.S. Attorney Michael DiGiacomo announced that Jaquez Thomas, 22, of Jamestown, was sentenced to 96 months in prison by U.S. District Judge John L. […]The post Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/04/10/jamestown-man-sentenced-to-8-years-in-federal-prison-for-role-in-drug-conspiracy/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...vement in a drug trafficking conspiracy involving **fentanyl** and cocaine. U.S. Attorney Michael DiGiacomo anno...
 ... years in federal prison for his involvement in a **drug** trafficking conspiracy involving fentanyl and coc...
 ...entenced to 8 Years in Federal Prison for Role in **Drug** Conspiracy appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Rochester Man Pleads Guilty to Federal Drug and Firearm Charges</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — A Rochester man has pleaded guilty to federal drug trafficking and firearm offenses following a multi-agency investigation into narcotics activity in Monroe County. Juan Sosa, 30, of Rochester, entered his plea before Chief U.S. District Judge Elizabeth A. Wolford to charges of possession with intent to distribute 100 […]The post Rochester Man Pleads Guilty to Federal Drug and Firearm Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D8" s="2">
         <v>46122</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/rochester-man-pleads-guilty-to-federal-drug-and-firearm-charges/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>.... — A Rochester man has pleaded guilty to federal **drug** trafficking and firearm offenses following a mult...
 ...…]The post Rochester Man Pleads Guilty to Federal **Drug** and Firearm Charges appeared first on WNY News No...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>7 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>46121</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...rosecutors say that between 2020 to 2022, Thomas distributed quantities of **fentanyl** and cocaine he received from Joseph Zaso... and, used Facebook and Cash Ap...
 ...bsp;During the conspiracy... Thomas was accused of supplying quantities of **fentanyl** to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Ma...
@@ -670,64 +695,64 @@
 ...d Thomas’ Allen Street residence... and seized a loaded handgun, and **drug** paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted ...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D10" s="2">
         <v>46121</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
 ...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
 ...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>46118</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://tinyurl.com/23hv4ts3</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,15 +406,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -426,28 +426,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46123</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Fri., Apr. 10, 2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>20 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>California man convicted of drug conspiracy involving Jamestown-area dealer isentenced to 10 years, six-months in federal prison...Another key player in Jamestown-area drug trafficking circles will spend more than 10 years in federal prison.  U.S. Attorney Michael DiGiacomo announced Thursday that 43 year-old La D. Huynh of Chula Vista, Calif., who was convicted of narcotics conspiracy, was sentenced in U.S. District Court in Buffalo to 126 months in prison.  Prosecutors say that Huynh, a California-based drug trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and marijuana to other members of the conspiracy.  They included Jun Martinez, a Jamestown-based drug trafficker.  In 2019... after receiving a large amount of meth... there was a payment issue between Martinez and Huynh, and Martinez stopped taking calls from Huynh.  However... sometime in 2020... Huynh and Martinez restarted their operations... and, Huynh began shipping quantities of cocaine... a heroin/fentanyl mix... and meth in the mail, from the San Diego-area.  In September of 2020... Martinez traveled to the San Diego area and met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and fentanyl.   After the transaction... Martinez and Hughes started traveling back to the Jamestown-area... but, during the return trip... they were stopped by an Illinois State Police Trooper.  A search of the vehicle led to discovery of about 6,300 grams of methamphetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuana products... and ,they were arrested.  Martinez was previously convicted and is awaiting sentencing.Two city men indicted on drug, firearms, and kidnapping charges...Two men from Jamestown have been indicted on federal charges for drug trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury has returned a superseding indictment charging 50 year-old Blake Smith -- also known as "Sweets..." and 45 year-old Willie Graham -- also known as "Wu..." with narcotics conspiracy, Hobbs Act Robbery, kidnapping, use of a firearm during a crime of violence, and use of a firearm in furtherance of drug trafficking.  DiGiacomo adds that Smith is also charged with possession of firearms in furtherance of drug trafficking, and distribution of fentanyl causing serious bodily injury.  Prosecutors say that between February 2017, and January 2024... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, fentanyl, and cocaine in the Jamestown area.  During the conspiracy, Smith possessed a firearm.  They add that between May 9 and 11 of 2023... Smith sold fentanyl causing serious bodily injury to individuals identified as R. P. and D.C.  In March of that year... Smith and Graham are also accused of kidnapped an individual identified as D.D... and, also stole a 25-thousand dollar check from D.D. while brandishing a firearm.  Both men face a maximum of life in prison if convicted.CLPOA looking ahead to what's next after Judge annuls NYS Freshwater Wetlands Regulation Act...The head of one of the lake groups that successfully sued New York State over it's Wetland Regulations is pleased with the outcome.  However... Chautauqua Lake Property Owners Association President Jim Wehrfritz says they're also waiting to see how the Department of Environmental Conservation responds to the State Supreme Court decision annuling those regulations.  Wehrfritz says they could appeal, or they could do the environmental due diligence, and try to bring the regulations forward again.  He says... for the CLPOA... it's gratefying to see their approximately three year effort be successful... along with the other groups involved.  The Chautauqua Lake Partnership was also a plaintiff in the suit.  He says that will be one of the three main topics at tomorrow morning's 15th meeting of the CLPOA since it formed.  Wehrfritz says they'll also review the recent Chautauqua Lake Symposium... and, further discuss their push to create a centralized lake authority and district they feel would better oversee the lake.   Tomorrow's CLPOA meeting will be held at the Lawson Boat Center in Bemus Point at 9 a.m., and, will run until 10:30 a.m.  Wehrfritz says you can also Zoom into the meeting by going to Zoom -- and punching in: 6346503547... and, the password is CLPOA -- all lower case.Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient..." and, the real work on the spending plan should have been done weeks ago.  He says this week was especially frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over $262-billion... while the Assembly and Senate bills are between $8-million and $10-billion higher.  The budget was due by Apr. 1.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>46122</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911734/wjtn-news-headlines-for-fri-apr-10-2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...say that Huynh, a California-based drug trafficker, supplied quantities of **methamphetamine**, heroin/fentanyl, cocaine, and marijuana to other members of the conspirac...
 ...met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of **methamphetamine**, cocaine, and fentanyl.   After the transaction... Martinez and Hughe...
@@ -471,37 +496,37 @@
 ...hetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and **marijuana** products... and ,they were arrested.  Martinez was previously convict...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>(WNY News Now) – A California man has been sentenced to 126 months in federal prison for his role in a multi-state narcotics trafficking operation involving methamphetamine, fentanyl, cocaine, and marijuana shipped between California and Western New York. BUFFALO, N.Y. — U.S. Attorney Michael DiGiacomo announced that La D. Huynh, 43, of Chula Vista, California, […]The post California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D5" s="2">
         <v>46122</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/california-man-sentenced-to-more-than-10-years-in-federal-prison-for-cross-country-drug-trafficking-conspiracy/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...i-state narcotics trafficking operation involving **methamphetamine**, fentanyl, cocaine, and marijuana shipped between...
 ... trafficking operation involving methamphetamine, **fentanyl**, cocaine, and marijuana shipped between Californi...
@@ -509,78 +534,43 @@
 ...involving methamphetamine, fentanyl, cocaine, and **marijuana** shipped between California and Western New York. ...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — Two Jamestown men have been charged in a federal superseding indictment alleging narcotics trafficking, kidnapping, and armed robbery tied to a multi-year drug conspiracy involving fentanyl, heroin, and cocaine. A federal grand jury has returned a superseding indictment charging Blake D. Smith, also known as “Sweets,” and Willie […]The post Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="2">
         <v>46122</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/two-jamestown-men-charged-in-federal-superseding-indictment-involving-fentanyl-sales-kidnapping-and-armed-robbery/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...ry tied to a multi-year drug conspiracy involving **fentanyl**, heroin, and cocaine. A federal grand jury has re...
 ...arged in Federal Superseding Indictment Involving **Fentanyl** Sales, Kidnapping, and Armed Robbery appeared fir...
 ...idnapping, and armed robbery tied to a multi-year **drug** conspiracy involving fentanyl, heroin, and cocain...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – NEWFANE, N.Y. — A two-vehicle crash in the Town of Newfane on April 8 left multiple people seriously injured, including a child, and resulted in a driving while intoxicated arrest under Leandra’s Law, according to the Niagara County Sheriff’s Office. Deputies responded at approximately 6:16 p.m. to the intersection of Day […]The post Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>46122</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/10/newfane-crash-leaves-multiple-injured-driver-charged-under-leandras-law/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...ncluding a child, and resulted in a driving while **intoxicated** arrest under Leandra’s Law, according to the Niag...</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -595,12 +585,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy</t>
+          <t>Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has been sentenced to eight years in federal prison for his involvement in a drug trafficking conspiracy involving fentanyl and cocaine. U.S. Attorney Michael DiGiacomo announced that Jaquez Thomas, 22, of Jamestown, was sentenced to 96 months in prison by U.S. District Judge John L. […]The post Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – NEWFANE, N.Y. — A two-vehicle crash in the Town of Newfane on April 8 left multiple people seriously injured, including a child, and resulted in a driving while intoxicated arrest under Leandra’s Law, according to the Niagara County Sheriff’s Office. Deputies responded at approximately 6:16 p.m. to the intersection of Day […]The post Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -608,83 +598,118 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/04/10/newfane-crash-leaves-multiple-injured-driver-charged-under-leandras-law/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...ncluding a child, and resulted in a driving while **intoxicated** arrest under Leandra’s Law, according to the Niag...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has been sentenced to eight years in federal prison for his involvement in a drug trafficking conspiracy involving fentanyl and cocaine. U.S. Attorney Michael DiGiacomo announced that Jaquez Thomas, 22, of Jamestown, was sentenced to 96 months in prison by U.S. District Judge John L. […]The post Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46122</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/04/10/jamestown-man-sentenced-to-8-years-in-federal-prison-for-role-in-drug-conspiracy/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...vement in a drug trafficking conspiracy involving **fentanyl** and cocaine. U.S. Attorney Michael DiGiacomo anno...
 ... years in federal prison for his involvement in a **drug** trafficking conspiracy involving fentanyl and coc...
 ...entenced to 8 Years in Federal Prison for Role in **Drug** Conspiracy appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Rochester Man Pleads Guilty to Federal Drug and Firearm Charges</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — A Rochester man has pleaded guilty to federal drug trafficking and firearm offenses following a multi-agency investigation into narcotics activity in Monroe County. Juan Sosa, 30, of Rochester, entered his plea before Chief U.S. District Judge Elizabeth A. Wolford to charges of possession with intent to distribute 100 […]The post Rochester Man Pleads Guilty to Federal Drug and Firearm Charges appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>46122</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/rochester-man-pleads-guilty-to-federal-drug-and-firearm-charges/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>.... — A Rochester man has pleaded guilty to federal **drug** trafficking and firearm offenses following a mult...
 ...…]The post Rochester Man Pleads Guilty to Federal **Drug** and Firearm Charges appeared first on WNY News No...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>7 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D10" s="2">
         <v>46121</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...rosecutors say that between 2020 to 2022, Thomas distributed quantities of **fentanyl** and cocaine he received from Joseph Zaso... and, used Facebook and Cash Ap...
 ...bsp;During the conspiracy... Thomas was accused of supplying quantities of **fentanyl** to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Ma...
@@ -695,64 +720,64 @@
 ...d Thomas’ Allen Street residence... and seized a loaded handgun, and **drug** paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted ...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>46121</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
 ...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
 ...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <v>46118</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://tinyurl.com/23hv4ts3</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,78 +401,226 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
+          <t>WJTN News Headlines for Monday, Apr. 13, 2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
+          <t>Fire destroys condemned home on Prendergast Ave; but, fire crews save two adjacent homes...Fire has destroyed a vacant and condemned home on Jamestown's northside... but, quick work by firefighters saved two neighoring homes.  City Fire Battlion Chief Nate Alm says firefighters were called to the scene at 612 Prendergast Ave. shortly after 7 p.m. Friday... and, first arriving crews found the home fully-engulfed in flames... and they moved quickly to knock down the flames, and protect the two adjacent hmes.  Alm says the family living in one was safely evacuated... along with their pets.  He says an off-duty shift of 15 firefighters and a commander was called in to assist.  No injuries were reported... but, he says crews were at the scene for nearly five-and-a-half hours.  The cause is under investigation... and the home at 612 Prendergast will be torn down.Man from Jamestown and woman from Buffalo indicted on federal drug conspiracy charges...A man from Jamestown... and, a woman from Buffalo have been indicted on a federal charge for allegedly being involved in a narcotics conspiracy.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury returned the indictment charging 41 year-old Brandon Murray... and, 35 year-old Latika Saintkitts... with narcotics conspiracy.  DiGiacomo says the charge carries a mandatory minimum of 10 years in prison...  and a maximum of life. In addition, Saintkitts is charged with distribution of crack cocaine and fentanyl.  Prosecutors say that between 2021, and September 2024, Murray and Saintkitts conspired with others to possess and distribute fentanyl, methamphetamine, and heroin.  In addition, in April of 2024, Saintkitts possessed and distributed crack cocaine... and, in June of that year... she possessed and distributed fentanyl.  Murray was detained... and, Saintkitts was released on conditions.Charges now filed against man involved in stand-off last week in Fredonia...Charges have now been filed against a man who barricaded himself for several hours inside a White Street home in the Village of Fredonia last week... prompting a shelter in place order for the area.  Fredonia Police say a White Street resident reported on Wednesday that 44-year-old Kyle Denhardt was unwanted... refused to leave her residence, and was possibly in possession of a handgun.  Officers responded... and, helped the woman off the property, then began communicating with Denhardt.  A perimeter was established and maintained with assistance from Dunkirk police... University Police... and State Police.  While the area was closed off to vehicle and pedestrian traffic, State Police Special Operations Response Teams were deployed... along with an Unmanned Aerial Systems unit.  After warrants were obtained, Denhardt surrendered peacefully after several hours of negotiations to a special State Police Team.  When police executed the search warrant, they discovered a large cache of weaponry, including a ghost gun, high-capacity magazines, ammunition, rifle parts, and related accessories.-----Denhardt, who is a resident of Maryland and South Carolina, faces charged including:  second-degree menacing... second-degree criminal trespass... second-degree criminal possession of a weapon... and, two counts of third-degree criminal possession of a weapon.  He was taken to the county jail on $400,000 cash bail.Woman arrested in town of Hanover for incident with stun gun...A woman has been arrested for allegedly displaying an electric stun gun during an altercation in the town of Hanover.  Sheriff's officers say they were called to the scene about 7:30 a.m. last Thursday on a report of the incident.  Deputies say they found that 26 year-old Allyson Lycett had pulled out the stun gun during the altercation... and, was arrested for fourth-degree criminal possession of a weapon.  Lycett was arraigned... and, issued an appearance ticket for Hanover Town Court at a later date.Lake Property Owner's hold first meeting since court ruling "annuls" wetland regulations...With last week's State Supreme Court ruling... the state Department of Environmental Conservation may have to do a full-blown environmental impact statement on any new wetland regulations.  That from Chautauqua Lake Property Owners Association president Jim Wehrfritz during the CLPOA's most recent meeting last Saturday in Bemus Point.  Wehrfritz says the court's annulment of the regulations "demand accountabilty."  Wehrfritz says the DEC may have to issue a "positive declaration..." meaning that the regulations would have to consider economic and social issues in those regulations.  Wehrfritz... however... cautioned that if the DEC were to implement new wetland regulations.. they would be more "broadbased" because it would have to be for the entire state.  He later focused on the June 2024 plan for the lake proposed by Dr. Robert Richardson at North Carolina State University.  Wehrfritz feels it needs to be acted on, because it's time to have a plan that can be acted on.  He says the CLPOA also feels there needs to be a study of the lake's condition... and, the wetlands regulations on property values on the lake.State Supreme Court rules in favor of village connecting with the No. County Water District...A State Supreme Court judge has sided with the village of Fredonia in a lawsuit that sought to annul a resolution for the village's project to connect with the North County Water District.  In an 11-page ruling last Wednesday... Judge Grace Hanlon denied the request that was filed in October by members of the "Save Our Reservoir" group, who argued that the village violated the State Environmental Quality Review Act... General Municipal Law... and, the village's Zoning Code.  Judge Hanlon determined that the village -- "neither abused its discretion nor was arbitrary or capricious in its determination" with regard to its SEQRA analysis.</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911992/wjtn-news-headlines-for-monday-apr-13-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...y and Saintkitts conspired with others to possess and distribute fentanyl, **methamphetamine**, and heroin.  In addition, in April of 2024, Saintkitts possessed and...
+... In addition, Saintkitts is charged with distribution of crack cocaine and **fentanyl**.  Prosecutors say that between 2021, and September 2024, Murray and S...
+...024, Murray and Saintkitts conspired with others to possess and distribute **fentanyl**, methamphetamine, and heroin.  In addition, in April of 2024, Saintki...
+...rack cocaine... and, in June of that year... she possessed and distributed **fentanyl**.  Murray was detained... and, Saintkitts was released on conditions.C...
+...be torn down.Man from Jamestown and woman from Buffalo indicted on federal **drug** conspiracy charges...A man from Jamestown... and, a woman from Buffalo hav...</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jamestown Man and Buffalo Woman Indicted on Federal Narcotics Conspiracy Charges in Western New York</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A federal grand jury has indicted a Jamestown man and a Buffalo woman on narcotics conspiracy charges tied to the distribution of fentanyl, methamphetamine, heroin, and crack cocaine in Western New York. A federal grand jury returned an indictment charging Brandon Murray, 41, of Jamestown, and Latika Saintkitts, […]The post Jamestown Man and Buffalo Woman Indicted on Federal Narcotics Conspiracy Charges in Western New York appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46123</v>
+        <v>46125</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+          <t>https://wnynewsnow.com/2026/04/13/jamestown-man-and-buffalo-woman-indicted-on-federal-narcotics-conspiracy-charges-in-western-new-york/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...acy charges tied to the distribution of fentanyl, **methamphetamine**, heroin, and crack cocaine in Western New York. A...
+...cs conspiracy charges tied to the distribution of **fentanyl**, methamphetamine, heroin, and crack cocaine in We...</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Two Olean Residents Arrested After Methamphetamine Seizure on Interstate 86 in Great Valley</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A traffic stop on Interstate 86 in the Town of Great Valley led to the arrest of two Olean residents after deputies reportedly discovered more than 15 grams of methamphetamine and drug paraphernalia, according to the Cattaraugus County Sheriff’s Office. The incident occurred on April 11, 2026, at approximately 1:33 a.m. […]The post Two Olean Residents Arrested After Methamphetamine Seizure on Interstate 86 in Great Valley appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46125</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/13/two-olean-residents-arrested-after-methamphetamine-seizure-on-interstate-86-in-great-valley/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...uties reportedly discovered more than 15 grams of **methamphetamine** and drug paraphernalia, according to the Cattarau...
+...m. […]The post Two Olean Residents Arrested After **Methamphetamine** Seizure on Interstate 86 in Great Valley appeared...
+...covered more than 15 grams of methamphetamine and **drug** paraphernalia, according to the Cattaraugus Count...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mayville Man Charged with DWI Following Early Morning Investigation on Route 430</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now)- A 43-year-old Mayville resident was charged with driving while intoxicated after deputies investigated a suspicious situation early Saturday morning in the Town of Chautauqua. CHAUTAUQUA, N.Y. — A Mayville man is facing driving while intoxicated (DWI) charges following a sheriff’s investigation on Route 430 during the early morning hours of April 11, […]The post Mayville Man Charged with DWI Following Early Morning Investigation on Route 430 appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46125</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/13/mayville-man-charged-with-dwi-following-early-morning-investigation-on-route-430/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>... Mayville resident was charged with driving while **intoxicated** after deputies investigated a suspicious situatio...
+...UA, N.Y. — A Mayville man is facing driving while **intoxicated** (DWI) charges following a sheriff’s investigation...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46124</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46123</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Fri., Apr. 10, 2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>20 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>California man convicted of drug conspiracy involving Jamestown-area dealer isentenced to 10 years, six-months in federal prison...Another key player in Jamestown-area drug trafficking circles will spend more than 10 years in federal prison.  U.S. Attorney Michael DiGiacomo announced Thursday that 43 year-old La D. Huynh of Chula Vista, Calif., who was convicted of narcotics conspiracy, was sentenced in U.S. District Court in Buffalo to 126 months in prison.  Prosecutors say that Huynh, a California-based drug trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and marijuana to other members of the conspiracy.  They included Jun Martinez, a Jamestown-based drug trafficker.  In 2019... after receiving a large amount of meth... there was a payment issue between Martinez and Huynh, and Martinez stopped taking calls from Huynh.  However... sometime in 2020... Huynh and Martinez restarted their operations... and, Huynh began shipping quantities of cocaine... a heroin/fentanyl mix... and meth in the mail, from the San Diego-area.  In September of 2020... Martinez traveled to the San Diego area and met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and fentanyl.   After the transaction... Martinez and Hughes started traveling back to the Jamestown-area... but, during the return trip... they were stopped by an Illinois State Police Trooper.  A search of the vehicle led to discovery of about 6,300 grams of methamphetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuana products... and ,they were arrested.  Martinez was previously convicted and is awaiting sentencing.Two city men indicted on drug, firearms, and kidnapping charges...Two men from Jamestown have been indicted on federal charges for drug trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury has returned a superseding indictment charging 50 year-old Blake Smith -- also known as "Sweets..." and 45 year-old Willie Graham -- also known as "Wu..." with narcotics conspiracy, Hobbs Act Robbery, kidnapping, use of a firearm during a crime of violence, and use of a firearm in furtherance of drug trafficking.  DiGiacomo adds that Smith is also charged with possession of firearms in furtherance of drug trafficking, and distribution of fentanyl causing serious bodily injury.  Prosecutors say that between February 2017, and January 2024... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, fentanyl, and cocaine in the Jamestown area.  During the conspiracy, Smith possessed a firearm.  They add that between May 9 and 11 of 2023... Smith sold fentanyl causing serious bodily injury to individuals identified as R. P. and D.C.  In March of that year... Smith and Graham are also accused of kidnapped an individual identified as D.D... and, also stole a 25-thousand dollar check from D.D. while brandishing a firearm.  Both men face a maximum of life in prison if convicted.CLPOA looking ahead to what's next after Judge annuls NYS Freshwater Wetlands Regulation Act...The head of one of the lake groups that successfully sued New York State over it's Wetland Regulations is pleased with the outcome.  However... Chautauqua Lake Property Owners Association President Jim Wehrfritz says they're also waiting to see how the Department of Environmental Conservation responds to the State Supreme Court decision annuling those regulations.  Wehrfritz says they could appeal, or they could do the environmental due diligence, and try to bring the regulations forward again.  He says... for the CLPOA... it's gratefying to see their approximately three year effort be successful... along with the other groups involved.  The Chautauqua Lake Partnership was also a plaintiff in the suit.  He says that will be one of the three main topics at tomorrow morning's 15th meeting of the CLPOA since it formed.  Wehrfritz says they'll also review the recent Chautauqua Lake Symposium... and, further discuss their push to create a centralized lake authority and district they feel would better oversee the lake.   Tomorrow's CLPOA meeting will be held at the Lawson Boat Center in Bemus Point at 9 a.m., and, will run until 10:30 a.m.  Wehrfritz says you can also Zoom into the meeting by going to Zoom -- and punching in: 6346503547... and, the password is CLPOA -- all lower case.Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient..." and, the real work on the spending plan should have been done weeks ago.  He says this week was especially frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over $262-billion... while the Assembly and Senate bills are between $8-million and $10-billion higher.  The budget was due by Apr. 1.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D8" s="2">
         <v>46122</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911734/wjtn-news-headlines-for-fri-apr-10-2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...say that Huynh, a California-based drug trafficker, supplied quantities of **methamphetamine**, heroin/fentanyl, cocaine, and marijuana to other members of the conspirac...
 ...met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of **methamphetamine**, cocaine, and fentanyl.   After the transaction... Martinez and Hughe...
@@ -496,37 +644,37 @@
 ...hetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and **marijuana** products... and ,they were arrested.  Martinez was previously convict...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>(WNY News Now) – A California man has been sentenced to 126 months in federal prison for his role in a multi-state narcotics trafficking operation involving methamphetamine, fentanyl, cocaine, and marijuana shipped between California and Western New York. BUFFALO, N.Y. — U.S. Attorney Michael DiGiacomo announced that La D. Huynh, 43, of Chula Vista, California, […]The post California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D9" s="2">
         <v>46122</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/california-man-sentenced-to-more-than-10-years-in-federal-prison-for-cross-country-drug-trafficking-conspiracy/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...i-state narcotics trafficking operation involving **methamphetamine**, fentanyl, cocaine, and marijuana shipped between...
 ... trafficking operation involving methamphetamine, **fentanyl**, cocaine, and marijuana shipped between Californi...
@@ -534,182 +682,146 @@
 ...involving methamphetamine, fentanyl, cocaine, and **marijuana** shipped between California and Western New York. ...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — Two Jamestown men have been charged in a federal superseding indictment alleging narcotics trafficking, kidnapping, and armed robbery tied to a multi-year drug conspiracy involving fentanyl, heroin, and cocaine. A federal grand jury has returned a superseding indictment charging Blake D. Smith, also known as “Sweets,” and Willie […]The post Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D10" s="2">
         <v>46122</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/two-jamestown-men-charged-in-federal-superseding-indictment-involving-fentanyl-sales-kidnapping-and-armed-robbery/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...ry tied to a multi-year drug conspiracy involving **fentanyl**, heroin, and cocaine. A federal grand jury has re...
 ...arged in Federal Superseding Indictment Involving **Fentanyl** Sales, Kidnapping, and Armed Robbery appeared fir...
 ...idnapping, and armed robbery tied to a multi-year **drug** conspiracy involving fentanyl, heroin, and cocain...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>(WNY News Now) – NEWFANE, N.Y. — A two-vehicle crash in the Town of Newfane on April 8 left multiple people seriously injured, including a child, and resulted in a driving while intoxicated arrest under Leandra’s Law, according to the Niagara County Sheriff’s Office. Deputies responded at approximately 6:16 p.m. to the intersection of Day […]The post Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D11" s="2">
         <v>46122</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/newfane-crash-leaves-multiple-injured-driver-charged-under-leandras-law/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...ncluding a child, and resulted in a driving while **intoxicated** arrest under Leandra’s Law, according to the Niag...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has been sentenced to eight years in federal prison for his involvement in a drug trafficking conspiracy involving fentanyl and cocaine. U.S. Attorney Michael DiGiacomo announced that Jaquez Thomas, 22, of Jamestown, was sentenced to 96 months in prison by U.S. District Judge John L. […]The post Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D12" s="2">
         <v>46122</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/10/jamestown-man-sentenced-to-8-years-in-federal-prison-for-role-in-drug-conspiracy/</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...vement in a drug trafficking conspiracy involving **fentanyl** and cocaine. U.S. Attorney Michael DiGiacomo anno...
 ... years in federal prison for his involvement in a **drug** trafficking conspiracy involving fentanyl and coc...
 ...entenced to 8 Years in Federal Prison for Role in **Drug** Conspiracy appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rochester Man Pleads Guilty to Federal Drug and Firearm Charges</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Rochester man has pleaded guilty to federal drug trafficking and firearm offenses following a multi-agency investigation into narcotics activity in Monroe County. Juan Sosa, 30, of Rochester, entered his plea before Chief U.S. District Judge Elizabeth A. Wolford to charges of possession with intent to distribute 100 […]The post Rochester Man Pleads Guilty to Federal Drug and Firearm Charges appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46122</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/10/rochester-man-pleads-guilty-to-federal-drug-and-firearm-charges/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>.... — A Rochester man has pleaded guilty to federal **drug** trafficking and firearm offenses following a mult...
-...…]The post Rochester Man Pleads Guilty to Federal **Drug** and Firearm Charges appeared first on WNY News No...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>7 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D13" s="2">
         <v>46121</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...rosecutors say that between 2020 to 2022, Thomas distributed quantities of **fentanyl** and cocaine he received from Joseph Zaso... and, used Facebook and Cash Ap...
 ...bsp;During the conspiracy... Thomas was accused of supplying quantities of **fentanyl** to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Ma...
@@ -720,66 +832,46 @@
 ...d Thomas’ Allen Street residence... and seized a loaded handgun, and **drug** paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted ...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D14" s="2">
         <v>46121</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
 ...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
 ...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dunkirk Man Charged With Shooting Dunkirk Officer Faces More Charges - WRFA-LP 107.9 FM</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46118</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/23hv4ts3</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,28 +401,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 58-year-old Ashville resident was charged with driving while intoxicated after deputies responded to a trespassing complaint in the Town of Harmony late Thursday night. The Chautauqua County Sheriff’s Office reports that deputies were called to a trespassing incident in the Town of Harmony at approximately 10:38 p.m. on April 9, […]The post Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46126</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/14/ashville-man-charged-with-dwi-following-trespassing-investigation-in-town-of-harmony/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>... Ashville resident was charged with driving while **intoxicated** after deputies responded to a trespassing complai...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Monday, Apr. 13, 2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Fire destroys condemned home on Prendergast Ave; but, fire crews save two adjacent homes...Fire has destroyed a vacant and condemned home on Jamestown's northside... but, quick work by firefighters saved two neighoring homes.  City Fire Battlion Chief Nate Alm says firefighters were called to the scene at 612 Prendergast Ave. shortly after 7 p.m. Friday... and, first arriving crews found the home fully-engulfed in flames... and they moved quickly to knock down the flames, and protect the two adjacent hmes.  Alm says the family living in one was safely evacuated... along with their pets.  He says an off-duty shift of 15 firefighters and a commander was called in to assist.  No injuries were reported... but, he says crews were at the scene for nearly five-and-a-half hours.  The cause is under investigation... and the home at 612 Prendergast will be torn down.Man from Jamestown and woman from Buffalo indicted on federal drug conspiracy charges...A man from Jamestown... and, a woman from Buffalo have been indicted on a federal charge for allegedly being involved in a narcotics conspiracy.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury returned the indictment charging 41 year-old Brandon Murray... and, 35 year-old Latika Saintkitts... with narcotics conspiracy.  DiGiacomo says the charge carries a mandatory minimum of 10 years in prison...  and a maximum of life. In addition, Saintkitts is charged with distribution of crack cocaine and fentanyl.  Prosecutors say that between 2021, and September 2024, Murray and Saintkitts conspired with others to possess and distribute fentanyl, methamphetamine, and heroin.  In addition, in April of 2024, Saintkitts possessed and distributed crack cocaine... and, in June of that year... she possessed and distributed fentanyl.  Murray was detained... and, Saintkitts was released on conditions.Charges now filed against man involved in stand-off last week in Fredonia...Charges have now been filed against a man who barricaded himself for several hours inside a White Street home in the Village of Fredonia last week... prompting a shelter in place order for the area.  Fredonia Police say a White Street resident reported on Wednesday that 44-year-old Kyle Denhardt was unwanted... refused to leave her residence, and was possibly in possession of a handgun.  Officers responded... and, helped the woman off the property, then began communicating with Denhardt.  A perimeter was established and maintained with assistance from Dunkirk police... University Police... and State Police.  While the area was closed off to vehicle and pedestrian traffic, State Police Special Operations Response Teams were deployed... along with an Unmanned Aerial Systems unit.  After warrants were obtained, Denhardt surrendered peacefully after several hours of negotiations to a special State Police Team.  When police executed the search warrant, they discovered a large cache of weaponry, including a ghost gun, high-capacity magazines, ammunition, rifle parts, and related accessories.-----Denhardt, who is a resident of Maryland and South Carolina, faces charged including:  second-degree menacing... second-degree criminal trespass... second-degree criminal possession of a weapon... and, two counts of third-degree criminal possession of a weapon.  He was taken to the county jail on $400,000 cash bail.Woman arrested in town of Hanover for incident with stun gun...A woman has been arrested for allegedly displaying an electric stun gun during an altercation in the town of Hanover.  Sheriff's officers say they were called to the scene about 7:30 a.m. last Thursday on a report of the incident.  Deputies say they found that 26 year-old Allyson Lycett had pulled out the stun gun during the altercation... and, was arrested for fourth-degree criminal possession of a weapon.  Lycett was arraigned... and, issued an appearance ticket for Hanover Town Court at a later date.Lake Property Owner's hold first meeting since court ruling "annuls" wetland regulations...With last week's State Supreme Court ruling... the state Department of Environmental Conservation may have to do a full-blown environmental impact statement on any new wetland regulations.  That from Chautauqua Lake Property Owners Association president Jim Wehrfritz during the CLPOA's most recent meeting last Saturday in Bemus Point.  Wehrfritz says the court's annulment of the regulations "demand accountabilty."  Wehrfritz says the DEC may have to issue a "positive declaration..." meaning that the regulations would have to consider economic and social issues in those regulations.  Wehrfritz... however... cautioned that if the DEC were to implement new wetland regulations.. they would be more "broadbased" because it would have to be for the entire state.  He later focused on the June 2024 plan for the lake proposed by Dr. Robert Richardson at North Carolina State University.  Wehrfritz feels it needs to be acted on, because it's time to have a plan that can be acted on.  He says the CLPOA also feels there needs to be a study of the lake's condition... and, the wetlands regulations on property values on the lake.State Supreme Court rules in favor of village connecting with the No. County Water District...A State Supreme Court judge has sided with the village of Fredonia in a lawsuit that sought to annul a resolution for the village's project to connect with the North County Water District.  In an 11-page ruling last Wednesday... Judge Grace Hanlon denied the request that was filed in October by members of the "Save Our Reservoir" group, who argued that the village violated the State Environmental Quality Review Act... General Municipal Law... and, the village's Zoning Code.  Judge Hanlon determined that the village -- "neither abused its discretion nor was arbitrary or capricious in its determination" with regard to its SEQRA analysis.</t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D3" s="2">
         <v>46125</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911992/wjtn-news-headlines-for-monday-apr-13-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...y and Saintkitts conspired with others to possess and distribute fentanyl, **methamphetamine**, and heroin.  In addition, in April of 2024, Saintkitts possessed and...
 ... In addition, Saintkitts is charged with distribution of crack cocaine and **fentanyl**.  Prosecutors say that between 2021, and September 2024, Murray and S...
@@ -431,143 +466,118 @@
 ...be torn down.Man from Jamestown and woman from Buffalo indicted on federal **drug** conspiracy charges...A man from Jamestown... and, a woman from Buffalo hav...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Jamestown Man and Buffalo Woman Indicted on Federal Narcotics Conspiracy Charges in Western New York</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — A federal grand jury has indicted a Jamestown man and a Buffalo woman on narcotics conspiracy charges tied to the distribution of fentanyl, methamphetamine, heroin, and crack cocaine in Western New York. A federal grand jury returned an indictment charging Brandon Murray, 41, of Jamestown, and Latika Saintkitts, […]The post Jamestown Man and Buffalo Woman Indicted on Federal Narcotics Conspiracy Charges in Western New York appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="2">
         <v>46125</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/13/jamestown-man-and-buffalo-woman-indicted-on-federal-narcotics-conspiracy-charges-in-western-new-york/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...acy charges tied to the distribution of fentanyl, **methamphetamine**, heroin, and crack cocaine in Western New York. A...
 ...cs conspiracy charges tied to the distribution of **fentanyl**, methamphetamine, heroin, and crack cocaine in We...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Two Olean Residents Arrested After Methamphetamine Seizure on Interstate 86 in Great Valley</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>(WNY News Now) – A traffic stop on Interstate 86 in the Town of Great Valley led to the arrest of two Olean residents after deputies reportedly discovered more than 15 grams of methamphetamine and drug paraphernalia, according to the Cattaraugus County Sheriff’s Office. The incident occurred on April 11, 2026, at approximately 1:33 a.m. […]The post Two Olean Residents Arrested After Methamphetamine Seizure on Interstate 86 in Great Valley appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D5" s="2">
         <v>46125</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/13/two-olean-residents-arrested-after-methamphetamine-seizure-on-interstate-86-in-great-valley/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...uties reportedly discovered more than 15 grams of **methamphetamine** and drug paraphernalia, according to the Cattarau...
 ...m. […]The post Two Olean Residents Arrested After **Methamphetamine** Seizure on Interstate 86 in Great Valley appeared...
 ...covered more than 15 grams of methamphetamine and **drug** paraphernalia, according to the Cattaraugus Count...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Mayville Man Charged with DWI Following Early Morning Investigation on Route 430</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>(WNY News Now)- A 43-year-old Mayville resident was charged with driving while intoxicated after deputies investigated a suspicious situation early Saturday morning in the Town of Chautauqua. CHAUTAUQUA, N.Y. — A Mayville man is facing driving while intoxicated (DWI) charges following a sheriff’s investigation on Route 430 during the early morning hours of April 11, […]The post Mayville Man Charged with DWI Following Early Morning Investigation on Route 430 appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="2">
         <v>46125</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/13/mayville-man-charged-with-dwi-following-early-morning-investigation-on-route-430/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>... Mayville resident was charged with driving while **intoxicated** after deputies investigated a suspicious situatio...
 ...UA, N.Y. — A Mayville man is facing driving while **intoxicated** (DWI) charges following a sheriff’s investigation...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>46124</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
@@ -579,15 +589,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D7" s="2">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -599,28 +609,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46123</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Fri., Apr. 10, 2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>20 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>California man convicted of drug conspiracy involving Jamestown-area dealer isentenced to 10 years, six-months in federal prison...Another key player in Jamestown-area drug trafficking circles will spend more than 10 years in federal prison.  U.S. Attorney Michael DiGiacomo announced Thursday that 43 year-old La D. Huynh of Chula Vista, Calif., who was convicted of narcotics conspiracy, was sentenced in U.S. District Court in Buffalo to 126 months in prison.  Prosecutors say that Huynh, a California-based drug trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and marijuana to other members of the conspiracy.  They included Jun Martinez, a Jamestown-based drug trafficker.  In 2019... after receiving a large amount of meth... there was a payment issue between Martinez and Huynh, and Martinez stopped taking calls from Huynh.  However... sometime in 2020... Huynh and Martinez restarted their operations... and, Huynh began shipping quantities of cocaine... a heroin/fentanyl mix... and meth in the mail, from the San Diego-area.  In September of 2020... Martinez traveled to the San Diego area and met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and fentanyl.   After the transaction... Martinez and Hughes started traveling back to the Jamestown-area... but, during the return trip... they were stopped by an Illinois State Police Trooper.  A search of the vehicle led to discovery of about 6,300 grams of methamphetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuana products... and ,they were arrested.  Martinez was previously convicted and is awaiting sentencing.Two city men indicted on drug, firearms, and kidnapping charges...Two men from Jamestown have been indicted on federal charges for drug trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury has returned a superseding indictment charging 50 year-old Blake Smith -- also known as "Sweets..." and 45 year-old Willie Graham -- also known as "Wu..." with narcotics conspiracy, Hobbs Act Robbery, kidnapping, use of a firearm during a crime of violence, and use of a firearm in furtherance of drug trafficking.  DiGiacomo adds that Smith is also charged with possession of firearms in furtherance of drug trafficking, and distribution of fentanyl causing serious bodily injury.  Prosecutors say that between February 2017, and January 2024... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, fentanyl, and cocaine in the Jamestown area.  During the conspiracy, Smith possessed a firearm.  They add that between May 9 and 11 of 2023... Smith sold fentanyl causing serious bodily injury to individuals identified as R. P. and D.C.  In March of that year... Smith and Graham are also accused of kidnapped an individual identified as D.D... and, also stole a 25-thousand dollar check from D.D. while brandishing a firearm.  Both men face a maximum of life in prison if convicted.CLPOA looking ahead to what's next after Judge annuls NYS Freshwater Wetlands Regulation Act...The head of one of the lake groups that successfully sued New York State over it's Wetland Regulations is pleased with the outcome.  However... Chautauqua Lake Property Owners Association President Jim Wehrfritz says they're also waiting to see how the Department of Environmental Conservation responds to the State Supreme Court decision annuling those regulations.  Wehrfritz says they could appeal, or they could do the environmental due diligence, and try to bring the regulations forward again.  He says... for the CLPOA... it's gratefying to see their approximately three year effort be successful... along with the other groups involved.  The Chautauqua Lake Partnership was also a plaintiff in the suit.  He says that will be one of the three main topics at tomorrow morning's 15th meeting of the CLPOA since it formed.  Wehrfritz says they'll also review the recent Chautauqua Lake Symposium... and, further discuss their push to create a centralized lake authority and district they feel would better oversee the lake.   Tomorrow's CLPOA meeting will be held at the Lawson Boat Center in Bemus Point at 9 a.m., and, will run until 10:30 a.m.  Wehrfritz says you can also Zoom into the meeting by going to Zoom -- and punching in: 6346503547... and, the password is CLPOA -- all lower case.Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient..." and, the real work on the spending plan should have been done weeks ago.  He says this week was especially frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over $262-billion... while the Assembly and Senate bills are between $8-million and $10-billion higher.  The budget was due by Apr. 1.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>46122</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911734/wjtn-news-headlines-for-fri-apr-10-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...say that Huynh, a California-based drug trafficker, supplied quantities of **methamphetamine**, heroin/fentanyl, cocaine, and marijuana to other members of the conspirac...
 ...met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of **methamphetamine**, cocaine, and fentanyl.   After the transaction... Martinez and Hughe...
@@ -644,184 +679,37 @@
 ...hetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and **marijuana** products... and ,they were arrested.  Martinez was previously convict...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – A California man has been sentenced to 126 months in federal prison for his role in a multi-state narcotics trafficking operation involving methamphetamine, fentanyl, cocaine, and marijuana shipped between California and Western New York. BUFFALO, N.Y. — U.S. Attorney Michael DiGiacomo announced that La D. Huynh, 43, of Chula Vista, California, […]The post California Man Sentenced to More Than 10 Years in Federal Prison for Cross-Country Drug Trafficking Conspiracy appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46122</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/10/california-man-sentenced-to-more-than-10-years-in-federal-prison-for-cross-country-drug-trafficking-conspiracy/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>...i-state narcotics trafficking operation involving **methamphetamine**, fentanyl, cocaine, and marijuana shipped between...
-... trafficking operation involving methamphetamine, **fentanyl**, cocaine, and marijuana shipped between Californi...
-...Than 10 Years in Federal Prison for Cross-Country **Drug** Trafficking Conspiracy appeared first on WNY News...
-...involving methamphetamine, fentanyl, cocaine, and **marijuana** shipped between California and Western New York. ...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery</t>
+          <t>7 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — Two Jamestown men have been charged in a federal superseding indictment alleging narcotics trafficking, kidnapping, and armed robbery tied to a multi-year drug conspiracy involving fentanyl, heroin, and cocaine. A federal grand jury has returned a superseding indictment charging Blake D. Smith, also known as “Sweets,” and Willie […]The post Two Jamestown Men Charged in Federal Superseding Indictment Involving Fentanyl Sales, Kidnapping, and Armed Robbery appeared first on WNY News Now.</t>
+          <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
         </is>
       </c>
       <c r="D10" s="2">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/10/two-jamestown-men-charged-in-federal-superseding-indictment-involving-fentanyl-sales-kidnapping-and-armed-robbery/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>...ry tied to a multi-year drug conspiracy involving **fentanyl**, heroin, and cocaine. A federal grand jury has re...
-...arged in Federal Superseding Indictment Involving **Fentanyl** Sales, Kidnapping, and Armed Robbery appeared fir...
-...idnapping, and armed robbery tied to a multi-year **drug** conspiracy involving fentanyl, heroin, and cocain...</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – NEWFANE, N.Y. — A two-vehicle crash in the Town of Newfane on April 8 left multiple people seriously injured, including a child, and resulted in a driving while intoxicated arrest under Leandra’s Law, according to the Niagara County Sheriff’s Office. Deputies responded at approximately 6:16 p.m. to the intersection of Day […]The post Newfane Crash Leaves Multiple Injured, Driver Charged Under Leandra’s Law appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46122</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/10/newfane-crash-leaves-multiple-injured-driver-charged-under-leandras-law/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...ncluding a child, and resulted in a driving while **intoxicated** arrest under Leandra’s Law, according to the Niag...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Jamestown man has been sentenced to eight years in federal prison for his involvement in a drug trafficking conspiracy involving fentanyl and cocaine. U.S. Attorney Michael DiGiacomo announced that Jaquez Thomas, 22, of Jamestown, was sentenced to 96 months in prison by U.S. District Judge John L. […]The post Jamestown Man Sentenced to 8 Years in Federal Prison for Role in Drug Conspiracy appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46122</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/10/jamestown-man-sentenced-to-8-years-in-federal-prison-for-role-in-drug-conspiracy/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>...vement in a drug trafficking conspiracy involving **fentanyl** and cocaine. U.S. Attorney Michael DiGiacomo anno...
-... years in federal prison for his involvement in a **drug** trafficking conspiracy involving fentanyl and coc...
-...entenced to 8 Years in Federal Prison for Role in **Drug** Conspiracy appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>7 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46121</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>...rosecutors say that between 2020 to 2022, Thomas distributed quantities of **fentanyl** and cocaine he received from Joseph Zaso... and, used Facebook and Cash Ap...
 ...bsp;During the conspiracy... Thomas was accused of supplying quantities of **fentanyl** to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Ma...
@@ -832,44 +720,44 @@
 ...d Thomas’ Allen Street residence... and seized a loaded handgun, and **drug** paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted ...</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>3 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D14" s="2">
+      <c r="D11" s="2">
         <v>46121</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
 ...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
 ...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,63 +401,164 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t xml:space="preserve">WJTN News Headlines for Thurs., Apr. 15, 2026   </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony</t>
+          <t>2 keyword references (WJTN)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(WNY News Now) – A 58-year-old Ashville resident was charged with driving while intoxicated after deputies responded to a trespassing complaint in the Town of Harmony late Thursday night. The Chautauqua County Sheriff’s Office reports that deputies were called to a trespassing incident in the Town of Harmony at approximately 10:38 p.m. on April 9, […]The post Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony appeared first on WNY News Now.</t>
+          <t>State Legislature approves new budget extender, spending plan now two week's late... The New York state legislature has again approved a one-week budget extension as talks on a new spending plan continue.  Lawmakers approved the $3.4-billion extender late Monday... then adjourned as the Apr. 1 deadline gets further in the rear-view mirror.  Minority Republicans continue to blast the the process... which has included Governor Kathy Hochul... Assembly Speaker Carl Heastie... and, Senate Majority Leader Andrea Stewart-Cousins.  Assembly Minority Leader Ed Ra saying -- "each day that goes by without an approved state spending plan is a day Albany has failed.  Deadlines exist for a reason -- and everyday New Yorkers face consequences when they’re missed."  Ra urged the legislature to open up the process.Jamestown man arrested for pulling another man from car... and, punching him several times during incident...A city man has been arrested for allegedly pulling another man from his car... and, then punching him several times in the face.  Jamestown police were called to the scene at East Sixth and Winsor Streets about 4 p.m. Monday on a report of a fight.  Officers say their investigation found that 27 year-old Charles Dean had engaged in the fight after forcibly removing the man from his vehicle... and, then hitting him multiple times with a closed fist.  Dean was arrested without incident for third-degree assault.... and jailed pending arraignment.Issue with deer brought before City Council committee...The issue of too many deer in the city of Jamestown has been raised again before the City Council... but, the state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce calls is a "touchy issue" with many wanting some kind of action taken... but, many also worried about safety of an in-city harvest.  Dolce says there are a handful of suggestions for dealing the deer issue... but, he says no matter what is decided... cost will always be a factor.  Dolce adds that the way one community handles it doen't always work for everyone.  He says it depends on the amount of unused land there it, and the fact that one community that did a controlled hunt, really didn't solve the issue.  However... Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation to allow hunters to obtain more deer tags, and possibly extending the season so there can be a later take.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down.Jamestown native, career worker in diplomatic services, named as new president at Chautauqua Institution...A Jamestown native who has a long history with Chautauqua Institution has been named as the institution's new president.  The Institution's board has announced that Mark Coolidge Johnson -- a veteran U.S. diplomat and third-generation Chautauquan has been appointed to lead Chautauqua Institution -- beginning at the end of the 2026 Summer Season.  The chair of the institution's board, Laurie Branch, announced Johnson's appointment Tuesday... noting that he brings more than 30 years of diplomatic service as a Senior Foreign Service Officer... attorney and third-generation Chautauquan to the institution.  Currently... Branch says Johnson serves as Deputy Chief of Mission at the U.S. Embassy in Mexico City -- the largest American diplomatic mission in the world -- where he oversees more than 3-thousand employees... nine consulates and nine consular agencies with a $282-million operating budget.  Johnson is the son of the late Joe Johnson, who served the Institution for 20 years as Vice President of Finance, and is also the grandson of a Chautauqua grounds engineer.  He holds a juris doctorate from American University’s Washington College of Law.  Johnson calls the appointment the "honor of a lifetime to return home and lead this extraordinary community into it's next chapter." City woman arrested for Felony DWI following personal injury accident in downtown Jamestown...A woman from Jamestown has been arrested for allegedly driving drunk... and, leaving the scene of a property damage accident.  City police say they were called to a downtown business shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicle had left the scene... and, tracked it back to the owner's address.  Police say they then made contact with the driver... identified as 36 year-old Leonela Rodriguez... and, found she had been driving while intoxicated at the time of the accident.  Rodriguez was taken into custody without incident... and, taken to the city jail pending arraignment on charges of DWI... leaving the scene of a property damage accident... and, unlicensed operation.  Officers add that Rodriguez has a previous DWAI conviction... making this a Felony.Pair of women arrested in Lakewood for alleged fight in front of children...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.  </t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/14/ashville-man-charged-with-dwi-following-trespassing-investigation-in-town-of-harmony/</t>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912391/wjtn-news-headlines-for-thurs-apr-15-2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>... Ashville resident was charged with driving while **intoxicated** after deputies responded to a trespassing complai...</t>
+          <t>... as 36 year-old Leonela Rodriguez... and, found she had been driving while **intoxicated** at the time of the accident.  Rodriguez was taken into custody withou...
+...amount of unused land there it, and the fact that one community that did a **controlled** hunt, really didn't solve the issue.  However... Mayor Kim Ecklund sa...</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Buffalo man has pleaded guilty in federal court to his role in a multi-state narcotics conspiracy involving the shipment and distribution of large quantities of cocaine across the Western District of New York. Steven Hoskins, 44, of Buffalo, New York, entered a guilty plea before John L. […]The post Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46127</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/15/buffalo-man-pleads-guilty-in-federal-cocaine-trafficking-conspiracy-case/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 40-year-old Little Valley man was arrested following a traffic stop on Lebanon Road in the Town of Coldspring on April 11, 2026, after deputies reported multiple vehicle and traffic violations and subsequent intoxication findings. The Cattaraugus County Sheriff’s Office reports that Benjamin I. Hilliard, 40, of Little Valley, was taken […]The post Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46127</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/15/coldspring-traffic-stop-leads-to-dwi-arrest-on-lebanon-road/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...ple vehicle and traffic violations and subsequent **intoxication** findings. The Cattaraugus County Sheriff’s Office...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 58-year-old Ashville resident was charged with driving while intoxicated after deputies responded to a trespassing complaint in the Town of Harmony late Thursday night. The Chautauqua County Sheriff’s Office reports that deputies were called to a trespassing incident in the Town of Harmony at approximately 10:38 p.m. on April 9, […]The post Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46126</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/14/ashville-man-charged-with-dwi-following-trespassing-investigation-in-town-of-harmony/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>... Ashville resident was charged with driving while **intoxicated** after deputies responded to a trespassing complai...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Monday, Apr. 13, 2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Fire destroys condemned home on Prendergast Ave; but, fire crews save two adjacent homes...Fire has destroyed a vacant and condemned home on Jamestown's northside... but, quick work by firefighters saved two neighoring homes.  City Fire Battlion Chief Nate Alm says firefighters were called to the scene at 612 Prendergast Ave. shortly after 7 p.m. Friday... and, first arriving crews found the home fully-engulfed in flames... and they moved quickly to knock down the flames, and protect the two adjacent hmes.  Alm says the family living in one was safely evacuated... along with their pets.  He says an off-duty shift of 15 firefighters and a commander was called in to assist.  No injuries were reported... but, he says crews were at the scene for nearly five-and-a-half hours.  The cause is under investigation... and the home at 612 Prendergast will be torn down.Man from Jamestown and woman from Buffalo indicted on federal drug conspiracy charges...A man from Jamestown... and, a woman from Buffalo have been indicted on a federal charge for allegedly being involved in a narcotics conspiracy.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury returned the indictment charging 41 year-old Brandon Murray... and, 35 year-old Latika Saintkitts... with narcotics conspiracy.  DiGiacomo says the charge carries a mandatory minimum of 10 years in prison...  and a maximum of life. In addition, Saintkitts is charged with distribution of crack cocaine and fentanyl.  Prosecutors say that between 2021, and September 2024, Murray and Saintkitts conspired with others to possess and distribute fentanyl, methamphetamine, and heroin.  In addition, in April of 2024, Saintkitts possessed and distributed crack cocaine... and, in June of that year... she possessed and distributed fentanyl.  Murray was detained... and, Saintkitts was released on conditions.Charges now filed against man involved in stand-off last week in Fredonia...Charges have now been filed against a man who barricaded himself for several hours inside a White Street home in the Village of Fredonia last week... prompting a shelter in place order for the area.  Fredonia Police say a White Street resident reported on Wednesday that 44-year-old Kyle Denhardt was unwanted... refused to leave her residence, and was possibly in possession of a handgun.  Officers responded... and, helped the woman off the property, then began communicating with Denhardt.  A perimeter was established and maintained with assistance from Dunkirk police... University Police... and State Police.  While the area was closed off to vehicle and pedestrian traffic, State Police Special Operations Response Teams were deployed... along with an Unmanned Aerial Systems unit.  After warrants were obtained, Denhardt surrendered peacefully after several hours of negotiations to a special State Police Team.  When police executed the search warrant, they discovered a large cache of weaponry, including a ghost gun, high-capacity magazines, ammunition, rifle parts, and related accessories.-----Denhardt, who is a resident of Maryland and South Carolina, faces charged including:  second-degree menacing... second-degree criminal trespass... second-degree criminal possession of a weapon... and, two counts of third-degree criminal possession of a weapon.  He was taken to the county jail on $400,000 cash bail.Woman arrested in town of Hanover for incident with stun gun...A woman has been arrested for allegedly displaying an electric stun gun during an altercation in the town of Hanover.  Sheriff's officers say they were called to the scene about 7:30 a.m. last Thursday on a report of the incident.  Deputies say they found that 26 year-old Allyson Lycett had pulled out the stun gun during the altercation... and, was arrested for fourth-degree criminal possession of a weapon.  Lycett was arraigned... and, issued an appearance ticket for Hanover Town Court at a later date.Lake Property Owner's hold first meeting since court ruling "annuls" wetland regulations...With last week's State Supreme Court ruling... the state Department of Environmental Conservation may have to do a full-blown environmental impact statement on any new wetland regulations.  That from Chautauqua Lake Property Owners Association president Jim Wehrfritz during the CLPOA's most recent meeting last Saturday in Bemus Point.  Wehrfritz says the court's annulment of the regulations "demand accountabilty."  Wehrfritz says the DEC may have to issue a "positive declaration..." meaning that the regulations would have to consider economic and social issues in those regulations.  Wehrfritz... however... cautioned that if the DEC were to implement new wetland regulations.. they would be more "broadbased" because it would have to be for the entire state.  He later focused on the June 2024 plan for the lake proposed by Dr. Robert Richardson at North Carolina State University.  Wehrfritz feels it needs to be acted on, because it's time to have a plan that can be acted on.  He says the CLPOA also feels there needs to be a study of the lake's condition... and, the wetlands regulations on property values on the lake.State Supreme Court rules in favor of village connecting with the No. County Water District...A State Supreme Court judge has sided with the village of Fredonia in a lawsuit that sought to annul a resolution for the village's project to connect with the North County Water District.  In an 11-page ruling last Wednesday... Judge Grace Hanlon denied the request that was filed in October by members of the "Save Our Reservoir" group, who argued that the village violated the State Environmental Quality Review Act... General Municipal Law... and, the village's Zoning Code.  Judge Hanlon determined that the village -- "neither abused its discretion nor was arbitrary or capricious in its determination" with regard to its SEQRA analysis.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D6" s="2">
         <v>46125</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911992/wjtn-news-headlines-for-monday-apr-13-2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...y and Saintkitts conspired with others to possess and distribute fentanyl, **methamphetamine**, and heroin.  In addition, in April of 2024, Saintkitts possessed and...
 ... In addition, Saintkitts is charged with distribution of crack cocaine and **fentanyl**.  Prosecutors say that between 2021, and September 2024, Murray and S...
@@ -466,118 +567,9 @@
 ...be torn down.Man from Jamestown and woman from Buffalo indicted on federal **drug** conspiracy charges...A man from Jamestown... and, a woman from Buffalo hav...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Jamestown Man and Buffalo Woman Indicted on Federal Narcotics Conspiracy Charges in Western New York</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A federal grand jury has indicted a Jamestown man and a Buffalo woman on narcotics conspiracy charges tied to the distribution of fentanyl, methamphetamine, heroin, and crack cocaine in Western New York. A federal grand jury returned an indictment charging Brandon Murray, 41, of Jamestown, and Latika Saintkitts, […]The post Jamestown Man and Buffalo Woman Indicted on Federal Narcotics Conspiracy Charges in Western New York appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46125</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/13/jamestown-man-and-buffalo-woman-indicted-on-federal-narcotics-conspiracy-charges-in-western-new-york/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...acy charges tied to the distribution of fentanyl, **methamphetamine**, heroin, and crack cocaine in Western New York. A...
-...cs conspiracy charges tied to the distribution of **fentanyl**, methamphetamine, heroin, and crack cocaine in We...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Two Olean Residents Arrested After Methamphetamine Seizure on Interstate 86 in Great Valley</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – A traffic stop on Interstate 86 in the Town of Great Valley led to the arrest of two Olean residents after deputies reportedly discovered more than 15 grams of methamphetamine and drug paraphernalia, according to the Cattaraugus County Sheriff’s Office. The incident occurred on April 11, 2026, at approximately 1:33 a.m. […]The post Two Olean Residents Arrested After Methamphetamine Seizure on Interstate 86 in Great Valley appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46125</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/13/two-olean-residents-arrested-after-methamphetamine-seizure-on-interstate-86-in-great-valley/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>...uties reportedly discovered more than 15 grams of **methamphetamine** and drug paraphernalia, according to the Cattarau...
-...m. […]The post Two Olean Residents Arrested After **Methamphetamine** Seizure on Interstate 86 in Great Valley appeared...
-...covered more than 15 grams of methamphetamine and **drug** paraphernalia, according to the Cattaraugus Count...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mayville Man Charged with DWI Following Early Morning Investigation on Route 430</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(WNY News Now)- A 43-year-old Mayville resident was charged with driving while intoxicated after deputies investigated a suspicious situation early Saturday morning in the Town of Chautauqua. CHAUTAUQUA, N.Y. — A Mayville man is facing driving while intoxicated (DWI) charges following a sheriff’s investigation on Route 430 during the early morning hours of April 11, […]The post Mayville Man Charged with DWI Following Early Morning Investigation on Route 430 appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>46125</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/13/mayville-man-charged-with-dwi-following-early-morning-investigation-on-route-430/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>... Mayville resident was charged with driving while **intoxicated** after deputies investigated a suspicious situatio...
-...UA, N.Y. — A Mayville man is facing driving while **intoxicated** (DWI) charges following a sheriff’s investigation...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -726,43 +718,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Wed., Apr. 8, 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jamestown man arrested following overnight, domestic incident...A city man is accused of assaulting and choking another person in front of a young child during an overnight domestic incident on Jamestown's westside.  City police were called to the unidentified location about 12:30 a.m., and, determined that 29 year-old Jesse Young had assaulted and obstructed the breathing of the victim.  Officers add Young also endangered the child... and, he was arrested for third-degree assault... endangering the welfare of a child... and, criminal obstruction of breathing.  He was jailed pending arraignment.Buffalo man arrested for resisting arrest while police try to break up domestic incident...A man from Buffalo has been arrested for allegedly resisting Jamestown police while they were trying to break-up a domestic dispute involving the man.  City police were called to the area of East Eighth Street and Lakeview Avenue just after 1:30 a.m. Wednesday for a fight on a sidewalk involving 22 year-old Marc Staples, Jr., and a female victim.  Officers say Staples tried to physically interfere with officers... and, then refused their commands.  Police say he pulled away when they tried to take him into custody.  But... after a brief struggle... Staples was arrested for disorderly conduct... second-degree obstructing governmental administration... and, resisting arrest.  He was jailed pending arraignment. Falconer man arrested for alleged assault while brandishing knife...A Falconer man has been arrested for allegedly getting into an altercation with another person... and, then threatening them with a knife.  Ellicott Town Police say they were called to the Budget Inn on Main Street shortly before 1:30 a.m. Tuesday morning for an alleged assault.  Officers say 43 year-old Rodolfo Tanco III would not allow the victim to leave the room... pinning them against a wall by the throat.  Police say Tanco then took the knife and held it to the victim's cheek.  However... the victim was finally able to get away and call police.  Officers obtained a warrant... and, later arrested Tanco for second-degree harassment... third-degree menacing... and criminal obstruction of breathing.  Officers also found that Tanco had an outstanding 2022 warrant for a separate incident in the town of Ellicott.  He was taken to the county jail pending centralized arraignment.United Way seeks volunteers for Literacy Week coming up later in April...The United Way of Chautauqua County is looking for volunteers to participate in it's upcoming Literacy Week.  This year's event is scheduled for April 20-24 at eight schools across the county.  United Way Community Relations Coordinator Dan Siracuse says the initiative began several years ago as a Literacy Day -- prior to the United Way's merger -- and expanded into a week-long event last year.  Siracuse says it's a great way to promote literacy in Chautauqua County... with readers going in to read to the children.  After that... they will provide each child with a book they can read.  Last year's Literacy Week reached nearly 2,000 students and involved more than 70 volunteers visiting 118 classrooms across six school districts.  Siracuse says many businesses and organizations also participated... including Purina, Dunkirk Police, and the Chautauqua Professionals group.  Elementary schools in Brocton, Dunkirk, Forestville, Fredonia, Ripley, Sherman and Sinclairville are currently signed up to participate this year.  Siracuse says you can call the United Way at 483-1561 if you're interested in volunteering.  You can also text "readchq" to 41444.Woman arrested on shoplifting and drug charges in Lakewood...A woman has been arrested for allegedly shoplifting more than $300 worth of merchandise from a Lakewood store... and, being found in possession of illegal drugs.  Lakewood-Busti Police say they were called to an "in-progress" shoplifting at the Wal-Mart SuperCenter at 350 Fairmount Ave. about 10:30 p.m. Monday.  Officers say they found Stephanie Derby had concealed $311 worth of item on her person.  She was also allegedly found with a quantity of methamphetamine... and, she's charged with petty larceny... and, seventh-degree criminal possession of a controlled substance.  Derby was issued an appearance ticket for Busti Town Court.City man and woman arrested for trespassing inside condemned home...A man and woman from Jamestown have been arrested for allegedly trespassing inside a condemned home on the city's eastside.  City police say they responded to a complaint shortly before Noon last Saturday of someone being inside the vacant residence.  When they arrived... they found 52 year-old Michael Cook... and, 34 year-old Ashley Stingel... who were not allowed on the property.  Officers arrested both without incident for third-degree criminal trespass... and, they were taken to the city jail pending arraignment.City man arrested on bench warrants following street check in Jamestown...A man from Jamestown... known to police... has been arrested after leading officers on a foot chase while performing a street check.  Police say a Gun-Involved Violence Enforcement  (GIVE) Detail spotted 28 year-old Todd Dellahoy walking in the area of Newland Avenue and Sampson Street shortly before 7 p.m. last Thursday.  Officers say they knew Dellahoy was warranted on a bench warrant issued by Jamestown City Court.  Police got out of their patrol car and ordered him to stop... but, he ran off before being caught after a short foot chase.  He was arrested for resisting arrest... in addition to the warrant... and, taken to the city jail pending arraignment.</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46121</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911417/wjtn-news-headlines-for-wed-apr-8-2026</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>... item on her person.  She was also allegedly found with a quantity of **methamphetamine**... and, she's charged with petty larceny... and, seventh-degree criminal p...
-...bsp;You can also text "readchq" to 41444.Woman arrested on shoplifting and **drug** charges in Lakewood...A woman has been arrested for allegedly shoplifting ...
-...charged with petty larceny... and, seventh-degree criminal possession of a **controlled** substance.  Derby was issued an appearance ticket for Busti Town Cour...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,164 +401,268 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/24l8w486</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dunkirk man charged in narcotics probe - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2dbujwph</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Understanding Purity and Potency in Cannabis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/17/understanding-purity-and-potency-in-cannabis/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Have you ever wondered why purity and potency in **cannabis** matter? Many people focus only on the experience,...
+...e a big difference. Purity and potency affect how **cannabis** works in the body and how safe it is to use. When...
+...e […]The post Understanding Purity and Potency in **Cannabis** appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dunkirk man charged after fentanyl, meth seized in Pomfret - observertoday.com</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46128</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2ct7u5n9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Apr. 16, 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>City woman dies in single-car crash on I-90 south of Buffalo...A woman from Jamestown has been killed in a one-car crash on the New York State Thruway south of Buffalo.  State Police in Buffalo say they responded to the scene about 7:30 a.m. Wednesday in the town of Evans.  Troopers say they found that a mini-van... operated by 69 year-old Linda Haney... was eastbound on the I-90 when the crash occured.  They say the vehicle left the driving lane and crossed into the passing lane before traveling onto the north shoulder and overturning.  Troopers say Haney was seriously hurt... and, was flown to the Erie County Medical Center where she later died.  State Police say their Bureau of Criminal Investigation is still actively investigating the collision.Dunkirk man arrested following major drug raid in town of Pomfret...A Dunkirk man faces multiple drug possession charges following a raid on a town of Pomfret home this past Tuesday.  Sheriff's officers say their narcotics investigators... along with those from Jamestown... executed a search warrant at 5341 Van Buren Rd. shortly before 10 a.m.  Outside the home... they found 43 year-old Andrew Betts... and he was detained.  Inside the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scales and packaging materials and nearly $1,200 in cash.  Betts was charged with two counts of both second and third-degree criminal possession of a controlled substance... one of seventh-degree criminal possession... second-degree criminally using drug paraphernalia... and, first-degree criminal nuisance.  He was taken to the county jail pending centralized arraignment program.  Anyone with information about illegal drug -- or other criminal activity -- is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.  For the JPD tip linek... call 483-8477.City lawmakers discuss possible remendies on ongoing deer isse in Jamestown...It's been quiet in recent months... however... the issue of too many deer in the city of Jamestown has been raised up again to the City Council.  But.. in this case... New York state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce says there are three main issues to consider... the cost, how effective it may be, and the safety of the residents.  He adds that the way one community handles it doen't always work for everyone.  He says every city is unique, with some more spread out, and others with denser populations.  Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation.  She says it would involve more hunters being allowed to take more deer... and, extending the season for them.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down... and, that's allowed the deer population to grow.Gillibrand leads another push for a war powers measure to end war in Iran...Democrats in the U.S. Senate have seen a fourth effort to pass a resolution withdrawing forces from the conflict in Iran -- until Congress authorizes further action -- go down to defeat.  The measure was co-sponsored by New York Democrat Kirsten Gillibrand... who says the president and Congress need to focus on skyrocketing costs... including that for gasoline.  Gillibrand says it's putting further strain on working families, who are already struggling to make ends meet."  Whenever she gets back to New York state... she says people question why more isn't being down to reduce those prices... including a woman from Orange County... who's trying to make it on just social security with an ex-husband dealing with Parkinson's Disease.  She told Gillibrand that she's fearful she may have to sell their home if costs don't come down.  The current cease-fire ends in about a week... and, the war in Iran is heading towards the two-month old mark.  Gillibrand says she believes once that is reached... some Republicans may be ready to support the move.Pair of woman arrested following fight in Lakewood's Hartley Park...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.Jamestown woman accused of driving drunk, leaving the scene following downtown accident...A city woman is accused of driving drunk when her car crashed... and, then leaving the scene of the accident in downtown Jamestown.  City police say they were called to the scene shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicles had left the scene... and, tracked it back to the owner's address.  Police say they then found the driver... identified as 36 year-old Leonela Rodriguez... and, determined that she had been driving while intoxicated at the time of the accident.  Rodriguez was arrested without incident for Felony DWI... leaving the scene of a property damage accident... and, unlicensed operation.  </t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46128</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912536/wjtn-news-headlines-for-thurs-apr-16-2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>... the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of **methamphetamine**... 37.5 dosage units of clonazepam, scales and packaging materials and nea...
+...was detained.  Inside the home... investigatiors found 173.7-grams of **fentanyl**... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scale...
+... actively investigating the collision.Dunkirk man arrested following major **drug** raid in town of Pomfret...A Dunkirk man faces multiple drug possession cha...
+...ollowing major drug raid in town of Pomfret...A Dunkirk man faces multiple **drug** possession charges following a raid on a town of Pomfret home this past Tu...
+...ne of seventh-degree criminal possession... second-degree criminally using **drug** paraphernalia... and, first-degree criminal nuisance.  He was taken t...
+...ntralized arraignment program.  Anyone with information about illegal **drug** -- or other criminal activity -- is asked to call the Sheriff's Office Nar...
+...r-old Leonela Rodriguez... and, determined that she had been driving while **intoxicated** at the time of the accident.  Rodriguez was arrested without incident...
+...d with two counts of both second and third-degree criminal possession of a **controlled** substance... one of seventh-degree criminal possession... second-degree cr...</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_MediaOne_WJTN.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t xml:space="preserve">WJTN News Headlines for Thurs., Apr. 15, 2026   </t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>State Legislature approves new budget extender, spending plan now two week's late... The New York state legislature has again approved a one-week budget extension as talks on a new spending plan continue.  Lawmakers approved the $3.4-billion extender late Monday... then adjourned as the Apr. 1 deadline gets further in the rear-view mirror.  Minority Republicans continue to blast the the process... which has included Governor Kathy Hochul... Assembly Speaker Carl Heastie... and, Senate Majority Leader Andrea Stewart-Cousins.  Assembly Minority Leader Ed Ra saying -- "each day that goes by without an approved state spending plan is a day Albany has failed.  Deadlines exist for a reason -- and everyday New Yorkers face consequences when they’re missed."  Ra urged the legislature to open up the process.Jamestown man arrested for pulling another man from car... and, punching him several times during incident...A city man has been arrested for allegedly pulling another man from his car... and, then punching him several times in the face.  Jamestown police were called to the scene at East Sixth and Winsor Streets about 4 p.m. Monday on a report of a fight.  Officers say their investigation found that 27 year-old Charles Dean had engaged in the fight after forcibly removing the man from his vehicle... and, then hitting him multiple times with a closed fist.  Dean was arrested without incident for third-degree assault.... and jailed pending arraignment.Issue with deer brought before City Council committee...The issue of too many deer in the city of Jamestown has been raised again before the City Council... but, the state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce calls is a "touchy issue" with many wanting some kind of action taken... but, many also worried about safety of an in-city harvest.  Dolce says there are a handful of suggestions for dealing the deer issue... but, he says no matter what is decided... cost will always be a factor.  Dolce adds that the way one community handles it doen't always work for everyone.  He says it depends on the amount of unused land there it, and the fact that one community that did a controlled hunt, really didn't solve the issue.  However... Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation to allow hunters to obtain more deer tags, and possibly extending the season so there can be a later take.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down.Jamestown native, career worker in diplomatic services, named as new president at Chautauqua Institution...A Jamestown native who has a long history with Chautauqua Institution has been named as the institution's new president.  The Institution's board has announced that Mark Coolidge Johnson -- a veteran U.S. diplomat and third-generation Chautauquan has been appointed to lead Chautauqua Institution -- beginning at the end of the 2026 Summer Season.  The chair of the institution's board, Laurie Branch, announced Johnson's appointment Tuesday... noting that he brings more than 30 years of diplomatic service as a Senior Foreign Service Officer... attorney and third-generation Chautauquan to the institution.  Currently... Branch says Johnson serves as Deputy Chief of Mission at the U.S. Embassy in Mexico City -- the largest American diplomatic mission in the world -- where he oversees more than 3-thousand employees... nine consulates and nine consular agencies with a $282-million operating budget.  Johnson is the son of the late Joe Johnson, who served the Institution for 20 years as Vice President of Finance, and is also the grandson of a Chautauqua grounds engineer.  He holds a juris doctorate from American University’s Washington College of Law.  Johnson calls the appointment the "honor of a lifetime to return home and lead this extraordinary community into it's next chapter." City woman arrested for Felony DWI following personal injury accident in downtown Jamestown...A woman from Jamestown has been arrested for allegedly driving drunk... and, leaving the scene of a property damage accident.  City police say they were called to a downtown business shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicle had left the scene... and, tracked it back to the owner's address.  Police say they then made contact with the driver... identified as 36 year-old Leonela Rodriguez... and, found she had been driving while intoxicated at the time of the accident.  Rodriguez was taken into custody without incident... and, taken to the city jail pending arraignment on charges of DWI... leaving the scene of a property damage accident... and, unlicensed operation.  Officers add that Rodriguez has a previous DWAI conviction... making this a Felony.Pair of women arrested in Lakewood for alleged fight in front of children...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.  </t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D7" s="2">
         <v>46127</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912391/wjtn-news-headlines-for-thurs-apr-15-2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>... as 36 year-old Leonela Rodriguez... and, found she had been driving while **intoxicated** at the time of the accident.  Rodriguez was taken into custody withou...
 ...amount of unused land there it, and the fact that one community that did a **controlled** hunt, really didn't solve the issue.  However... Mayor Kim Ecklund sa...</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — A Buffalo man has pleaded guilty in federal court to his role in a multi-state narcotics conspiracy involving the shipment and distribution of large quantities of cocaine across the Western District of New York. Steven Hoskins, 44, of Buffalo, New York, entered a guilty plea before John L. […]The post Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D8" s="2">
         <v>46127</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/15/buffalo-man-pleads-guilty-in-federal-cocaine-trafficking-conspiracy-case/</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>(WNY News Now) – A 40-year-old Little Valley man was arrested following a traffic stop on Lebanon Road in the Town of Coldspring on April 11, 2026, after deputies reported multiple vehicle and traffic violations and subsequent intoxication findings. The Cattaraugus County Sheriff’s Office reports that Benjamin I. Hilliard, 40, of Little Valley, was taken […]The post Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D9" s="2">
         <v>46127</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/15/coldspring-traffic-stop-leads-to-dwi-arrest-on-lebanon-road/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...ple vehicle and traffic violations and subsequent **intoxication** findings. The Cattaraugus County Sheriff’s Office...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – A 58-year-old Ashville resident was charged with driving while intoxicated after deputies responded to a trespassing complaint in the Town of Harmony late Thursday night. The Chautauqua County Sheriff’s Office reports that deputies were called to a trespassing incident in the Town of Harmony at approximately 10:38 p.m. on April 9, […]The post Ashville Man Charged with DWI Following Trespassing Investigation in Town of Harmony appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46126</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/14/ashville-man-charged-with-dwi-following-trespassing-investigation-in-town-of-harmony/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>... Ashville resident was charged with driving while **intoxicated** after deputies responded to a trespassing complai...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Monday, Apr. 13, 2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Fire destroys condemned home on Prendergast Ave; but, fire crews save two adjacent homes...Fire has destroyed a vacant and condemned home on Jamestown's northside... but, quick work by firefighters saved two neighoring homes.  City Fire Battlion Chief Nate Alm says firefighters were called to the scene at 612 Prendergast Ave. shortly after 7 p.m. Friday... and, first arriving crews found the home fully-engulfed in flames... and they moved quickly to knock down the flames, and protect the two adjacent hmes.  Alm says the family living in one was safely evacuated... along with their pets.  He says an off-duty shift of 15 firefighters and a commander was called in to assist.  No injuries were reported... but, he says crews were at the scene for nearly five-and-a-half hours.  The cause is under investigation... and the home at 612 Prendergast will be torn down.Man from Jamestown and woman from Buffalo indicted on federal drug conspiracy charges...A man from Jamestown... and, a woman from Buffalo have been indicted on a federal charge for allegedly being involved in a narcotics conspiracy.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury returned the indictment charging 41 year-old Brandon Murray... and, 35 year-old Latika Saintkitts... with narcotics conspiracy.  DiGiacomo says the charge carries a mandatory minimum of 10 years in prison...  and a maximum of life. In addition, Saintkitts is charged with distribution of crack cocaine and fentanyl.  Prosecutors say that between 2021, and September 2024, Murray and Saintkitts conspired with others to possess and distribute fentanyl, methamphetamine, and heroin.  In addition, in April of 2024, Saintkitts possessed and distributed crack cocaine... and, in June of that year... she possessed and distributed fentanyl.  Murray was detained... and, Saintkitts was released on conditions.Charges now filed against man involved in stand-off last week in Fredonia...Charges have now been filed against a man who barricaded himself for several hours inside a White Street home in the Village of Fredonia last week... prompting a shelter in place order for the area.  Fredonia Police say a White Street resident reported on Wednesday that 44-year-old Kyle Denhardt was unwanted... refused to leave her residence, and was possibly in possession of a handgun.  Officers responded... and, helped the woman off the property, then began communicating with Denhardt.  A perimeter was established and maintained with assistance from Dunkirk police... University Police... and State Police.  While the area was closed off to vehicle and pedestrian traffic, State Police Special Operations Response Teams were deployed... along with an Unmanned Aerial Systems unit.  After warrants were obtained, Denhardt surrendered peacefully after several hours of negotiations to a special State Police Team.  When police executed the search warrant, they discovered a large cache of weaponry, including a ghost gun, high-capacity magazines, ammunition, rifle parts, and related accessories.-----Denhardt, who is a resident of Maryland and South Carolina, faces charged including:  second-degree menacing... second-degree criminal trespass... second-degree criminal possession of a weapon... and, two counts of third-degree criminal possession of a weapon.  He was taken to the county jail on $400,000 cash bail.Woman arrested in town of Hanover for incident with stun gun...A woman has been arrested for allegedly displaying an electric stun gun during an altercation in the town of Hanover.  Sheriff's officers say they were called to the scene about 7:30 a.m. last Thursday on a report of the incident.  Deputies say they found that 26 year-old Allyson Lycett had pulled out the stun gun during the altercation... and, was arrested for fourth-degree criminal possession of a weapon.  Lycett was arraigned... and, issued an appearance ticket for Hanover Town Court at a later date.Lake Property Owner's hold first meeting since court ruling "annuls" wetland regulations...With last week's State Supreme Court ruling... the state Department of Environmental Conservation may have to do a full-blown environmental impact statement on any new wetland regulations.  That from Chautauqua Lake Property Owners Association president Jim Wehrfritz during the CLPOA's most recent meeting last Saturday in Bemus Point.  Wehrfritz says the court's annulment of the regulations "demand accountabilty."  Wehrfritz says the DEC may have to issue a "positive declaration..." meaning that the regulations would have to consider economic and social issues in those regulations.  Wehrfritz... however... cautioned that if the DEC were to implement new wetland regulations.. they would be more "broadbased" because it would have to be for the entire state.  He later focused on the June 2024 plan for the lake proposed by Dr. Robert Richardson at North Carolina State University.  Wehrfritz feels it needs to be acted on, because it's time to have a plan that can be acted on.  He says the CLPOA also feels there needs to be a study of the lake's condition... and, the wetlands regulations on property values on the lake.State Supreme Court rules in favor of village connecting with the No. County Water District...A State Supreme Court judge has sided with the village of Fredonia in a lawsuit that sought to annul a resolution for the village's project to connect with the North County Water District.  In an 11-page ruling last Wednesday... Judge Grace Hanlon denied the request that was filed in October by members of the "Save Our Reservoir" group, who argued that the village violated the State Environmental Quality Review Act... General Municipal Law... and, the village's Zoning Code.  Judge Hanlon determined that the village -- "neither abused its discretion nor was arbitrary or capricious in its determination" with regard to its SEQRA analysis.</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D10" s="2">
         <v>46125</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911992/wjtn-news-headlines-for-monday-apr-13-2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...y and Saintkitts conspired with others to possess and distribute fentanyl, **methamphetamine**, and heroin.  In addition, in April of 2024, Saintkitts possessed and...
 ... In addition, Saintkitts is charged with distribution of crack cocaine and **fentanyl**.  Prosecutors say that between 2021, and September 2024, Murray and S...
@@ -567,87 +671,87 @@
 ...be torn down.Man from Jamestown and woman from Buffalo indicted on federal **drug** conspiracy charges...A man from Jamestown... and, a woman from Buffalo hav...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Chautauqua_Today</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D11" s="2">
         <v>46124</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Chautauqua_Today</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D12" s="2">
         <v>46123</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Fri., Apr. 10, 2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>20 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>California man convicted of drug conspiracy involving Jamestown-area dealer isentenced to 10 years, six-months in federal prison...Another key player in Jamestown-area drug trafficking circles will spend more than 10 years in federal prison.  U.S. Attorney Michael DiGiacomo announced Thursday that 43 year-old La D. Huynh of Chula Vista, Calif., who was convicted of narcotics conspiracy, was sentenced in U.S. District Court in Buffalo to 126 months in prison.  Prosecutors say that Huynh, a California-based drug trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and marijuana to other members of the conspiracy.  They included Jun Martinez, a Jamestown-based drug trafficker.  In 2019... after receiving a large amount of meth... there was a payment issue between Martinez and Huynh, and Martinez stopped taking calls from Huynh.  However... sometime in 2020... Huynh and Martinez restarted their operations... and, Huynh began shipping quantities of cocaine... a heroin/fentanyl mix... and meth in the mail, from the San Diego-area.  In September of 2020... Martinez traveled to the San Diego area and met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and fentanyl.   After the transaction... Martinez and Hughes started traveling back to the Jamestown-area... but, during the return trip... they were stopped by an Illinois State Police Trooper.  A search of the vehicle led to discovery of about 6,300 grams of methamphetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuana products... and ,they were arrested.  Martinez was previously convicted and is awaiting sentencing.Two city men indicted on drug, firearms, and kidnapping charges...Two men from Jamestown have been indicted on federal charges for drug trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury has returned a superseding indictment charging 50 year-old Blake Smith -- also known as "Sweets..." and 45 year-old Willie Graham -- also known as "Wu..." with narcotics conspiracy, Hobbs Act Robbery, kidnapping, use of a firearm during a crime of violence, and use of a firearm in furtherance of drug trafficking.  DiGiacomo adds that Smith is also charged with possession of firearms in furtherance of drug trafficking, and distribution of fentanyl causing serious bodily injury.  Prosecutors say that between February 2017, and January 2024... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, fentanyl, and cocaine in the Jamestown area.  During the conspiracy, Smith possessed a firearm.  They add that between May 9 and 11 of 2023... Smith sold fentanyl causing serious bodily injury to individuals identified as R. P. and D.C.  In March of that year... Smith and Graham are also accused of kidnapped an individual identified as D.D... and, also stole a 25-thousand dollar check from D.D. while brandishing a firearm.  Both men face a maximum of life in prison if convicted.CLPOA looking ahead to what's next after Judge annuls NYS Freshwater Wetlands Regulation Act...The head of one of the lake groups that successfully sued New York State over it's Wetland Regulations is pleased with the outcome.  However... Chautauqua Lake Property Owners Association President Jim Wehrfritz says they're also waiting to see how the Department of Environmental Conservation responds to the State Supreme Court decision annuling those regulations.  Wehrfritz says they could appeal, or they could do the environmental due diligence, and try to bring the regulations forward again.  He says... for the CLPOA... it's gratefying to see their approximately three year effort be successful... along with the other groups involved.  The Chautauqua Lake Partnership was also a plaintiff in the suit.  He says that will be one of the three main topics at tomorrow morning's 15th meeting of the CLPOA since it formed.  Wehrfritz says they'll also review the recent Chautauqua Lake Symposium... and, further discuss their push to create a centralized lake authority and district they feel would better oversee the lake.   Tomorrow's CLPOA meeting will be held at the Lawson Boat Center in Bemus Point at 9 a.m., and, will run until 10:30 a.m.  Wehrfritz says you can also Zoom into the meeting by going to Zoom -- and punching in: 6346503547... and, the password is CLPOA -- all lower case.Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient..." and, the real work on the spending plan should have been done weeks ago.  He says this week was especially frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over $262-billion... while the Assembly and Senate bills are between $8-million and $10-billion higher.  The budget was due by Apr. 1.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment.</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D13" s="2">
         <v>46122</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911734/wjtn-news-headlines-for-fri-apr-10-2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...say that Huynh, a California-based drug trafficker, supplied quantities of **methamphetamine**, heroin/fentanyl, cocaine, and marijuana to other members of the conspirac...
 ...met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of **methamphetamine**, cocaine, and fentanyl.   After the transaction... Martinez and Hughe...
@@ -671,48 +775,7 @@
 ...hetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and **marijuana** products... and ,they were arrested.  Martinez was previously convict...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Thurs., Apr. 9, 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>7 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Several hour stand-off in Fredonia ends peacefully...A several-hour long stand-off involving several law enforcement agencies in the village of Fredonia was resolved peacefully late last night.  Fredonia Police lifted a "shelter in place" which went into effect early Wednesday afternoon for residents on White Street.  The incident that prompted the shelter in place was -- police said -- "resolved peacefully and without injuries to anyone involved, and the area of White Street is now safe."  Fredonia Police thanked the several agencies that assisted them... including the New York State Police... Dunkirk City Police...  SUNY Fredonia Police... County EMS... and, the Chautauqua County District Attorney’s Office... among others.  Police say more information will be released as it becomes available pending further investigation.  This was the third such "Shelter-in-Place" incident in the Dunkirk-Fredonia area in the past month.City man to spend 8 years in federal prison for role in drug conspiracy...A man from Jamestown convicted for his role in a drug trafficking conspiracy will spend the next eight-years in federal prison.  U.S. Attorney Michael DiGiacomo has announced that 22 year-old Jaquez Thomas received the 96-month prison term from U.S. District Court Judge John Sinatra, Jr. Wednesday.  Prosecutors say that between 2020 to 2022, Thomas distributed quantities of fentanyl and cocaine he received from Joseph Zaso... and, used Facebook and Cash App to conduct his drug trafficking activities.  During the conspiracy... Thomas was accused of supplying quantities of fentanyl to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Maisonet in 2022... whom city police made three undercover drug purchases from.  In July 2022, police raided Thomas’ Allen Street residence... and seized a loaded handgun, and drug paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted and are awaiting sentencing.  Jose Maisonet was previously convicted and sentenced in a separate case.Molitor calls State Supreme Court ruling "annulling" NYS Freshwater Wetland's Regulations "significant..."A New York State Supreme Court ruling has "annulled" the Department of Environmental Conservation’s Freshwater Wetlands Act regulations.  The ruling was issued by Judge Richard Platkin in Albany County Supreme Court Wednesday... saying that the DEC failed to comply with it's own State Environmental Quality Review Act by not conducting proper environmental studies.  Local State Assemblyman Andrew Molitor was pleased with the ruling.. noting that -- while the groups involved made different kinds of arguments -- the SEQRA one stood out... and, that was "the winning argument."  The plaintiffs in the case included the Chautauqua Lake Partnership and the Chautauqua Lake Property Owners Association.  Molitor expects the state to file an appeal... which may mean there won't be an immediate striking down of the regulations.  He says the state would likely try to get a "stay" in the decision pending the appeal.  Molitor adds that... if the state is able to appeal the matter... the case would likely wind up at New York's highest court... the Court of Appeals.  He calls the decision a "significant one for our region and property owners across New York State."Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient."  He says the governor has the last half of the previous year to get a budget assembled, and two talk with the Senate and Assembly leadership to find areas of agreement and disagreement.  Molitor says this week was very frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over 262-billion dollars... while the Assembly and Senate bills are being $8-billion and $10-billion higher.  The budget was due by Apr. 1.City man arrested for assault in town of Ellicott...A man from Jamestown is accused of punching and injuring another person during an incident last Friday night in the town of Ellicott.  Town Police say they were called to the unidentified location shortly after 7 p.m. on a report of an assault.  Officers say they found that 38 year-old Shaun Clutter had gotten into an argument with the victim before punching the person in the nose.  Clutter then left the scene... but, was later found in the city.  He was arrested for third-degree assault.  The victim was treated at the scene by Falconer fire rescuers... and, then taken to UPMC Chautauqua Hospital for further treatment.  Clutter was taken to the county jail for centralized arraignment... and will appear in Ellicott Town Court at a later date.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment. </t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>46121</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911554/wjtn-news-headlines-for-thurs-apr-9-2026</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>...rosecutors say that between 2020 to 2022, Thomas distributed quantities of **fentanyl** and cocaine he received from Joseph Zaso... and, used Facebook and Cash Ap...
-...bsp;During the conspiracy... Thomas was accused of supplying quantities of **fentanyl** to Justin Yuchnitz and Joseph Thayer.  He also conspired with Jose Ma...
-... in the past month.City man to spend 8 years in federal prison for role in **drug** conspiracy...A man from Jamestown convicted for his role in a drug traffic...
-...role in drug conspiracy...A man from Jamestown convicted for his role in a **drug** trafficking conspiracy will spend the next eight-years in federal prison. ...
-...eceived from Joseph Zaso... and, used Facebook and Cash App to conduct his **drug** trafficking activities.  During the conspiracy... Thomas was accused ...
-...pired with Jose Maisonet in 2022... whom city police made three undercover **drug** purchases from.  In July 2022, police raided Thomas’ Allen Stre...
-...d Thomas’ Allen Street residence... and seized a loaded handgun, and **drug** paraphernalia.  Zaso, Thayer, and Yuchnitz were previously convicted ...</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -421,12 +421,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dunkirk man charged in narcotics probe - observertoday.com</t>
+          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -434,7 +439,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2dbujwph</t>
+          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -727,60 +742,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Fri., Apr. 10, 2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>California man convicted of drug conspiracy involving Jamestown-area dealer isentenced to 10 years, six-months in federal prison...Another key player in Jamestown-area drug trafficking circles will spend more than 10 years in federal prison.  U.S. Attorney Michael DiGiacomo announced Thursday that 43 year-old La D. Huynh of Chula Vista, Calif., who was convicted of narcotics conspiracy, was sentenced in U.S. District Court in Buffalo to 126 months in prison.  Prosecutors say that Huynh, a California-based drug trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and marijuana to other members of the conspiracy.  They included Jun Martinez, a Jamestown-based drug trafficker.  In 2019... after receiving a large amount of meth... there was a payment issue between Martinez and Huynh, and Martinez stopped taking calls from Huynh.  However... sometime in 2020... Huynh and Martinez restarted their operations... and, Huynh began shipping quantities of cocaine... a heroin/fentanyl mix... and meth in the mail, from the San Diego-area.  In September of 2020... Martinez traveled to the San Diego area and met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and fentanyl.   After the transaction... Martinez and Hughes started traveling back to the Jamestown-area... but, during the return trip... they were stopped by an Illinois State Police Trooper.  A search of the vehicle led to discovery of about 6,300 grams of methamphetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuana products... and ,they were arrested.  Martinez was previously convicted and is awaiting sentencing.Two city men indicted on drug, firearms, and kidnapping charges...Two men from Jamestown have been indicted on federal charges for drug trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury has returned a superseding indictment charging 50 year-old Blake Smith -- also known as "Sweets..." and 45 year-old Willie Graham -- also known as "Wu..." with narcotics conspiracy, Hobbs Act Robbery, kidnapping, use of a firearm during a crime of violence, and use of a firearm in furtherance of drug trafficking.  DiGiacomo adds that Smith is also charged with possession of firearms in furtherance of drug trafficking, and distribution of fentanyl causing serious bodily injury.  Prosecutors say that between February 2017, and January 2024... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, fentanyl, and cocaine in the Jamestown area.  During the conspiracy, Smith possessed a firearm.  They add that between May 9 and 11 of 2023... Smith sold fentanyl causing serious bodily injury to individuals identified as R. P. and D.C.  In March of that year... Smith and Graham are also accused of kidnapped an individual identified as D.D... and, also stole a 25-thousand dollar check from D.D. while brandishing a firearm.  Both men face a maximum of life in prison if convicted.CLPOA looking ahead to what's next after Judge annuls NYS Freshwater Wetlands Regulation Act...The head of one of the lake groups that successfully sued New York State over it's Wetland Regulations is pleased with the outcome.  However... Chautauqua Lake Property Owners Association President Jim Wehrfritz says they're also waiting to see how the Department of Environmental Conservation responds to the State Supreme Court decision annuling those regulations.  Wehrfritz says they could appeal, or they could do the environmental due diligence, and try to bring the regulations forward again.  He says... for the CLPOA... it's gratefying to see their approximately three year effort be successful... along with the other groups involved.  The Chautauqua Lake Partnership was also a plaintiff in the suit.  He says that will be one of the three main topics at tomorrow morning's 15th meeting of the CLPOA since it formed.  Wehrfritz says they'll also review the recent Chautauqua Lake Symposium... and, further discuss their push to create a centralized lake authority and district they feel would better oversee the lake.   Tomorrow's CLPOA meeting will be held at the Lawson Boat Center in Bemus Point at 9 a.m., and, will run until 10:30 a.m.  Wehrfritz says you can also Zoom into the meeting by going to Zoom -- and punching in: 6346503547... and, the password is CLPOA -- all lower case.Molitor becoming "increasingly frustrated" by late state budget...Chautauqua County's Assemblyman says he's become "increasingly frustrated" by a state budget that's now just-over a week late.  The legislature was called back to Albany Tuesday to act on another one-week extender as legislative leaders and Governor Kathy Hochul try to work out details of a new spending plan.  Molitor... a Westfield Republican... says the current system is "very inefficient..." and, the real work on the spending plan should have been done weeks ago.  He says this week was especially frustrating because lawmakers were called back into session Tuesday to approve the $3.2-billion "extender..." and, then were sent home again.  Governor Hochul's proposed budget totals just over $262-billion... while the Assembly and Senate bills are between $8-million and $10-billion higher.  The budget was due by Apr. 1.City man arrested for trespassing inside condemned building...A man from Jamestown has been arrested for allegedly trespassing inside a condemned building on West Second Street -- near Jefferson Street.  City police were called to the location on a trespass complaint about 2 p.m. Wednesday... and, found 44 year-old Hector DeJesus inside the building.  Officers arrested DeJesus without incident for third-degree criminal trespassing.  He was taken to the city jail pending arraignment.</t>
-        </is>
-      </c>
-      <c r="D13" s="2">
-        <v>46122</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911734/wjtn-news-headlines-for-fri-apr-10-2026</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>...say that Huynh, a California-based drug trafficker, supplied quantities of **methamphetamine**, heroin/fentanyl, cocaine, and marijuana to other members of the conspirac...
-...met with Huynh and co-conspirator Kevin Hughes, receiving large amounts of **methamphetamine**, cocaine, and fentanyl.   After the transaction... Martinez and Hughe...
-...er.  A search of the vehicle led to discovery of about 6,300 grams of **methamphetamine**, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and marijuan...
-...rnia-based drug trafficker, supplied quantities of methamphetamine, heroin/**fentanyl**, cocaine, and marijuana to other members of the conspiracy.  They inc...
-... operations... and, Huynh began shipping quantities of cocaine... a heroin/**fentanyl** mix... and meth in the mail, from the San Diego-area.  In September o...
-...tor Kevin Hughes, receiving large amounts of methamphetamine, cocaine, and **fentanyl**.   After the transaction... Martinez and Hughes started traveling bac...
-...iscovery of about 6,300 grams of methamphetamine, more than 3,100 grams of **fentanyl**... 2,241 grams of cocaine, and marijuana products... and ,they were arrest...
-...ession of firearms in furtherance of drug trafficking, and distribution of **fentanyl** causing serious bodily injury.  Prosecutors say that between February...
-.... Smith and Graham conspired with Joseph Zaso, and others, to sell heroin, **fentanyl**, and cocaine in the Jamestown area.  During the conspiracy, Smith pos...
-... a firearm.  They add that between May 9 and 11 of 2023... Smith sold **fentanyl** causing serious bodily injury to individuals identified as R. P. and D.C. ...
-California man convicted of **drug** conspiracy involving Jamestown-area dealer isentenced to 10 years, six-mon...
-...years, six-months in federal prison...Another key player in Jamestown-area **drug** trafficking circles will spend more than 10 years in federal prison.  ...
-...126 months in prison.  Prosecutors say that Huynh, a California-based **drug** trafficker, supplied quantities of methamphetamine, heroin/fentanyl, cocai...
-...ers of the conspiracy.  They included Jun Martinez, a Jamestown-based **drug** trafficker.  In 2019... after receiving a large amount of meth... the...
-...s previously convicted and is awaiting sentencing.Two city men indicted on **drug**, firearms, and kidnapping charges...Two men from Jamestown have been indic...
-...charges...Two men from Jamestown have been indicted on federal charges for **drug** trafficking... robbery and kidnapping.  U.S. Attorney Michael DiGiaco...
-...firearm during a crime of violence, and use of a firearm in furtherance of **drug** trafficking.  DiGiacomo adds that Smith is also charged with possessi...
-...s that Smith is also charged with possession of firearms in furtherance of **drug** trafficking, and distribution of fentanyl causing serious bodily injury. &amp;...
-...ker, supplied quantities of methamphetamine, heroin/fentanyl, cocaine, and **marijuana** to other members of the conspiracy.  They included Jun Martinez, a Ja...
-...hetamine, more than 3,100 grams of fentanyl... 2,241 grams of cocaine, and **marijuana** products... and ,they were arrested.  Martinez was previously convict...</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -406,32 +406,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
+          <t>Expanding Tools Control Foreign-Related Economic Activity - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24l8w486</t>
+          <t>https://tinyurl.com/2ce949hz</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -439,17 +434,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/24l8w486</t>
         </is>
       </c>
     </row>
@@ -461,12 +446,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Understanding Purity and Potency in Cannabis</t>
+          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -474,56 +459,66 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Understanding Purity and Potency in Cannabis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/04/17/understanding-purity-and-potency-in-cannabis/</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Have you ever wondered why purity and potency in **cannabis** matter? Many people focus only on the experience,...
 ...e a big difference. Purity and potency affect how **cannabis** works in the body and how safe it is to use. When...
 ...e […]The post Understanding Purity and Potency in **Cannabis** appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dunkirk man charged after fentanyl, meth seized in Pomfret - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>46128</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2ct7u5n9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Thurs., Apr. 16, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>City woman dies in single-car crash on I-90 south of Buffalo...A woman from Jamestown has been killed in a one-car crash on the New York State Thruway south of Buffalo.  State Police in Buffalo say they responded to the scene about 7:30 a.m. Wednesday in the town of Evans.  Troopers say they found that a mini-van... operated by 69 year-old Linda Haney... was eastbound on the I-90 when the crash occured.  They say the vehicle left the driving lane and crossed into the passing lane before traveling onto the north shoulder and overturning.  Troopers say Haney was seriously hurt... and, was flown to the Erie County Medical Center where she later died.  State Police say their Bureau of Criminal Investigation is still actively investigating the collision.Dunkirk man arrested following major drug raid in town of Pomfret...A Dunkirk man faces multiple drug possession charges following a raid on a town of Pomfret home this past Tuesday.  Sheriff's officers say their narcotics investigators... along with those from Jamestown... executed a search warrant at 5341 Van Buren Rd. shortly before 10 a.m.  Outside the home... they found 43 year-old Andrew Betts... and he was detained.  Inside the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scales and packaging materials and nearly $1,200 in cash.  Betts was charged with two counts of both second and third-degree criminal possession of a controlled substance... one of seventh-degree criminal possession... second-degree criminally using drug paraphernalia... and, first-degree criminal nuisance.  He was taken to the county jail pending centralized arraignment program.  Anyone with information about illegal drug -- or other criminal activity -- is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.  For the JPD tip linek... call 483-8477.City lawmakers discuss possible remendies on ongoing deer isse in Jamestown...It's been quiet in recent months... however... the issue of too many deer in the city of Jamestown has been raised up again to the City Council.  But.. in this case... New York state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce says there are three main issues to consider... the cost, how effective it may be, and the safety of the residents.  He adds that the way one community handles it doen't always work for everyone.  He says every city is unique, with some more spread out, and others with denser populations.  Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation.  She says it would involve more hunters being allowed to take more deer... and, extending the season for them.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down... and, that's allowed the deer population to grow.Gillibrand leads another push for a war powers measure to end war in Iran...Democrats in the U.S. Senate have seen a fourth effort to pass a resolution withdrawing forces from the conflict in Iran -- until Congress authorizes further action -- go down to defeat.  The measure was co-sponsored by New York Democrat Kirsten Gillibrand... who says the president and Congress need to focus on skyrocketing costs... including that for gasoline.  Gillibrand says it's putting further strain on working families, who are already struggling to make ends meet."  Whenever she gets back to New York state... she says people question why more isn't being down to reduce those prices... including a woman from Orange County... who's trying to make it on just social security with an ex-husband dealing with Parkinson's Disease.  She told Gillibrand that she's fearful she may have to sell their home if costs don't come down.  The current cease-fire ends in about a week... and, the war in Iran is heading towards the two-month old mark.  Gillibrand says she believes once that is reached... some Republicans may be ready to support the move.Pair of woman arrested following fight in Lakewood's Hartley Park...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.Jamestown woman accused of driving drunk, leaving the scene following downtown accident...A city woman is accused of driving drunk when her car crashed... and, then leaving the scene of the accident in downtown Jamestown.  City police say they were called to the scene shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicles had left the scene... and, tracked it back to the owner's address.  Police say they then found the driver... identified as 36 year-old Leonela Rodriguez... and, determined that she had been driving while intoxicated at the time of the accident.  Rodriguez was arrested without incident for Felony DWI... leaving the scene of a property damage accident... and, unlicensed operation.  </t>
+          <t>Dunkirk man charged after fentanyl, meth seized in Pomfret - observertoday.com</t>
         </is>
       </c>
       <c r="D6" s="2">
@@ -531,10 +526,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/2ct7u5n9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Apr. 16, 2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>City woman dies in single-car crash on I-90 south of Buffalo...A woman from Jamestown has been killed in a one-car crash on the New York State Thruway south of Buffalo.  State Police in Buffalo say they responded to the scene about 7:30 a.m. Wednesday in the town of Evans.  Troopers say they found that a mini-van... operated by 69 year-old Linda Haney... was eastbound on the I-90 when the crash occured.  They say the vehicle left the driving lane and crossed into the passing lane before traveling onto the north shoulder and overturning.  Troopers say Haney was seriously hurt... and, was flown to the Erie County Medical Center where she later died.  State Police say their Bureau of Criminal Investigation is still actively investigating the collision.Dunkirk man arrested following major drug raid in town of Pomfret...A Dunkirk man faces multiple drug possession charges following a raid on a town of Pomfret home this past Tuesday.  Sheriff's officers say their narcotics investigators... along with those from Jamestown... executed a search warrant at 5341 Van Buren Rd. shortly before 10 a.m.  Outside the home... they found 43 year-old Andrew Betts... and he was detained.  Inside the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scales and packaging materials and nearly $1,200 in cash.  Betts was charged with two counts of both second and third-degree criminal possession of a controlled substance... one of seventh-degree criminal possession... second-degree criminally using drug paraphernalia... and, first-degree criminal nuisance.  He was taken to the county jail pending centralized arraignment program.  Anyone with information about illegal drug -- or other criminal activity -- is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.  For the JPD tip linek... call 483-8477.City lawmakers discuss possible remendies on ongoing deer isse in Jamestown...It's been quiet in recent months... however... the issue of too many deer in the city of Jamestown has been raised up again to the City Council.  But.. in this case... New York state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce says there are three main issues to consider... the cost, how effective it may be, and the safety of the residents.  He adds that the way one community handles it doen't always work for everyone.  He says every city is unique, with some more spread out, and others with denser populations.  Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation.  She says it would involve more hunters being allowed to take more deer... and, extending the season for them.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down... and, that's allowed the deer population to grow.Gillibrand leads another push for a war powers measure to end war in Iran...Democrats in the U.S. Senate have seen a fourth effort to pass a resolution withdrawing forces from the conflict in Iran -- until Congress authorizes further action -- go down to defeat.  The measure was co-sponsored by New York Democrat Kirsten Gillibrand... who says the president and Congress need to focus on skyrocketing costs... including that for gasoline.  Gillibrand says it's putting further strain on working families, who are already struggling to make ends meet."  Whenever she gets back to New York state... she says people question why more isn't being down to reduce those prices... including a woman from Orange County... who's trying to make it on just social security with an ex-husband dealing with Parkinson's Disease.  She told Gillibrand that she's fearful she may have to sell their home if costs don't come down.  The current cease-fire ends in about a week... and, the war in Iran is heading towards the two-month old mark.  Gillibrand says she believes once that is reached... some Republicans may be ready to support the move.Pair of woman arrested following fight in Lakewood's Hartley Park...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.Jamestown woman accused of driving drunk, leaving the scene following downtown accident...A city woman is accused of driving drunk when her car crashed... and, then leaving the scene of the accident in downtown Jamestown.  City police say they were called to the scene shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicles had left the scene... and, tracked it back to the owner's address.  Police say they then found the driver... identified as 36 year-old Leonela Rodriguez... and, determined that she had been driving while intoxicated at the time of the accident.  Rodriguez was arrested without incident for Felony DWI... leaving the scene of a property damage accident... and, unlicensed operation.  </t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46128</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912536/wjtn-news-headlines-for-thurs-apr-16-2026</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>... the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of **methamphetamine**... 37.5 dosage units of clonazepam, scales and packaging materials and nea...
 ...was detained.  Inside the home... investigatiors found 173.7-grams of **fentanyl**... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scale...
@@ -546,75 +566,45 @@
 ...d with two counts of both second and third-degree criminal possession of a **controlled** substance... one of seventh-degree criminal possession... second-degree cr...</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t xml:space="preserve">WJTN News Headlines for Thurs., Apr. 15, 2026   </t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>State Legislature approves new budget extender, spending plan now two week's late... The New York state legislature has again approved a one-week budget extension as talks on a new spending plan continue.  Lawmakers approved the $3.4-billion extender late Monday... then adjourned as the Apr. 1 deadline gets further in the rear-view mirror.  Minority Republicans continue to blast the the process... which has included Governor Kathy Hochul... Assembly Speaker Carl Heastie... and, Senate Majority Leader Andrea Stewart-Cousins.  Assembly Minority Leader Ed Ra saying -- "each day that goes by without an approved state spending plan is a day Albany has failed.  Deadlines exist for a reason -- and everyday New Yorkers face consequences when they’re missed."  Ra urged the legislature to open up the process.Jamestown man arrested for pulling another man from car... and, punching him several times during incident...A city man has been arrested for allegedly pulling another man from his car... and, then punching him several times in the face.  Jamestown police were called to the scene at East Sixth and Winsor Streets about 4 p.m. Monday on a report of a fight.  Officers say their investigation found that 27 year-old Charles Dean had engaged in the fight after forcibly removing the man from his vehicle... and, then hitting him multiple times with a closed fist.  Dean was arrested without incident for third-degree assault.... and jailed pending arraignment.Issue with deer brought before City Council committee...The issue of too many deer in the city of Jamestown has been raised again before the City Council... but, the state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce calls is a "touchy issue" with many wanting some kind of action taken... but, many also worried about safety of an in-city harvest.  Dolce says there are a handful of suggestions for dealing the deer issue... but, he says no matter what is decided... cost will always be a factor.  Dolce adds that the way one community handles it doen't always work for everyone.  He says it depends on the amount of unused land there it, and the fact that one community that did a controlled hunt, really didn't solve the issue.  However... Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation to allow hunters to obtain more deer tags, and possibly extending the season so there can be a later take.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down.Jamestown native, career worker in diplomatic services, named as new president at Chautauqua Institution...A Jamestown native who has a long history with Chautauqua Institution has been named as the institution's new president.  The Institution's board has announced that Mark Coolidge Johnson -- a veteran U.S. diplomat and third-generation Chautauquan has been appointed to lead Chautauqua Institution -- beginning at the end of the 2026 Summer Season.  The chair of the institution's board, Laurie Branch, announced Johnson's appointment Tuesday... noting that he brings more than 30 years of diplomatic service as a Senior Foreign Service Officer... attorney and third-generation Chautauquan to the institution.  Currently... Branch says Johnson serves as Deputy Chief of Mission at the U.S. Embassy in Mexico City -- the largest American diplomatic mission in the world -- where he oversees more than 3-thousand employees... nine consulates and nine consular agencies with a $282-million operating budget.  Johnson is the son of the late Joe Johnson, who served the Institution for 20 years as Vice President of Finance, and is also the grandson of a Chautauqua grounds engineer.  He holds a juris doctorate from American University’s Washington College of Law.  Johnson calls the appointment the "honor of a lifetime to return home and lead this extraordinary community into it's next chapter." City woman arrested for Felony DWI following personal injury accident in downtown Jamestown...A woman from Jamestown has been arrested for allegedly driving drunk... and, leaving the scene of a property damage accident.  City police say they were called to a downtown business shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicle had left the scene... and, tracked it back to the owner's address.  Police say they then made contact with the driver... identified as 36 year-old Leonela Rodriguez... and, found she had been driving while intoxicated at the time of the accident.  Rodriguez was taken into custody without incident... and, taken to the city jail pending arraignment on charges of DWI... leaving the scene of a property damage accident... and, unlicensed operation.  Officers add that Rodriguez has a previous DWAI conviction... making this a Felony.Pair of women arrested in Lakewood for alleged fight in front of children...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.  </t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D8" s="2">
         <v>46127</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912391/wjtn-news-headlines-for-thurs-apr-15-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>... as 36 year-old Leonela Rodriguez... and, found she had been driving while **intoxicated** at the time of the accident.  Rodriguez was taken into custody withou...
 ...amount of unused land there it, and the fact that one community that did a **controlled** hunt, really didn't solve the issue.  However... Mayor Kim Ecklund sa...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Buffalo man has pleaded guilty in federal court to his role in a multi-state narcotics conspiracy involving the shipment and distribution of large quantities of cocaine across the Western District of New York. Steven Hoskins, 44, of Buffalo, New York, entered a guilty plea before John L. […]The post Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>46127</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/15/buffalo-man-pleads-guilty-in-federal-cocaine-trafficking-conspiracy-case/</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -626,12 +616,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road</t>
+          <t>Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(WNY News Now) – A 40-year-old Little Valley man was arrested following a traffic stop on Lebanon Road in the Town of Coldspring on April 11, 2026, after deputies reported multiple vehicle and traffic violations and subsequent intoxication findings. The Cattaraugus County Sheriff’s Office reports that Benjamin I. Hilliard, 40, of Little Valley, was taken […]The post Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Buffalo man has pleaded guilty in federal court to his role in a multi-state narcotics conspiracy involving the shipment and distribution of large quantities of cocaine across the Western District of New York. Steven Hoskins, 44, of Buffalo, New York, entered a guilty plea before John L. […]The post Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D9" s="2">
@@ -639,12 +629,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/15/coldspring-traffic-stop-leads-to-dwi-arrest-on-lebanon-road/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>...ple vehicle and traffic violations and subsequent **intoxication** findings. The Cattaraugus County Sheriff’s Office...</t>
+          <t>https://wnynewsnow.com/2026/04/15/buffalo-man-pleads-guilty-in-federal-cocaine-trafficking-conspiracy-case/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -656,28 +641,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 40-year-old Little Valley man was arrested following a traffic stop on Lebanon Road in the Town of Coldspring on April 11, 2026, after deputies reported multiple vehicle and traffic violations and subsequent intoxication findings. The Cattaraugus County Sheriff’s Office reports that Benjamin I. Hilliard, 40, of Little Valley, was taken […]The post Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>46127</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/15/coldspring-traffic-stop-leads-to-dwi-arrest-on-lebanon-road/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>...ple vehicle and traffic violations and subsequent **intoxication** findings. The Cattaraugus County Sheriff’s Office...</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Monday, Apr. 13, 2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Fire destroys condemned home on Prendergast Ave; but, fire crews save two adjacent homes...Fire has destroyed a vacant and condemned home on Jamestown's northside... but, quick work by firefighters saved two neighoring homes.  City Fire Battlion Chief Nate Alm says firefighters were called to the scene at 612 Prendergast Ave. shortly after 7 p.m. Friday... and, first arriving crews found the home fully-engulfed in flames... and they moved quickly to knock down the flames, and protect the two adjacent hmes.  Alm says the family living in one was safely evacuated... along with their pets.  He says an off-duty shift of 15 firefighters and a commander was called in to assist.  No injuries were reported... but, he says crews were at the scene for nearly five-and-a-half hours.  The cause is under investigation... and the home at 612 Prendergast will be torn down.Man from Jamestown and woman from Buffalo indicted on federal drug conspiracy charges...A man from Jamestown... and, a woman from Buffalo have been indicted on a federal charge for allegedly being involved in a narcotics conspiracy.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury returned the indictment charging 41 year-old Brandon Murray... and, 35 year-old Latika Saintkitts... with narcotics conspiracy.  DiGiacomo says the charge carries a mandatory minimum of 10 years in prison...  and a maximum of life. In addition, Saintkitts is charged with distribution of crack cocaine and fentanyl.  Prosecutors say that between 2021, and September 2024, Murray and Saintkitts conspired with others to possess and distribute fentanyl, methamphetamine, and heroin.  In addition, in April of 2024, Saintkitts possessed and distributed crack cocaine... and, in June of that year... she possessed and distributed fentanyl.  Murray was detained... and, Saintkitts was released on conditions.Charges now filed against man involved in stand-off last week in Fredonia...Charges have now been filed against a man who barricaded himself for several hours inside a White Street home in the Village of Fredonia last week... prompting a shelter in place order for the area.  Fredonia Police say a White Street resident reported on Wednesday that 44-year-old Kyle Denhardt was unwanted... refused to leave her residence, and was possibly in possession of a handgun.  Officers responded... and, helped the woman off the property, then began communicating with Denhardt.  A perimeter was established and maintained with assistance from Dunkirk police... University Police... and State Police.  While the area was closed off to vehicle and pedestrian traffic, State Police Special Operations Response Teams were deployed... along with an Unmanned Aerial Systems unit.  After warrants were obtained, Denhardt surrendered peacefully after several hours of negotiations to a special State Police Team.  When police executed the search warrant, they discovered a large cache of weaponry, including a ghost gun, high-capacity magazines, ammunition, rifle parts, and related accessories.-----Denhardt, who is a resident of Maryland and South Carolina, faces charged including:  second-degree menacing... second-degree criminal trespass... second-degree criminal possession of a weapon... and, two counts of third-degree criminal possession of a weapon.  He was taken to the county jail on $400,000 cash bail.Woman arrested in town of Hanover for incident with stun gun...A woman has been arrested for allegedly displaying an electric stun gun during an altercation in the town of Hanover.  Sheriff's officers say they were called to the scene about 7:30 a.m. last Thursday on a report of the incident.  Deputies say they found that 26 year-old Allyson Lycett had pulled out the stun gun during the altercation... and, was arrested for fourth-degree criminal possession of a weapon.  Lycett was arraigned... and, issued an appearance ticket for Hanover Town Court at a later date.Lake Property Owner's hold first meeting since court ruling "annuls" wetland regulations...With last week's State Supreme Court ruling... the state Department of Environmental Conservation may have to do a full-blown environmental impact statement on any new wetland regulations.  That from Chautauqua Lake Property Owners Association president Jim Wehrfritz during the CLPOA's most recent meeting last Saturday in Bemus Point.  Wehrfritz says the court's annulment of the regulations "demand accountabilty."  Wehrfritz says the DEC may have to issue a "positive declaration..." meaning that the regulations would have to consider economic and social issues in those regulations.  Wehrfritz... however... cautioned that if the DEC were to implement new wetland regulations.. they would be more "broadbased" because it would have to be for the entire state.  He later focused on the June 2024 plan for the lake proposed by Dr. Robert Richardson at North Carolina State University.  Wehrfritz feels it needs to be acted on, because it's time to have a plan that can be acted on.  He says the CLPOA also feels there needs to be a study of the lake's condition... and, the wetlands regulations on property values on the lake.State Supreme Court rules in favor of village connecting with the No. County Water District...A State Supreme Court judge has sided with the village of Fredonia in a lawsuit that sought to annul a resolution for the village's project to connect with the North County Water District.  In an 11-page ruling last Wednesday... Judge Grace Hanlon denied the request that was filed in October by members of the "Save Our Reservoir" group, who argued that the village violated the State Environmental Quality Review Act... General Municipal Law... and, the village's Zoning Code.  Judge Hanlon determined that the village -- "neither abused its discretion nor was arbitrary or capricious in its determination" with regard to its SEQRA analysis.</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>46125</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911992/wjtn-news-headlines-for-monday-apr-13-2026</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...y and Saintkitts conspired with others to possess and distribute fentanyl, **methamphetamine**, and heroin.  In addition, in April of 2024, Saintkitts possessed and...
 ... In addition, Saintkitts is charged with distribution of crack cocaine and **fentanyl**.  Prosecutors say that between 2021, and September 2024, Murray and S...
@@ -686,34 +706,9 @@
 ...be torn down.Man from Jamestown and woman from Buffalo indicted on federal **drug** conspiracy charges...A man from Jamestown... and, a woman from Buffalo hav...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>46124</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
@@ -725,15 +720,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stockton Man Charged with Criminal Contempt, Possession of Controlled SubstanceA Stockton man was arrested for possession of a controlled substance after a reported altercation. Deputies with the Chautauqua County Sheriff's Office responded to an address in the Town of Stockton on Friday around 6:24PM for an alleged disorderly ...Brian Valencia</t>
+          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D12" s="2">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367488</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -401,20 +401,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Expanding Tools Control Foreign-Related Economic Activity - The Jamestown Foundation</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ripley Woman Arrested in Westfield on Drug ChargeA report of a disorderly person led to the arrest of a Ripley woman on a drug-related charge on Saturday. Chautauqua County Sheriff's deputies received the call just before 12:45 PM, with the suspect located by Westfield Police. After an investigatio...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2ce949hz</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367568</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
@@ -426,32 +431,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
+          <t>Expanding Tools Control Foreign-Related Economic Activity - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24l8w486</t>
+          <t>https://tinyurl.com/2ce949hz</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
         </is>
       </c>
       <c r="D4" s="2">
@@ -459,17 +459,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/24l8w486</t>
         </is>
       </c>
     </row>
@@ -481,12 +471,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Understanding Purity and Potency in Cannabis</t>
+          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
@@ -494,56 +484,66 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Understanding Purity and Potency in Cannabis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/04/17/understanding-purity-and-potency-in-cannabis/</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Have you ever wondered why purity and potency in **cannabis** matter? Many people focus only on the experience,...
 ...e a big difference. Purity and potency affect how **cannabis** works in the body and how safe it is to use. When...
 ...e […]The post Understanding Purity and Potency in **Cannabis** appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Dunkirk man charged after fentanyl, meth seized in Pomfret - observertoday.com</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>46128</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/2ct7u5n9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WJTN News Headlines for Thurs., Apr. 16, 2026</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>City woman dies in single-car crash on I-90 south of Buffalo...A woman from Jamestown has been killed in a one-car crash on the New York State Thruway south of Buffalo.  State Police in Buffalo say they responded to the scene about 7:30 a.m. Wednesday in the town of Evans.  Troopers say they found that a mini-van... operated by 69 year-old Linda Haney... was eastbound on the I-90 when the crash occured.  They say the vehicle left the driving lane and crossed into the passing lane before traveling onto the north shoulder and overturning.  Troopers say Haney was seriously hurt... and, was flown to the Erie County Medical Center where she later died.  State Police say their Bureau of Criminal Investigation is still actively investigating the collision.Dunkirk man arrested following major drug raid in town of Pomfret...A Dunkirk man faces multiple drug possession charges following a raid on a town of Pomfret home this past Tuesday.  Sheriff's officers say their narcotics investigators... along with those from Jamestown... executed a search warrant at 5341 Van Buren Rd. shortly before 10 a.m.  Outside the home... they found 43 year-old Andrew Betts... and he was detained.  Inside the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scales and packaging materials and nearly $1,200 in cash.  Betts was charged with two counts of both second and third-degree criminal possession of a controlled substance... one of seventh-degree criminal possession... second-degree criminally using drug paraphernalia... and, first-degree criminal nuisance.  He was taken to the county jail pending centralized arraignment program.  Anyone with information about illegal drug -- or other criminal activity -- is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.  For the JPD tip linek... call 483-8477.City lawmakers discuss possible remendies on ongoing deer isse in Jamestown...It's been quiet in recent months... however... the issue of too many deer in the city of Jamestown has been raised up again to the City Council.  But.. in this case... New York state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce says there are three main issues to consider... the cost, how effective it may be, and the safety of the residents.  He adds that the way one community handles it doen't always work for everyone.  He says every city is unique, with some more spread out, and others with denser populations.  Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation.  She says it would involve more hunters being allowed to take more deer... and, extending the season for them.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down... and, that's allowed the deer population to grow.Gillibrand leads another push for a war powers measure to end war in Iran...Democrats in the U.S. Senate have seen a fourth effort to pass a resolution withdrawing forces from the conflict in Iran -- until Congress authorizes further action -- go down to defeat.  The measure was co-sponsored by New York Democrat Kirsten Gillibrand... who says the president and Congress need to focus on skyrocketing costs... including that for gasoline.  Gillibrand says it's putting further strain on working families, who are already struggling to make ends meet."  Whenever she gets back to New York state... she says people question why more isn't being down to reduce those prices... including a woman from Orange County... who's trying to make it on just social security with an ex-husband dealing with Parkinson's Disease.  She told Gillibrand that she's fearful she may have to sell their home if costs don't come down.  The current cease-fire ends in about a week... and, the war in Iran is heading towards the two-month old mark.  Gillibrand says she believes once that is reached... some Republicans may be ready to support the move.Pair of woman arrested following fight in Lakewood's Hartley Park...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.Jamestown woman accused of driving drunk, leaving the scene following downtown accident...A city woman is accused of driving drunk when her car crashed... and, then leaving the scene of the accident in downtown Jamestown.  City police say they were called to the scene shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicles had left the scene... and, tracked it back to the owner's address.  Police say they then found the driver... identified as 36 year-old Leonela Rodriguez... and, determined that she had been driving while intoxicated at the time of the accident.  Rodriguez was arrested without incident for Felony DWI... leaving the scene of a property damage accident... and, unlicensed operation.  </t>
+          <t>Dunkirk man charged after fentanyl, meth seized in Pomfret - observertoday.com</t>
         </is>
       </c>
       <c r="D7" s="2">
@@ -551,10 +551,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/2ct7u5n9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WJTN News Headlines for Thurs., Apr. 16, 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8 keyword references (WJTN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>City woman dies in single-car crash on I-90 south of Buffalo...A woman from Jamestown has been killed in a one-car crash on the New York State Thruway south of Buffalo.  State Police in Buffalo say they responded to the scene about 7:30 a.m. Wednesday in the town of Evans.  Troopers say they found that a mini-van... operated by 69 year-old Linda Haney... was eastbound on the I-90 when the crash occured.  They say the vehicle left the driving lane and crossed into the passing lane before traveling onto the north shoulder and overturning.  Troopers say Haney was seriously hurt... and, was flown to the Erie County Medical Center where she later died.  State Police say their Bureau of Criminal Investigation is still actively investigating the collision.Dunkirk man arrested following major drug raid in town of Pomfret...A Dunkirk man faces multiple drug possession charges following a raid on a town of Pomfret home this past Tuesday.  Sheriff's officers say their narcotics investigators... along with those from Jamestown... executed a search warrant at 5341 Van Buren Rd. shortly before 10 a.m.  Outside the home... they found 43 year-old Andrew Betts... and he was detained.  Inside the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scales and packaging materials and nearly $1,200 in cash.  Betts was charged with two counts of both second and third-degree criminal possession of a controlled substance... one of seventh-degree criminal possession... second-degree criminally using drug paraphernalia... and, first-degree criminal nuisance.  He was taken to the county jail pending centralized arraignment program.  Anyone with information about illegal drug -- or other criminal activity -- is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.  For the JPD tip linek... call 483-8477.City lawmakers discuss possible remendies on ongoing deer isse in Jamestown...It's been quiet in recent months... however... the issue of too many deer in the city of Jamestown has been raised up again to the City Council.  But.. in this case... New York state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce says there are three main issues to consider... the cost, how effective it may be, and the safety of the residents.  He adds that the way one community handles it doen't always work for everyone.  He says every city is unique, with some more spread out, and others with denser populations.  Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation.  She says it would involve more hunters being allowed to take more deer... and, extending the season for them.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down... and, that's allowed the deer population to grow.Gillibrand leads another push for a war powers measure to end war in Iran...Democrats in the U.S. Senate have seen a fourth effort to pass a resolution withdrawing forces from the conflict in Iran -- until Congress authorizes further action -- go down to defeat.  The measure was co-sponsored by New York Democrat Kirsten Gillibrand... who says the president and Congress need to focus on skyrocketing costs... including that for gasoline.  Gillibrand says it's putting further strain on working families, who are already struggling to make ends meet."  Whenever she gets back to New York state... she says people question why more isn't being down to reduce those prices... including a woman from Orange County... who's trying to make it on just social security with an ex-husband dealing with Parkinson's Disease.  She told Gillibrand that she's fearful she may have to sell their home if costs don't come down.  The current cease-fire ends in about a week... and, the war in Iran is heading towards the two-month old mark.  Gillibrand says she believes once that is reached... some Republicans may be ready to support the move.Pair of woman arrested following fight in Lakewood's Hartley Park...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.Jamestown woman accused of driving drunk, leaving the scene following downtown accident...A city woman is accused of driving drunk when her car crashed... and, then leaving the scene of the accident in downtown Jamestown.  City police say they were called to the scene shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicles had left the scene... and, tracked it back to the owner's address.  Police say they then found the driver... identified as 36 year-old Leonela Rodriguez... and, determined that she had been driving while intoxicated at the time of the accident.  Rodriguez was arrested without incident for Felony DWI... leaving the scene of a property damage accident... and, unlicensed operation.  </t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46128</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912536/wjtn-news-headlines-for-thurs-apr-16-2026</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>... the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of **methamphetamine**... 37.5 dosage units of clonazepam, scales and packaging materials and nea...
 ...was detained.  Inside the home... investigatiors found 173.7-grams of **fentanyl**... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scale...
@@ -566,75 +591,45 @@
 ...d with two counts of both second and third-degree criminal possession of a **controlled** substance... one of seventh-degree criminal possession... second-degree cr...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t xml:space="preserve">WJTN News Headlines for Thurs., Apr. 15, 2026   </t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>State Legislature approves new budget extender, spending plan now two week's late... The New York state legislature has again approved a one-week budget extension as talks on a new spending plan continue.  Lawmakers approved the $3.4-billion extender late Monday... then adjourned as the Apr. 1 deadline gets further in the rear-view mirror.  Minority Republicans continue to blast the the process... which has included Governor Kathy Hochul... Assembly Speaker Carl Heastie... and, Senate Majority Leader Andrea Stewart-Cousins.  Assembly Minority Leader Ed Ra saying -- "each day that goes by without an approved state spending plan is a day Albany has failed.  Deadlines exist for a reason -- and everyday New Yorkers face consequences when they’re missed."  Ra urged the legislature to open up the process.Jamestown man arrested for pulling another man from car... and, punching him several times during incident...A city man has been arrested for allegedly pulling another man from his car... and, then punching him several times in the face.  Jamestown police were called to the scene at East Sixth and Winsor Streets about 4 p.m. Monday on a report of a fight.  Officers say their investigation found that 27 year-old Charles Dean had engaged in the fight after forcibly removing the man from his vehicle... and, then hitting him multiple times with a closed fist.  Dean was arrested without incident for third-degree assault.... and jailed pending arraignment.Issue with deer brought before City Council committee...The issue of too many deer in the city of Jamestown has been raised again before the City Council... but, the state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce calls is a "touchy issue" with many wanting some kind of action taken... but, many also worried about safety of an in-city harvest.  Dolce says there are a handful of suggestions for dealing the deer issue... but, he says no matter what is decided... cost will always be a factor.  Dolce adds that the way one community handles it doen't always work for everyone.  He says it depends on the amount of unused land there it, and the fact that one community that did a controlled hunt, really didn't solve the issue.  However... Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation to allow hunters to obtain more deer tags, and possibly extending the season so there can be a later take.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down.Jamestown native, career worker in diplomatic services, named as new president at Chautauqua Institution...A Jamestown native who has a long history with Chautauqua Institution has been named as the institution's new president.  The Institution's board has announced that Mark Coolidge Johnson -- a veteran U.S. diplomat and third-generation Chautauquan has been appointed to lead Chautauqua Institution -- beginning at the end of the 2026 Summer Season.  The chair of the institution's board, Laurie Branch, announced Johnson's appointment Tuesday... noting that he brings more than 30 years of diplomatic service as a Senior Foreign Service Officer... attorney and third-generation Chautauquan to the institution.  Currently... Branch says Johnson serves as Deputy Chief of Mission at the U.S. Embassy in Mexico City -- the largest American diplomatic mission in the world -- where he oversees more than 3-thousand employees... nine consulates and nine consular agencies with a $282-million operating budget.  Johnson is the son of the late Joe Johnson, who served the Institution for 20 years as Vice President of Finance, and is also the grandson of a Chautauqua grounds engineer.  He holds a juris doctorate from American University’s Washington College of Law.  Johnson calls the appointment the "honor of a lifetime to return home and lead this extraordinary community into it's next chapter." City woman arrested for Felony DWI following personal injury accident in downtown Jamestown...A woman from Jamestown has been arrested for allegedly driving drunk... and, leaving the scene of a property damage accident.  City police say they were called to a downtown business shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicle had left the scene... and, tracked it back to the owner's address.  Police say they then made contact with the driver... identified as 36 year-old Leonela Rodriguez... and, found she had been driving while intoxicated at the time of the accident.  Rodriguez was taken into custody without incident... and, taken to the city jail pending arraignment on charges of DWI... leaving the scene of a property damage accident... and, unlicensed operation.  Officers add that Rodriguez has a previous DWAI conviction... making this a Felony.Pair of women arrested in Lakewood for alleged fight in front of children...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.  </t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>46127</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912391/wjtn-news-headlines-for-thurs-apr-15-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>... as 36 year-old Leonela Rodriguez... and, found she had been driving while **intoxicated** at the time of the accident.  Rodriguez was taken into custody withou...
 ...amount of unused land there it, and the fact that one community that did a **controlled** hunt, really didn't solve the issue.  However... Mayor Kim Ecklund sa...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – BUFFALO, N.Y. — A Buffalo man has pleaded guilty in federal court to his role in a multi-state narcotics conspiracy involving the shipment and distribution of large quantities of cocaine across the Western District of New York. Steven Hoskins, 44, of Buffalo, New York, entered a guilty plea before John L. […]The post Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>46127</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/15/buffalo-man-pleads-guilty-in-federal-cocaine-trafficking-conspiracy-case/</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -646,12 +641,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road</t>
+          <t>Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(WNY News Now) – A 40-year-old Little Valley man was arrested following a traffic stop on Lebanon Road in the Town of Coldspring on April 11, 2026, after deputies reported multiple vehicle and traffic violations and subsequent intoxication findings. The Cattaraugus County Sheriff’s Office reports that Benjamin I. Hilliard, 40, of Little Valley, was taken […]The post Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – BUFFALO, N.Y. — A Buffalo man has pleaded guilty in federal court to his role in a multi-state narcotics conspiracy involving the shipment and distribution of large quantities of cocaine across the Western District of New York. Steven Hoskins, 44, of Buffalo, New York, entered a guilty plea before John L. […]The post Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D10" s="2">
@@ -659,12 +654,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/15/coldspring-traffic-stop-leads-to-dwi-arrest-on-lebanon-road/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>...ple vehicle and traffic violations and subsequent **intoxication** findings. The Cattaraugus County Sheriff’s Office...</t>
+          <t>https://wnynewsnow.com/2026/04/15/buffalo-man-pleads-guilty-in-federal-cocaine-trafficking-conspiracy-case/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -676,28 +666,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 40-year-old Little Valley man was arrested following a traffic stop on Lebanon Road in the Town of Coldspring on April 11, 2026, after deputies reported multiple vehicle and traffic violations and subsequent intoxication findings. The Cattaraugus County Sheriff’s Office reports that Benjamin I. Hilliard, 40, of Little Valley, was taken […]The post Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46127</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/15/coldspring-traffic-stop-leads-to-dwi-arrest-on-lebanon-road/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>...ple vehicle and traffic violations and subsequent **intoxication** findings. The Cattaraugus County Sheriff’s Office...</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>WJTN News Headlines for Monday, Apr. 13, 2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>5 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Fire destroys condemned home on Prendergast Ave; but, fire crews save two adjacent homes...Fire has destroyed a vacant and condemned home on Jamestown's northside... but, quick work by firefighters saved two neighoring homes.  City Fire Battlion Chief Nate Alm says firefighters were called to the scene at 612 Prendergast Ave. shortly after 7 p.m. Friday... and, first arriving crews found the home fully-engulfed in flames... and they moved quickly to knock down the flames, and protect the two adjacent hmes.  Alm says the family living in one was safely evacuated... along with their pets.  He says an off-duty shift of 15 firefighters and a commander was called in to assist.  No injuries were reported... but, he says crews were at the scene for nearly five-and-a-half hours.  The cause is under investigation... and the home at 612 Prendergast will be torn down.Man from Jamestown and woman from Buffalo indicted on federal drug conspiracy charges...A man from Jamestown... and, a woman from Buffalo have been indicted on a federal charge for allegedly being involved in a narcotics conspiracy.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury returned the indictment charging 41 year-old Brandon Murray... and, 35 year-old Latika Saintkitts... with narcotics conspiracy.  DiGiacomo says the charge carries a mandatory minimum of 10 years in prison...  and a maximum of life. In addition, Saintkitts is charged with distribution of crack cocaine and fentanyl.  Prosecutors say that between 2021, and September 2024, Murray and Saintkitts conspired with others to possess and distribute fentanyl, methamphetamine, and heroin.  In addition, in April of 2024, Saintkitts possessed and distributed crack cocaine... and, in June of that year... she possessed and distributed fentanyl.  Murray was detained... and, Saintkitts was released on conditions.Charges now filed against man involved in stand-off last week in Fredonia...Charges have now been filed against a man who barricaded himself for several hours inside a White Street home in the Village of Fredonia last week... prompting a shelter in place order for the area.  Fredonia Police say a White Street resident reported on Wednesday that 44-year-old Kyle Denhardt was unwanted... refused to leave her residence, and was possibly in possession of a handgun.  Officers responded... and, helped the woman off the property, then began communicating with Denhardt.  A perimeter was established and maintained with assistance from Dunkirk police... University Police... and State Police.  While the area was closed off to vehicle and pedestrian traffic, State Police Special Operations Response Teams were deployed... along with an Unmanned Aerial Systems unit.  After warrants were obtained, Denhardt surrendered peacefully after several hours of negotiations to a special State Police Team.  When police executed the search warrant, they discovered a large cache of weaponry, including a ghost gun, high-capacity magazines, ammunition, rifle parts, and related accessories.-----Denhardt, who is a resident of Maryland and South Carolina, faces charged including:  second-degree menacing... second-degree criminal trespass... second-degree criminal possession of a weapon... and, two counts of third-degree criminal possession of a weapon.  He was taken to the county jail on $400,000 cash bail.Woman arrested in town of Hanover for incident with stun gun...A woman has been arrested for allegedly displaying an electric stun gun during an altercation in the town of Hanover.  Sheriff's officers say they were called to the scene about 7:30 a.m. last Thursday on a report of the incident.  Deputies say they found that 26 year-old Allyson Lycett had pulled out the stun gun during the altercation... and, was arrested for fourth-degree criminal possession of a weapon.  Lycett was arraigned... and, issued an appearance ticket for Hanover Town Court at a later date.Lake Property Owner's hold first meeting since court ruling "annuls" wetland regulations...With last week's State Supreme Court ruling... the state Department of Environmental Conservation may have to do a full-blown environmental impact statement on any new wetland regulations.  That from Chautauqua Lake Property Owners Association president Jim Wehrfritz during the CLPOA's most recent meeting last Saturday in Bemus Point.  Wehrfritz says the court's annulment of the regulations "demand accountabilty."  Wehrfritz says the DEC may have to issue a "positive declaration..." meaning that the regulations would have to consider economic and social issues in those regulations.  Wehrfritz... however... cautioned that if the DEC were to implement new wetland regulations.. they would be more "broadbased" because it would have to be for the entire state.  He later focused on the June 2024 plan for the lake proposed by Dr. Robert Richardson at North Carolina State University.  Wehrfritz feels it needs to be acted on, because it's time to have a plan that can be acted on.  He says the CLPOA also feels there needs to be a study of the lake's condition... and, the wetlands regulations on property values on the lake.State Supreme Court rules in favor of village connecting with the No. County Water District...A State Supreme Court judge has sided with the village of Fredonia in a lawsuit that sought to annul a resolution for the village's project to connect with the North County Water District.  In an 11-page ruling last Wednesday... Judge Grace Hanlon denied the request that was filed in October by members of the "Save Our Reservoir" group, who argued that the village violated the State Environmental Quality Review Act... General Municipal Law... and, the village's Zoning Code.  Judge Hanlon determined that the village -- "neither abused its discretion nor was arbitrary or capricious in its determination" with regard to its SEQRA analysis.</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <v>46125</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911992/wjtn-news-headlines-for-monday-apr-13-2026</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...y and Saintkitts conspired with others to possess and distribute fentanyl, **methamphetamine**, and heroin.  In addition, in April of 2024, Saintkitts possessed and...
 ... In addition, Saintkitts is charged with distribution of crack cocaine and **fentanyl**.  Prosecutors say that between 2021, and September 2024, Murray and S...
@@ -706,34 +731,9 @@
 ...be torn down.Man from Jamestown and woman from Buffalo indicted on federal **drug** conspiracy charges...A man from Jamestown... and, a woman from Buffalo hav...</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chautauqua_Today</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Two Fredonia Residents Charged with Drug PossessionTwo Fredonia residents were recently arrested by Fredonia Police on drug-related charges in the village. On April 4th, officers took Christopher McNett into custody at about 12:15 PM on a charge of 7th-degree criminal possession of a controlled subs...Greg Larson, News Director</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46124</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367509</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -401,65 +401,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jamestown Man Charged with DWI Following Welfare Check Call</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ripley Woman Arrested in Westfield on Drug ChargeA report of a disorderly person led to the arrest of a Ripley woman on a drug-related charge on Saturday. Chautauqua County Sheriff's deputies received the call just before 12:45 PM, with the suspect located by Westfield Police. After an investigatio...Greg Larson, News Director</t>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Jamestown man was taken into custody Sunday afternoon after police responded to a welfare check on the city’s west side and determined he was allegedly operating a vehicle while intoxicated. According to the Jamestown Police Department, officers from the 2nd Platoon were dispatched at approximately 4:00 p.m. […]The post Jamestown Man Charged with DWI Following Welfare Check Call appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367568</t>
+          <t>https://wnynewsnow.com/2026/04/20/jamestown-man-charged-with-dwi-following-welfare-check-call/</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>...rmined he was allegedly operating a vehicle while **intoxicated**. According to the Jamestown Police Department, of...</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Expanding Tools Control Foreign-Related Economic Activity - The Jamestown Foundation</t>
+          <t>Ripley Woman Charged With Drug Possession Following Disorderly Person Complaint</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – RIPLEY, N.Y. — A Ripley woman is facing a misdemeanor drug charge after deputies responded to a report of a disorderly person Saturday afternoon. According to the Chautauqua County Sheriff’s Office, deputies were dispatched to the Town of Ripley at approximately 12:42 p.m. on April 18 for a reported disturbance. The […]The post Ripley Woman Charged With Drug Possession Following Disorderly Person Complaint appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2ce949hz</t>
+          <t>https://wnynewsnow.com/2026/04/20/ripley-woman-charged-with-drug-possession-following-disorderly-person-complaint/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...EY, N.Y. — A Ripley woman is facing a misdemeanor **drug** charge after deputies responded to a report of a ...
+...rbance. The […]The post Ripley Woman Charged With **Drug** Possession Following Disorderly Person Complaint ...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Google_search</t>
+          <t>WNY News Now</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
+          <t>Fredonia Woman Charged with DWI Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – FREDONIA, N.Y. — A Dunkirk woman is facing multiple charges after a traffic stop early Saturday morning in the Village of Fredonia led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on Eagle Street at approximately 2:19 a.m. on April 18. […]The post Fredonia Woman Charged with DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D4" s="2">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24l8w486</t>
+          <t>https://wnynewsnow.com/2026/04/20/fredonia-woman-charged-with-dwi-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...in the Village of Fredonia led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
@@ -471,25 +512,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
+          <t>South Dayton Man Charged with DWI Following Traffic Stop in Hanover</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – A South Dayton man was charged with driving while intoxicated after deputies conducted a traffic stop in the Town of Hanover on April 18. According to the Chautauqua County Sheriff’s Office, the incident occurred on April 18, 2026, at approximately 2:22 a.m. in the Town of Hanover. Deputies reported that they […]The post South Dayton Man Charged with DWI Following Traffic Stop in Hanover appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
+          <t>https://wnynewsnow.com/2026/04/20/south-dayton-man-charged-with-dwi-following-traffic-stop-in-hanover/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
+          <t>...A South Dayton man was charged with driving while **intoxicated** after deputies conducted a traffic stop in the To...</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -501,85 +542,185 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ripley Woman Arrested in Westfield on Drug ChargeA report of a disorderly person led to the arrest of a Ripley woman on a drug-related charge on Saturday. Chautauqua County Sheriff's deputies received the call just before 12:45 PM, with the suspect located by Westfield Police. After an investigatio...Greg Larson, News Director</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>46131</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367568</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Expanding Tools Control Foreign-Related Economic Activity - The Jamestown Foundation</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>46130</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/2ce949hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Google_search</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/24l8w486</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Understanding Purity and Potency in Cannabis</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D10" s="2">
         <v>46129</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/17/understanding-purity-and-potency-in-cannabis/</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Have you ever wondered why purity and potency in **cannabis** matter? Many people focus only on the experience,...
 ...e a big difference. Purity and potency affect how **cannabis** works in the body and how safe it is to use. When...
 ...e […]The post Understanding Purity and Potency in **Cannabis** appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Google_search</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Dunkirk man charged after fentanyl, meth seized in Pomfret - observertoday.com</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D11" s="2">
         <v>46128</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://tinyurl.com/2ct7u5n9</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>WJTN News Headlines for Thurs., Apr. 16, 2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>8 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>City woman dies in single-car crash on I-90 south of Buffalo...A woman from Jamestown has been killed in a one-car crash on the New York State Thruway south of Buffalo.  State Police in Buffalo say they responded to the scene about 7:30 a.m. Wednesday in the town of Evans.  Troopers say they found that a mini-van... operated by 69 year-old Linda Haney... was eastbound on the I-90 when the crash occured.  They say the vehicle left the driving lane and crossed into the passing lane before traveling onto the north shoulder and overturning.  Troopers say Haney was seriously hurt... and, was flown to the Erie County Medical Center where she later died.  State Police say their Bureau of Criminal Investigation is still actively investigating the collision.Dunkirk man arrested following major drug raid in town of Pomfret...A Dunkirk man faces multiple drug possession charges following a raid on a town of Pomfret home this past Tuesday.  Sheriff's officers say their narcotics investigators... along with those from Jamestown... executed a search warrant at 5341 Van Buren Rd. shortly before 10 a.m.  Outside the home... they found 43 year-old Andrew Betts... and he was detained.  Inside the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scales and packaging materials and nearly $1,200 in cash.  Betts was charged with two counts of both second and third-degree criminal possession of a controlled substance... one of seventh-degree criminal possession... second-degree criminally using drug paraphernalia... and, first-degree criminal nuisance.  He was taken to the county jail pending centralized arraignment program.  Anyone with information about illegal drug -- or other criminal activity -- is asked to call the Sheriff's Office Narcotics Investigators Tip line at 1-800-344-8702 or 664-2420.  For the JPD tip linek... call 483-8477.City lawmakers discuss possible remendies on ongoing deer isse in Jamestown...It's been quiet in recent months... however... the issue of too many deer in the city of Jamestown has been raised up again to the City Council.  But.. in this case... New York state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce says there are three main issues to consider... the cost, how effective it may be, and the safety of the residents.  He adds that the way one community handles it doen't always work for everyone.  He says every city is unique, with some more spread out, and others with denser populations.  Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation.  She says it would involve more hunters being allowed to take more deer... and, extending the season for them.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down... and, that's allowed the deer population to grow.Gillibrand leads another push for a war powers measure to end war in Iran...Democrats in the U.S. Senate have seen a fourth effort to pass a resolution withdrawing forces from the conflict in Iran -- until Congress authorizes further action -- go down to defeat.  The measure was co-sponsored by New York Democrat Kirsten Gillibrand... who says the president and Congress need to focus on skyrocketing costs... including that for gasoline.  Gillibrand says it's putting further strain on working families, who are already struggling to make ends meet."  Whenever she gets back to New York state... she says people question why more isn't being down to reduce those prices... including a woman from Orange County... who's trying to make it on just social security with an ex-husband dealing with Parkinson's Disease.  She told Gillibrand that she's fearful she may have to sell their home if costs don't come down.  The current cease-fire ends in about a week... and, the war in Iran is heading towards the two-month old mark.  Gillibrand says she believes once that is reached... some Republicans may be ready to support the move.Pair of woman arrested following fight in Lakewood's Hartley Park...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.Jamestown woman accused of driving drunk, leaving the scene following downtown accident...A city woman is accused of driving drunk when her car crashed... and, then leaving the scene of the accident in downtown Jamestown.  City police say they were called to the scene shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicles had left the scene... and, tracked it back to the owner's address.  Police say they then found the driver... identified as 36 year-old Leonela Rodriguez... and, determined that she had been driving while intoxicated at the time of the accident.  Rodriguez was arrested without incident for Felony DWI... leaving the scene of a property damage accident... and, unlicensed operation.  </t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D12" s="2">
         <v>46128</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912536/wjtn-news-headlines-for-thurs-apr-16-2026</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>... the home... investigatiors found 173.7-grams of fentanyl... 92.7 grams of **methamphetamine**... 37.5 dosage units of clonazepam, scales and packaging materials and nea...
 ...was detained.  Inside the home... investigatiors found 173.7-grams of **fentanyl**... 92.7 grams of methamphetamine... 37.5 dosage units of clonazepam, scale...
@@ -591,149 +732,110 @@
 ...d with two counts of both second and third-degree criminal possession of a **controlled** substance... one of seventh-degree criminal possession... second-degree cr...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">WJTN News Headlines for Thurs., Apr. 15, 2026   </t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2 keyword references (WJTN)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>State Legislature approves new budget extender, spending plan now two week's late... The New York state legislature has again approved a one-week budget extension as talks on a new spending plan continue.  Lawmakers approved the $3.4-billion extender late Monday... then adjourned as the Apr. 1 deadline gets further in the rear-view mirror.  Minority Republicans continue to blast the the process... which has included Governor Kathy Hochul... Assembly Speaker Carl Heastie... and, Senate Majority Leader Andrea Stewart-Cousins.  Assembly Minority Leader Ed Ra saying -- "each day that goes by without an approved state spending plan is a day Albany has failed.  Deadlines exist for a reason -- and everyday New Yorkers face consequences when they’re missed."  Ra urged the legislature to open up the process.Jamestown man arrested for pulling another man from car... and, punching him several times during incident...A city man has been arrested for allegedly pulling another man from his car... and, then punching him several times in the face.  Jamestown police were called to the scene at East Sixth and Winsor Streets about 4 p.m. Monday on a report of a fight.  Officers say their investigation found that 27 year-old Charles Dean had engaged in the fight after forcibly removing the man from his vehicle... and, then hitting him multiple times with a closed fist.  Dean was arrested without incident for third-degree assault.... and jailed pending arraignment.Issue with deer brought before City Council committee...The issue of too many deer in the city of Jamestown has been raised again before the City Council... but, the state may soon be offering some help.  The Council's Public Safety Committee discussed the matter with one resident this week... and, Chairman Tony Dolce says lawmakers may -- or may not -- want to look at tackling it.  Dolce calls is a "touchy issue" with many wanting some kind of action taken... but, many also worried about safety of an in-city harvest.  Dolce says there are a handful of suggestions for dealing the deer issue... but, he says no matter what is decided... cost will always be a factor.  Dolce adds that the way one community handles it doen't always work for everyone.  He says it depends on the amount of unused land there it, and the fact that one community that did a controlled hunt, really didn't solve the issue.  However... Mayor Kim Ecklund says there may be some help on the horizon with a proposal being considered by the state Department of Environmental Conservation to allow hunters to obtain more deer tags, and possibly extending the season so there can be a later take.  Ecklund says the DEC has recognized that deer takes during recent hunting seasons has been down.Jamestown native, career worker in diplomatic services, named as new president at Chautauqua Institution...A Jamestown native who has a long history with Chautauqua Institution has been named as the institution's new president.  The Institution's board has announced that Mark Coolidge Johnson -- a veteran U.S. diplomat and third-generation Chautauquan has been appointed to lead Chautauqua Institution -- beginning at the end of the 2026 Summer Season.  The chair of the institution's board, Laurie Branch, announced Johnson's appointment Tuesday... noting that he brings more than 30 years of diplomatic service as a Senior Foreign Service Officer... attorney and third-generation Chautauquan to the institution.  Currently... Branch says Johnson serves as Deputy Chief of Mission at the U.S. Embassy in Mexico City -- the largest American diplomatic mission in the world -- where he oversees more than 3-thousand employees... nine consulates and nine consular agencies with a $282-million operating budget.  Johnson is the son of the late Joe Johnson, who served the Institution for 20 years as Vice President of Finance, and is also the grandson of a Chautauqua grounds engineer.  He holds a juris doctorate from American University’s Washington College of Law.  Johnson calls the appointment the "honor of a lifetime to return home and lead this extraordinary community into it's next chapter." City woman arrested for Felony DWI following personal injury accident in downtown Jamestown...A woman from Jamestown has been arrested for allegedly driving drunk... and, leaving the scene of a property damage accident.  City police say they were called to a downtown business shortly after 11 p.m. Tuesday for a reported accident.  Officers say they were told one of the vehicle had left the scene... and, tracked it back to the owner's address.  Police say they then made contact with the driver... identified as 36 year-old Leonela Rodriguez... and, found she had been driving while intoxicated at the time of the accident.  Rodriguez was taken into custody without incident... and, taken to the city jail pending arraignment on charges of DWI... leaving the scene of a property damage accident... and, unlicensed operation.  Officers add that Rodriguez has a previous DWAI conviction... making this a Felony.Pair of women arrested in Lakewood for alleged fight in front of children...Two women have been arrested for allegedly fighting at Lakewood's Hartley Park in front of children this past Monday night.  Lakewood-Busti Police say they were called to the scene on Terrace Avenue about 8:20 p.m., and investigated.  Officers determined that Jessica Spagnualo, and Mackenzie Haskins were each at fault... and, both were arrested for second-degree harassment... disorderly conduct... and, five counts each of endangering the welfare of a child.  They were both issued appearance tickets for Busti Town Court at a later date.  </t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D13" s="2">
         <v>46127</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/912391/wjtn-news-headlines-for-thurs-apr-15-2026</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>... as 36 year-old Leonela Rodriguez... and, found she had been driving while **intoxicated** at the time of the accident.  Rodriguez was taken into custody withou...
 ...amount of unused land there it, and the fact that one community that did a **controlled** hunt, really didn't solve the issue.  However... Mayor Kim Ecklund sa...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>(WNY News Now) – BUFFALO, N.Y. — A Buffalo man has pleaded guilty in federal court to his role in a multi-state narcotics conspiracy involving the shipment and distribution of large quantities of cocaine across the Western District of New York. Steven Hoskins, 44, of Buffalo, New York, entered a guilty plea before John L. […]The post Buffalo Man Pleads Guilty in Federal Cocaine Trafficking Conspiracy Case appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D14" s="2">
         <v>46127</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/15/buffalo-man-pleads-guilty-in-federal-cocaine-trafficking-conspiracy-case/</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>WNY News Now</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>(WNY News Now) – A 40-year-old Little Valley man was arrested following a traffic stop on Lebanon Road in the Town of Coldspring on April 11, 2026, after deputies reported multiple vehicle and traffic violations and subsequent intoxication findings. The Cattaraugus County Sheriff’s Office reports that Benjamin I. Hilliard, 40, of Little Valley, was taken […]The post Coldspring Traffic Stop Leads to DWI Arrest on Lebanon Road appeared first on WNY News Now.</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D15" s="2">
         <v>46127</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://wnynewsnow.com/2026/04/15/coldspring-traffic-stop-leads-to-dwi-arrest-on-lebanon-road/</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...ple vehicle and traffic violations and subsequent **intoxication** findings. The Cattaraugus County Sheriff’s Office...</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WJTN News Headlines for Monday, Apr. 13, 2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5 keyword references (WJTN)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Fire destroys condemned home on Prendergast Ave; but, fire crews save two adjacent homes...Fire has destroyed a vacant and condemned home on Jamestown's northside... but, quick work by firefighters saved two neighoring homes.  City Fire Battlion Chief Nate Alm says firefighters were called to the scene at 612 Prendergast Ave. shortly after 7 p.m. Friday... and, first arriving crews found the home fully-engulfed in flames... and they moved quickly to knock down the flames, and protect the two adjacent hmes.  Alm says the family living in one was safely evacuated... along with their pets.  He says an off-duty shift of 15 firefighters and a commander was called in to assist.  No injuries were reported... but, he says crews were at the scene for nearly five-and-a-half hours.  The cause is under investigation... and the home at 612 Prendergast will be torn down.Man from Jamestown and woman from Buffalo indicted on federal drug conspiracy charges...A man from Jamestown... and, a woman from Buffalo have been indicted on a federal charge for allegedly being involved in a narcotics conspiracy.  U.S. Attorney Michael DiGiacomo has announced that a federal grand jury returned the indictment charging 41 year-old Brandon Murray... and, 35 year-old Latika Saintkitts... with narcotics conspiracy.  DiGiacomo says the charge carries a mandatory minimum of 10 years in prison...  and a maximum of life. In addition, Saintkitts is charged with distribution of crack cocaine and fentanyl.  Prosecutors say that between 2021, and September 2024, Murray and Saintkitts conspired with others to possess and distribute fentanyl, methamphetamine, and heroin.  In addition, in April of 2024, Saintkitts possessed and distributed crack cocaine... and, in June of that year... she possessed and distributed fentanyl.  Murray was detained... and, Saintkitts was released on conditions.Charges now filed against man involved in stand-off last week in Fredonia...Charges have now been filed against a man who barricaded himself for several hours inside a White Street home in the Village of Fredonia last week... prompting a shelter in place order for the area.  Fredonia Police say a White Street resident reported on Wednesday that 44-year-old Kyle Denhardt was unwanted... refused to leave her residence, and was possibly in possession of a handgun.  Officers responded... and, helped the woman off the property, then began communicating with Denhardt.  A perimeter was established and maintained with assistance from Dunkirk police... University Police... and State Police.  While the area was closed off to vehicle and pedestrian traffic, State Police Special Operations Response Teams were deployed... along with an Unmanned Aerial Systems unit.  After warrants were obtained, Denhardt surrendered peacefully after several hours of negotiations to a special State Police Team.  When police executed the search warrant, they discovered a large cache of weaponry, including a ghost gun, high-capacity magazines, ammunition, rifle parts, and related accessories.-----Denhardt, who is a resident of Maryland and South Carolina, faces charged including:  second-degree menacing... second-degree criminal trespass... second-degree criminal possession of a weapon... and, two counts of third-degree criminal possession of a weapon.  He was taken to the county jail on $400,000 cash bail.Woman arrested in town of Hanover for incident with stun gun...A woman has been arrested for allegedly displaying an electric stun gun during an altercation in the town of Hanover.  Sheriff's officers say they were called to the scene about 7:30 a.m. last Thursday on a report of the incident.  Deputies say they found that 26 year-old Allyson Lycett had pulled out the stun gun during the altercation... and, was arrested for fourth-degree criminal possession of a weapon.  Lycett was arraigned... and, issued an appearance ticket for Hanover Town Court at a later date.Lake Property Owner's hold first meeting since court ruling "annuls" wetland regulations...With last week's State Supreme Court ruling... the state Department of Environmental Conservation may have to do a full-blown environmental impact statement on any new wetland regulations.  That from Chautauqua Lake Property Owners Association president Jim Wehrfritz during the CLPOA's most recent meeting last Saturday in Bemus Point.  Wehrfritz says the court's annulment of the regulations "demand accountabilty."  Wehrfritz says the DEC may have to issue a "positive declaration..." meaning that the regulations would have to consider economic and social issues in those regulations.  Wehrfritz... however... cautioned that if the DEC were to implement new wetland regulations.. they would be more "broadbased" because it would have to be for the entire state.  He later focused on the June 2024 plan for the lake proposed by Dr. Robert Richardson at North Carolina State University.  Wehrfritz feels it needs to be acted on, because it's time to have a plan that can be acted on.  He says the CLPOA also feels there needs to be a study of the lake's condition... and, the wetlands regulations on property values on the lake.State Supreme Court rules in favor of village connecting with the No. County Water District...A State Supreme Court judge has sided with the village of Fredonia in a lawsuit that sought to annul a resolution for the village's project to connect with the North County Water District.  In an 11-page ruling last Wednesday... Judge Grace Hanlon denied the request that was filed in October by members of the "Save Our Reservoir" group, who argued that the village violated the State Environmental Quality Review Act... General Municipal Law... and, the village's Zoning Code.  Judge Hanlon determined that the village -- "neither abused its discretion nor was arbitrary or capricious in its determination" with regard to its SEQRA analysis.</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>46125</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://mediaonegroupradio.com/news-and-closings/local-news-headlines/911992/wjtn-news-headlines-for-monday-apr-13-2026</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>...y and Saintkitts conspired with others to possess and distribute fentanyl, **methamphetamine**, and heroin.  In addition, in April of 2024, Saintkitts possessed and...
-... In addition, Saintkitts is charged with distribution of crack cocaine and **fentanyl**.  Prosecutors say that between 2021, and September 2024, Murray and S...
-...024, Murray and Saintkitts conspired with others to possess and distribute **fentanyl**, methamphetamine, and heroin.  In addition, in April of 2024, Saintki...
-...rack cocaine... and, in June of that year... she possessed and distributed **fentanyl**.  Murray was detained... and, Saintkitts was released on conditions.C...
-...be torn down.Man from Jamestown and woman from Buffalo indicted on federal **drug** conspiracy charges...A man from Jamestown... and, a woman from Buffalo hav...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>News_search_MediaOne_WJTN.R</t>
         </is>
       </c>
     </row>

--- a/Combined_results.xlsx
+++ b/Combined_results.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
@@ -406,25 +406,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jamestown Man Charged with DWI Following Welfare Check Call</t>
+          <t>Falconer Man Charged With Felony DWI Following Motorcycle Stop in Town of Ellicott</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Jamestown man was taken into custody Sunday afternoon after police responded to a welfare check on the city’s west side and determined he was allegedly operating a vehicle while intoxicated. According to the Jamestown Police Department, officers from the 2nd Platoon were dispatched at approximately 4:00 p.m. […]The post Jamestown Man Charged with DWI Following Welfare Check Call appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – A 55-year-old Falconer man faces felony charges after Town of Ellicott police say he was operating a motorcycle while allegedly intoxicated and riding on a sidewalk during a traffic stop on April 10, 2026. The Town of Ellicott Police Department reported the arrest of Jason R. Reed, 55, of Falconer, following […]The post Falconer Man Charged With Felony DWI Following Motorcycle Stop in Town of Ellicott appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/20/jamestown-man-charged-with-dwi-following-welfare-check-call/</t>
+          <t>https://wnynewsnow.com/2026/04/21/falconer-man-charged-with-felony-dwi-following-motorcycle-stop-in-town-of-ellicott/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>...rmined he was allegedly operating a vehicle while **intoxicated**. According to the Jamestown Police Department, of...</t>
+          <t>...say he was operating a motorcycle while allegedly **intoxicated** and riding on a sidewalk during a traffic stop on...</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -441,12 +441,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ripley Woman Charged With Drug Possession Following Disorderly Person Complaint</t>
+          <t>Jamestown Man Charged with DWI Following Welfare Check Call</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(WNY News Now) – RIPLEY, N.Y. — A Ripley woman is facing a misdemeanor drug charge after deputies responded to a report of a disorderly person Saturday afternoon. According to the Chautauqua County Sheriff’s Office, deputies were dispatched to the Town of Ripley at approximately 12:42 p.m. on April 18 for a reported disturbance. The […]The post Ripley Woman Charged With Drug Possession Following Disorderly Person Complaint appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – JAMESTOWN, N.Y. — A Jamestown man was taken into custody Sunday afternoon after police responded to a welfare check on the city’s west side and determined he was allegedly operating a vehicle while intoxicated. According to the Jamestown Police Department, officers from the 2nd Platoon were dispatched at approximately 4:00 p.m. […]The post Jamestown Man Charged with DWI Following Welfare Check Call appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D3" s="2">
@@ -454,50 +454,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>https://wnynewsnow.com/2026/04/20/jamestown-man-charged-with-dwi-following-welfare-check-call/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...rmined he was allegedly operating a vehicle while **intoxicated**. According to the Jamestown Police Department, of...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ripley Woman Charged With Drug Possession Following Disorderly Person Complaint</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – RIPLEY, N.Y. — A Ripley woman is facing a misdemeanor drug charge after deputies responded to a report of a disorderly person Saturday afternoon. According to the Chautauqua County Sheriff’s Office, deputies were dispatched to the Town of Ripley at approximately 12:42 p.m. on April 18 for a reported disturbance. The […]The post Ripley Woman Charged With Drug Possession Following Disorderly Person Complaint appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>46132</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>https://wnynewsnow.com/2026/04/20/ripley-woman-charged-with-drug-possession-following-disorderly-person-complaint/</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...EY, N.Y. — A Ripley woman is facing a misdemeanor **drug** charge after deputies responded to a report of a ...
 ...rbance. The […]The post Ripley Woman Charged With **Drug** Possession Following Disorderly Person Complaint ...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WNY News Now</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Fredonia Woman Charged with DWI Following Early Morning Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – FREDONIA, N.Y. — A Dunkirk woman is facing multiple charges after a traffic stop early Saturday morning in the Village of Fredonia led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on Eagle Street at approximately 2:19 a.m. on April 18. […]The post Fredonia Woman Charged with DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>46132</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://wnynewsnow.com/2026/04/20/fredonia-woman-charged-with-dwi-following-early-morning-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...in the Village of Fredonia led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>News_search_WNY_News_Now.R</t>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South Dayton Man Charged with DWI Following Traffic Stop in Hanover</t>
+          <t>Fredonia Woman Charged with DWI Following Early Morning Traffic Stop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(WNY News Now) – A South Dayton man was charged with driving while intoxicated after deputies conducted a traffic stop in the Town of Hanover on April 18. According to the Chautauqua County Sheriff’s Office, the incident occurred on April 18, 2026, at approximately 2:22 a.m. in the Town of Hanover. Deputies reported that they […]The post South Dayton Man Charged with DWI Following Traffic Stop in Hanover appeared first on WNY News Now.</t>
+          <t>(WNY News Now) – FREDONIA, N.Y. — A Dunkirk woman is facing multiple charges after a traffic stop early Saturday morning in the Village of Fredonia led to a driving while intoxicated investigation. According to the Chautauqua County Sheriff’s Office, deputies conducted a traffic stop on Eagle Street at approximately 2:19 a.m. on April 18. […]The post Fredonia Woman Charged with DWI Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D5" s="2">
@@ -525,12 +525,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/20/south-dayton-man-charged-with-dwi-following-traffic-stop-in-hanover/</t>
+          <t>https://wnynewsnow.com/2026/04/20/fredonia-woman-charged-with-dwi-following-early-morning-traffic-stop/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>...A South Dayton man was charged with driving while **intoxicated** after deputies conducted a traffic stop in the To...</t>
+          <t>...in the Village of Fredonia led to a driving while **intoxicated** investigation. According to the Chautauqua County...</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -542,45 +542,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chautauqua_Today</t>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>South Dayton Man Charged with DWI Following Traffic Stop in Hanover</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ripley Woman Arrested in Westfield on Drug ChargeA report of a disorderly person led to the arrest of a Ripley woman on a drug-related charge on Saturday. Chautauqua County Sheriff's deputies received the call just before 12:45 PM, with the suspect located by Westfield Police. After an investigatio...Greg Larson, News Director</t>
+          <t>(WNY News Now) – A South Dayton man was charged with driving while intoxicated after deputies conducted a traffic stop in the Town of Hanover on April 18. According to the Chautauqua County Sheriff’s Office, the incident occurred on April 18, 2026, at approximately 2:22 a.m. in the Town of Hanover. Deputies reported that they […]The post South Dayton Man Charged with DWI Following Traffic Stop in Hanover appeared first on WNY News Now.</t>
         </is>
       </c>
       <c r="D6" s="2">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367568</t>
+          <t>https://wnynewsnow.com/2026/04/20/south-dayton-man-charged-with-dwi-following-traffic-stop-in-hanover/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>...A South Dayton man was charged with driving while **intoxicated** after deputies conducted a traffic stop in the To...</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>News_search_Chautauqua_Today.R</t>
+          <t>News_search_WNY_News_Now.R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Google_search</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Expanding Tools Control Foreign-Related Economic Activity - The Jamestown Foundation</t>
+          <t>Chautauqua_Today</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ripley Woman Arrested in Westfield on Drug ChargeA report of a disorderly person led to the arrest of a Ripley woman on a drug-related charge on Saturday. Chautauqua County Sheriff's deputies received the call just before 12:45 PM, with the suspect located by Westfield Police. After an investigatio...Greg Larson, News Director</t>
         </is>
       </c>
       <c r="D7" s="2">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/2ce949hz</t>
+          <t>https://chautauquatoday.com/blotter/details.cfm?clientid=25&amp;id=367568</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>News_search_Chautauqua_Today.R</t>
         </is>
       </c>
     </row>
@@ -592,32 +607,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
+          <t>Expanding Tools Control Foreign-Related Economic Activity - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D8" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://tinyurl.com/24l8w486</t>
+          <t>https://tinyurl.com/2ce949hz</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+          <t>Dunkirk Man Charged In Narcotics Probe - Post Journal</t>
         </is>
       </c>
       <c r="D9" s="2">
@@ -625,34 +635,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>News_search_WNY_News_Now.R</t>
+          <t>https://tinyurl.com/24l8w486</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WNY News Now</t>
+          <t>Google_search</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Understanding Purity and Potency in Cannabis</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
+          <t>Dunkirk man charged in narcotics probe - observertoday.com</t>
         </is>
       </c>
       <c r="D10" s="2">
@@ -660,67 +655,127 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>https://tinyurl.com/2dbujwph</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(WNY News Now) – A 25-year-old Cherry Creek woman faces multiple charges after an early morning traffic stop in Jamestown led to a driving while intoxicated investigation. Jamestown — On April 12, 2026, at approximately 5:04 a.m., officers with the Jamestown Police Department’s Third Platoon conducted a traffic stop at the intersection of Newland Avenue […]The post Jamestown Woman Charged with DWI and Resisting Arrest Following Early Morning Traffic Stop appeared first on WNY News Now.</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>46129</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://wnynewsnow.com/2026/04/17/jamestown-woman-charged-with-dwi-and-resisting-arrest-following-early-morning-traffic-stop/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>... traffic stop in Jamestown led to a driving while **intoxicated** investigation. Jamestown — On April 12, 2026, at ...</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>News_search_WNY_News_Now.R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WNY News Now</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Understanding Purity and Potency in Cannabis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Have you ever wondered why purity and potency in cannabis matter? Many people focus only on the experience, but understanding these two factors can make a big difference. Purity and potency affect how cannabis works in the body and how safe it is to use. When you understand them, you can make better and more […]The post Understanding Purity and Potency in Cannabis appeared first on WNY News Now.</t>
+        </is>
+      </c>
+   